--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -53755,6 +53755,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2322">
+      <c r="A2322" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2322" t="n">
+        <v>1010</v>
+      </c>
+      <c r="C2322" t="n">
+        <v>2.52999997138977</v>
+      </c>
+      <c r="D2322" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E2322" t="n">
+        <v>2.52999997138977</v>
+      </c>
+      <c r="F2322" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G2322" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -53778,6 +53778,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2323">
+      <c r="A2323" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2323" t="n">
+        <v>17879</v>
+      </c>
+      <c r="C2323" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="D2323" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="E2323" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="F2323" t="n">
+        <v>2.47000002861023</v>
+      </c>
+      <c r="G2323" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -53801,6 +53801,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2324">
+      <c r="A2324" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2324" t="n">
+        <v>8817</v>
+      </c>
+      <c r="C2324" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="D2324" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="E2324" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="F2324" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="G2324" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -53824,6 +53824,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2325">
+      <c r="A2325" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2325" t="n">
+        <v>2065</v>
+      </c>
+      <c r="C2325" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="D2325" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="E2325" t="n">
+        <v>2.4300000667572</v>
+      </c>
+      <c r="F2325" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="G2325" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -53665,22 +53665,22 @@
     </row>
     <row r="2318">
       <c r="A2318" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2318" t="n">
-        <v>12467</v>
+        <v>2304</v>
       </c>
       <c r="C2318" t="n">
-        <v>2.5</v>
+        <v>2.5699999332428</v>
       </c>
       <c r="D2318" t="n">
-        <v>2.34999990463257</v>
+        <v>2.45000004768372</v>
       </c>
       <c r="E2318" t="n">
-        <v>2.40000009536743</v>
+        <v>2.45000004768372</v>
       </c>
       <c r="F2318" t="n">
-        <v>2.41000008583069</v>
+        <v>2.45000004768372</v>
       </c>
       <c r="G2318" t="s">
         <v>7</v>
@@ -53688,19 +53688,19 @@
     </row>
     <row r="2319">
       <c r="A2319" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2319" t="n">
-        <v>660</v>
+        <v>12467</v>
       </c>
       <c r="C2319" t="n">
-        <v>2.49000000953674</v>
+        <v>2.5</v>
       </c>
       <c r="D2319" t="n">
-        <v>2.36999988555908</v>
+        <v>2.34999990463257</v>
       </c>
       <c r="E2319" t="n">
-        <v>2.49000000953674</v>
+        <v>2.40000009536743</v>
       </c>
       <c r="F2319" t="n">
         <v>2.41000008583069</v>
@@ -53711,22 +53711,22 @@
     </row>
     <row r="2320">
       <c r="A2320" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2320" t="n">
-        <v>1450</v>
+        <v>660</v>
       </c>
       <c r="C2320" t="n">
-        <v>2.48000001907349</v>
+        <v>2.49000000953674</v>
       </c>
       <c r="D2320" t="n">
-        <v>2.3199999332428</v>
+        <v>2.36999988555908</v>
       </c>
       <c r="E2320" t="n">
-        <v>2.32999992370605</v>
+        <v>2.49000000953674</v>
       </c>
       <c r="F2320" t="n">
-        <v>2.48000001907349</v>
+        <v>2.41000008583069</v>
       </c>
       <c r="G2320" t="s">
         <v>7</v>
@@ -53734,22 +53734,22 @@
     </row>
     <row r="2321">
       <c r="A2321" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2321" t="n">
-        <v>7860</v>
+        <v>1450</v>
       </c>
       <c r="C2321" t="n">
-        <v>2.52999997138977</v>
+        <v>2.48000001907349</v>
       </c>
       <c r="D2321" t="n">
-        <v>2.40000009536743</v>
+        <v>2.3199999332428</v>
       </c>
       <c r="E2321" t="n">
-        <v>2.47000002861023</v>
+        <v>2.32999992370605</v>
       </c>
       <c r="F2321" t="n">
-        <v>2.49000000953674</v>
+        <v>2.48000001907349</v>
       </c>
       <c r="G2321" t="s">
         <v>7</v>
@@ -53757,22 +53757,22 @@
     </row>
     <row r="2322">
       <c r="A2322" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2322" t="n">
-        <v>1010</v>
+        <v>7860</v>
       </c>
       <c r="C2322" t="n">
         <v>2.52999997138977</v>
       </c>
       <c r="D2322" t="n">
-        <v>2.5</v>
+        <v>2.40000009536743</v>
       </c>
       <c r="E2322" t="n">
-        <v>2.52999997138977</v>
+        <v>2.47000002861023</v>
       </c>
       <c r="F2322" t="n">
-        <v>2.5</v>
+        <v>2.49000000953674</v>
       </c>
       <c r="G2322" t="s">
         <v>7</v>
@@ -53780,22 +53780,22 @@
     </row>
     <row r="2323">
       <c r="A2323" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2323" t="n">
-        <v>17879</v>
+        <v>1010</v>
       </c>
       <c r="C2323" t="n">
-        <v>2.51999998092651</v>
+        <v>2.52999997138977</v>
       </c>
       <c r="D2323" t="n">
-        <v>2.26999998092651</v>
+        <v>2.5</v>
       </c>
       <c r="E2323" t="n">
-        <v>2.48000001907349</v>
+        <v>2.52999997138977</v>
       </c>
       <c r="F2323" t="n">
-        <v>2.47000002861023</v>
+        <v>2.5</v>
       </c>
       <c r="G2323" t="s">
         <v>7</v>
@@ -53803,22 +53803,22 @@
     </row>
     <row r="2324">
       <c r="A2324" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2324" t="n">
-        <v>8817</v>
+        <v>17879</v>
       </c>
       <c r="C2324" t="n">
-        <v>2.44000005722046</v>
+        <v>2.51999998092651</v>
       </c>
       <c r="D2324" t="n">
-        <v>2.3199999332428</v>
+        <v>2.26999998092651</v>
       </c>
       <c r="E2324" t="n">
-        <v>2.44000005722046</v>
+        <v>2.48000001907349</v>
       </c>
       <c r="F2324" t="n">
-        <v>2.38000011444092</v>
+        <v>2.47000002861023</v>
       </c>
       <c r="G2324" t="s">
         <v>7</v>
@@ -53826,24 +53826,47 @@
     </row>
     <row r="2325">
       <c r="A2325" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2325" t="n">
-        <v>2065</v>
+        <v>8817</v>
       </c>
       <c r="C2325" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="D2325" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="E2325" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="F2325" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="G2325" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2326">
+      <c r="A2326" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2326" t="n">
+        <v>1573</v>
+      </c>
+      <c r="C2326" t="n">
         <v>2.45000004768372</v>
       </c>
-      <c r="D2325" t="n">
-        <v>2.34999990463257</v>
-      </c>
-      <c r="E2325" t="n">
-        <v>2.4300000667572</v>
-      </c>
-      <c r="F2325" t="n">
-        <v>2.45000004768372</v>
-      </c>
-      <c r="G2325" t="s">
+      <c r="D2326" t="n">
+        <v>2.32999992370605</v>
+      </c>
+      <c r="E2326" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="F2326" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="G2326" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -499,7 +499,7 @@
         <v>11.25</v>
       </c>
       <c r="G5" t="n">
-        <v>9.45229434967041</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.62033462524414</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>9.70435428619385</v>
+        <v>9.70435523986816</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G16" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G18" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G20" t="n">
-        <v>9.61193180084229</v>
+        <v>9.61193084716797</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>9.61193180084229</v>
+        <v>9.61193084716797</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G22" t="n">
-        <v>9.64553928375244</v>
+        <v>9.64553833007812</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>11.25</v>
       </c>
       <c r="G28" t="n">
-        <v>9.45229434967041</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G29" t="n">
-        <v>9.56151866912842</v>
+        <v>9.56151962280273</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G30" t="n">
-        <v>9.51950836181641</v>
+        <v>9.51950931549072</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G39" t="n">
-        <v>9.64553928375244</v>
+        <v>9.64553833007812</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G42" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>9.77157020568848</v>
+        <v>9.77156925201416</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G49" t="n">
-        <v>9.77157020568848</v>
+        <v>9.77156925201416</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G50" t="n">
-        <v>9.76316928863525</v>
+        <v>9.76316833496094</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G53" t="n">
-        <v>9.77997207641602</v>
+        <v>9.77997303009033</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G54" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G60" t="n">
-        <v>10.0320339202881</v>
+        <v>10.0320329666138</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G61" t="n">
-        <v>10.0320339202881</v>
+        <v>10.0320329666138</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G62" t="n">
-        <v>9.99002456665039</v>
+        <v>9.99002265930176</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G63" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G64" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G66" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G68" t="n">
-        <v>9.99002456665039</v>
+        <v>9.99002265930176</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>11.75</v>
       </c>
       <c r="G70" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G71" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G73" t="n">
-        <v>10.0572395324707</v>
+        <v>10.057240486145</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G76" t="n">
-        <v>10.0488367080688</v>
+        <v>10.0488376617432</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G77" t="n">
-        <v>10.0320339202881</v>
+        <v>10.0320329666138</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G80" t="n">
-        <v>10.0488367080688</v>
+        <v>10.0488376617432</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G81" t="n">
-        <v>9.89760112762451</v>
+        <v>9.8976001739502</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G82" t="n">
-        <v>9.99002456665039</v>
+        <v>9.99002265930176</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>11.75</v>
       </c>
       <c r="G83" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G85" t="n">
-        <v>9.90600299835205</v>
+        <v>9.90600395202637</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G87" t="n">
-        <v>9.89760112762451</v>
+        <v>9.8976001739502</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G88" t="n">
-        <v>9.90600299835205</v>
+        <v>9.90600395202637</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>11.75</v>
       </c>
       <c r="G91" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>11.75</v>
       </c>
       <c r="G92" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>11.75</v>
       </c>
       <c r="G93" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>11.75</v>
       </c>
       <c r="G95" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G97" t="n">
-        <v>10.0488367080688</v>
+        <v>10.0488376617432</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G98" t="n">
-        <v>9.98162174224854</v>
+        <v>9.98162269592285</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G105" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>9.62033462524414</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>9.62033462524414</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G113" t="n">
-        <v>9.64553928375244</v>
+        <v>9.64553833007812</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>11.75</v>
       </c>
       <c r="G118" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>11.75</v>
       </c>
       <c r="G130" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G139" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G143" t="n">
-        <v>9.32626247406006</v>
+        <v>9.32626342773438</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G144" t="n">
-        <v>9.32626247406006</v>
+        <v>9.32626342773438</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G145" t="n">
-        <v>9.32626247406006</v>
+        <v>9.32626342773438</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G148" t="n">
-        <v>9.62033462524414</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>9.70435428619385</v>
+        <v>9.70435523986816</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>9.70435428619385</v>
+        <v>9.70435523986816</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>11.25</v>
       </c>
       <c r="G157" t="n">
-        <v>9.45229434967041</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>9.32626247406006</v>
+        <v>9.32626342773438</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>11</v>
       </c>
       <c r="G159" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224090576172</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G160" t="n">
-        <v>9.32626247406006</v>
+        <v>9.32626342773438</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>11</v>
       </c>
       <c r="G164" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224090576172</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>11</v>
       </c>
       <c r="G165" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224090576172</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>11</v>
       </c>
       <c r="G166" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224090576172</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>9.32626247406006</v>
+        <v>9.32626342773438</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>11</v>
       </c>
       <c r="G168" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224090576172</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>11</v>
       </c>
       <c r="G177" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224090576172</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>9.32626247406006</v>
+        <v>9.32626342773438</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>11.25</v>
       </c>
       <c r="G180" t="n">
-        <v>9.45229434967041</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>11.25</v>
       </c>
       <c r="G181" t="n">
-        <v>9.45229434967041</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>11</v>
       </c>
       <c r="G182" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224090576172</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>9.1582202911377</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G184" t="n">
-        <v>9.11621189117432</v>
+        <v>9.1162109375</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G186" t="n">
-        <v>8.94817161560059</v>
+        <v>8.94816970825195</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>8.94817161560059</v>
+        <v>8.94816970825195</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>8.99018096923828</v>
+        <v>8.99017906188965</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>10.75</v>
       </c>
       <c r="G190" t="n">
-        <v>9.03219223022461</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>9.11621189117432</v>
+        <v>9.1162109375</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>9.11621189117432</v>
+        <v>9.1162109375</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>10.75</v>
       </c>
       <c r="G193" t="n">
-        <v>9.03219223022461</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>10.75</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03219223022461</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>8.99018096923828</v>
+        <v>8.99017906188965</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>10.75</v>
       </c>
       <c r="G196" t="n">
-        <v>9.03219223022461</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>9.1582202911377</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>9.1582202911377</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>9.1582202911377</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G201" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G202" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G203" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G204" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G205" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G206" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G207" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G209" t="n">
-        <v>9.41619968414307</v>
+        <v>9.41619873046875</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G210" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>9.41619968414307</v>
+        <v>9.41619873046875</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>9.41619968414307</v>
+        <v>9.41619873046875</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G214" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>8.98623561859131</v>
+        <v>8.98623657226562</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G218" t="n">
-        <v>8.85724830627441</v>
+        <v>8.8572473526001</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>8.85724830627441</v>
+        <v>8.8572473526001</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G225" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>8.98623561859131</v>
+        <v>8.98623657226562</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>10.5</v>
       </c>
       <c r="G228" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>8.85724830627441</v>
+        <v>8.8572473526001</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G232" t="n">
-        <v>9.41619968414307</v>
+        <v>9.41619873046875</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G236" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G237" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.5</v>
       </c>
       <c r="G238" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G248" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.5</v>
       </c>
       <c r="G255" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>10.5</v>
       </c>
       <c r="G256" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>10.5</v>
       </c>
       <c r="G257" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>10.5</v>
       </c>
       <c r="G258" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.5</v>
       </c>
       <c r="G262" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>8.85724830627441</v>
+        <v>8.8572473526001</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G265" t="n">
-        <v>8.85724830627441</v>
+        <v>8.8572473526001</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>8.85724830627441</v>
+        <v>8.8572473526001</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G268" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G277" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G278" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G279" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G281" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G282" t="n">
-        <v>8.51327610015869</v>
+        <v>8.51327705383301</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.25529861450195</v>
+        <v>8.25529956817627</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G290" t="n">
-        <v>8.32409286499023</v>
+        <v>8.32409381866455</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G292" t="n">
-        <v>8.41008567810059</v>
+        <v>8.41008472442627</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G293" t="n">
-        <v>8.41008567810059</v>
+        <v>8.41008472442627</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G294" t="n">
-        <v>8.32409286499023</v>
+        <v>8.32409381866455</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G295" t="n">
-        <v>8.32409286499023</v>
+        <v>8.32409381866455</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G303" t="n">
-        <v>8.53047561645508</v>
+        <v>8.53047466278076</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>8.13490867614746</v>
+        <v>8.13490962982178</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>7.70494556427002</v>
+        <v>7.70494508743286</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.5</v>
       </c>
       <c r="G318" t="n">
-        <v>7.3093786239624</v>
+        <v>7.30937910079956</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G319" t="n">
-        <v>7.36097478866577</v>
+        <v>7.36097431182861</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G322" t="n">
-        <v>7.18898963928223</v>
+        <v>7.18898868560791</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G323" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>9</v>
       </c>
       <c r="G327" t="n">
-        <v>7.739342212677</v>
+        <v>7.73934316635132</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G329" t="n">
-        <v>7.65334892272949</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>7.48136425018311</v>
+        <v>7.48136472702026</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G331" t="n">
-        <v>7.72214365005493</v>
+        <v>7.72214412689209</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G332" t="n">
-        <v>7.72214365005493</v>
+        <v>7.72214412689209</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>7.70494556427002</v>
+        <v>7.70494508743286</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>7.65334892272949</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G335" t="n">
-        <v>7.65334892272949</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G336" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>7.41256999969482</v>
+        <v>7.41257047653198</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G340" t="n">
-        <v>7.29218006134033</v>
+        <v>7.29217958450317</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G341" t="n">
-        <v>7.13739395141602</v>
+        <v>7.13739442825317</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G342" t="n">
-        <v>7.0857982635498</v>
+        <v>7.08579778671265</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G344" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G345" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G346" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G347" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G348" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G349" t="n">
-        <v>7.0857982635498</v>
+        <v>7.08579778671265</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G350" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G356" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G357" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G358" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G364" t="n">
-        <v>6.63863563537598</v>
+        <v>6.63863611221313</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G365" t="n">
-        <v>6.79342317581177</v>
+        <v>6.79342269897461</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G367" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260593414307</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G369" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260593414307</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260593414307</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G371" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260593414307</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>7.13739395141602</v>
+        <v>7.13739442825317</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>7.05140113830566</v>
+        <v>7.05140066146851</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G375" t="n">
-        <v>6.79342317581177</v>
+        <v>6.79342269897461</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G376" t="n">
-        <v>6.77622413635254</v>
+        <v>6.7762246131897</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G385" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G386" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G387" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G388" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G395" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>6.79342317581177</v>
+        <v>6.79342269897461</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>6.79342317581177</v>
+        <v>6.79342269897461</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G408" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>7.24058485031128</v>
+        <v>7.24058532714844</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G410" t="n">
-        <v>7.46416568756104</v>
+        <v>7.46416664123535</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G412" t="n">
-        <v>7.48136425018311</v>
+        <v>7.48136472702026</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.65334892272949</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G415" t="n">
-        <v>7.61895275115967</v>
+        <v>7.61895132064819</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G416" t="n">
-        <v>7.72214365005493</v>
+        <v>7.72214412689209</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G417" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G419" t="n">
-        <v>7.41256999969482</v>
+        <v>7.41257047653198</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>7.34377574920654</v>
+        <v>7.3437762260437</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>7.34377574920654</v>
+        <v>7.3437762260437</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G422" t="n">
-        <v>7.36097478866577</v>
+        <v>7.36097431182861</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>8.5</v>
       </c>
       <c r="G423" t="n">
-        <v>7.3093786239624</v>
+        <v>7.30937910079956</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>7.65334892272949</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>8.5</v>
       </c>
       <c r="G428" t="n">
-        <v>7.3093786239624</v>
+        <v>7.30937910079956</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G429" t="n">
-        <v>7.29218006134033</v>
+        <v>7.29217958450317</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>7.13739395141602</v>
+        <v>7.13739442825317</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.5</v>
       </c>
       <c r="G431" t="n">
-        <v>7.3093786239624</v>
+        <v>7.30937910079956</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>9</v>
       </c>
       <c r="G433" t="n">
-        <v>7.739342212677</v>
+        <v>7.73934316635132</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G435" t="n">
-        <v>7.65334892272949</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>7.48136425018311</v>
+        <v>7.48136472702026</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G452" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G453" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G454" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G455" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G457" t="n">
-        <v>7.64425468444824</v>
+        <v>7.6442551612854</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G458" t="n">
-        <v>7.64425468444824</v>
+        <v>7.6442551612854</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.25</v>
       </c>
       <c r="G459" t="n">
-        <v>7.33315134048462</v>
+        <v>7.33315086364746</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.25</v>
       </c>
       <c r="G460" t="n">
-        <v>7.33315134048462</v>
+        <v>7.33315086364746</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.25</v>
       </c>
       <c r="G467" t="n">
-        <v>7.33315134048462</v>
+        <v>7.33315086364746</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>8</v>
       </c>
       <c r="G468" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>7.2887077331543</v>
+        <v>7.28870725631714</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.5</v>
       </c>
       <c r="G474" t="n">
-        <v>7.5553674697876</v>
+        <v>7.55536699295044</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.5</v>
       </c>
       <c r="G475" t="n">
-        <v>7.5553674697876</v>
+        <v>7.55536699295044</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>8.5</v>
       </c>
       <c r="G476" t="n">
-        <v>7.5553674697876</v>
+        <v>7.55536699295044</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.25</v>
       </c>
       <c r="G478" t="n">
-        <v>7.33315134048462</v>
+        <v>7.33315086364746</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G479" t="n">
-        <v>7.2887077331543</v>
+        <v>7.28870725631714</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G480" t="n">
-        <v>7.46648025512695</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G481" t="n">
-        <v>7.46648025512695</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G482" t="n">
-        <v>7.46648025512695</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G493" t="n">
-        <v>7.46648025512695</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>7.59981155395508</v>
+        <v>7.59981107711792</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>8</v>
       </c>
       <c r="G498" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8</v>
       </c>
       <c r="G500" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G503" t="n">
-        <v>7.022047996521</v>
+        <v>7.02204751968384</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8</v>
       </c>
       <c r="G504" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>8</v>
       </c>
       <c r="G505" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>8</v>
       </c>
       <c r="G506" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>8</v>
       </c>
       <c r="G509" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>8</v>
       </c>
       <c r="G511" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>8</v>
       </c>
       <c r="G512" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>7.75</v>
       </c>
       <c r="G514" t="n">
-        <v>6.88871765136719</v>
+        <v>6.88871812820435</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>6.97760438919067</v>
+        <v>6.97760391235352</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G533" t="n">
-        <v>6.71094465255737</v>
+        <v>6.71094417572021</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.39984083175659</v>
+        <v>6.39984035491943</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>7.25</v>
       </c>
       <c r="G536" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>7.25</v>
       </c>
       <c r="G537" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>7.25</v>
       </c>
       <c r="G538" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>7.25</v>
       </c>
       <c r="G539" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>7.25</v>
       </c>
       <c r="G541" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.39984083175659</v>
+        <v>6.39984035491943</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>6.39984083175659</v>
+        <v>6.39984035491943</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G548" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G550" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G551" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G552" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>7.25</v>
       </c>
       <c r="G553" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G556" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G557" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G559" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>7.25</v>
       </c>
       <c r="G575" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G586" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G590" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6.75</v>
       </c>
       <c r="G596" t="n">
-        <v>5.99985074996948</v>
+        <v>5.99985122680664</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G599" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G605" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G606" t="n">
-        <v>5.82207775115967</v>
+        <v>5.82207727432251</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G616" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G618" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G619" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>6.75</v>
       </c>
       <c r="G632" t="n">
-        <v>5.99985074996948</v>
+        <v>5.99985122680664</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G634" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>6.25</v>
       </c>
       <c r="G645" t="n">
-        <v>5.55541753768921</v>
+        <v>5.55541706085205</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G653" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G662" t="n">
-        <v>5.37764406204224</v>
+        <v>5.37764453887939</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5.75</v>
       </c>
       <c r="G664" t="n">
-        <v>5.11098384857178</v>
+        <v>5.11098432540894</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>4.07101011276245</v>
+        <v>4.07100963592529</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G670" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G671" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G672" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G673" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G674" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G675" t="n">
-        <v>3.82212734222412</v>
+        <v>3.8221275806427</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.5</v>
       </c>
       <c r="G677" t="n">
-        <v>3.99990034103394</v>
+        <v>3.99990057945251</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.89323663711548</v>
+        <v>3.8932363986969</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>3.73324012756348</v>
+        <v>3.73324036598206</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G682" t="n">
-        <v>3.75101757049561</v>
+        <v>3.75101804733276</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G683" t="n">
-        <v>3.64435386657715</v>
+        <v>3.64435362815857</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G685" t="n">
-        <v>3.80435013771057</v>
+        <v>3.80434989929199</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.5</v>
       </c>
       <c r="G689" t="n">
-        <v>3.99990034103394</v>
+        <v>3.99990057945251</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G690" t="n">
-        <v>4.08878707885742</v>
+        <v>4.08878755569458</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>3.96434617042542</v>
+        <v>3.96434593200684</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.5</v>
       </c>
       <c r="G698" t="n">
-        <v>3.99990034103394</v>
+        <v>3.99990057945251</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G702" t="n">
-        <v>3.89323663711548</v>
+        <v>3.8932363986969</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G704" t="n">
-        <v>3.90212512016296</v>
+        <v>3.90212535858154</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G708" t="n">
-        <v>3.83101582527161</v>
+        <v>3.83101558685303</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>3.83101582527161</v>
+        <v>3.83101558685303</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>3.71546339988708</v>
+        <v>3.71546292304993</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G712" t="n">
-        <v>3.75101757049561</v>
+        <v>3.75101804733276</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G716" t="n">
-        <v>3.80435013771057</v>
+        <v>3.80434989929199</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G718" t="n">
-        <v>3.89323663711548</v>
+        <v>3.8932363986969</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G719" t="n">
-        <v>4.08878707885742</v>
+        <v>4.08878755569458</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G720" t="n">
-        <v>4.06212091445923</v>
+        <v>4.06212139129639</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G722" t="n">
-        <v>4.10656404495239</v>
+        <v>4.10656452178955</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G723" t="n">
-        <v>4.10656404495239</v>
+        <v>4.10656452178955</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>4.38185501098633</v>
+        <v>4.38185453414917</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>4.75</v>
       </c>
       <c r="G731" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G734" t="n">
-        <v>4.38185501098633</v>
+        <v>4.38185453414917</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G735" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G736" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G737" t="n">
-        <v>4.40935611724854</v>
+        <v>4.40935564041138</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G740" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.75</v>
       </c>
       <c r="G743" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G744" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G747" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G752" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G759" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>4.08850908279419</v>
+        <v>4.08850860595703</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G784" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G786" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G787" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>4.07934141159058</v>
+        <v>4.07934188842773</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G789" t="n">
-        <v>4.07934141159058</v>
+        <v>4.07934188842773</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>4.04267358779907</v>
+        <v>4.04267311096191</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G797" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G798" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>3.91433453559875</v>
+        <v>3.91433477401733</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.86849904060364</v>
+        <v>3.86849927902222</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G807" t="n">
-        <v>3.88683319091797</v>
+        <v>3.88683342933655</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G808" t="n">
-        <v>3.88683319091797</v>
+        <v>3.88683342933655</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G813" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G816" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G819" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.75</v>
       </c>
       <c r="G821" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G825" t="n">
-        <v>4.51936054229736</v>
+        <v>4.51936006546021</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>4.51019334793091</v>
+        <v>4.51019382476807</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.75</v>
       </c>
       <c r="G829" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.04267358779907</v>
+        <v>4.04267311096191</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>3.94183588027954</v>
+        <v>3.94183611869812</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G840" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G844" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>4.96854639053345</v>
+        <v>4.96854686737061</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>5.1152195930481</v>
+        <v>5.11521911621094</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G862" t="n">
-        <v>5.13355350494385</v>
+        <v>5.13355398178101</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G863" t="n">
-        <v>5.1518874168396</v>
+        <v>5.15188789367676</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>5.00521516799927</v>
+        <v>5.00521469116211</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G873" t="n">
-        <v>5.39023113250732</v>
+        <v>5.39023160934448</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G874" t="n">
-        <v>5.39023113250732</v>
+        <v>5.39023160934448</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G878" t="n">
-        <v>5.61024045944214</v>
+        <v>5.6102409362793</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G882" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>5.88525247573853</v>
+        <v>5.88525295257568</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>5.94025468826294</v>
+        <v>5.9402551651001</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G893" t="n">
-        <v>5.83025074005127</v>
+        <v>5.83025026321411</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G906" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G910" t="n">
-        <v>6.19693326950073</v>
+        <v>6.19693279266357</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>6.38027429580688</v>
+        <v>6.38027381896973</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G913" t="n">
-        <v>6.28860378265381</v>
+        <v>6.28860330581665</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>6.47194480895996</v>
+        <v>6.4719443321228</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G920" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G922" t="n">
-        <v>6.58194875717163</v>
+        <v>6.58194923400879</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G924" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G927" t="n">
-        <v>6.61861705780029</v>
+        <v>6.61861753463745</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>6.58194875717163</v>
+        <v>6.58194923400879</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G931" t="n">
-        <v>6.61861705780029</v>
+        <v>6.61861753463745</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G937" t="n">
-        <v>6.54528093338013</v>
+        <v>6.54528045654297</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G939" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>6.85696077346802</v>
+        <v>6.85696125030518</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G956" t="n">
-        <v>6.78362464904785</v>
+        <v>6.78362417221069</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -60900,6 +60900,32 @@
         <v>2.40000009536743</v>
       </c>
       <c r="H2328" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2329" t="n">
+        <v>8311</v>
+      </c>
+      <c r="C2329" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D2329" t="n">
+        <v>2.30999994277954</v>
+      </c>
+      <c r="E2329" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="F2329" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G2329" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="H2329" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -499,7 +499,7 @@
         <v>11.25</v>
       </c>
       <c r="G5" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229434967041</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G12" t="n">
-        <v>9.67074584960938</v>
+        <v>9.67074680328369</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>9.70435523986816</v>
+        <v>9.70435428619385</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>9.52791213989258</v>
+        <v>9.52791118621826</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G22" t="n">
-        <v>9.64553833007812</v>
+        <v>9.64553928375244</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>11.25</v>
       </c>
       <c r="G28" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229434967041</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G31" t="n">
-        <v>9.52791213989258</v>
+        <v>9.52791118621826</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G33" t="n">
-        <v>9.56992149353027</v>
+        <v>9.56992340087891</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G34" t="n">
-        <v>9.52791213989258</v>
+        <v>9.52791118621826</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G37" t="n">
-        <v>9.56992149353027</v>
+        <v>9.56992340087891</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G39" t="n">
-        <v>9.64553833007812</v>
+        <v>9.64553928375244</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>9.77156925201416</v>
+        <v>9.77157020568848</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G49" t="n">
-        <v>9.77156925201416</v>
+        <v>9.77157020568848</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G50" t="n">
-        <v>9.76316833496094</v>
+        <v>9.76316738128662</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G51" t="n">
-        <v>10.1832704544067</v>
+        <v>10.1832685470581</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G57" t="n">
-        <v>9.95641613006592</v>
+        <v>9.9564151763916</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>9.95641613006592</v>
+        <v>9.9564151763916</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G60" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320320129395</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G61" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320320129395</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G62" t="n">
-        <v>9.99002265930176</v>
+        <v>9.99002456665039</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G67" t="n">
-        <v>9.93961048126221</v>
+        <v>9.93961143493652</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G68" t="n">
-        <v>9.99002265930176</v>
+        <v>9.99002456665039</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>9.95641613006592</v>
+        <v>9.9564151763916</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G74" t="n">
-        <v>10.0656414031982</v>
+        <v>10.0656404495239</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>9.99842548370361</v>
+        <v>9.9984245300293</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G76" t="n">
-        <v>10.0488376617432</v>
+        <v>10.0488386154175</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G77" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320320129395</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>9.99842548370361</v>
+        <v>9.9984245300293</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G80" t="n">
-        <v>10.0488376617432</v>
+        <v>10.0488386154175</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G81" t="n">
-        <v>9.8976001739502</v>
+        <v>9.89760112762451</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G82" t="n">
-        <v>9.99002265930176</v>
+        <v>9.99002456665039</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G85" t="n">
-        <v>9.90600395202637</v>
+        <v>9.90600299835205</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G87" t="n">
-        <v>9.8976001739502</v>
+        <v>9.89760112762451</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G88" t="n">
-        <v>9.90600395202637</v>
+        <v>9.90600299835205</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G97" t="n">
-        <v>10.0488376617432</v>
+        <v>10.0488386154175</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G98" t="n">
-        <v>9.98162269592285</v>
+        <v>9.98162078857422</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G113" t="n">
-        <v>9.64553833007812</v>
+        <v>9.64553928375244</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G115" t="n">
-        <v>9.72956085205078</v>
+        <v>9.72955989837646</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G123" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G132" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G133" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G143" t="n">
-        <v>9.32626342773438</v>
+        <v>9.32626247406006</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G144" t="n">
-        <v>9.32626342773438</v>
+        <v>9.32626247406006</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G145" t="n">
-        <v>9.32626342773438</v>
+        <v>9.32626247406006</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>9.70435523986816</v>
+        <v>9.70435428619385</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>9.70435523986816</v>
+        <v>9.70435428619385</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>11.25</v>
       </c>
       <c r="G157" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229434967041</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>9.32626342773438</v>
+        <v>9.32626247406006</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>11</v>
       </c>
       <c r="G159" t="n">
-        <v>9.24224090576172</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G160" t="n">
-        <v>9.32626342773438</v>
+        <v>9.32626247406006</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>11</v>
       </c>
       <c r="G164" t="n">
-        <v>9.24224090576172</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>11</v>
       </c>
       <c r="G165" t="n">
-        <v>9.24224090576172</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>11</v>
       </c>
       <c r="G166" t="n">
-        <v>9.24224090576172</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>9.32626342773438</v>
+        <v>9.32626247406006</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>11</v>
       </c>
       <c r="G168" t="n">
-        <v>9.24224090576172</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G171" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G176" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>11</v>
       </c>
       <c r="G177" t="n">
-        <v>9.24224090576172</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>9.32626342773438</v>
+        <v>9.32626247406006</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>11.25</v>
       </c>
       <c r="G180" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229434967041</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>11.25</v>
       </c>
       <c r="G181" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229434967041</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>11</v>
       </c>
       <c r="G182" t="n">
-        <v>9.24224090576172</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G185" t="n">
-        <v>9.0742015838623</v>
+        <v>9.07420063018799</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>8.99017906188965</v>
+        <v>8.99018096923828</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G189" t="n">
-        <v>9.0742015838623</v>
+        <v>9.07420063018799</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>8.99017906188965</v>
+        <v>8.99018096923828</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>9.0742015838623</v>
+        <v>9.07420063018799</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G209" t="n">
-        <v>9.41619873046875</v>
+        <v>9.41619968414307</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>9.41619873046875</v>
+        <v>9.41619968414307</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>9.41619873046875</v>
+        <v>9.41619968414307</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G232" t="n">
-        <v>9.41619873046875</v>
+        <v>9.41619968414307</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G235" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G243" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11</v>
       </c>
       <c r="G245" t="n">
-        <v>9.45919609069824</v>
+        <v>9.45919704437256</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11</v>
       </c>
       <c r="G246" t="n">
-        <v>9.45919609069824</v>
+        <v>9.45919704437256</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G249" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G250" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G252" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G254" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>10</v>
       </c>
       <c r="G270" t="n">
-        <v>8.59926891326904</v>
+        <v>8.59926986694336</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G282" t="n">
-        <v>8.51327705383301</v>
+        <v>8.51327610015869</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10</v>
       </c>
       <c r="G285" t="n">
-        <v>8.59926891326904</v>
+        <v>8.59926986694336</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G290" t="n">
-        <v>8.32409381866455</v>
+        <v>8.32409286499023</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G292" t="n">
-        <v>8.41008472442627</v>
+        <v>8.41008567810059</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G293" t="n">
-        <v>8.41008472442627</v>
+        <v>8.41008567810059</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G294" t="n">
-        <v>8.32409381866455</v>
+        <v>8.32409286499023</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G295" t="n">
-        <v>8.32409381866455</v>
+        <v>8.32409286499023</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>10</v>
       </c>
       <c r="G299" t="n">
-        <v>8.59926891326904</v>
+        <v>8.59926986694336</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>10</v>
       </c>
       <c r="G300" t="n">
-        <v>8.59926891326904</v>
+        <v>8.59926986694336</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10</v>
       </c>
       <c r="G301" t="n">
-        <v>8.59926891326904</v>
+        <v>8.59926986694336</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>10</v>
       </c>
       <c r="G302" t="n">
-        <v>8.59926891326904</v>
+        <v>8.59926986694336</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G303" t="n">
-        <v>8.53047466278076</v>
+        <v>8.53047561645508</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>8.13490962982178</v>
+        <v>8.13490867614746</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G307" t="n">
-        <v>8.03171730041504</v>
+        <v>8.03171920776367</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G309" t="n">
-        <v>8.03171730041504</v>
+        <v>8.03171920776367</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G310" t="n">
-        <v>7.87693071365356</v>
+        <v>7.87693119049072</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>7.87693071365356</v>
+        <v>7.87693119049072</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>7.82533550262451</v>
+        <v>7.82533502578735</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G319" t="n">
-        <v>7.36097431182861</v>
+        <v>7.36097526550293</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G322" t="n">
-        <v>7.18898868560791</v>
+        <v>7.18898916244507</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>7.20618772506714</v>
+        <v>7.2061882019043</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G326" t="n">
-        <v>7.20618772506714</v>
+        <v>7.2061882019043</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G328" t="n">
-        <v>7.82533550262451</v>
+        <v>7.82533502578735</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G331" t="n">
-        <v>7.72214412689209</v>
+        <v>7.72214317321777</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G332" t="n">
-        <v>7.72214412689209</v>
+        <v>7.72214317321777</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G336" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G338" t="n">
-        <v>7.53296041488647</v>
+        <v>7.53295993804932</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G341" t="n">
-        <v>7.13739442825317</v>
+        <v>7.13739347457886</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G343" t="n">
-        <v>7.06859970092773</v>
+        <v>7.06860017776489</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G344" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G346" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G347" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G348" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G356" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G357" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G358" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>6.74182748794556</v>
+        <v>6.7418270111084</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>6.74182748794556</v>
+        <v>6.7418270111084</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>6.74182748794556</v>
+        <v>6.7418270111084</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G365" t="n">
-        <v>6.79342269897461</v>
+        <v>6.79342317581177</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G367" t="n">
-        <v>6.98260593414307</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G369" t="n">
-        <v>6.98260593414307</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>6.98260593414307</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G371" t="n">
-        <v>6.98260593414307</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>7.13739442825317</v>
+        <v>7.13739347457886</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>7.05140066146851</v>
+        <v>7.05140113830566</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G375" t="n">
-        <v>6.79342269897461</v>
+        <v>6.79342317581177</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G376" t="n">
-        <v>6.7762246131897</v>
+        <v>6.77622509002686</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>6.84501886367798</v>
+        <v>6.84501838684082</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>6.84501886367798</v>
+        <v>6.84501838684082</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G385" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G386" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G387" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G388" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>6.84501886367798</v>
+        <v>6.84501838684082</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G393" t="n">
-        <v>6.69023132324219</v>
+        <v>6.69023180007935</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G395" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G399" t="n">
-        <v>6.89661455154419</v>
+        <v>6.89661407470703</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>6.79342269897461</v>
+        <v>6.79342317581177</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>6.79342269897461</v>
+        <v>6.79342317581177</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G408" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>7.24058532714844</v>
+        <v>7.24058485031128</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G411" t="n">
-        <v>7.53296041488647</v>
+        <v>7.53295993804932</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G414" t="n">
-        <v>7.44696712493896</v>
+        <v>7.44696807861328</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G415" t="n">
-        <v>7.61895132064819</v>
+        <v>7.61895227432251</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G416" t="n">
-        <v>7.72214412689209</v>
+        <v>7.72214317321777</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G418" t="n">
-        <v>7.53296041488647</v>
+        <v>7.53295993804932</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>7.3437762260437</v>
+        <v>7.34377670288086</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>7.3437762260437</v>
+        <v>7.34377670288086</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G422" t="n">
-        <v>7.36097431182861</v>
+        <v>7.36097526550293</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G427" t="n">
-        <v>7.42976903915405</v>
+        <v>7.42976856231689</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>7.13739442825317</v>
+        <v>7.13739347457886</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>7.78233909606934</v>
+        <v>7.78233814239502</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G452" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G453" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G454" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G455" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G457" t="n">
-        <v>7.6442551612854</v>
+        <v>7.64425468444824</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G458" t="n">
-        <v>7.6442551612854</v>
+        <v>7.64425468444824</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>7.37759494781494</v>
+        <v>7.37759447097778</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G470" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>7.28870725631714</v>
+        <v>7.2887077331543</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.5</v>
       </c>
       <c r="G474" t="n">
-        <v>7.55536699295044</v>
+        <v>7.55536794662476</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.5</v>
       </c>
       <c r="G475" t="n">
-        <v>7.55536699295044</v>
+        <v>7.55536794662476</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>8.5</v>
       </c>
       <c r="G476" t="n">
-        <v>7.55536699295044</v>
+        <v>7.55536794662476</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>7.37759494781494</v>
+        <v>7.37759447097778</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G479" t="n">
-        <v>7.28870725631714</v>
+        <v>7.2887077331543</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G499" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G502" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G503" t="n">
-        <v>7.02204751968384</v>
+        <v>7.022047996521</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G513" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>7.75</v>
       </c>
       <c r="G514" t="n">
-        <v>6.88871812820435</v>
+        <v>6.88871765136719</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>6.97760391235352</v>
+        <v>6.97760438919067</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>7.5</v>
       </c>
       <c r="G517" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G518" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>7.5</v>
       </c>
       <c r="G519" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>7.5</v>
       </c>
       <c r="G520" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G521" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>7.5</v>
       </c>
       <c r="G525" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>7.5</v>
       </c>
       <c r="G526" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>7.5</v>
       </c>
       <c r="G527" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>7.5</v>
       </c>
       <c r="G528" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G530" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G533" t="n">
-        <v>6.71094417572021</v>
+        <v>6.71094465255737</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.39984035491943</v>
+        <v>6.39984083175659</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>7.25</v>
       </c>
       <c r="G536" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>7.25</v>
       </c>
       <c r="G537" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>7.25</v>
       </c>
       <c r="G538" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>7.25</v>
       </c>
       <c r="G539" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>7.25</v>
       </c>
       <c r="G541" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.39984035491943</v>
+        <v>6.39984083175659</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>6.39984035491943</v>
+        <v>6.39984083175659</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G552" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>7.25</v>
       </c>
       <c r="G553" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G556" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G557" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G559" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G569" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G571" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G573" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G574" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>7.25</v>
       </c>
       <c r="G575" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G576" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G582" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G583" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G586" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G590" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G595" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6.5</v>
       </c>
       <c r="G597" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G599" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G605" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G607" t="n">
-        <v>5.86652088165283</v>
+        <v>5.86652040481567</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G609" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G616" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G618" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G619" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G622" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G624" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G625" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G626" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G627" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G628" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G629" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G631" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.86652088165283</v>
+        <v>5.86652040481567</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G634" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.5</v>
       </c>
       <c r="G635" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>6.5</v>
       </c>
       <c r="G636" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.5</v>
       </c>
       <c r="G637" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>6.5</v>
       </c>
       <c r="G638" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.5</v>
       </c>
       <c r="G639" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>6.5</v>
       </c>
       <c r="G640" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G641" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>5.6443042755127</v>
+        <v>5.64430379867554</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>6.25</v>
       </c>
       <c r="G645" t="n">
-        <v>5.55541706085205</v>
+        <v>5.55541753768921</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.6443042755127</v>
+        <v>5.64430379867554</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>6.5</v>
       </c>
       <c r="G649" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>6.5</v>
       </c>
       <c r="G651" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>6.5</v>
       </c>
       <c r="G652" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G653" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G654" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G666" t="n">
-        <v>4.35544729232788</v>
+        <v>4.35544681549072</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>4.26656055450439</v>
+        <v>4.26656103134155</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>4.07100963592529</v>
+        <v>4.07101011276245</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G670" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G671" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G672" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G673" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G674" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G675" t="n">
-        <v>3.8221275806427</v>
+        <v>3.82212734222412</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G676" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.5</v>
       </c>
       <c r="G677" t="n">
-        <v>3.99990057945251</v>
+        <v>3.99990081787109</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G678" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G680" t="n">
-        <v>3.8576819896698</v>
+        <v>3.85768222808838</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G682" t="n">
-        <v>3.75101804733276</v>
+        <v>3.75101757049561</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G683" t="n">
-        <v>3.64435362815857</v>
+        <v>3.64435386657715</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G684" t="n">
-        <v>3.68879747390747</v>
+        <v>3.68879723548889</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G685" t="n">
-        <v>3.80434989929199</v>
+        <v>3.80435013771057</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G686" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>3.8576819896698</v>
+        <v>3.85768222808838</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.5</v>
       </c>
       <c r="G689" t="n">
-        <v>3.99990057945251</v>
+        <v>3.99990081787109</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G691" t="n">
-        <v>3.98212337493896</v>
+        <v>3.98212313652039</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G694" t="n">
-        <v>3.8576819896698</v>
+        <v>3.85768222808838</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.5</v>
       </c>
       <c r="G698" t="n">
-        <v>3.99990057945251</v>
+        <v>3.99990081787109</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>3.98212337493896</v>
+        <v>3.98212313652039</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G700" t="n">
-        <v>3.98212337493896</v>
+        <v>3.98212313652039</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G701" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>3.76879501342773</v>
+        <v>3.76879477500916</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G704" t="n">
-        <v>3.90212535858154</v>
+        <v>3.90212512016296</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G705" t="n">
-        <v>3.88434743881226</v>
+        <v>3.88434791564941</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G706" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>3.88434743881226</v>
+        <v>3.88434791564941</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G708" t="n">
-        <v>3.83101558685303</v>
+        <v>3.83101606369019</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>3.83101558685303</v>
+        <v>3.83101606369019</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>3.71546292304993</v>
+        <v>3.71546316146851</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G711" t="n">
-        <v>3.76879501342773</v>
+        <v>3.76879477500916</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G712" t="n">
-        <v>3.75101804733276</v>
+        <v>3.75101757049561</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G713" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G714" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G716" t="n">
-        <v>3.80434989929199</v>
+        <v>3.80435013771057</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>3.88434743881226</v>
+        <v>3.88434791564941</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>4.13323068618774</v>
+        <v>4.13323020935059</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G727" t="n">
-        <v>4.09767627716064</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>4.38185453414917</v>
+        <v>4.38185501098633</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>4.75</v>
       </c>
       <c r="G731" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G734" t="n">
-        <v>4.38185453414917</v>
+        <v>4.38185501098633</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G735" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G736" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G737" t="n">
-        <v>4.40935564041138</v>
+        <v>4.40935611724854</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>4.37268781661987</v>
+        <v>4.37268733978271</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>4.37268781661987</v>
+        <v>4.37268733978271</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G740" t="n">
-        <v>4.32685232162476</v>
+        <v>4.3268518447876</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.75</v>
       </c>
       <c r="G743" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G744" t="n">
-        <v>4.32685232162476</v>
+        <v>4.3268518447876</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G747" t="n">
-        <v>4.23518180847168</v>
+        <v>4.23518133163452</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>4.23518180847168</v>
+        <v>4.23518133163452</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G752" t="n">
-        <v>4.18934679031372</v>
+        <v>4.18934631347656</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G759" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.18934679031372</v>
+        <v>4.18934631347656</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>4.21684789657593</v>
+        <v>4.21684741973877</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>4.08850860595703</v>
+        <v>4.08850908279419</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G784" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G786" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G787" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>4.07934188842773</v>
+        <v>4.07934141159058</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G789" t="n">
-        <v>4.07934188842773</v>
+        <v>4.07934141159058</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>4.04267311096191</v>
+        <v>4.04267358779907</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G797" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G798" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>3.91433477401733</v>
+        <v>3.91433453559875</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.86849927902222</v>
+        <v>3.86849904060364</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G807" t="n">
-        <v>3.88683342933655</v>
+        <v>3.88683319091797</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G808" t="n">
-        <v>3.88683342933655</v>
+        <v>3.88683319091797</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G813" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>4.37268781661987</v>
+        <v>4.37268733978271</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G816" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G819" t="n">
-        <v>4.32685232162476</v>
+        <v>4.3268518447876</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.75</v>
       </c>
       <c r="G821" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G825" t="n">
-        <v>4.51936006546021</v>
+        <v>4.51936054229736</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>4.51019382476807</v>
+        <v>4.51019334793091</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.75</v>
       </c>
       <c r="G829" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.04267311096191</v>
+        <v>4.04267358779907</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>3.94183611869812</v>
+        <v>3.94183588027954</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>4.21684789657593</v>
+        <v>4.21684741973877</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G840" t="n">
-        <v>4.18934679031372</v>
+        <v>4.18934631347656</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>4.23518180847168</v>
+        <v>4.23518133163452</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G844" t="n">
-        <v>4.21684789657593</v>
+        <v>4.21684741973877</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>4.96854686737061</v>
+        <v>4.96854639053345</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>5.11521911621094</v>
+        <v>5.1152195930481</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G862" t="n">
-        <v>5.13355398178101</v>
+        <v>5.13355350494385</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G863" t="n">
-        <v>5.15188789367676</v>
+        <v>5.1518874168396</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>5.00521469116211</v>
+        <v>5.00521516799927</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G873" t="n">
-        <v>5.39023160934448</v>
+        <v>5.39023113250732</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G874" t="n">
-        <v>5.39023160934448</v>
+        <v>5.39023113250732</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G878" t="n">
-        <v>5.6102409362793</v>
+        <v>5.61024045944214</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G882" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>5.88525295257568</v>
+        <v>5.88525247573853</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>5.9402551651001</v>
+        <v>5.94025468826294</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G893" t="n">
-        <v>5.83025026321411</v>
+        <v>5.83025074005127</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>5.92192077636719</v>
+        <v>5.92192125320435</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>5.92192077636719</v>
+        <v>5.92192125320435</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>5.92192077636719</v>
+        <v>5.92192125320435</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G906" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G910" t="n">
-        <v>6.19693279266357</v>
+        <v>6.19693326950073</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>6.38027381896973</v>
+        <v>6.38027429580688</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G913" t="n">
-        <v>6.28860330581665</v>
+        <v>6.28860378265381</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>6.4719443321228</v>
+        <v>6.47194480895996</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G920" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G922" t="n">
-        <v>6.58194923400879</v>
+        <v>6.58194875717163</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G924" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G927" t="n">
-        <v>6.61861753463745</v>
+        <v>6.61861705780029</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>6.58194923400879</v>
+        <v>6.58194875717163</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G931" t="n">
-        <v>6.61861753463745</v>
+        <v>6.61861705780029</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G937" t="n">
-        <v>6.54528045654297</v>
+        <v>6.54528093338013</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G939" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>6.85696125030518</v>
+        <v>6.85696077346802</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G956" t="n">
-        <v>6.78362417221069</v>
+        <v>6.78362464904785</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -60926,6 +60926,32 @@
         <v>2.40000009536743</v>
       </c>
       <c r="H2329" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2330" t="n">
+        <v>5886</v>
+      </c>
+      <c r="C2330" t="n">
+        <v>2.42000007629395</v>
+      </c>
+      <c r="D2330" t="n">
+        <v>2.39000010490417</v>
+      </c>
+      <c r="E2330" t="n">
+        <v>2.39000010490417</v>
+      </c>
+      <c r="F2330" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G2330" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="H2330" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2" t="n">
-        <v>9.40188026428223</v>
+        <v>9.40188121795654</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.41868495941162</v>
+        <v>9.41868591308594</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394306182861</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394306182861</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>11.5</v>
       </c>
       <c r="G9" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G11" t="n">
-        <v>9.73796272277832</v>
+        <v>9.73796367645264</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G12" t="n">
-        <v>9.67074680328369</v>
+        <v>9.67074584960938</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033462524414</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>11.5</v>
       </c>
       <c r="G15" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G20" t="n">
-        <v>9.61193084716797</v>
+        <v>9.61193180084229</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>9.61193084716797</v>
+        <v>9.61193180084229</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G24" t="n">
-        <v>9.40188026428223</v>
+        <v>9.40188121795654</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G33" t="n">
-        <v>9.56992340087891</v>
+        <v>9.56992244720459</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G37" t="n">
-        <v>9.56992340087891</v>
+        <v>9.56992244720459</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G40" t="n">
-        <v>9.73796272277832</v>
+        <v>9.73796367645264</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G41" t="n">
-        <v>9.73796272277832</v>
+        <v>9.73796367645264</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G42" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>11.5</v>
       </c>
       <c r="G47" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G50" t="n">
-        <v>9.76316738128662</v>
+        <v>9.76316833496094</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G51" t="n">
-        <v>10.1832685470581</v>
+        <v>10.1832695007324</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440391540527</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440391540527</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G57" t="n">
-        <v>9.9564151763916</v>
+        <v>9.95641613006592</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>9.9564151763916</v>
+        <v>9.95641613006592</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G60" t="n">
-        <v>10.0320320129395</v>
+        <v>10.0320329666138</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G61" t="n">
-        <v>10.0320320129395</v>
+        <v>10.0320329666138</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G63" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G64" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G66" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>9.9564151763916</v>
+        <v>9.95641613006592</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G71" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440391540527</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G74" t="n">
-        <v>10.0656404495239</v>
+        <v>10.0656414031982</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G76" t="n">
-        <v>10.0488386154175</v>
+        <v>10.0488367080688</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G77" t="n">
-        <v>10.0320320129395</v>
+        <v>10.0320329666138</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G80" t="n">
-        <v>10.0488386154175</v>
+        <v>10.0488367080688</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440391540527</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440391540527</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440391540527</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G97" t="n">
-        <v>10.0488386154175</v>
+        <v>10.0488367080688</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G99" t="n">
-        <v>9.97321891784668</v>
+        <v>9.973219871521</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G104" t="n">
-        <v>9.73796272277832</v>
+        <v>9.73796367645264</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G106" t="n">
-        <v>9.62873554229736</v>
+        <v>9.62873458862305</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G107" t="n">
-        <v>9.62873554229736</v>
+        <v>9.62873458862305</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G108" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394306182861</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033462524414</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>11.5</v>
       </c>
       <c r="G110" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033462524414</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>11.5</v>
       </c>
       <c r="G114" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>11.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>11.5</v>
       </c>
       <c r="G137" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G148" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033462524414</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>11.5</v>
       </c>
       <c r="G154" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>11</v>
       </c>
       <c r="G159" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G161" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>11</v>
       </c>
       <c r="G164" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>11</v>
       </c>
       <c r="G165" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>11</v>
       </c>
       <c r="G166" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>11</v>
       </c>
       <c r="G168" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>9.28425216674805</v>
+        <v>9.28425312042236</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G170" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G171" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G176" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>11</v>
       </c>
       <c r="G177" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G179" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>11</v>
       </c>
       <c r="G182" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>9.15822124481201</v>
+        <v>9.1582202911377</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G185" t="n">
-        <v>9.07420063018799</v>
+        <v>9.0742015838623</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>8.99018096923828</v>
+        <v>8.99018001556396</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G189" t="n">
-        <v>9.07420063018799</v>
+        <v>9.0742015838623</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>8.99018096923828</v>
+        <v>8.99018001556396</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>9.15822124481201</v>
+        <v>9.1582202911377</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>9.15822124481201</v>
+        <v>9.1582202911377</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>9.07420063018799</v>
+        <v>9.0742015838623</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>9.15822124481201</v>
+        <v>9.1582202911377</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G222" t="n">
-        <v>9.07222938537598</v>
+        <v>9.07223033905029</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G225" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G235" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G243" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11</v>
       </c>
       <c r="G245" t="n">
-        <v>9.45919704437256</v>
+        <v>9.45919609069824</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11</v>
       </c>
       <c r="G246" t="n">
-        <v>9.45919704437256</v>
+        <v>9.45919609069824</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G249" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G250" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G252" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G254" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>9.07222938537598</v>
+        <v>9.07223033905029</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G268" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>10</v>
       </c>
       <c r="G270" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>8.3412914276123</v>
+        <v>8.34129047393799</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10</v>
       </c>
       <c r="G285" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>8.3412914276123</v>
+        <v>8.34129047393799</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>8.3412914276123</v>
+        <v>8.34129047393799</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.5</v>
       </c>
       <c r="G296" t="n">
-        <v>8.1693058013916</v>
+        <v>8.16930484771729</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>10</v>
       </c>
       <c r="G299" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>10</v>
       </c>
       <c r="G300" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10</v>
       </c>
       <c r="G301" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>10</v>
       </c>
       <c r="G302" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>8.3412914276123</v>
+        <v>8.34129047393799</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>8.13490867614746</v>
+        <v>8.13490962982178</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G307" t="n">
-        <v>8.03171920776367</v>
+        <v>8.03171825408936</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G309" t="n">
-        <v>8.03171920776367</v>
+        <v>8.03171825408936</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G310" t="n">
-        <v>7.87693119049072</v>
+        <v>7.87693023681641</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>7.87693119049072</v>
+        <v>7.87693023681641</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>7.70494508743286</v>
+        <v>7.70494604110718</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.5</v>
       </c>
       <c r="G318" t="n">
-        <v>7.30937910079956</v>
+        <v>7.30937814712524</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>7.2061882019043</v>
+        <v>7.20618772506714</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G326" t="n">
-        <v>7.2061882019043</v>
+        <v>7.20618772506714</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>9</v>
       </c>
       <c r="G327" t="n">
-        <v>7.73934316635132</v>
+        <v>7.739342212677</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>7.48136472702026</v>
+        <v>7.48136377334595</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>7.70494508743286</v>
+        <v>7.70494604110718</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G338" t="n">
-        <v>7.53295993804932</v>
+        <v>7.53296041488647</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G340" t="n">
-        <v>7.29217958450317</v>
+        <v>7.29218006134033</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G341" t="n">
-        <v>7.13739347457886</v>
+        <v>7.13739395141602</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>6.9138126373291</v>
+        <v>6.91381311416626</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>6.7418270111084</v>
+        <v>6.74182748794556</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>6.7418270111084</v>
+        <v>6.74182748794556</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>6.7418270111084</v>
+        <v>6.74182748794556</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G367" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260688781738</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G369" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260688781738</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260688781738</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G371" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260688781738</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>7.13739347457886</v>
+        <v>7.13739395141602</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G374" t="n">
-        <v>6.75902605056763</v>
+        <v>6.75902557373047</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G376" t="n">
-        <v>6.77622509002686</v>
+        <v>6.7762246131897</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G383" t="n">
-        <v>6.93101167678833</v>
+        <v>6.93101119995117</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>6.9138126373291</v>
+        <v>6.91381311416626</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>6.93101167678833</v>
+        <v>6.93101119995117</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G399" t="n">
-        <v>6.89661407470703</v>
+        <v>6.89661455154419</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G405" t="n">
-        <v>6.75902605056763</v>
+        <v>6.75902557373047</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G411" t="n">
-        <v>7.53295993804932</v>
+        <v>7.53296041488647</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G412" t="n">
-        <v>7.48136472702026</v>
+        <v>7.48136377334595</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G414" t="n">
-        <v>7.44696807861328</v>
+        <v>7.44696712493896</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G417" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G418" t="n">
-        <v>7.53295993804932</v>
+        <v>7.53296041488647</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>7.34377670288086</v>
+        <v>7.3437762260437</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>7.34377670288086</v>
+        <v>7.3437762260437</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>8.5</v>
       </c>
       <c r="G423" t="n">
-        <v>7.30937910079956</v>
+        <v>7.30937814712524</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>8.5</v>
       </c>
       <c r="G428" t="n">
-        <v>7.30937910079956</v>
+        <v>7.30937814712524</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G429" t="n">
-        <v>7.29217958450317</v>
+        <v>7.29218006134033</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>7.13739347457886</v>
+        <v>7.13739395141602</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.5</v>
       </c>
       <c r="G431" t="n">
-        <v>7.30937910079956</v>
+        <v>7.30937814712524</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>9</v>
       </c>
       <c r="G433" t="n">
-        <v>7.73934316635132</v>
+        <v>7.739342212677</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>7.48136472702026</v>
+        <v>7.48136377334595</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>7.78233814239502</v>
+        <v>7.78233909606934</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>7.37759447097778</v>
+        <v>7.37759494781494</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.5</v>
       </c>
       <c r="G474" t="n">
-        <v>7.55536794662476</v>
+        <v>7.55536699295044</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.5</v>
       </c>
       <c r="G475" t="n">
-        <v>7.55536794662476</v>
+        <v>7.55536699295044</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>8.5</v>
       </c>
       <c r="G476" t="n">
-        <v>7.55536794662476</v>
+        <v>7.55536699295044</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>7.37759447097778</v>
+        <v>7.37759494781494</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G480" t="n">
-        <v>7.46648073196411</v>
+        <v>7.46648025512695</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G481" t="n">
-        <v>7.46648073196411</v>
+        <v>7.46648025512695</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G482" t="n">
-        <v>7.46648073196411</v>
+        <v>7.46648025512695</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G493" t="n">
-        <v>7.46648073196411</v>
+        <v>7.46648025512695</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>7.59981107711792</v>
+        <v>7.59981155395508</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>7.25</v>
       </c>
       <c r="G536" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>7.25</v>
       </c>
       <c r="G537" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>7.25</v>
       </c>
       <c r="G538" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>7.25</v>
       </c>
       <c r="G539" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>7.25</v>
       </c>
       <c r="G541" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>7.25</v>
       </c>
       <c r="G553" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>7</v>
       </c>
       <c r="G554" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G571" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G573" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G574" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>7.25</v>
       </c>
       <c r="G575" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G576" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7</v>
       </c>
       <c r="G579" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>7</v>
       </c>
       <c r="G580" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>7</v>
       </c>
       <c r="G581" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G582" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G583" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>7</v>
       </c>
       <c r="G584" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>7</v>
       </c>
       <c r="G585" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>7</v>
       </c>
       <c r="G589" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6.75</v>
       </c>
       <c r="G596" t="n">
-        <v>5.99985122680664</v>
+        <v>5.99985074996948</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6.5</v>
       </c>
       <c r="G597" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G606" t="n">
-        <v>5.82207727432251</v>
+        <v>5.82207775115967</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G609" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>7</v>
       </c>
       <c r="G611" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>7</v>
       </c>
       <c r="G612" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>7</v>
       </c>
       <c r="G613" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>7</v>
       </c>
       <c r="G614" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7</v>
       </c>
       <c r="G615" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G622" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G624" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G625" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G626" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G627" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G628" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G631" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>6.75</v>
       </c>
       <c r="G632" t="n">
-        <v>5.99985122680664</v>
+        <v>5.99985074996948</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.5</v>
       </c>
       <c r="G635" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>6.5</v>
       </c>
       <c r="G636" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.5</v>
       </c>
       <c r="G637" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>6.5</v>
       </c>
       <c r="G638" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.5</v>
       </c>
       <c r="G639" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>6.5</v>
       </c>
       <c r="G640" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>6.25</v>
       </c>
       <c r="G645" t="n">
-        <v>5.55541753768921</v>
+        <v>5.55541706085205</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>6.5</v>
       </c>
       <c r="G649" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>6.5</v>
       </c>
       <c r="G651" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>6.5</v>
       </c>
       <c r="G652" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>6</v>
       </c>
       <c r="G655" t="n">
-        <v>5.33320093154907</v>
+        <v>5.33320045471191</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>6</v>
       </c>
       <c r="G661" t="n">
-        <v>5.33320093154907</v>
+        <v>5.33320045471191</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5.75</v>
       </c>
       <c r="G664" t="n">
-        <v>5.11098432540894</v>
+        <v>5.11098384857178</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>4.07101011276245</v>
+        <v>4.07100963592529</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.5</v>
       </c>
       <c r="G677" t="n">
-        <v>3.99990081787109</v>
+        <v>3.99990034103394</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.8932363986969</v>
+        <v>3.89323687553406</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>3.73324036598206</v>
+        <v>3.73324012756348</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G684" t="n">
-        <v>3.68879723548889</v>
+        <v>3.68879747390747</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G686" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101360321045</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.5</v>
       </c>
       <c r="G689" t="n">
-        <v>3.99990081787109</v>
+        <v>3.99990034103394</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G690" t="n">
-        <v>4.08878755569458</v>
+        <v>4.08878707885742</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G691" t="n">
-        <v>3.98212313652039</v>
+        <v>3.98212361335754</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101360321045</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101360321045</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.5</v>
       </c>
       <c r="G698" t="n">
-        <v>3.99990081787109</v>
+        <v>3.99990034103394</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>3.98212313652039</v>
+        <v>3.98212361335754</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G700" t="n">
-        <v>3.98212313652039</v>
+        <v>3.98212361335754</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G701" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101360321045</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G702" t="n">
-        <v>3.8932363986969</v>
+        <v>3.89323687553406</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>3.76879477500916</v>
+        <v>3.76879501342773</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G711" t="n">
-        <v>3.76879477500916</v>
+        <v>3.76879501342773</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G718" t="n">
-        <v>3.8932363986969</v>
+        <v>3.89323687553406</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G719" t="n">
-        <v>4.08878755569458</v>
+        <v>4.08878707885742</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -60952,6 +60952,32 @@
         <v>2.40000009536743</v>
       </c>
       <c r="H2330" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2331">
+      <c r="A2331" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2331" t="n">
+        <v>3688</v>
+      </c>
+      <c r="C2331" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="D2331" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="E2331" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="F2331" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="G2331" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="H2331" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2" t="n">
-        <v>9.40188121795654</v>
+        <v>9.40188026428223</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.41868591308594</v>
+        <v>9.41868495941162</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>11.25</v>
       </c>
       <c r="G5" t="n">
-        <v>9.45229434967041</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.65394306182861</v>
+        <v>9.65394115447998</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>9.57832336425781</v>
+        <v>9.57832431793213</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.65394306182861</v>
+        <v>9.65394115447998</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>11.5</v>
       </c>
       <c r="G9" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>9.57832336425781</v>
+        <v>9.57832431793213</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G11" t="n">
-        <v>9.73796367645264</v>
+        <v>9.737961769104</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.62033462524414</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>11.5</v>
       </c>
       <c r="G15" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G16" t="n">
-        <v>9.63713836669922</v>
+        <v>9.6371374130249</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G18" t="n">
-        <v>9.63713836669922</v>
+        <v>9.6371374130249</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>9.57832336425781</v>
+        <v>9.57832431793213</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G20" t="n">
-        <v>9.61193180084229</v>
+        <v>9.6119327545166</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>9.61193180084229</v>
+        <v>9.6119327545166</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G22" t="n">
-        <v>9.64553928375244</v>
+        <v>9.64554023742676</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>9.53631401062012</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G24" t="n">
-        <v>9.40188121795654</v>
+        <v>9.40188026428223</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>11.25</v>
       </c>
       <c r="G28" t="n">
-        <v>9.45229434967041</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G29" t="n">
-        <v>9.56151962280273</v>
+        <v>9.56151866912842</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G30" t="n">
-        <v>9.51950931549072</v>
+        <v>9.51950836181641</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G31" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G34" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>9.53631401062012</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G39" t="n">
-        <v>9.64553928375244</v>
+        <v>9.64554023742676</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G40" t="n">
-        <v>9.73796367645264</v>
+        <v>9.737961769104</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G41" t="n">
-        <v>9.73796367645264</v>
+        <v>9.737961769104</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G42" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G45" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198143005371</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>9.77157020568848</v>
+        <v>9.77157115936279</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>11.5</v>
       </c>
       <c r="G47" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G49" t="n">
-        <v>9.77157020568848</v>
+        <v>9.77157115936279</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G50" t="n">
-        <v>9.76316833496094</v>
+        <v>9.76316928863525</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G51" t="n">
-        <v>10.1832695007324</v>
+        <v>10.1832714080811</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>9.91440391540527</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G54" t="n">
-        <v>9.63713836669922</v>
+        <v>9.6371374130249</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>9.91440391540527</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G60" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320339202881</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G61" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320339202881</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G63" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G64" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198143005371</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G66" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G67" t="n">
-        <v>9.93961143493652</v>
+        <v>9.93960952758789</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>11.75</v>
       </c>
       <c r="G70" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G71" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>9.91440391540527</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G73" t="n">
-        <v>10.057240486145</v>
+        <v>10.0572395324707</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>9.9984245300293</v>
+        <v>9.99842643737793</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G76" t="n">
-        <v>10.0488367080688</v>
+        <v>10.0488376617432</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G77" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320339202881</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>9.9984245300293</v>
+        <v>9.99842643737793</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G80" t="n">
-        <v>10.0488367080688</v>
+        <v>10.0488376617432</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>11.75</v>
       </c>
       <c r="G83" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.91440391540527</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G85" t="n">
-        <v>9.90600299835205</v>
+        <v>9.90600204467773</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>9.91440391540527</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G88" t="n">
-        <v>9.90600299835205</v>
+        <v>9.90600204467773</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>11.75</v>
       </c>
       <c r="G91" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>11.75</v>
       </c>
       <c r="G92" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>11.75</v>
       </c>
       <c r="G93" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>9.91440391540527</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>11.75</v>
       </c>
       <c r="G95" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G97" t="n">
-        <v>10.0488367080688</v>
+        <v>10.0488376617432</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G98" t="n">
-        <v>9.98162078857422</v>
+        <v>9.98162174224854</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G102" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198143005371</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G103" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198143005371</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G104" t="n">
-        <v>9.73796367645264</v>
+        <v>9.737961769104</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G105" t="n">
-        <v>9.63713836669922</v>
+        <v>9.6371374130249</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G106" t="n">
-        <v>9.62873458862305</v>
+        <v>9.62873649597168</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G107" t="n">
-        <v>9.62873458862305</v>
+        <v>9.62873649597168</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G108" t="n">
-        <v>9.65394306182861</v>
+        <v>9.65394115447998</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>9.62033462524414</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>11.5</v>
       </c>
       <c r="G110" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>9.62033462524414</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>9.53631401062012</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G113" t="n">
-        <v>9.64553928375244</v>
+        <v>9.64554023742676</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>11.5</v>
       </c>
       <c r="G114" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G115" t="n">
-        <v>9.72955989837646</v>
+        <v>9.72956085205078</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>11.75</v>
       </c>
       <c r="G118" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G123" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>11.75</v>
       </c>
       <c r="G130" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G132" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G133" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>11.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>11.5</v>
       </c>
       <c r="G137" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G139" t="n">
-        <v>9.57832336425781</v>
+        <v>9.57832431793213</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G148" t="n">
-        <v>9.62033462524414</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>9.57832336425781</v>
+        <v>9.57832431793213</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>9.57832336425781</v>
+        <v>9.57832431793213</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>11.5</v>
       </c>
       <c r="G154" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G155" t="n">
-        <v>9.53631401062012</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>11.25</v>
       </c>
       <c r="G157" t="n">
-        <v>9.45229434967041</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>11</v>
       </c>
       <c r="G159" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G161" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>11</v>
       </c>
       <c r="G164" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>11</v>
       </c>
       <c r="G165" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>11</v>
       </c>
       <c r="G166" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>11</v>
       </c>
       <c r="G168" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>9.28425312042236</v>
+        <v>9.28425216674805</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G170" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>9.57832336425781</v>
+        <v>9.57832431793213</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>11</v>
       </c>
       <c r="G177" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G179" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>11.25</v>
       </c>
       <c r="G180" t="n">
-        <v>9.45229434967041</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>11.25</v>
       </c>
       <c r="G181" t="n">
-        <v>9.45229434967041</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>11</v>
       </c>
       <c r="G182" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>9.1582202911377</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G184" t="n">
-        <v>9.1162109375</v>
+        <v>9.11621189117432</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G185" t="n">
-        <v>9.0742015838623</v>
+        <v>9.07420253753662</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G186" t="n">
-        <v>8.94816970825195</v>
+        <v>8.94817066192627</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>8.94816970825195</v>
+        <v>8.94817066192627</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>8.99018001556396</v>
+        <v>8.9901819229126</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G189" t="n">
-        <v>9.0742015838623</v>
+        <v>9.07420253753662</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>9.1162109375</v>
+        <v>9.11621189117432</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>9.1162109375</v>
+        <v>9.11621189117432</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>8.99018001556396</v>
+        <v>8.9901819229126</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>9.1582202911377</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>9.1582202911377</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>9.0742015838623</v>
+        <v>9.07420253753662</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>9.1582202911377</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G201" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G202" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G203" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G204" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G205" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G206" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G207" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G210" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G214" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>8.98623657226562</v>
+        <v>8.98623561859131</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G218" t="n">
-        <v>8.8572473526001</v>
+        <v>8.85724830627441</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>8.8572473526001</v>
+        <v>8.85724830627441</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G222" t="n">
-        <v>9.07223033905029</v>
+        <v>9.07222938537598</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G223" t="n">
-        <v>8.90024471282959</v>
+        <v>8.90024566650391</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G225" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>8.90024471282959</v>
+        <v>8.90024566650391</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>8.98623657226562</v>
+        <v>8.98623561859131</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>10.5</v>
       </c>
       <c r="G228" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>8.8572473526001</v>
+        <v>8.85724830627441</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G236" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G237" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.5</v>
       </c>
       <c r="G238" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G248" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.5</v>
       </c>
       <c r="G255" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>10.5</v>
       </c>
       <c r="G256" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>10.5</v>
       </c>
       <c r="G257" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>10.5</v>
       </c>
       <c r="G258" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.5</v>
       </c>
       <c r="G262" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>8.8572473526001</v>
+        <v>8.85724830627441</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>9.07223033905029</v>
+        <v>9.07222938537598</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G265" t="n">
-        <v>8.8572473526001</v>
+        <v>8.85724830627441</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>8.8572473526001</v>
+        <v>8.85724830627441</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G268" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G272" t="n">
-        <v>8.28969573974609</v>
+        <v>8.28969669342041</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G273" t="n">
-        <v>8.28969573974609</v>
+        <v>8.28969669342041</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G277" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G278" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G279" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G281" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G282" t="n">
-        <v>8.51327610015869</v>
+        <v>8.51327705383301</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G288" t="n">
-        <v>8.22090244293213</v>
+        <v>8.22090148925781</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.25529956817627</v>
+        <v>8.25529861450195</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.5</v>
       </c>
       <c r="G296" t="n">
-        <v>8.16930484771729</v>
+        <v>8.1693058013916</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G303" t="n">
-        <v>8.53047561645508</v>
+        <v>8.53047466278076</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>8.13490962982178</v>
+        <v>8.13490867614746</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G307" t="n">
-        <v>8.03171825408936</v>
+        <v>8.03171730041504</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G309" t="n">
-        <v>8.03171825408936</v>
+        <v>8.03171730041504</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G310" t="n">
-        <v>7.87693023681641</v>
+        <v>7.87693071365356</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>7.87693023681641</v>
+        <v>7.87693071365356</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>7.82533502578735</v>
+        <v>7.82533550262451</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>7.70494604110718</v>
+        <v>7.70494556427002</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.5</v>
       </c>
       <c r="G318" t="n">
-        <v>7.30937814712524</v>
+        <v>7.3093786239624</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G319" t="n">
-        <v>7.36097526550293</v>
+        <v>7.36097478866577</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G324" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G328" t="n">
-        <v>7.82533502578735</v>
+        <v>7.82533550262451</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G329" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>7.48136377334595</v>
+        <v>7.48136425018311</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G331" t="n">
-        <v>7.72214317321777</v>
+        <v>7.72214365005493</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G332" t="n">
-        <v>7.72214317321777</v>
+        <v>7.72214365005493</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>7.70494604110718</v>
+        <v>7.70494556427002</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G335" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G336" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>7.41257047653198</v>
+        <v>7.41256952285767</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G340" t="n">
-        <v>7.29218006134033</v>
+        <v>7.29218053817749</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G342" t="n">
-        <v>7.08579778671265</v>
+        <v>7.0857982635498</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G343" t="n">
-        <v>7.06860017776489</v>
+        <v>7.06859970092773</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G349" t="n">
-        <v>7.08579778671265</v>
+        <v>7.0857982635498</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>6.91381311416626</v>
+        <v>6.9138126373291</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>6.74182748794556</v>
+        <v>6.7418270111084</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>6.74182748794556</v>
+        <v>6.7418270111084</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>6.74182748794556</v>
+        <v>6.7418270111084</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G365" t="n">
-        <v>6.79342317581177</v>
+        <v>6.79342269897461</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G367" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G369" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G371" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G374" t="n">
-        <v>6.75902557373047</v>
+        <v>6.75902605056763</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G375" t="n">
-        <v>6.79342317581177</v>
+        <v>6.79342269897461</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G376" t="n">
-        <v>6.7762246131897</v>
+        <v>6.77622413635254</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>6.84501838684082</v>
+        <v>6.84501886367798</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>6.84501838684082</v>
+        <v>6.84501886367798</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G383" t="n">
-        <v>6.93101119995117</v>
+        <v>6.93101167678833</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>6.91381311416626</v>
+        <v>6.9138126373291</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>6.84501838684082</v>
+        <v>6.84501886367798</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G393" t="n">
-        <v>6.69023180007935</v>
+        <v>6.69023132324219</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>6.93101119995117</v>
+        <v>6.93101167678833</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>6.79342317581177</v>
+        <v>6.79342269897461</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G405" t="n">
-        <v>6.75902557373047</v>
+        <v>6.75902605056763</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>6.79342317581177</v>
+        <v>6.79342269897461</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G410" t="n">
-        <v>7.46416664123535</v>
+        <v>7.46416521072388</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G412" t="n">
-        <v>7.48136377334595</v>
+        <v>7.48136425018311</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G415" t="n">
-        <v>7.61895227432251</v>
+        <v>7.61895275115967</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G416" t="n">
-        <v>7.72214317321777</v>
+        <v>7.72214365005493</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G417" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G419" t="n">
-        <v>7.41257047653198</v>
+        <v>7.41256952285767</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G422" t="n">
-        <v>7.36097526550293</v>
+        <v>7.36097478866577</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>8.5</v>
       </c>
       <c r="G423" t="n">
-        <v>7.30937814712524</v>
+        <v>7.3093786239624</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G427" t="n">
-        <v>7.42976856231689</v>
+        <v>7.42976903915405</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>8.5</v>
       </c>
       <c r="G428" t="n">
-        <v>7.30937814712524</v>
+        <v>7.3093786239624</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G429" t="n">
-        <v>7.29218006134033</v>
+        <v>7.29218053817749</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.5</v>
       </c>
       <c r="G431" t="n">
-        <v>7.30937814712524</v>
+        <v>7.3093786239624</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G435" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>7.48136377334595</v>
+        <v>7.48136425018311</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>7.78233909606934</v>
+        <v>7.78234004974365</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G446" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G449" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G450" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G451" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G452" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G453" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G454" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G455" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G457" t="n">
-        <v>7.64425468444824</v>
+        <v>7.6442551612854</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G458" t="n">
-        <v>7.64425468444824</v>
+        <v>7.6442551612854</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>8</v>
       </c>
       <c r="G468" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G469" t="n">
-        <v>7.15537786483765</v>
+        <v>7.15537738800049</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G470" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.5</v>
       </c>
       <c r="G474" t="n">
-        <v>7.55536699295044</v>
+        <v>7.5553674697876</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.5</v>
       </c>
       <c r="G475" t="n">
-        <v>7.55536699295044</v>
+        <v>7.5553674697876</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>8.5</v>
       </c>
       <c r="G476" t="n">
-        <v>7.55536699295044</v>
+        <v>7.5553674697876</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>7.59981155395508</v>
+        <v>7.59981107711792</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>8</v>
       </c>
       <c r="G498" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G499" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8</v>
       </c>
       <c r="G500" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G502" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G503" t="n">
-        <v>7.022047996521</v>
+        <v>7.02204751968384</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8</v>
       </c>
       <c r="G504" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>8</v>
       </c>
       <c r="G505" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>8</v>
       </c>
       <c r="G506" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>8</v>
       </c>
       <c r="G509" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>8</v>
       </c>
       <c r="G511" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>8</v>
       </c>
       <c r="G512" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G513" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G515" t="n">
-        <v>7.15537786483765</v>
+        <v>7.15537738800049</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>7.5</v>
       </c>
       <c r="G517" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G518" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761383056641</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>7.5</v>
       </c>
       <c r="G519" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>7.5</v>
       </c>
       <c r="G520" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G521" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761383056641</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761383056641</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761383056641</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>7.5</v>
       </c>
       <c r="G525" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>7.5</v>
       </c>
       <c r="G526" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>7.5</v>
       </c>
       <c r="G527" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>7.5</v>
       </c>
       <c r="G528" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761383056641</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G530" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761383056641</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>6.53317070007324</v>
+        <v>6.5331711769104</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G533" t="n">
-        <v>6.71094465255737</v>
+        <v>6.71094417572021</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>6.53317070007324</v>
+        <v>6.5331711769104</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761383056641</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761383056641</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G548" t="n">
-        <v>6.53317070007324</v>
+        <v>6.5331711769104</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761383056641</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G550" t="n">
-        <v>6.53317070007324</v>
+        <v>6.5331711769104</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G551" t="n">
-        <v>6.53317070007324</v>
+        <v>6.5331711769104</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>7</v>
       </c>
       <c r="G554" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G569" t="n">
-        <v>5.95540714263916</v>
+        <v>5.95540761947632</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7</v>
       </c>
       <c r="G579" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>7</v>
       </c>
       <c r="G580" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>7</v>
       </c>
       <c r="G581" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>7</v>
       </c>
       <c r="G584" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>7</v>
       </c>
       <c r="G585" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>7</v>
       </c>
       <c r="G589" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G595" t="n">
-        <v>5.95540714263916</v>
+        <v>5.95540761947632</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G607" t="n">
-        <v>5.86652040481567</v>
+        <v>5.86652088165283</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>5.95540714263916</v>
+        <v>5.95540761947632</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>7</v>
       </c>
       <c r="G611" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>7</v>
       </c>
       <c r="G612" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>7</v>
       </c>
       <c r="G613" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>7</v>
       </c>
       <c r="G614" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7</v>
       </c>
       <c r="G615" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G629" t="n">
-        <v>5.95540714263916</v>
+        <v>5.95540761947632</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.86652040481567</v>
+        <v>5.86652088165283</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G641" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>5.64430379867554</v>
+        <v>5.6443042755127</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>6.25</v>
       </c>
       <c r="G645" t="n">
-        <v>5.55541706085205</v>
+        <v>5.55541753768921</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.64430379867554</v>
+        <v>5.6443042755127</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G654" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>6</v>
       </c>
       <c r="G655" t="n">
-        <v>5.33320045471191</v>
+        <v>5.33320093154907</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>6</v>
       </c>
       <c r="G661" t="n">
-        <v>5.33320045471191</v>
+        <v>5.33320093154907</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G662" t="n">
-        <v>5.37764453887939</v>
+        <v>5.37764406204224</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5.75</v>
       </c>
       <c r="G664" t="n">
-        <v>5.11098384857178</v>
+        <v>5.11098432540894</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G666" t="n">
-        <v>4.35544681549072</v>
+        <v>4.35544729232788</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>4.26656103134155</v>
+        <v>4.26656055450439</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>4.07100963592529</v>
+        <v>4.07101011276245</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G670" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G671" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G672" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G673" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G674" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G675" t="n">
-        <v>3.82212734222412</v>
+        <v>3.8221275806427</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G676" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G678" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.89323687553406</v>
+        <v>3.89323663711548</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G680" t="n">
-        <v>3.85768222808838</v>
+        <v>3.85768175125122</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G682" t="n">
-        <v>3.75101757049561</v>
+        <v>3.75101780891418</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G685" t="n">
-        <v>3.80435013771057</v>
+        <v>3.80434989929199</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G686" t="n">
-        <v>3.91101360321045</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>3.85768222808838</v>
+        <v>3.85768175125122</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G690" t="n">
-        <v>4.08878707885742</v>
+        <v>4.08878755569458</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G691" t="n">
-        <v>3.98212361335754</v>
+        <v>3.98212337493896</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>3.96434593200684</v>
+        <v>3.96434569358826</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G694" t="n">
-        <v>3.85768222808838</v>
+        <v>3.85768175125122</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.91101360321045</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.91101360321045</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G697" t="n">
-        <v>3.95545697212219</v>
+        <v>3.95545744895935</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>3.98212361335754</v>
+        <v>3.98212337493896</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G700" t="n">
-        <v>3.98212361335754</v>
+        <v>3.98212337493896</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G701" t="n">
-        <v>3.91101360321045</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G702" t="n">
-        <v>3.89323687553406</v>
+        <v>3.89323663711548</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>3.76879501342773</v>
+        <v>3.76879525184631</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G705" t="n">
-        <v>3.88434791564941</v>
+        <v>3.88434743881226</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G706" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>3.88434791564941</v>
+        <v>3.88434743881226</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G708" t="n">
-        <v>3.83101606369019</v>
+        <v>3.83101558685303</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>3.83101606369019</v>
+        <v>3.83101558685303</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G711" t="n">
-        <v>3.76879501342773</v>
+        <v>3.76879525184631</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G712" t="n">
-        <v>3.75101757049561</v>
+        <v>3.75101780891418</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G713" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G714" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G716" t="n">
-        <v>3.80435013771057</v>
+        <v>3.80434989929199</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>3.88434791564941</v>
+        <v>3.88434743881226</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G718" t="n">
-        <v>3.89323687553406</v>
+        <v>3.89323663711548</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G719" t="n">
-        <v>4.08878707885742</v>
+        <v>4.08878755569458</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>4.13323020935059</v>
+        <v>4.13323068618774</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>4.38185501098633</v>
+        <v>4.38185453414917</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>4.75</v>
       </c>
       <c r="G731" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G734" t="n">
-        <v>4.38185501098633</v>
+        <v>4.38185453414917</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G735" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G736" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G737" t="n">
-        <v>4.40935611724854</v>
+        <v>4.40935564041138</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G740" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.75</v>
       </c>
       <c r="G743" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G744" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G747" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G752" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G759" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>4.08850908279419</v>
+        <v>4.08850860595703</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G784" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G786" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G787" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>4.07934141159058</v>
+        <v>4.07934188842773</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G789" t="n">
-        <v>4.07934141159058</v>
+        <v>4.07934188842773</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>4.04267358779907</v>
+        <v>4.04267311096191</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G797" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G798" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>3.91433453559875</v>
+        <v>3.91433477401733</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.86849904060364</v>
+        <v>3.86849927902222</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G807" t="n">
-        <v>3.88683319091797</v>
+        <v>3.88683342933655</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G808" t="n">
-        <v>3.88683319091797</v>
+        <v>3.88683342933655</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G813" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G816" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G819" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.75</v>
       </c>
       <c r="G821" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G825" t="n">
-        <v>4.51936054229736</v>
+        <v>4.51936006546021</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>4.51019334793091</v>
+        <v>4.51019382476807</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.75</v>
       </c>
       <c r="G829" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.04267358779907</v>
+        <v>4.04267311096191</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>3.94183588027954</v>
+        <v>3.94183611869812</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G840" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G844" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>4.96854639053345</v>
+        <v>4.96854686737061</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>5.1152195930481</v>
+        <v>5.11521911621094</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G862" t="n">
-        <v>5.13355350494385</v>
+        <v>5.13355398178101</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G863" t="n">
-        <v>5.1518874168396</v>
+        <v>5.15188789367676</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>5.00521516799927</v>
+        <v>5.00521469116211</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G873" t="n">
-        <v>5.39023113250732</v>
+        <v>5.39023160934448</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G874" t="n">
-        <v>5.39023113250732</v>
+        <v>5.39023160934448</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G878" t="n">
-        <v>5.61024045944214</v>
+        <v>5.6102409362793</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G882" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>5.88525247573853</v>
+        <v>5.88525295257568</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>5.94025468826294</v>
+        <v>5.9402551651001</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G893" t="n">
-        <v>5.83025074005127</v>
+        <v>5.83025026321411</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G906" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G910" t="n">
-        <v>6.19693326950073</v>
+        <v>6.19693279266357</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>6.38027429580688</v>
+        <v>6.38027381896973</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G913" t="n">
-        <v>6.28860378265381</v>
+        <v>6.28860330581665</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>6.47194480895996</v>
+        <v>6.4719443321228</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G920" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G922" t="n">
-        <v>6.58194875717163</v>
+        <v>6.58194923400879</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G924" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G927" t="n">
-        <v>6.61861705780029</v>
+        <v>6.61861753463745</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>6.58194875717163</v>
+        <v>6.58194923400879</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G931" t="n">
-        <v>6.61861705780029</v>
+        <v>6.61861753463745</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G937" t="n">
-        <v>6.54528093338013</v>
+        <v>6.54528045654297</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G939" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>6.85696077346802</v>
+        <v>6.85696125030518</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G956" t="n">
-        <v>6.78362464904785</v>
+        <v>6.78362417221069</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -60978,6 +60978,32 @@
         <v>2.44000005722046</v>
       </c>
       <c r="H2331" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="A2332" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2332" t="n">
+        <v>4595</v>
+      </c>
+      <c r="C2332" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="D2332" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="E2332" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="F2332" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="G2332" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="H2332" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -447,7 +447,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G3" t="n">
-        <v>9.44389057159424</v>
+        <v>9.44388961791992</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394115447998</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394115447998</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>11.5</v>
       </c>
       <c r="G9" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G12" t="n">
-        <v>9.67074584960938</v>
+        <v>9.67074680328369</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033462524414</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>11.5</v>
       </c>
       <c r="G15" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G16" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G18" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G20" t="n">
-        <v>9.61193180084229</v>
+        <v>9.61193084716797</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>9.61193180084229</v>
+        <v>9.61193084716797</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G22" t="n">
-        <v>9.64554023742676</v>
+        <v>9.64553928375244</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G29" t="n">
-        <v>9.56151866912842</v>
+        <v>9.56151962280273</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G31" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G34" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G39" t="n">
-        <v>9.64554023742676</v>
+        <v>9.64553928375244</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G42" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G45" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198143005371</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>9.77157115936279</v>
+        <v>9.77156925201416</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>11.5</v>
       </c>
       <c r="G47" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G49" t="n">
-        <v>9.77157115936279</v>
+        <v>9.77156925201416</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G50" t="n">
-        <v>9.76316928863525</v>
+        <v>9.76316738128662</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G51" t="n">
-        <v>10.1832714080811</v>
+        <v>10.1832695007324</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G53" t="n">
-        <v>9.77997207641602</v>
+        <v>9.77997398376465</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G54" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G57" t="n">
-        <v>9.95641613006592</v>
+        <v>9.9564151763916</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>9.95641613006592</v>
+        <v>9.9564151763916</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>10.0404357910156</v>
+        <v>10.0404367446899</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G63" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G64" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198143005371</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G66" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G67" t="n">
-        <v>9.93961048126221</v>
+        <v>9.93961143493652</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>9.95641613006592</v>
+        <v>9.9564151763916</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G71" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G73" t="n">
-        <v>10.0572395324707</v>
+        <v>10.057240486145</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G76" t="n">
-        <v>10.0488367080688</v>
+        <v>10.0488386154175</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G79" t="n">
-        <v>10.0404357910156</v>
+        <v>10.0404367446899</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G80" t="n">
-        <v>10.0488367080688</v>
+        <v>10.0488386154175</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G81" t="n">
-        <v>9.89760112762451</v>
+        <v>9.8976001739502</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G87" t="n">
-        <v>9.89760112762451</v>
+        <v>9.8976001739502</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G97" t="n">
-        <v>10.0488367080688</v>
+        <v>10.0488386154175</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G99" t="n">
-        <v>9.97321891784668</v>
+        <v>9.97321796417236</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G102" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198143005371</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G103" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198143005371</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G105" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G108" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394115447998</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033462524414</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>11.5</v>
       </c>
       <c r="G110" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033462524414</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G113" t="n">
-        <v>9.64554023742676</v>
+        <v>9.64553928375244</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>11.5</v>
       </c>
       <c r="G114" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>11.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>11.5</v>
       </c>
       <c r="G137" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G143" t="n">
-        <v>9.32626247406006</v>
+        <v>9.32626342773438</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G144" t="n">
-        <v>9.32626247406006</v>
+        <v>9.32626342773438</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G145" t="n">
-        <v>9.32626247406006</v>
+        <v>9.32626342773438</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G148" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033462524414</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>11.5</v>
       </c>
       <c r="G154" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>9.32626247406006</v>
+        <v>9.32626342773438</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G160" t="n">
-        <v>9.32626247406006</v>
+        <v>9.32626342773438</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>9.32626247406006</v>
+        <v>9.32626342773438</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>9.28425216674805</v>
+        <v>9.28425121307373</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>9.32626247406006</v>
+        <v>9.32626342773438</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G185" t="n">
-        <v>9.0742015838623</v>
+        <v>9.07420063018799</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G189" t="n">
-        <v>9.0742015838623</v>
+        <v>9.07420063018799</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>9.0742015838623</v>
+        <v>9.07420063018799</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G201" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G202" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G203" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G204" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G205" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G206" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G207" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G210" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G214" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>8.98623561859131</v>
+        <v>8.98623657226562</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G218" t="n">
-        <v>8.85724830627441</v>
+        <v>8.8572473526001</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>8.85724830627441</v>
+        <v>8.8572473526001</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G222" t="n">
-        <v>9.07222938537598</v>
+        <v>9.07223033905029</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>8.98623561859131</v>
+        <v>8.98623657226562</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>10.5</v>
       </c>
       <c r="G228" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>8.85724830627441</v>
+        <v>8.8572473526001</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G235" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G236" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G237" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.5</v>
       </c>
       <c r="G238" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G243" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11</v>
       </c>
       <c r="G245" t="n">
-        <v>9.45919609069824</v>
+        <v>9.45919704437256</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11</v>
       </c>
       <c r="G246" t="n">
-        <v>9.45919609069824</v>
+        <v>9.45919704437256</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G248" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G249" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G250" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G252" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G254" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.5</v>
       </c>
       <c r="G255" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>10.5</v>
       </c>
       <c r="G256" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>10.5</v>
       </c>
       <c r="G257" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>10.5</v>
       </c>
       <c r="G258" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.5</v>
       </c>
       <c r="G262" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>8.85724830627441</v>
+        <v>8.8572473526001</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>9.07222938537598</v>
+        <v>9.07223033905029</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G265" t="n">
-        <v>8.85724830627441</v>
+        <v>8.8572473526001</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G266" t="n">
-        <v>8.85724830627441</v>
+        <v>8.8572473526001</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>8.49607849121094</v>
+        <v>8.49607753753662</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G282" t="n">
-        <v>8.51327610015869</v>
+        <v>8.51327705383301</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G288" t="n">
-        <v>8.22090244293213</v>
+        <v>8.22090148925781</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.25529861450195</v>
+        <v>8.25529956817627</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G290" t="n">
-        <v>8.32409286499023</v>
+        <v>8.32409381866455</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G292" t="n">
-        <v>8.41008567810059</v>
+        <v>8.41008472442627</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G293" t="n">
-        <v>8.41008567810059</v>
+        <v>8.41008472442627</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G294" t="n">
-        <v>8.32409286499023</v>
+        <v>8.32409381866455</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G295" t="n">
-        <v>8.32409286499023</v>
+        <v>8.32409381866455</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>8.13490867614746</v>
+        <v>8.13490772247314</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G310" t="n">
-        <v>7.87693071365356</v>
+        <v>7.87693119049072</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>7.87693071365356</v>
+        <v>7.87693119049072</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>7.70494556427002</v>
+        <v>7.70494508743286</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.5</v>
       </c>
       <c r="G318" t="n">
-        <v>7.3093786239624</v>
+        <v>7.30937910079956</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G323" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G324" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>7.20618772506714</v>
+        <v>7.2061882019043</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G326" t="n">
-        <v>7.20618772506714</v>
+        <v>7.2061882019043</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>9</v>
       </c>
       <c r="G327" t="n">
-        <v>7.739342212677</v>
+        <v>7.73934316635132</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G329" t="n">
-        <v>7.65334892272949</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G331" t="n">
-        <v>7.72214365005493</v>
+        <v>7.72214317321777</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G332" t="n">
-        <v>7.72214365005493</v>
+        <v>7.72214317321777</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>7.70494556427002</v>
+        <v>7.70494508743286</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>7.65334892272949</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G335" t="n">
-        <v>7.65334892272949</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>7.41256999969482</v>
+        <v>7.41256952285767</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G338" t="n">
-        <v>7.53296041488647</v>
+        <v>7.53295993804932</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G340" t="n">
-        <v>7.29218006134033</v>
+        <v>7.29217958450317</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G341" t="n">
-        <v>7.13739395141602</v>
+        <v>7.13739347457886</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G342" t="n">
-        <v>7.0857982635498</v>
+        <v>7.08579778671265</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G344" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G345" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G346" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G347" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G348" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G349" t="n">
-        <v>7.0857982635498</v>
+        <v>7.08579778671265</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G350" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G356" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G357" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G358" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G364" t="n">
-        <v>6.63863563537598</v>
+        <v>6.63863611221313</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>7.13739395141602</v>
+        <v>7.13739347457886</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>7.05140113830566</v>
+        <v>7.05140066146851</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G374" t="n">
-        <v>6.75902605056763</v>
+        <v>6.75902557373047</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G376" t="n">
-        <v>6.77622413635254</v>
+        <v>6.7762246131897</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G385" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G386" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G387" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G388" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G393" t="n">
-        <v>6.69023132324219</v>
+        <v>6.69023180007935</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G395" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G405" t="n">
-        <v>6.75902605056763</v>
+        <v>6.75902557373047</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G408" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>7.24058485031128</v>
+        <v>7.24058532714844</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G410" t="n">
-        <v>7.46416568756104</v>
+        <v>7.46416664123535</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G411" t="n">
-        <v>7.53296041488647</v>
+        <v>7.53295993804932</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.65334892272949</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G414" t="n">
-        <v>7.44696712493896</v>
+        <v>7.44696760177612</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G416" t="n">
-        <v>7.72214365005493</v>
+        <v>7.72214317321777</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G418" t="n">
-        <v>7.53296041488647</v>
+        <v>7.53295993804932</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G419" t="n">
-        <v>7.41256999969482</v>
+        <v>7.41256952285767</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>7.34377574920654</v>
+        <v>7.3437762260437</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>7.34377574920654</v>
+        <v>7.3437762260437</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>8.5</v>
       </c>
       <c r="G423" t="n">
-        <v>7.3093786239624</v>
+        <v>7.30937910079956</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>7.65334892272949</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>8.5</v>
       </c>
       <c r="G428" t="n">
-        <v>7.3093786239624</v>
+        <v>7.30937910079956</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G429" t="n">
-        <v>7.29218006134033</v>
+        <v>7.29217958450317</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>7.13739395141602</v>
+        <v>7.13739347457886</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.5</v>
       </c>
       <c r="G431" t="n">
-        <v>7.3093786239624</v>
+        <v>7.30937910079956</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>9</v>
       </c>
       <c r="G433" t="n">
-        <v>7.739342212677</v>
+        <v>7.73934316635132</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G435" t="n">
-        <v>7.65334892272949</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G437" t="n">
-        <v>7.61035346984863</v>
+        <v>7.61035394668579</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G446" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G449" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G450" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G451" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.25</v>
       </c>
       <c r="G459" t="n">
-        <v>7.33315134048462</v>
+        <v>7.33315086364746</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.25</v>
       </c>
       <c r="G460" t="n">
-        <v>7.33315134048462</v>
+        <v>7.33315086364746</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>7.37759494781494</v>
+        <v>7.37759447097778</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.25</v>
       </c>
       <c r="G467" t="n">
-        <v>7.33315134048462</v>
+        <v>7.33315086364746</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>8</v>
       </c>
       <c r="G468" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G469" t="n">
-        <v>7.15537786483765</v>
+        <v>7.1553783416748</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G470" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>7.2887077331543</v>
+        <v>7.28870725631714</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.5</v>
       </c>
       <c r="G474" t="n">
-        <v>7.5553674697876</v>
+        <v>7.55536794662476</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.5</v>
       </c>
       <c r="G475" t="n">
-        <v>7.5553674697876</v>
+        <v>7.55536794662476</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>8.5</v>
       </c>
       <c r="G476" t="n">
-        <v>7.5553674697876</v>
+        <v>7.55536794662476</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>7.37759494781494</v>
+        <v>7.37759447097778</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.25</v>
       </c>
       <c r="G478" t="n">
-        <v>7.33315134048462</v>
+        <v>7.33315086364746</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G479" t="n">
-        <v>7.2887077331543</v>
+        <v>7.28870725631714</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G480" t="n">
-        <v>7.46648025512695</v>
+        <v>7.46648120880127</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G481" t="n">
-        <v>7.46648025512695</v>
+        <v>7.46648120880127</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G482" t="n">
-        <v>7.46648025512695</v>
+        <v>7.46648120880127</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G493" t="n">
-        <v>7.46648025512695</v>
+        <v>7.46648120880127</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>7.59981155395508</v>
+        <v>7.59981107711792</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>8</v>
       </c>
       <c r="G498" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G499" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8</v>
       </c>
       <c r="G500" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G502" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8</v>
       </c>
       <c r="G504" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>8</v>
       </c>
       <c r="G505" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>8</v>
       </c>
       <c r="G506" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>8</v>
       </c>
       <c r="G509" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>8</v>
       </c>
       <c r="G511" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>8</v>
       </c>
       <c r="G512" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G513" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>7.75</v>
       </c>
       <c r="G514" t="n">
-        <v>6.88871765136719</v>
+        <v>6.88871812820435</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G515" t="n">
-        <v>7.15537786483765</v>
+        <v>7.1553783416748</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>6.97760438919067</v>
+        <v>6.97760391235352</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G518" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G521" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G530" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.39984083175659</v>
+        <v>6.39984035491943</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.39984083175659</v>
+        <v>6.39984035491943</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>6.39984083175659</v>
+        <v>6.39984035491943</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G548" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G550" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G551" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G552" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G556" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G569" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G571" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G572" t="n">
-        <v>6.17762422561646</v>
+        <v>6.1776237487793</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G586" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G595" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6.75</v>
       </c>
       <c r="G596" t="n">
-        <v>5.99985074996948</v>
+        <v>5.99985122680664</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G599" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G600" t="n">
-        <v>5.59986114501953</v>
+        <v>5.59986066818237</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G601" t="n">
-        <v>5.59986114501953</v>
+        <v>5.59986066818237</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G602" t="n">
-        <v>5.59986114501953</v>
+        <v>5.59986066818237</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G605" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G606" t="n">
-        <v>5.82207775115967</v>
+        <v>5.82207727432251</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G609" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G616" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G618" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G619" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G622" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G624" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G625" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G626" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G627" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G628" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G629" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G631" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>6.75</v>
       </c>
       <c r="G632" t="n">
-        <v>5.99985074996948</v>
+        <v>5.99985122680664</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G634" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G641" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G643" t="n">
-        <v>5.59986114501953</v>
+        <v>5.59986066818237</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G653" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G654" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G656" t="n">
-        <v>5.59986114501953</v>
+        <v>5.59986066818237</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5.75</v>
       </c>
       <c r="G664" t="n">
-        <v>5.11098384857178</v>
+        <v>5.11098432540894</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G670" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G671" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G672" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G673" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G674" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G676" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.5</v>
       </c>
       <c r="G677" t="n">
-        <v>3.99990034103394</v>
+        <v>3.99990105628967</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G678" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.89323663711548</v>
+        <v>3.8932363986969</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G680" t="n">
-        <v>3.8576819896698</v>
+        <v>3.85768222808838</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>3.73324012756348</v>
+        <v>3.73324060440063</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G683" t="n">
-        <v>3.64435386657715</v>
+        <v>3.64435362815857</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G684" t="n">
-        <v>3.68879747390747</v>
+        <v>3.68879723548889</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>3.8576819896698</v>
+        <v>3.85768222808838</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.5</v>
       </c>
       <c r="G689" t="n">
-        <v>3.99990034103394</v>
+        <v>3.99990105628967</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G691" t="n">
-        <v>3.98212337493896</v>
+        <v>3.98212313652039</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>3.96434617042542</v>
+        <v>3.96434593200684</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G694" t="n">
-        <v>3.8576819896698</v>
+        <v>3.85768222808838</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.5</v>
       </c>
       <c r="G698" t="n">
-        <v>3.99990034103394</v>
+        <v>3.99990105628967</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>3.98212337493896</v>
+        <v>3.98212313652039</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G700" t="n">
-        <v>3.98212337493896</v>
+        <v>3.98212313652039</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G702" t="n">
-        <v>3.89323663711548</v>
+        <v>3.8932363986969</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>3.76879501342773</v>
+        <v>3.76879477500916</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G704" t="n">
-        <v>3.90212512016296</v>
+        <v>3.90212488174438</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G705" t="n">
-        <v>3.88434743881226</v>
+        <v>3.88434791564941</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G706" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>3.88434743881226</v>
+        <v>3.88434791564941</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G708" t="n">
-        <v>3.83101582527161</v>
+        <v>3.83101558685303</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>3.83101582527161</v>
+        <v>3.83101558685303</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>3.71546339988708</v>
+        <v>3.71546316146851</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G711" t="n">
-        <v>3.76879501342773</v>
+        <v>3.76879477500916</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G713" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G714" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G715" t="n">
-        <v>3.81323838233948</v>
+        <v>3.81323862075806</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>3.88434743881226</v>
+        <v>3.88434791564941</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G718" t="n">
-        <v>3.89323663711548</v>
+        <v>3.8932363986969</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G722" t="n">
-        <v>4.10656404495239</v>
+        <v>4.10656452178955</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G723" t="n">
-        <v>4.10656404495239</v>
+        <v>4.10656452178955</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>4.38185501098633</v>
+        <v>4.38185453414917</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>4.75</v>
       </c>
       <c r="G731" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G734" t="n">
-        <v>4.38185501098633</v>
+        <v>4.38185453414917</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G735" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G736" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G737" t="n">
-        <v>4.40935611724854</v>
+        <v>4.40935564041138</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G740" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.75</v>
       </c>
       <c r="G743" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G744" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G747" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G752" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G759" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>4.08850908279419</v>
+        <v>4.08850860595703</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G784" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G786" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G787" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>4.07934141159058</v>
+        <v>4.07934188842773</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G789" t="n">
-        <v>4.07934141159058</v>
+        <v>4.07934188842773</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>4.04267358779907</v>
+        <v>4.04267311096191</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G797" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G798" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>3.91433453559875</v>
+        <v>3.91433477401733</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.86849904060364</v>
+        <v>3.86849927902222</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G807" t="n">
-        <v>3.88683319091797</v>
+        <v>3.88683342933655</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G808" t="n">
-        <v>3.88683319091797</v>
+        <v>3.88683342933655</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G813" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G816" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G819" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.75</v>
       </c>
       <c r="G821" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G825" t="n">
-        <v>4.51936054229736</v>
+        <v>4.51936006546021</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>4.51019334793091</v>
+        <v>4.51019382476807</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.75</v>
       </c>
       <c r="G829" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.04267358779907</v>
+        <v>4.04267311096191</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>3.94183588027954</v>
+        <v>3.94183611869812</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G840" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G844" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>4.96854639053345</v>
+        <v>4.96854686737061</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>5.1152195930481</v>
+        <v>5.11521911621094</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G862" t="n">
-        <v>5.13355350494385</v>
+        <v>5.13355398178101</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G863" t="n">
-        <v>5.1518874168396</v>
+        <v>5.15188789367676</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>5.00521516799927</v>
+        <v>5.00521469116211</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G873" t="n">
-        <v>5.39023113250732</v>
+        <v>5.39023160934448</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G874" t="n">
-        <v>5.39023113250732</v>
+        <v>5.39023160934448</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G878" t="n">
-        <v>5.61024045944214</v>
+        <v>5.6102409362793</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G882" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>5.88525247573853</v>
+        <v>5.88525295257568</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>5.94025468826294</v>
+        <v>5.9402551651001</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G893" t="n">
-        <v>5.83025074005127</v>
+        <v>5.83025026321411</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G906" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G910" t="n">
-        <v>6.19693326950073</v>
+        <v>6.19693279266357</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>6.38027429580688</v>
+        <v>6.38027381896973</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G913" t="n">
-        <v>6.28860378265381</v>
+        <v>6.28860330581665</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>6.47194480895996</v>
+        <v>6.4719443321228</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G920" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G922" t="n">
-        <v>6.58194875717163</v>
+        <v>6.58194923400879</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G924" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G927" t="n">
-        <v>6.61861705780029</v>
+        <v>6.61861753463745</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>6.58194875717163</v>
+        <v>6.58194923400879</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G931" t="n">
-        <v>6.61861705780029</v>
+        <v>6.61861753463745</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G937" t="n">
-        <v>6.54528093338013</v>
+        <v>6.54528045654297</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G939" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>6.85696077346802</v>
+        <v>6.85696125030518</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G956" t="n">
-        <v>6.78362464904785</v>
+        <v>6.78362417221069</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -61056,6 +61056,32 @@
         <v>2.38000011444092</v>
       </c>
       <c r="H2334" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2335" t="n">
+        <v>4168</v>
+      </c>
+      <c r="C2335" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="D2335" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="E2335" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="F2335" t="n">
+        <v>2.4300000667572</v>
+      </c>
+      <c r="G2335" t="n">
+        <v>2.4300000667572</v>
+      </c>
+      <c r="H2335" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -54139,8 +54139,31 @@
       <c r="E2338" t="n">
         <v>2.41000008583069</v>
       </c>
-      <c r="F2338"/>
+      <c r="F2338" t="n">
+        <v>2.30999994277954</v>
+      </c>
       <c r="G2338" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2339">
+      <c r="A2339" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2339" t="n">
+        <v>3561</v>
+      </c>
+      <c r="C2339" t="n">
+        <v>2.39000010490417</v>
+      </c>
+      <c r="D2339" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E2339" t="n">
+        <v>2.39000010490417</v>
+      </c>
+      <c r="F2339"/>
+      <c r="G2339" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -54162,8 +54162,31 @@
       <c r="E2339" t="n">
         <v>2.39000010490417</v>
       </c>
-      <c r="F2339"/>
+      <c r="F2339" t="n">
+        <v>2.34999990463257</v>
+      </c>
       <c r="G2339" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2340">
+      <c r="A2340" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2340" t="n">
+        <v>1322</v>
+      </c>
+      <c r="C2340" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="D2340" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E2340" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="F2340"/>
+      <c r="G2340" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -54180,13 +54180,36 @@
         <v>2.34999990463257</v>
       </c>
       <c r="D2340" t="n">
-        <v>2.33999991416931</v>
+        <v>2.29999995231628</v>
       </c>
       <c r="E2340" t="n">
         <v>2.34999990463257</v>
       </c>
-      <c r="F2340"/>
+      <c r="F2340" t="n">
+        <v>2.29999995231628</v>
+      </c>
       <c r="G2340" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2341">
+      <c r="A2341" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2341" t="n">
+        <v>260</v>
+      </c>
+      <c r="C2341" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D2341" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E2341" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F2341"/>
+      <c r="G2341" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -54208,8 +54208,31 @@
       <c r="E2341" t="n">
         <v>2.33999991416931</v>
       </c>
-      <c r="F2341"/>
+      <c r="F2341" t="n">
+        <v>2.33999991416931</v>
+      </c>
       <c r="G2341" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="A2342" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2342" t="n">
+        <v>3493</v>
+      </c>
+      <c r="C2342" t="n">
+        <v>2.36999988555908</v>
+      </c>
+      <c r="D2342" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="E2342" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="F2342"/>
+      <c r="G2342" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -54238,6 +54238,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2343">
+      <c r="A2343" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2343" t="n">
+        <v>4235</v>
+      </c>
+      <c r="C2343" t="n">
+        <v>2.42000007629395</v>
+      </c>
+      <c r="D2343" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="E2343" t="n">
+        <v>2.36999988555908</v>
+      </c>
+      <c r="F2343" t="n">
+        <v>2.42000007629395</v>
+      </c>
+      <c r="G2343" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -447,7 +447,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G3" t="n">
-        <v>9.44388961791992</v>
+        <v>9.44389057159424</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.4186840057373</v>
+        <v>9.41868495941162</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.65394115447998</v>
+        <v>9.6539421081543</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.65394115447998</v>
+        <v>9.6539421081543</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.62033271789551</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G16" t="n">
-        <v>9.63713932037354</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791023254395</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G18" t="n">
-        <v>9.63713932037354</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G22" t="n">
-        <v>9.64553928375244</v>
+        <v>9.64554023742676</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G30" t="n">
-        <v>9.51950931549072</v>
+        <v>9.51950836181641</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G31" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791023254395</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G34" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791023254395</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G39" t="n">
-        <v>9.64553928375244</v>
+        <v>9.64554023742676</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G54" t="n">
-        <v>9.63713932037354</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G73" t="n">
-        <v>10.057240486145</v>
+        <v>10.0572395324707</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G74" t="n">
-        <v>10.0656404495239</v>
+        <v>10.0656414031982</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G85" t="n">
-        <v>9.90600299835205</v>
+        <v>9.90600395202637</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G88" t="n">
-        <v>9.90600299835205</v>
+        <v>9.90600395202637</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G99" t="n">
-        <v>9.97321796417236</v>
+        <v>9.97321891784668</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G105" t="n">
-        <v>9.63713932037354</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G106" t="n">
-        <v>9.62873554229736</v>
+        <v>9.62873649597168</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G107" t="n">
-        <v>9.62873554229736</v>
+        <v>9.62873649597168</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G108" t="n">
-        <v>9.65394115447998</v>
+        <v>9.6539421081543</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>9.62033271789551</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>9.62033271789551</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G113" t="n">
-        <v>9.64553928375244</v>
+        <v>9.64554023742676</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G148" t="n">
-        <v>9.62033271789551</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>11</v>
       </c>
       <c r="G159" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G161" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>11</v>
       </c>
       <c r="G164" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>11</v>
       </c>
       <c r="G165" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>11</v>
       </c>
       <c r="G166" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>11</v>
       </c>
       <c r="G168" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>9.28425216674805</v>
+        <v>9.28425121307373</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G170" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G171" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G176" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>11</v>
       </c>
       <c r="G177" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G179" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>11</v>
       </c>
       <c r="G182" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>9.15822219848633</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>10.75</v>
       </c>
       <c r="G190" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>10.75</v>
       </c>
       <c r="G193" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>10.75</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>10.75</v>
       </c>
       <c r="G196" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>9.15822219848633</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>9.15822219848633</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>9.15822219848633</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G209" t="n">
-        <v>9.41619968414307</v>
+        <v>9.41620063781738</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>9.41619968414307</v>
+        <v>9.41620063781738</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>9.41619968414307</v>
+        <v>9.41620063781738</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>8.98623657226562</v>
+        <v>8.98623752593994</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G217" t="n">
-        <v>8.72825813293457</v>
+        <v>8.72825717926025</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G222" t="n">
-        <v>9.07223033905029</v>
+        <v>9.07222843170166</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>8.98623657226562</v>
+        <v>8.98623752593994</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>10.5</v>
       </c>
       <c r="G228" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923393249512</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G232" t="n">
-        <v>9.41619968414307</v>
+        <v>9.41620063781738</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.5</v>
       </c>
       <c r="G238" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923393249512</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11</v>
       </c>
       <c r="G245" t="n">
-        <v>9.45919609069824</v>
+        <v>9.45919704437256</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11</v>
       </c>
       <c r="G246" t="n">
-        <v>9.45919609069824</v>
+        <v>9.45919704437256</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.5</v>
       </c>
       <c r="G255" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923393249512</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>10.5</v>
       </c>
       <c r="G256" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923393249512</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>10.5</v>
       </c>
       <c r="G257" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923393249512</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>10.5</v>
       </c>
       <c r="G258" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923393249512</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.5</v>
       </c>
       <c r="G262" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923393249512</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>9.07223033905029</v>
+        <v>9.07222843170166</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>8.49607753753662</v>
+        <v>8.49607849121094</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G277" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G278" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G279" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G281" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>8.72825813293457</v>
+        <v>8.72825717926025</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>8.72825813293457</v>
+        <v>8.72825717926025</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G288" t="n">
-        <v>8.22090148925781</v>
+        <v>8.22090244293213</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G290" t="n">
-        <v>8.32409381866455</v>
+        <v>8.32409286499023</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G292" t="n">
-        <v>8.41008567810059</v>
+        <v>8.41008472442627</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G293" t="n">
-        <v>8.41008567810059</v>
+        <v>8.41008472442627</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G294" t="n">
-        <v>8.32409381866455</v>
+        <v>8.32409286499023</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G295" t="n">
-        <v>8.32409381866455</v>
+        <v>8.32409286499023</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.5</v>
       </c>
       <c r="G296" t="n">
-        <v>8.1693058013916</v>
+        <v>8.16930675506592</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G310" t="n">
-        <v>7.87693119049072</v>
+        <v>7.87693166732788</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>7.87693119049072</v>
+        <v>7.87693166732788</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>7.82533502578735</v>
+        <v>7.82533597946167</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>7.70494508743286</v>
+        <v>7.7049446105957</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G324" t="n">
-        <v>6.86221742630005</v>
+        <v>6.86221694946289</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>7.20618772506714</v>
+        <v>7.2061882019043</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G326" t="n">
-        <v>7.20618772506714</v>
+        <v>7.2061882019043</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>9</v>
       </c>
       <c r="G327" t="n">
-        <v>7.73934364318848</v>
+        <v>7.73934316635132</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G328" t="n">
-        <v>7.82533502578735</v>
+        <v>7.82533597946167</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G329" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334892272949</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>7.48136425018311</v>
+        <v>7.48136472702026</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G331" t="n">
-        <v>7.72214317321777</v>
+        <v>7.72214412689209</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G332" t="n">
-        <v>7.72214317321777</v>
+        <v>7.72214412689209</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>7.70494508743286</v>
+        <v>7.7049446105957</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334892272949</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G335" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334892272949</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>7.41256952285767</v>
+        <v>7.41256999969482</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G342" t="n">
-        <v>7.08579778671265</v>
+        <v>7.0857982635498</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G343" t="n">
-        <v>7.06859970092773</v>
+        <v>7.06860017776489</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G349" t="n">
-        <v>7.08579778671265</v>
+        <v>7.0857982635498</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G351" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>8</v>
       </c>
       <c r="G359" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>6.74182748794556</v>
+        <v>6.7418270111084</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>6.74182748794556</v>
+        <v>6.7418270111084</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>6.74182748794556</v>
+        <v>6.7418270111084</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G367" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G369" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G371" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>7.05140066146851</v>
+        <v>7.05140113830566</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>6.84501886367798</v>
+        <v>6.84501838684082</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>6.84501886367798</v>
+        <v>6.84501838684082</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>6.86221742630005</v>
+        <v>6.86221694946289</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>6.86221742630005</v>
+        <v>6.86221694946289</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8</v>
       </c>
       <c r="G381" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8</v>
       </c>
       <c r="G382" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G383" t="n">
-        <v>6.93101119995117</v>
+        <v>6.93101167678833</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>8</v>
       </c>
       <c r="G390" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>6.86221742630005</v>
+        <v>6.86221694946289</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>6.84501886367798</v>
+        <v>6.84501838684082</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>6.93101119995117</v>
+        <v>6.93101167678833</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G399" t="n">
-        <v>6.89661455154419</v>
+        <v>6.89661407470703</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G400" t="n">
-        <v>7.01700353622437</v>
+        <v>7.01700401306152</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G401" t="n">
-        <v>7.01700353622437</v>
+        <v>7.01700401306152</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G410" t="n">
-        <v>7.46416664123535</v>
+        <v>7.46416616439819</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G412" t="n">
-        <v>7.48136425018311</v>
+        <v>7.48136472702026</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334892272949</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G415" t="n">
-        <v>7.61895275115967</v>
+        <v>7.61895227432251</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G416" t="n">
-        <v>7.72214317321777</v>
+        <v>7.72214412689209</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G417" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G419" t="n">
-        <v>7.41256952285767</v>
+        <v>7.41256999969482</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>7.34377670288086</v>
+        <v>7.3437762260437</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>7.34377670288086</v>
+        <v>7.3437762260437</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334892272949</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>9</v>
       </c>
       <c r="G433" t="n">
-        <v>7.73934364318848</v>
+        <v>7.73934316635132</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G435" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334892272949</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>7.48136425018311</v>
+        <v>7.48136472702026</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G437" t="n">
-        <v>7.61035346984863</v>
+        <v>7.61035394668579</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>7.78233909606934</v>
+        <v>7.78233861923218</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G446" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G449" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G450" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G451" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G469" t="n">
-        <v>7.1553783416748</v>
+        <v>7.15537786483765</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>7.28870725631714</v>
+        <v>7.2887077331543</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G479" t="n">
-        <v>7.28870725631714</v>
+        <v>7.2887077331543</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G480" t="n">
-        <v>7.46648120880127</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G481" t="n">
-        <v>7.46648120880127</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G482" t="n">
-        <v>7.46648120880127</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G493" t="n">
-        <v>7.46648120880127</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>7.75</v>
       </c>
       <c r="G514" t="n">
-        <v>6.88871812820435</v>
+        <v>6.88871765136719</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G515" t="n">
-        <v>7.1553783416748</v>
+        <v>7.15537786483765</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>6.97760391235352</v>
+        <v>6.97760438919067</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>7.5</v>
       </c>
       <c r="G517" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>7.5</v>
       </c>
       <c r="G519" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>7.5</v>
       </c>
       <c r="G520" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>7.5</v>
       </c>
       <c r="G525" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>7.5</v>
       </c>
       <c r="G526" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>7.5</v>
       </c>
       <c r="G527" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>7.5</v>
       </c>
       <c r="G528" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.39984035491943</v>
+        <v>6.39984083175659</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.39984035491943</v>
+        <v>6.39984083175659</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>6.39984035491943</v>
+        <v>6.39984083175659</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G552" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G556" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G572" t="n">
-        <v>6.1776237487793</v>
+        <v>6.17762422561646</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G573" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G574" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G576" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G582" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G583" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G586" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6.5</v>
       </c>
       <c r="G597" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G599" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G600" t="n">
-        <v>5.59986066818237</v>
+        <v>5.59986114501953</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G601" t="n">
-        <v>5.59986066818237</v>
+        <v>5.59986114501953</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G602" t="n">
-        <v>5.59986066818237</v>
+        <v>5.59986114501953</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G605" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G607" t="n">
-        <v>5.86652088165283</v>
+        <v>5.86652040481567</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G616" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G618" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G619" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.86652088165283</v>
+        <v>5.86652040481567</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G634" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.5</v>
       </c>
       <c r="G635" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>6.5</v>
       </c>
       <c r="G636" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.5</v>
       </c>
       <c r="G637" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>6.5</v>
       </c>
       <c r="G638" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.5</v>
       </c>
       <c r="G639" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>6.5</v>
       </c>
       <c r="G640" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G643" t="n">
-        <v>5.59986066818237</v>
+        <v>5.59986114501953</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>5.6443042755127</v>
+        <v>5.64430379867554</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.6443042755127</v>
+        <v>5.64430379867554</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>6.5</v>
       </c>
       <c r="G649" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>6.5</v>
       </c>
       <c r="G651" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>6.5</v>
       </c>
       <c r="G652" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G653" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G656" t="n">
-        <v>5.59986066818237</v>
+        <v>5.59986114501953</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G662" t="n">
-        <v>5.37764406204224</v>
+        <v>5.37764453887939</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G666" t="n">
-        <v>4.35544729232788</v>
+        <v>4.35544681549072</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>4.26656055450439</v>
+        <v>4.26656103134155</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G670" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G671" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G672" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G673" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G674" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.5</v>
       </c>
       <c r="G677" t="n">
-        <v>3.99990105628967</v>
+        <v>3.99990081787109</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>3.73324060440063</v>
+        <v>3.73324036598206</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G683" t="n">
-        <v>3.64435362815857</v>
+        <v>3.64435386657715</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G686" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.5</v>
       </c>
       <c r="G689" t="n">
-        <v>3.99990105628967</v>
+        <v>3.99990081787109</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G690" t="n">
-        <v>4.08878707885742</v>
+        <v>4.08878755569458</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.5</v>
       </c>
       <c r="G698" t="n">
-        <v>3.99990105628967</v>
+        <v>3.99990081787109</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G701" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G704" t="n">
-        <v>3.90212488174438</v>
+        <v>3.90212512016296</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G708" t="n">
-        <v>3.83101558685303</v>
+        <v>3.83101606369019</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>3.83101558685303</v>
+        <v>3.83101606369019</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G715" t="n">
-        <v>3.81323862075806</v>
+        <v>3.81323838233948</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G719" t="n">
-        <v>4.08878707885742</v>
+        <v>4.08878755569458</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G720" t="n">
-        <v>4.06212091445923</v>
+        <v>4.06212139129639</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>4.13323068618774</v>
+        <v>4.13323020935059</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G727" t="n">
-        <v>4.09767627716064</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>4.38185453414917</v>
+        <v>4.38185501098633</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>4.75</v>
       </c>
       <c r="G731" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G734" t="n">
-        <v>4.38185453414917</v>
+        <v>4.38185501098633</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G735" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G736" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G737" t="n">
-        <v>4.40935564041138</v>
+        <v>4.40935611724854</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>4.37268781661987</v>
+        <v>4.37268733978271</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>4.37268781661987</v>
+        <v>4.37268733978271</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G740" t="n">
-        <v>4.32685232162476</v>
+        <v>4.3268518447876</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.75</v>
       </c>
       <c r="G743" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G744" t="n">
-        <v>4.32685232162476</v>
+        <v>4.3268518447876</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G747" t="n">
-        <v>4.23518180847168</v>
+        <v>4.23518133163452</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>4.23518180847168</v>
+        <v>4.23518133163452</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G752" t="n">
-        <v>4.18934679031372</v>
+        <v>4.18934631347656</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G759" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.18934679031372</v>
+        <v>4.18934631347656</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>4.21684789657593</v>
+        <v>4.21684741973877</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>4.08850860595703</v>
+        <v>4.08850908279419</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G784" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G786" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G787" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>4.07934188842773</v>
+        <v>4.07934141159058</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G789" t="n">
-        <v>4.07934188842773</v>
+        <v>4.07934141159058</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>4.04267311096191</v>
+        <v>4.04267358779907</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G797" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G798" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>3.91433477401733</v>
+        <v>3.91433453559875</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.86849927902222</v>
+        <v>3.86849904060364</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G807" t="n">
-        <v>3.88683342933655</v>
+        <v>3.88683319091797</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G808" t="n">
-        <v>3.88683342933655</v>
+        <v>3.88683319091797</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G813" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>4.37268781661987</v>
+        <v>4.37268733978271</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G816" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G819" t="n">
-        <v>4.32685232162476</v>
+        <v>4.3268518447876</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.75</v>
       </c>
       <c r="G821" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G825" t="n">
-        <v>4.51936006546021</v>
+        <v>4.51936054229736</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>4.51019382476807</v>
+        <v>4.51019334793091</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.75</v>
       </c>
       <c r="G829" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.04267311096191</v>
+        <v>4.04267358779907</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>3.94183611869812</v>
+        <v>3.94183588027954</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>4.21684789657593</v>
+        <v>4.21684741973877</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G840" t="n">
-        <v>4.18934679031372</v>
+        <v>4.18934631347656</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>4.23518180847168</v>
+        <v>4.23518133163452</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G844" t="n">
-        <v>4.21684789657593</v>
+        <v>4.21684741973877</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>4.96854686737061</v>
+        <v>4.96854639053345</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>5.11521911621094</v>
+        <v>5.1152195930481</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G862" t="n">
-        <v>5.13355398178101</v>
+        <v>5.13355350494385</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G863" t="n">
-        <v>5.15188789367676</v>
+        <v>5.1518874168396</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>5.00521469116211</v>
+        <v>5.00521516799927</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G873" t="n">
-        <v>5.39023160934448</v>
+        <v>5.39023113250732</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G874" t="n">
-        <v>5.39023160934448</v>
+        <v>5.39023113250732</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G878" t="n">
-        <v>5.6102409362793</v>
+        <v>5.61024045944214</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G882" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>5.88525295257568</v>
+        <v>5.88525247573853</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>5.9402551651001</v>
+        <v>5.94025468826294</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G893" t="n">
-        <v>5.83025026321411</v>
+        <v>5.83025074005127</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>5.92192077636719</v>
+        <v>5.92192125320435</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>5.92192077636719</v>
+        <v>5.92192125320435</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>5.92192077636719</v>
+        <v>5.92192125320435</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G906" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G910" t="n">
-        <v>6.19693279266357</v>
+        <v>6.19693326950073</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>6.38027381896973</v>
+        <v>6.38027429580688</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G913" t="n">
-        <v>6.28860330581665</v>
+        <v>6.28860378265381</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>6.4719443321228</v>
+        <v>6.47194480895996</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G920" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G922" t="n">
-        <v>6.58194923400879</v>
+        <v>6.58194875717163</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G924" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G927" t="n">
-        <v>6.61861753463745</v>
+        <v>6.61861705780029</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>6.58194923400879</v>
+        <v>6.58194875717163</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G931" t="n">
-        <v>6.61861753463745</v>
+        <v>6.61861705780029</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G937" t="n">
-        <v>6.54528045654297</v>
+        <v>6.54528093338013</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G939" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>6.85696125030518</v>
+        <v>6.85696077346802</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G956" t="n">
-        <v>6.78362417221069</v>
+        <v>6.78362464904785</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -61342,6 +61342,32 @@
         <v>2.30999994277954</v>
       </c>
       <c r="H2345" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2346">
+      <c r="A2346" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2346" t="n">
+        <v>2426</v>
+      </c>
+      <c r="C2346" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="D2346" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E2346" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F2346" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="G2346" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="H2346" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2" t="n">
-        <v>9.40187931060791</v>
+        <v>9.40188121795654</v>
       </c>
       <c r="H2" t="n">
         <v>56600</v>
@@ -456,7 +456,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G3" t="n">
-        <v>9.44389057159424</v>
+        <v>9.44388961791992</v>
       </c>
       <c r="H3" t="n">
         <v>18800</v>
@@ -485,7 +485,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.4186840057373</v>
+        <v>9.41868495941162</v>
       </c>
       <c r="H4" t="n">
         <v>41600</v>
@@ -514,7 +514,7 @@
         <v>11.25</v>
       </c>
       <c r="G5" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229244232178</v>
       </c>
       <c r="H5" t="n">
         <v>13000</v>
@@ -572,7 +572,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H7" t="n">
         <v>14800</v>
@@ -630,7 +630,7 @@
         <v>11.5</v>
       </c>
       <c r="G9" t="n">
-        <v>9.66234493255615</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H9" t="n">
         <v>2200</v>
@@ -659,7 +659,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H10" t="n">
         <v>4000</v>
@@ -688,7 +688,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G11" t="n">
-        <v>9.73796272277832</v>
+        <v>9.737961769104</v>
       </c>
       <c r="H11" t="n">
         <v>7000</v>
@@ -717,7 +717,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G12" t="n">
-        <v>9.67074584960938</v>
+        <v>9.67074680328369</v>
       </c>
       <c r="H12" t="n">
         <v>1600</v>
@@ -746,7 +746,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033462524414</v>
       </c>
       <c r="H13" t="n">
         <v>1200</v>
@@ -775,7 +775,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>9.70435523986816</v>
+        <v>9.70435333251953</v>
       </c>
       <c r="H14" t="n">
         <v>21400</v>
@@ -804,7 +804,7 @@
         <v>11.5</v>
       </c>
       <c r="G15" t="n">
-        <v>9.66234493255615</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H15" t="n">
         <v>13400</v>
@@ -833,7 +833,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G16" t="n">
-        <v>9.63713836669922</v>
+        <v>9.6371374130249</v>
       </c>
       <c r="H16" t="n">
         <v>11400</v>
@@ -891,7 +891,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G18" t="n">
-        <v>9.63713836669922</v>
+        <v>9.6371374130249</v>
       </c>
       <c r="H18" t="n">
         <v>2600</v>
@@ -920,7 +920,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H19" t="n">
         <v>2400</v>
@@ -1007,7 +1007,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G22" t="n">
-        <v>9.64553928375244</v>
+        <v>9.64554023742676</v>
       </c>
       <c r="H22" t="n">
         <v>3400</v>
@@ -1036,7 +1036,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>9.53631401062012</v>
+        <v>9.53631496429443</v>
       </c>
       <c r="H23" t="n">
         <v>800</v>
@@ -1065,7 +1065,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G24" t="n">
-        <v>9.40187931060791</v>
+        <v>9.40188121795654</v>
       </c>
       <c r="H24" t="n">
         <v>600</v>
@@ -1094,7 +1094,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H25" t="n">
         <v>1600</v>
@@ -1123,7 +1123,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>11.25</v>
       </c>
       <c r="G28" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229244232178</v>
       </c>
       <c r="H28" t="n">
         <v>3600</v>
@@ -1239,7 +1239,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G30" t="n">
-        <v>9.51950836181641</v>
+        <v>9.51950931549072</v>
       </c>
       <c r="H30" t="n">
         <v>2600</v>
@@ -1326,7 +1326,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G33" t="n">
-        <v>9.56992244720459</v>
+        <v>9.56992053985596</v>
       </c>
       <c r="H33" t="n">
         <v>1800</v>
@@ -1442,7 +1442,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G37" t="n">
-        <v>9.56992244720459</v>
+        <v>9.56992053985596</v>
       </c>
       <c r="H37" t="n">
         <v>3000</v>
@@ -1471,7 +1471,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>9.53631401062012</v>
+        <v>9.53631496429443</v>
       </c>
       <c r="H38" t="n">
         <v>2400</v>
@@ -1500,7 +1500,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G39" t="n">
-        <v>9.64553928375244</v>
+        <v>9.64554023742676</v>
       </c>
       <c r="H39" t="n">
         <v>800</v>
@@ -1529,7 +1529,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G40" t="n">
-        <v>9.73796272277832</v>
+        <v>9.737961769104</v>
       </c>
       <c r="H40" t="n">
         <v>21400</v>
@@ -1558,7 +1558,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G41" t="n">
-        <v>9.73796272277832</v>
+        <v>9.737961769104</v>
       </c>
       <c r="H41" t="n">
         <v>1400</v>
@@ -1587,7 +1587,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G42" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H42" t="n">
         <v>7000</v>
@@ -1616,7 +1616,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H43" t="n">
         <v>2000</v>
@@ -1645,7 +1645,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H44" t="n">
         <v>4400</v>
@@ -1732,7 +1732,7 @@
         <v>11.5</v>
       </c>
       <c r="G47" t="n">
-        <v>9.66234493255615</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H47" t="n">
         <v>11200</v>
@@ -1761,7 +1761,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H48" t="n">
         <v>8800</v>
@@ -1906,7 +1906,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G53" t="n">
-        <v>9.77997398376465</v>
+        <v>9.77997303009033</v>
       </c>
       <c r="H53" t="n">
         <v>4200</v>
@@ -1935,7 +1935,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G54" t="n">
-        <v>9.63713836669922</v>
+        <v>9.6371374130249</v>
       </c>
       <c r="H54" t="n">
         <v>30200</v>
@@ -1964,7 +1964,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G55" t="n">
-        <v>9.8555908203125</v>
+        <v>9.85558986663818</v>
       </c>
       <c r="H55" t="n">
         <v>11800</v>
@@ -2022,7 +2022,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G57" t="n">
-        <v>9.95641613006592</v>
+        <v>9.9564151763916</v>
       </c>
       <c r="H57" t="n">
         <v>35400</v>
@@ -2051,7 +2051,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>9.95641613006592</v>
+        <v>9.9564151763916</v>
       </c>
       <c r="H58" t="n">
         <v>25000</v>
@@ -2167,7 +2167,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G62" t="n">
-        <v>9.99002456665039</v>
+        <v>9.99002265930176</v>
       </c>
       <c r="H62" t="n">
         <v>36400</v>
@@ -2341,7 +2341,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G68" t="n">
-        <v>9.99002456665039</v>
+        <v>9.99002265930176</v>
       </c>
       <c r="H68" t="n">
         <v>13600</v>
@@ -2370,7 +2370,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>9.95641613006592</v>
+        <v>9.9564151763916</v>
       </c>
       <c r="H69" t="n">
         <v>3200</v>
@@ -2515,7 +2515,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G74" t="n">
-        <v>10.0656414031982</v>
+        <v>10.0656404495239</v>
       </c>
       <c r="H74" t="n">
         <v>7000</v>
@@ -2747,7 +2747,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G82" t="n">
-        <v>9.99002456665039</v>
+        <v>9.99002265930176</v>
       </c>
       <c r="H82" t="n">
         <v>4200</v>
@@ -2834,7 +2834,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G85" t="n">
-        <v>9.90600299835205</v>
+        <v>9.90600395202637</v>
       </c>
       <c r="H85" t="n">
         <v>4200</v>
@@ -2921,7 +2921,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G88" t="n">
-        <v>9.90600299835205</v>
+        <v>9.90600395202637</v>
       </c>
       <c r="H88" t="n">
         <v>600</v>
@@ -2950,7 +2950,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H89" t="n">
         <v>22400</v>
@@ -2979,7 +2979,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H90" t="n">
         <v>2000</v>
@@ -3153,7 +3153,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H96" t="n">
         <v>2600</v>
@@ -3211,7 +3211,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G98" t="n">
-        <v>9.98162078857422</v>
+        <v>9.98162174224854</v>
       </c>
       <c r="H98" t="n">
         <v>13400</v>
@@ -3240,7 +3240,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G99" t="n">
-        <v>9.97321891784668</v>
+        <v>9.973219871521</v>
       </c>
       <c r="H99" t="n">
         <v>7400</v>
@@ -3298,7 +3298,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G101" t="n">
-        <v>9.8555908203125</v>
+        <v>9.85558986663818</v>
       </c>
       <c r="H101" t="n">
         <v>3600</v>
@@ -3385,7 +3385,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G104" t="n">
-        <v>9.73796272277832</v>
+        <v>9.737961769104</v>
       </c>
       <c r="H104" t="n">
         <v>1800</v>
@@ -3414,7 +3414,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G105" t="n">
-        <v>9.63713836669922</v>
+        <v>9.6371374130249</v>
       </c>
       <c r="H105" t="n">
         <v>6400</v>
@@ -3530,7 +3530,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033462524414</v>
       </c>
       <c r="H109" t="n">
         <v>9400</v>
@@ -3559,7 +3559,7 @@
         <v>11.5</v>
       </c>
       <c r="G110" t="n">
-        <v>9.66234493255615</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H110" t="n">
         <v>6400</v>
@@ -3588,7 +3588,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033462524414</v>
       </c>
       <c r="H111" t="n">
         <v>4600</v>
@@ -3617,7 +3617,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>9.53631401062012</v>
+        <v>9.53631496429443</v>
       </c>
       <c r="H112" t="n">
         <v>800</v>
@@ -3646,7 +3646,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G113" t="n">
-        <v>9.64553928375244</v>
+        <v>9.64554023742676</v>
       </c>
       <c r="H113" t="n">
         <v>2800</v>
@@ -3675,7 +3675,7 @@
         <v>11.5</v>
       </c>
       <c r="G114" t="n">
-        <v>9.66234493255615</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H114" t="n">
         <v>21600</v>
@@ -3704,7 +3704,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G115" t="n">
-        <v>9.72955989837646</v>
+        <v>9.72956085205078</v>
       </c>
       <c r="H115" t="n">
         <v>6000</v>
@@ -3733,7 +3733,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H116" t="n">
         <v>4600</v>
@@ -3762,7 +3762,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H117" t="n">
         <v>16400</v>
@@ -3820,7 +3820,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H119" t="n">
         <v>5400</v>
@@ -3849,7 +3849,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H120" t="n">
         <v>4800</v>
@@ -3878,7 +3878,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H121" t="n">
         <v>6200</v>
@@ -3907,7 +3907,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H122" t="n">
         <v>14000</v>
@@ -3936,7 +3936,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G123" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H123" t="n">
         <v>15800</v>
@@ -3965,7 +3965,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H124" t="n">
         <v>14200</v>
@@ -3994,7 +3994,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H125" t="n">
         <v>8000</v>
@@ -4023,7 +4023,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H126" t="n">
         <v>24600</v>
@@ -4052,7 +4052,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H127" t="n">
         <v>39200</v>
@@ -4081,7 +4081,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H128" t="n">
         <v>20000</v>
@@ -4110,7 +4110,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H129" t="n">
         <v>1600</v>
@@ -4168,7 +4168,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H131" t="n">
         <v>5600</v>
@@ -4197,7 +4197,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G132" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H132" t="n">
         <v>11400</v>
@@ -4226,7 +4226,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G133" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H133" t="n">
         <v>9800</v>
@@ -4255,7 +4255,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H134" t="n">
         <v>3400</v>
@@ -4284,7 +4284,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H135" t="n">
         <v>5600</v>
@@ -4313,7 +4313,7 @@
         <v>11.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.66234493255615</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H136" t="n">
         <v>9600</v>
@@ -4342,7 +4342,7 @@
         <v>11.5</v>
       </c>
       <c r="G137" t="n">
-        <v>9.66234493255615</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H137" t="n">
         <v>5800</v>
@@ -4371,7 +4371,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H138" t="n">
         <v>50800</v>
@@ -4400,7 +4400,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G139" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H139" t="n">
         <v>8000</v>
@@ -4516,7 +4516,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G143" t="n">
-        <v>9.32626342773438</v>
+        <v>9.32626247406006</v>
       </c>
       <c r="H143" t="n">
         <v>8800</v>
@@ -4545,7 +4545,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G144" t="n">
-        <v>9.32626342773438</v>
+        <v>9.32626247406006</v>
       </c>
       <c r="H144" t="n">
         <v>47000</v>
@@ -4574,7 +4574,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G145" t="n">
-        <v>9.32626342773438</v>
+        <v>9.32626247406006</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G148" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033462524414</v>
       </c>
       <c r="H148" t="n">
         <v>3400</v>
@@ -4748,7 +4748,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H151" t="n">
         <v>2000</v>
@@ -4777,7 +4777,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H152" t="n">
         <v>800</v>
@@ -4806,7 +4806,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>9.70435523986816</v>
+        <v>9.70435333251953</v>
       </c>
       <c r="H153" t="n">
         <v>19400</v>
@@ -4835,7 +4835,7 @@
         <v>11.5</v>
       </c>
       <c r="G154" t="n">
-        <v>9.66234493255615</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H154" t="n">
         <v>1000</v>
@@ -4864,7 +4864,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G155" t="n">
-        <v>9.53631401062012</v>
+        <v>9.53631496429443</v>
       </c>
       <c r="H155" t="n">
         <v>27200</v>
@@ -4893,7 +4893,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>9.70435523986816</v>
+        <v>9.70435333251953</v>
       </c>
       <c r="H156" t="n">
         <v>200</v>
@@ -4922,7 +4922,7 @@
         <v>11.25</v>
       </c>
       <c r="G157" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229244232178</v>
       </c>
       <c r="H157" t="n">
         <v>18800</v>
@@ -4951,7 +4951,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>9.32626342773438</v>
+        <v>9.32626247406006</v>
       </c>
       <c r="H158" t="n">
         <v>4800</v>
@@ -4980,7 +4980,7 @@
         <v>11</v>
       </c>
       <c r="G159" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H159" t="n">
         <v>14600</v>
@@ -5009,7 +5009,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G160" t="n">
-        <v>9.32626342773438</v>
+        <v>9.32626247406006</v>
       </c>
       <c r="H160" t="n">
         <v>400</v>
@@ -5125,7 +5125,7 @@
         <v>11</v>
       </c>
       <c r="G164" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H164" t="n">
         <v>18800</v>
@@ -5154,7 +5154,7 @@
         <v>11</v>
       </c>
       <c r="G165" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>11</v>
       </c>
       <c r="G166" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H166" t="n">
         <v>400</v>
@@ -5212,7 +5212,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>9.32626342773438</v>
+        <v>9.32626247406006</v>
       </c>
       <c r="H167" t="n">
         <v>15000</v>
@@ -5241,7 +5241,7 @@
         <v>11</v>
       </c>
       <c r="G168" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H168" t="n">
         <v>1200</v>
@@ -5270,7 +5270,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>9.28425216674805</v>
+        <v>9.28425312042236</v>
       </c>
       <c r="H169" t="n">
         <v>200</v>
@@ -5328,7 +5328,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G171" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H171" t="n">
         <v>2400</v>
@@ -5386,7 +5386,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H173" t="n">
         <v>3000</v>
@@ -5444,7 +5444,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H175" t="n">
         <v>1000</v>
@@ -5473,7 +5473,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G176" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H176" t="n">
         <v>18400</v>
@@ -5502,7 +5502,7 @@
         <v>11</v>
       </c>
       <c r="G177" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H177" t="n">
         <v>5200</v>
@@ -5531,7 +5531,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>9.32626342773438</v>
+        <v>9.32626247406006</v>
       </c>
       <c r="H178" t="n">
         <v>400</v>
@@ -5589,7 +5589,7 @@
         <v>11.25</v>
       </c>
       <c r="G180" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229244232178</v>
       </c>
       <c r="H180" t="n">
         <v>12000</v>
@@ -5618,7 +5618,7 @@
         <v>11.25</v>
       </c>
       <c r="G181" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229244232178</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>11</v>
       </c>
       <c r="G182" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H182" t="n">
         <v>10000</v>
@@ -5763,7 +5763,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G186" t="n">
-        <v>8.94817066192627</v>
+        <v>8.94816970825195</v>
       </c>
       <c r="H186" t="n">
         <v>25800</v>
@@ -5792,7 +5792,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>8.94817066192627</v>
+        <v>8.94816970825195</v>
       </c>
       <c r="H187" t="n">
         <v>600</v>
@@ -5879,7 +5879,7 @@
         <v>10.75</v>
       </c>
       <c r="G190" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219223022461</v>
       </c>
       <c r="H190" t="n">
         <v>400</v>
@@ -5966,7 +5966,7 @@
         <v>10.75</v>
       </c>
       <c r="G193" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219223022461</v>
       </c>
       <c r="H193" t="n">
         <v>400</v>
@@ -5995,7 +5995,7 @@
         <v>10.75</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219223022461</v>
       </c>
       <c r="H194" t="n">
         <v>600</v>
@@ -6053,7 +6053,7 @@
         <v>10.75</v>
       </c>
       <c r="G196" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219223022461</v>
       </c>
       <c r="H196" t="n">
         <v>10200</v>
@@ -6430,7 +6430,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G209" t="n">
-        <v>9.41620063781738</v>
+        <v>9.41619873046875</v>
       </c>
       <c r="H209" t="n">
         <v>200</v>
@@ -6517,7 +6517,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>9.41620063781738</v>
+        <v>9.41619873046875</v>
       </c>
       <c r="H212" t="n">
         <v>200</v>
@@ -6546,7 +6546,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>9.41620063781738</v>
+        <v>9.41619873046875</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>8.98623752593994</v>
+        <v>8.98623657226562</v>
       </c>
       <c r="H216" t="n">
         <v>7000</v>
@@ -6662,7 +6662,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G217" t="n">
-        <v>8.72825717926025</v>
+        <v>8.72825813293457</v>
       </c>
       <c r="H217" t="n">
         <v>31200</v>
@@ -6807,7 +6807,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G222" t="n">
-        <v>9.07222843170166</v>
+        <v>9.07222938537598</v>
       </c>
       <c r="H222" t="n">
         <v>8600</v>
@@ -6952,7 +6952,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>8.98623752593994</v>
+        <v>8.98623657226562</v>
       </c>
       <c r="H227" t="n">
         <v>2800</v>
@@ -6981,7 +6981,7 @@
         <v>10.5</v>
       </c>
       <c r="G228" t="n">
-        <v>9.02923393249512</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H228" t="n">
         <v>12000</v>
@@ -7097,7 +7097,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G232" t="n">
-        <v>9.41620063781738</v>
+        <v>9.41619873046875</v>
       </c>
       <c r="H232" t="n">
         <v>2000</v>
@@ -7271,7 +7271,7 @@
         <v>10.5</v>
       </c>
       <c r="G238" t="n">
-        <v>9.02923393249512</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H238" t="n">
         <v>3400</v>
@@ -7764,7 +7764,7 @@
         <v>10.5</v>
       </c>
       <c r="G255" t="n">
-        <v>9.02923393249512</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H255" t="n">
         <v>1000</v>
@@ -7793,7 +7793,7 @@
         <v>10.5</v>
       </c>
       <c r="G256" t="n">
-        <v>9.02923393249512</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>10.5</v>
       </c>
       <c r="G257" t="n">
-        <v>9.02923393249512</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H257" t="n">
         <v>400</v>
@@ -7851,7 +7851,7 @@
         <v>10.5</v>
       </c>
       <c r="G258" t="n">
-        <v>9.02923393249512</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>10.5</v>
       </c>
       <c r="G262" t="n">
-        <v>9.02923393249512</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H262" t="n">
         <v>800</v>
@@ -8025,7 +8025,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>9.07222843170166</v>
+        <v>9.07222938537598</v>
       </c>
       <c r="H264" t="n">
         <v>8000</v>
@@ -8547,7 +8547,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G282" t="n">
-        <v>8.51327610015869</v>
+        <v>8.51327705383301</v>
       </c>
       <c r="H282" t="n">
         <v>2000</v>
@@ -8576,7 +8576,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>8.72825717926025</v>
+        <v>8.72825813293457</v>
       </c>
       <c r="H283" t="n">
         <v>5000</v>
@@ -8605,7 +8605,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>8.72825717926025</v>
+        <v>8.72825813293457</v>
       </c>
       <c r="H284" t="n">
         <v>1000</v>
@@ -8721,7 +8721,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G288" t="n">
-        <v>8.22090244293213</v>
+        <v>8.22090148925781</v>
       </c>
       <c r="H288" t="n">
         <v>2600</v>
@@ -8750,7 +8750,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.25529861450195</v>
+        <v>8.25529956817627</v>
       </c>
       <c r="H289" t="n">
         <v>800</v>
@@ -8837,7 +8837,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G292" t="n">
-        <v>8.41008472442627</v>
+        <v>8.41008567810059</v>
       </c>
       <c r="H292" t="n">
         <v>3000</v>
@@ -8866,7 +8866,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G293" t="n">
-        <v>8.41008472442627</v>
+        <v>8.41008567810059</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         <v>9.5</v>
       </c>
       <c r="G296" t="n">
-        <v>8.16930675506592</v>
+        <v>8.1693058013916</v>
       </c>
       <c r="H296" t="n">
         <v>17200</v>
@@ -9156,7 +9156,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G303" t="n">
-        <v>8.53047561645508</v>
+        <v>8.53047466278076</v>
       </c>
       <c r="H303" t="n">
         <v>2000</v>
@@ -9272,7 +9272,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G307" t="n">
-        <v>8.03171825408936</v>
+        <v>8.03171730041504</v>
       </c>
       <c r="H307" t="n">
         <v>2000</v>
@@ -9330,7 +9330,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G309" t="n">
-        <v>8.03171825408936</v>
+        <v>8.03171730041504</v>
       </c>
       <c r="H309" t="n">
         <v>600</v>
@@ -9359,7 +9359,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G310" t="n">
-        <v>7.87693166732788</v>
+        <v>7.87693071365356</v>
       </c>
       <c r="H310" t="n">
         <v>200</v>
@@ -9388,7 +9388,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>7.87693166732788</v>
+        <v>7.87693071365356</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>7.82533597946167</v>
+        <v>7.82533550262451</v>
       </c>
       <c r="H312" t="n">
         <v>1200</v>
@@ -9446,7 +9446,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>7.7049446105957</v>
+        <v>7.70494604110718</v>
       </c>
       <c r="H313" t="n">
         <v>4200</v>
@@ -9475,7 +9475,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H314" t="n">
         <v>23200</v>
@@ -9504,7 +9504,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H315" t="n">
         <v>14000</v>
@@ -9533,7 +9533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H317" t="n">
         <v>4200</v>
@@ -9591,7 +9591,7 @@
         <v>8.5</v>
       </c>
       <c r="G318" t="n">
-        <v>7.30937910079956</v>
+        <v>7.30937814712524</v>
       </c>
       <c r="H318" t="n">
         <v>1600</v>
@@ -9620,7 +9620,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G319" t="n">
-        <v>7.36097526550293</v>
+        <v>7.36097431182861</v>
       </c>
       <c r="H319" t="n">
         <v>2400</v>
@@ -9649,7 +9649,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G320" t="n">
-        <v>7.32657814025879</v>
+        <v>7.32657766342163</v>
       </c>
       <c r="H320" t="n">
         <v>400</v>
@@ -9678,7 +9678,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G321" t="n">
-        <v>7.32657814025879</v>
+        <v>7.32657766342163</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G323" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H323" t="n">
         <v>800</v>
@@ -9881,7 +9881,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G328" t="n">
-        <v>7.82533597946167</v>
+        <v>7.82533550262451</v>
       </c>
       <c r="H328" t="n">
         <v>600</v>
@@ -9910,7 +9910,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G329" t="n">
-        <v>7.65334892272949</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H329" t="n">
         <v>600</v>
@@ -9968,7 +9968,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G331" t="n">
-        <v>7.72214412689209</v>
+        <v>7.72214317321777</v>
       </c>
       <c r="H331" t="n">
         <v>1800</v>
@@ -9997,7 +9997,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G332" t="n">
-        <v>7.72214412689209</v>
+        <v>7.72214317321777</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>7.7049446105957</v>
+        <v>7.70494604110718</v>
       </c>
       <c r="H333" t="n">
         <v>600</v>
@@ -10055,7 +10055,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>7.65334892272949</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H334" t="n">
         <v>800</v>
@@ -10084,7 +10084,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G335" t="n">
-        <v>7.65334892272949</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G336" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H336" t="n">
         <v>1000</v>
@@ -10171,7 +10171,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G338" t="n">
-        <v>7.53295993804932</v>
+        <v>7.53296041488647</v>
       </c>
       <c r="H338" t="n">
         <v>200</v>
@@ -10200,7 +10200,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H339" t="n">
         <v>400</v>
@@ -10229,7 +10229,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G340" t="n">
-        <v>7.29217958450317</v>
+        <v>7.29218006134033</v>
       </c>
       <c r="H340" t="n">
         <v>2800</v>
@@ -10258,7 +10258,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G341" t="n">
-        <v>7.13739347457886</v>
+        <v>7.13739395141602</v>
       </c>
       <c r="H341" t="n">
         <v>7000</v>
@@ -10287,7 +10287,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G342" t="n">
-        <v>7.0857982635498</v>
+        <v>7.08579778671265</v>
       </c>
       <c r="H342" t="n">
         <v>6600</v>
@@ -10316,7 +10316,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G343" t="n">
-        <v>7.06860017776489</v>
+        <v>7.06859922409058</v>
       </c>
       <c r="H343" t="n">
         <v>5200</v>
@@ -10374,7 +10374,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G345" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H345" t="n">
         <v>5400</v>
@@ -10490,7 +10490,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G349" t="n">
-        <v>7.0857982635498</v>
+        <v>7.08579778671265</v>
       </c>
       <c r="H349" t="n">
         <v>3522</v>
@@ -10519,7 +10519,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G350" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H350" t="n">
         <v>18548</v>
@@ -10548,7 +10548,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G351" t="n">
-        <v>6.94820928573608</v>
+        <v>6.94820976257324</v>
       </c>
       <c r="H351" t="n">
         <v>3182</v>
@@ -10577,7 +10577,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>6.91381216049194</v>
+        <v>6.9138126373291</v>
       </c>
       <c r="H352" t="n">
         <v>4342</v>
@@ -10664,7 +10664,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>6.94820928573608</v>
+        <v>6.94820976257324</v>
       </c>
       <c r="H355" t="n">
         <v>8049</v>
@@ -10780,7 +10780,7 @@
         <v>8</v>
       </c>
       <c r="G359" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H359" t="n">
         <v>140</v>
@@ -10867,7 +10867,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H362" t="n">
         <v>3100</v>
@@ -10954,7 +10954,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G365" t="n">
-        <v>6.79342317581177</v>
+        <v>6.79342269897461</v>
       </c>
       <c r="H365" t="n">
         <v>830</v>
@@ -11041,7 +11041,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H368" t="n">
         <v>200</v>
@@ -11157,7 +11157,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>7.13739347457886</v>
+        <v>7.13739395141602</v>
       </c>
       <c r="H372" t="n">
         <v>2867</v>
@@ -11186,7 +11186,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>7.05140113830566</v>
+        <v>7.05140066146851</v>
       </c>
       <c r="H373" t="n">
         <v>354</v>
@@ -11244,7 +11244,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G375" t="n">
-        <v>6.79342317581177</v>
+        <v>6.79342269897461</v>
       </c>
       <c r="H375" t="n">
         <v>950</v>
@@ -11302,7 +11302,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>6.84501838684082</v>
+        <v>6.84501886367798</v>
       </c>
       <c r="H377" t="n">
         <v>2353</v>
@@ -11331,7 +11331,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>6.84501838684082</v>
+        <v>6.84501886367798</v>
       </c>
       <c r="H378" t="n">
         <v>4149</v>
@@ -11418,7 +11418,7 @@
         <v>8</v>
       </c>
       <c r="G381" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H381" t="n">
         <v>1532</v>
@@ -11447,7 +11447,7 @@
         <v>8</v>
       </c>
       <c r="G382" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H382" t="n">
         <v>291</v>
@@ -11505,7 +11505,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>6.94820928573608</v>
+        <v>6.94820976257324</v>
       </c>
       <c r="H384" t="n">
         <v>124</v>
@@ -11650,7 +11650,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>6.91381216049194</v>
+        <v>6.9138126373291</v>
       </c>
       <c r="H389" t="n">
         <v>7543</v>
@@ -11679,7 +11679,7 @@
         <v>8</v>
       </c>
       <c r="G390" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H390" t="n">
         <v>7347</v>
@@ -11737,7 +11737,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>6.84501838684082</v>
+        <v>6.84501886367798</v>
       </c>
       <c r="H392" t="n">
         <v>2665</v>
@@ -11766,7 +11766,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G393" t="n">
-        <v>6.69023180007935</v>
+        <v>6.69023132324219</v>
       </c>
       <c r="H393" t="n">
         <v>24134</v>
@@ -11795,7 +11795,7 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H394" t="n">
         <v>1786</v>
@@ -11853,7 +11853,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>6.94820928573608</v>
+        <v>6.94820976257324</v>
       </c>
       <c r="H396" t="n">
         <v>1510</v>
@@ -11882,7 +11882,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>6.94820928573608</v>
+        <v>6.94820976257324</v>
       </c>
       <c r="H397" t="n">
         <v>4250</v>
@@ -11940,7 +11940,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G399" t="n">
-        <v>6.89661407470703</v>
+        <v>6.89661455154419</v>
       </c>
       <c r="H399" t="n">
         <v>3410</v>
@@ -12027,7 +12027,7 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H402" t="n">
         <v>6710</v>
@@ -12056,7 +12056,7 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H403" t="n">
         <v>2710</v>
@@ -12085,7 +12085,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>6.79342317581177</v>
+        <v>6.79342269897461</v>
       </c>
       <c r="H404" t="n">
         <v>57</v>
@@ -12172,7 +12172,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>6.79342317581177</v>
+        <v>6.79342269897461</v>
       </c>
       <c r="H407" t="n">
         <v>20699</v>
@@ -12230,7 +12230,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>7.24058485031128</v>
+        <v>7.24058532714844</v>
       </c>
       <c r="H409" t="n">
         <v>12395</v>
@@ -12288,7 +12288,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G411" t="n">
-        <v>7.53295993804932</v>
+        <v>7.53296041488647</v>
       </c>
       <c r="H411" t="n">
         <v>7212</v>
@@ -12346,7 +12346,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.65334892272949</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H413" t="n">
         <v>3920</v>
@@ -12404,7 +12404,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G415" t="n">
-        <v>7.61895227432251</v>
+        <v>7.61895132064819</v>
       </c>
       <c r="H415" t="n">
         <v>5660</v>
@@ -12433,7 +12433,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G416" t="n">
-        <v>7.72214412689209</v>
+        <v>7.72214317321777</v>
       </c>
       <c r="H416" t="n">
         <v>11289</v>
@@ -12462,7 +12462,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G417" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H417" t="n">
         <v>1940</v>
@@ -12491,7 +12491,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G418" t="n">
-        <v>7.53295993804932</v>
+        <v>7.53296041488647</v>
       </c>
       <c r="H418" t="n">
         <v>2536</v>
@@ -12607,7 +12607,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G422" t="n">
-        <v>7.36097526550293</v>
+        <v>7.36097431182861</v>
       </c>
       <c r="H422" t="n">
         <v>1868</v>
@@ -12636,7 +12636,7 @@
         <v>8.5</v>
       </c>
       <c r="G423" t="n">
-        <v>7.30937910079956</v>
+        <v>7.30937814712524</v>
       </c>
       <c r="H423" t="n">
         <v>1963</v>
@@ -12665,7 +12665,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>7.65334892272949</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H424" t="n">
         <v>13987</v>
@@ -12694,7 +12694,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H425" t="n">
         <v>1500</v>
@@ -12723,7 +12723,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H426" t="n">
         <v>822</v>
@@ -12752,7 +12752,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G427" t="n">
-        <v>7.42976856231689</v>
+        <v>7.42976903915405</v>
       </c>
       <c r="H427" t="n">
         <v>1502</v>
@@ -12781,7 +12781,7 @@
         <v>8.5</v>
       </c>
       <c r="G428" t="n">
-        <v>7.30937910079956</v>
+        <v>7.30937814712524</v>
       </c>
       <c r="H428" t="n">
         <v>1002</v>
@@ -12810,7 +12810,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G429" t="n">
-        <v>7.29217958450317</v>
+        <v>7.29218006134033</v>
       </c>
       <c r="H429" t="n">
         <v>314</v>
@@ -12839,7 +12839,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>7.13739347457886</v>
+        <v>7.13739395141602</v>
       </c>
       <c r="H430" t="n">
         <v>908</v>
@@ -12868,7 +12868,7 @@
         <v>8.5</v>
       </c>
       <c r="G431" t="n">
-        <v>7.30937910079956</v>
+        <v>7.30937814712524</v>
       </c>
       <c r="H431" t="n">
         <v>400</v>
@@ -12897,7 +12897,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H432" t="n">
         <v>7444</v>
@@ -12955,7 +12955,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H434" t="n">
         <v>1098</v>
@@ -12984,7 +12984,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G435" t="n">
-        <v>7.65334892272949</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H435" t="n">
         <v>1451</v>
@@ -13042,7 +13042,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G437" t="n">
-        <v>7.61035394668579</v>
+        <v>7.61035346984863</v>
       </c>
       <c r="H437" t="n">
         <v>5810</v>
@@ -13071,7 +13071,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H438" t="n">
         <v>5485</v>
@@ -13100,7 +13100,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H439" t="n">
         <v>572</v>
@@ -13129,7 +13129,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H440" t="n">
         <v>1662</v>
@@ -13158,7 +13158,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>7.78233861923218</v>
+        <v>7.78233909606934</v>
       </c>
       <c r="H442" t="n">
         <v>10</v>
@@ -13216,7 +13216,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H443" t="n">
         <v>4760</v>
@@ -13245,7 +13245,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H444" t="n">
         <v>800</v>
@@ -13274,7 +13274,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H445" t="n">
         <v>8557</v>
@@ -13303,7 +13303,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G446" t="n">
-        <v>7.43836736679077</v>
+        <v>7.43836688995361</v>
       </c>
       <c r="H446" t="n">
         <v>5102</v>
@@ -13332,7 +13332,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>7.43836736679077</v>
+        <v>7.43836688995361</v>
       </c>
       <c r="H447" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G449" t="n">
-        <v>7.43836736679077</v>
+        <v>7.43836688995361</v>
       </c>
       <c r="H449" t="n">
         <v>1237</v>
@@ -13419,7 +13419,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G450" t="n">
-        <v>7.43836736679077</v>
+        <v>7.43836688995361</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G451" t="n">
-        <v>7.43836736679077</v>
+        <v>7.43836688995361</v>
       </c>
       <c r="H451" t="n">
         <v>3000</v>
@@ -13477,7 +13477,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G452" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H452" t="n">
         <v>510</v>
@@ -13506,7 +13506,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G453" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H453" t="n">
         <v>2385</v>
@@ -13535,7 +13535,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G454" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H454" t="n">
         <v>200</v>
@@ -13564,7 +13564,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G455" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H455" t="n">
         <v>18119</v>
@@ -13593,7 +13593,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H456" t="n">
         <v>695</v>
@@ -13622,7 +13622,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G457" t="n">
-        <v>7.64425468444824</v>
+        <v>7.6442551612854</v>
       </c>
       <c r="H457" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G458" t="n">
-        <v>7.64425468444824</v>
+        <v>7.6442551612854</v>
       </c>
       <c r="H458" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>7.37759447097778</v>
+        <v>7.37759494781494</v>
       </c>
       <c r="H461" t="n">
         <v>6100</v>
@@ -13999,7 +13999,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G470" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H470" t="n">
         <v>3543</v>
@@ -14028,7 +14028,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>7.2887077331543</v>
+        <v>7.28870725631714</v>
       </c>
       <c r="H471" t="n">
         <v>30</v>
@@ -14115,7 +14115,7 @@
         <v>8.5</v>
       </c>
       <c r="G474" t="n">
-        <v>7.55536794662476</v>
+        <v>7.55536699295044</v>
       </c>
       <c r="H474" t="n">
         <v>3000</v>
@@ -14144,7 +14144,7 @@
         <v>8.5</v>
       </c>
       <c r="G475" t="n">
-        <v>7.55536794662476</v>
+        <v>7.55536699295044</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>8.5</v>
       </c>
       <c r="G476" t="n">
-        <v>7.55536794662476</v>
+        <v>7.55536699295044</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>7.37759447097778</v>
+        <v>7.37759494781494</v>
       </c>
       <c r="H477" t="n">
         <v>600</v>
@@ -14260,7 +14260,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G479" t="n">
-        <v>7.2887077331543</v>
+        <v>7.28870725631714</v>
       </c>
       <c r="H479" t="n">
         <v>3000</v>
@@ -14840,7 +14840,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G499" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H499" t="n">
         <v>21845</v>
@@ -14898,7 +14898,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H501" t="n">
         <v>40</v>
@@ -14927,7 +14927,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G502" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H502" t="n">
         <v>750</v>
@@ -14956,7 +14956,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G503" t="n">
-        <v>7.022047996521</v>
+        <v>7.02204751968384</v>
       </c>
       <c r="H503" t="n">
         <v>150</v>
@@ -15246,7 +15246,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G513" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H513" t="n">
         <v>115</v>
@@ -15275,7 +15275,7 @@
         <v>7.75</v>
       </c>
       <c r="G514" t="n">
-        <v>6.88871765136719</v>
+        <v>6.88871812820435</v>
       </c>
       <c r="H514" t="n">
         <v>1660</v>
@@ -15333,7 +15333,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>6.97760438919067</v>
+        <v>6.97760391235352</v>
       </c>
       <c r="H516" t="n">
         <v>192</v>
@@ -15362,7 +15362,7 @@
         <v>7.5</v>
       </c>
       <c r="G517" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H517" t="n">
         <v>2568</v>
@@ -15391,7 +15391,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G518" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H518" t="n">
         <v>2860</v>
@@ -15420,7 +15420,7 @@
         <v>7.5</v>
       </c>
       <c r="G519" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H519" t="n">
         <v>610</v>
@@ -15449,7 +15449,7 @@
         <v>7.5</v>
       </c>
       <c r="G520" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H520" t="n">
         <v>0</v>
@@ -15478,7 +15478,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G521" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H521" t="n">
         <v>300</v>
@@ -15507,7 +15507,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H522" t="n">
         <v>26</v>
@@ -15536,7 +15536,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H523" t="n">
         <v>16875</v>
@@ -15594,7 +15594,7 @@
         <v>7.5</v>
       </c>
       <c r="G525" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H525" t="n">
         <v>400</v>
@@ -15623,7 +15623,7 @@
         <v>7.5</v>
       </c>
       <c r="G526" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H526" t="n">
         <v>0</v>
@@ -15652,7 +15652,7 @@
         <v>7.5</v>
       </c>
       <c r="G527" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>7.5</v>
       </c>
       <c r="G528" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H528" t="n">
         <v>3103</v>
@@ -15710,7 +15710,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H529" t="n">
         <v>700</v>
@@ -15739,7 +15739,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G530" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -15826,7 +15826,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G533" t="n">
-        <v>6.71094465255737</v>
+        <v>6.71094417572021</v>
       </c>
       <c r="H533" t="n">
         <v>80</v>
@@ -15855,7 +15855,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.39984083175659</v>
+        <v>6.39984035491943</v>
       </c>
       <c r="H534" t="n">
         <v>2911</v>
@@ -15913,7 +15913,7 @@
         <v>7.25</v>
       </c>
       <c r="G536" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H536" t="n">
         <v>300</v>
@@ -15942,7 +15942,7 @@
         <v>7.25</v>
       </c>
       <c r="G537" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H537" t="n">
         <v>500</v>
@@ -15971,7 +15971,7 @@
         <v>7.25</v>
       </c>
       <c r="G538" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H538" t="n">
         <v>0</v>
@@ -16000,7 +16000,7 @@
         <v>7.25</v>
       </c>
       <c r="G539" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H539" t="n">
         <v>305</v>
@@ -16058,7 +16058,7 @@
         <v>7.25</v>
       </c>
       <c r="G541" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H541" t="n">
         <v>1320</v>
@@ -16087,7 +16087,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.39984083175659</v>
+        <v>6.39984035491943</v>
       </c>
       <c r="H542" t="n">
         <v>6172</v>
@@ -16116,7 +16116,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>6.39984083175659</v>
+        <v>6.39984035491943</v>
       </c>
       <c r="H543" t="n">
         <v>3219</v>
@@ -16174,7 +16174,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H545" t="n">
         <v>3438</v>
@@ -16232,7 +16232,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H547" t="n">
         <v>550</v>
@@ -16290,7 +16290,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H549" t="n">
         <v>450</v>
@@ -16377,7 +16377,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G552" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H552" t="n">
         <v>1717</v>
@@ -16406,7 +16406,7 @@
         <v>7.25</v>
       </c>
       <c r="G553" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H553" t="n">
         <v>343</v>
@@ -16493,7 +16493,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G556" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H556" t="n">
         <v>670</v>
@@ -16522,7 +16522,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G557" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H557" t="n">
         <v>3189</v>
@@ -16580,7 +16580,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G559" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H559" t="n">
         <v>7637</v>
@@ -16609,7 +16609,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H560" t="n">
         <v>3012</v>
@@ -16638,7 +16638,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16725,7 +16725,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H564" t="n">
         <v>300</v>
@@ -16754,7 +16754,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -16870,7 +16870,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G569" t="n">
-        <v>5.95540714263916</v>
+        <v>5.95540761947632</v>
       </c>
       <c r="H569" t="n">
         <v>6050</v>
@@ -16899,7 +16899,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H570" t="n">
         <v>3670</v>
@@ -16928,7 +16928,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G571" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G573" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H573" t="n">
         <v>4179</v>
@@ -17015,7 +17015,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G574" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H574" t="n">
         <v>2117</v>
@@ -17044,7 +17044,7 @@
         <v>7.25</v>
       </c>
       <c r="G575" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H575" t="n">
         <v>6238</v>
@@ -17073,7 +17073,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G576" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H576" t="n">
         <v>3710</v>
@@ -17102,7 +17102,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H577" t="n">
         <v>2610</v>
@@ -17131,7 +17131,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -17247,7 +17247,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G582" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H582" t="n">
         <v>2138</v>
@@ -17276,7 +17276,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G583" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H583" t="n">
         <v>18938</v>
@@ -17363,7 +17363,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G586" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H586" t="n">
         <v>2734</v>
@@ -17392,7 +17392,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H587" t="n">
         <v>3257</v>
@@ -17479,7 +17479,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G590" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H590" t="n">
         <v>8364</v>
@@ -17508,7 +17508,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H591" t="n">
         <v>200</v>
@@ -17537,7 +17537,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H592" t="n">
         <v>3684</v>
@@ -17566,7 +17566,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H593" t="n">
         <v>5400</v>
@@ -17624,7 +17624,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G595" t="n">
-        <v>5.95540714263916</v>
+        <v>5.95540761947632</v>
       </c>
       <c r="H595" t="n">
         <v>3897</v>
@@ -17682,7 +17682,7 @@
         <v>6.5</v>
       </c>
       <c r="G597" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H597" t="n">
         <v>12670</v>
@@ -17711,7 +17711,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H598" t="n">
         <v>8965</v>
@@ -17740,7 +17740,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G599" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H599" t="n">
         <v>11436</v>
@@ -17885,7 +17885,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H604" t="n">
         <v>52602</v>
@@ -17914,7 +17914,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G605" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H605" t="n">
         <v>2051</v>
@@ -17972,7 +17972,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G607" t="n">
-        <v>5.86652040481567</v>
+        <v>5.86652088165283</v>
       </c>
       <c r="H607" t="n">
         <v>17462</v>
@@ -18001,7 +18001,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>5.95540714263916</v>
+        <v>5.95540761947632</v>
       </c>
       <c r="H608" t="n">
         <v>23741</v>
@@ -18030,7 +18030,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G609" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H609" t="n">
         <v>3523</v>
@@ -18233,7 +18233,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G616" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H616" t="n">
         <v>3231</v>
@@ -18262,7 +18262,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G618" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H618" t="n">
         <v>2032</v>
@@ -18320,7 +18320,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G619" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H619" t="n">
         <v>50</v>
@@ -18349,7 +18349,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H620" t="n">
         <v>7613</v>
@@ -18378,7 +18378,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H621" t="n">
         <v>2570</v>
@@ -18407,7 +18407,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G622" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H622" t="n">
         <v>1100</v>
@@ -18436,7 +18436,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H623" t="n">
         <v>3777</v>
@@ -18465,7 +18465,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G624" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H624" t="n">
         <v>5586</v>
@@ -18494,7 +18494,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G625" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H625" t="n">
         <v>3300</v>
@@ -18523,7 +18523,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G626" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H626" t="n">
         <v>2368</v>
@@ -18552,7 +18552,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G627" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H627" t="n">
         <v>2744</v>
@@ -18581,7 +18581,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G628" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H628" t="n">
         <v>1005</v>
@@ -18610,7 +18610,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G629" t="n">
-        <v>5.95540714263916</v>
+        <v>5.95540761947632</v>
       </c>
       <c r="H629" t="n">
         <v>1200</v>
@@ -18639,7 +18639,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H630" t="n">
         <v>1307</v>
@@ -18668,7 +18668,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G631" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H631" t="n">
         <v>2750</v>
@@ -18726,7 +18726,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.86652040481567</v>
+        <v>5.86652088165283</v>
       </c>
       <c r="H633" t="n">
         <v>5366</v>
@@ -18755,7 +18755,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G634" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H634" t="n">
         <v>2000</v>
@@ -18784,7 +18784,7 @@
         <v>6.5</v>
       </c>
       <c r="G635" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H635" t="n">
         <v>12636</v>
@@ -18813,7 +18813,7 @@
         <v>6.5</v>
       </c>
       <c r="G636" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H636" t="n">
         <v>4185</v>
@@ -18842,7 +18842,7 @@
         <v>6.5</v>
       </c>
       <c r="G637" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H637" t="n">
         <v>0</v>
@@ -18871,7 +18871,7 @@
         <v>6.5</v>
       </c>
       <c r="G638" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H638" t="n">
         <v>3450</v>
@@ -18900,7 +18900,7 @@
         <v>6.5</v>
       </c>
       <c r="G639" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H639" t="n">
         <v>0</v>
@@ -18929,7 +18929,7 @@
         <v>6.5</v>
       </c>
       <c r="G640" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H640" t="n">
         <v>1550</v>
@@ -18958,7 +18958,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G641" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H641" t="n">
         <v>1959</v>
@@ -18987,7 +18987,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H642" t="n">
         <v>2879</v>
@@ -19045,7 +19045,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>5.64430379867554</v>
+        <v>5.6443042755127</v>
       </c>
       <c r="H644" t="n">
         <v>5286</v>
@@ -19074,7 +19074,7 @@
         <v>6.25</v>
       </c>
       <c r="G645" t="n">
-        <v>5.55541753768921</v>
+        <v>5.55541706085205</v>
       </c>
       <c r="H645" t="n">
         <v>3525</v>
@@ -19103,7 +19103,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.64430379867554</v>
+        <v>5.6443042755127</v>
       </c>
       <c r="H646" t="n">
         <v>297</v>
@@ -19132,7 +19132,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H647" t="n">
         <v>262</v>
@@ -19161,7 +19161,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H648" t="n">
         <v>2986</v>
@@ -19190,7 +19190,7 @@
         <v>6.5</v>
       </c>
       <c r="G649" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H649" t="n">
         <v>6789</v>
@@ -19248,7 +19248,7 @@
         <v>6.5</v>
       </c>
       <c r="G651" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H651" t="n">
         <v>1008</v>
@@ -19277,7 +19277,7 @@
         <v>6.5</v>
       </c>
       <c r="G652" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H652" t="n">
         <v>11094</v>
@@ -19306,7 +19306,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G653" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H653" t="n">
         <v>4753</v>
@@ -19335,7 +19335,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G654" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H654" t="n">
         <v>1310</v>
@@ -19683,7 +19683,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G666" t="n">
-        <v>4.35544681549072</v>
+        <v>4.35544729232788</v>
       </c>
       <c r="H666" t="n">
         <v>11395</v>
@@ -19712,7 +19712,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>4.26656103134155</v>
+        <v>4.26656055450439</v>
       </c>
       <c r="H667" t="n">
         <v>8251</v>
@@ -19741,7 +19741,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>4.07101011276245</v>
+        <v>4.07100963592529</v>
       </c>
       <c r="H668" t="n">
         <v>934</v>
@@ -19799,7 +19799,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G670" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H670" t="n">
         <v>10643</v>
@@ -19828,7 +19828,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G671" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -19857,7 +19857,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G672" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G673" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G674" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H674" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G675" t="n">
-        <v>3.82212734222412</v>
+        <v>3.8221275806427</v>
       </c>
       <c r="H675" t="n">
         <v>2991</v>
@@ -19973,7 +19973,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G676" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H676" t="n">
         <v>2454</v>
@@ -20002,7 +20002,7 @@
         <v>4.5</v>
       </c>
       <c r="G677" t="n">
-        <v>3.99990081787109</v>
+        <v>3.99990057945251</v>
       </c>
       <c r="H677" t="n">
         <v>2379</v>
@@ -20031,7 +20031,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G678" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H678" t="n">
         <v>6410</v>
@@ -20089,7 +20089,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G680" t="n">
-        <v>3.85768222808838</v>
+        <v>3.8576819896698</v>
       </c>
       <c r="H680" t="n">
         <v>4718</v>
@@ -20147,7 +20147,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G682" t="n">
-        <v>3.75101757049561</v>
+        <v>3.75101804733276</v>
       </c>
       <c r="H682" t="n">
         <v>2412</v>
@@ -20176,7 +20176,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G683" t="n">
-        <v>3.64435386657715</v>
+        <v>3.64435362815857</v>
       </c>
       <c r="H683" t="n">
         <v>1800</v>
@@ -20205,7 +20205,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G684" t="n">
-        <v>3.68879723548889</v>
+        <v>3.68879747390747</v>
       </c>
       <c r="H684" t="n">
         <v>1402</v>
@@ -20234,7 +20234,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G685" t="n">
-        <v>3.80435013771057</v>
+        <v>3.80434989929199</v>
       </c>
       <c r="H685" t="n">
         <v>3900</v>
@@ -20263,7 +20263,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G686" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H686" t="n">
         <v>4888</v>
@@ -20321,7 +20321,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>3.85768222808838</v>
+        <v>3.8576819896698</v>
       </c>
       <c r="H688" t="n">
         <v>1215</v>
@@ -20350,7 +20350,7 @@
         <v>4.5</v>
       </c>
       <c r="G689" t="n">
-        <v>3.99990081787109</v>
+        <v>3.99990057945251</v>
       </c>
       <c r="H689" t="n">
         <v>1891</v>
@@ -20408,7 +20408,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G691" t="n">
-        <v>3.98212313652039</v>
+        <v>3.98212337493896</v>
       </c>
       <c r="H691" t="n">
         <v>9728</v>
@@ -20495,7 +20495,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G694" t="n">
-        <v>3.85768222808838</v>
+        <v>3.8576819896698</v>
       </c>
       <c r="H694" t="n">
         <v>6301</v>
@@ -20524,7 +20524,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H695" t="n">
         <v>4540</v>
@@ -20553,7 +20553,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H696" t="n">
         <v>470</v>
@@ -20611,7 +20611,7 @@
         <v>4.5</v>
       </c>
       <c r="G698" t="n">
-        <v>3.99990081787109</v>
+        <v>3.99990057945251</v>
       </c>
       <c r="H698" t="n">
         <v>1703</v>
@@ -20640,7 +20640,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>3.98212313652039</v>
+        <v>3.98212337493896</v>
       </c>
       <c r="H699" t="n">
         <v>13560</v>
@@ -20669,7 +20669,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G700" t="n">
-        <v>3.98212313652039</v>
+        <v>3.98212337493896</v>
       </c>
       <c r="H700" t="n">
         <v>6239</v>
@@ -20698,7 +20698,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G701" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H701" t="n">
         <v>11088</v>
@@ -20756,7 +20756,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>3.76879477500916</v>
+        <v>3.76879501342773</v>
       </c>
       <c r="H703" t="n">
         <v>6306</v>
@@ -20785,7 +20785,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G704" t="n">
-        <v>3.90212512016296</v>
+        <v>3.90212535858154</v>
       </c>
       <c r="H704" t="n">
         <v>1895</v>
@@ -20814,7 +20814,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G705" t="n">
-        <v>3.88434791564941</v>
+        <v>3.88434743881226</v>
       </c>
       <c r="H705" t="n">
         <v>6050</v>
@@ -20843,7 +20843,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G706" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H706" t="n">
         <v>1629</v>
@@ -20872,7 +20872,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>3.88434791564941</v>
+        <v>3.88434743881226</v>
       </c>
       <c r="H707" t="n">
         <v>1037</v>
@@ -20901,7 +20901,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G708" t="n">
-        <v>3.83101606369019</v>
+        <v>3.83101558685303</v>
       </c>
       <c r="H708" t="n">
         <v>6323</v>
@@ -20930,7 +20930,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>3.83101606369019</v>
+        <v>3.83101558685303</v>
       </c>
       <c r="H709" t="n">
         <v>2542</v>
@@ -20959,7 +20959,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>3.71546316146851</v>
+        <v>3.71546292304993</v>
       </c>
       <c r="H710" t="n">
         <v>8368</v>
@@ -20988,7 +20988,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G711" t="n">
-        <v>3.76879477500916</v>
+        <v>3.76879501342773</v>
       </c>
       <c r="H711" t="n">
         <v>5939</v>
@@ -21017,7 +21017,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G712" t="n">
-        <v>3.75101757049561</v>
+        <v>3.75101804733276</v>
       </c>
       <c r="H712" t="n">
         <v>2662</v>
@@ -21046,7 +21046,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G713" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H713" t="n">
         <v>1264</v>
@@ -21075,7 +21075,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G714" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H714" t="n">
         <v>0</v>
@@ -21133,7 +21133,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G716" t="n">
-        <v>3.80435013771057</v>
+        <v>3.80434989929199</v>
       </c>
       <c r="H716" t="n">
         <v>685</v>
@@ -21162,7 +21162,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>3.88434791564941</v>
+        <v>3.88434743881226</v>
       </c>
       <c r="H717" t="n">
         <v>3887</v>
@@ -21278,7 +21278,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>4.13323020935059</v>
+        <v>4.13323068618774</v>
       </c>
       <c r="H721" t="n">
         <v>12913</v>
@@ -21452,7 +21452,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G727" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767627716064</v>
       </c>
       <c r="H727" t="n">
         <v>30466</v>
@@ -21539,7 +21539,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>4.38185501098633</v>
+        <v>4.38185453414917</v>
       </c>
       <c r="H730" t="n">
         <v>61399</v>
@@ -21568,7 +21568,7 @@
         <v>4.75</v>
       </c>
       <c r="G731" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H731" t="n">
         <v>16376</v>
@@ -21655,7 +21655,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G734" t="n">
-        <v>4.38185501098633</v>
+        <v>4.38185453414917</v>
       </c>
       <c r="H734" t="n">
         <v>34375</v>
@@ -21684,7 +21684,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G735" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H735" t="n">
         <v>17125</v>
@@ -21713,7 +21713,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G736" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H736" t="n">
         <v>9606</v>
@@ -21742,7 +21742,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G737" t="n">
-        <v>4.40935611724854</v>
+        <v>4.40935564041138</v>
       </c>
       <c r="H737" t="n">
         <v>2683</v>
@@ -21771,7 +21771,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H738" t="n">
         <v>600</v>
@@ -21800,7 +21800,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H739" t="n">
         <v>680</v>
@@ -21829,7 +21829,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G740" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H740" t="n">
         <v>7403</v>
@@ -21916,7 +21916,7 @@
         <v>4.75</v>
       </c>
       <c r="G743" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H743" t="n">
         <v>607</v>
@@ -21945,7 +21945,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G744" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H744" t="n">
         <v>11032</v>
@@ -22032,7 +22032,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G747" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H747" t="n">
         <v>2630</v>
@@ -22061,7 +22061,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H748" t="n">
         <v>1000</v>
@@ -22177,7 +22177,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G752" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H752" t="n">
         <v>1350</v>
@@ -22380,7 +22380,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G759" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H759" t="n">
         <v>3488</v>
@@ -22467,7 +22467,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H762" t="n">
         <v>4900</v>
@@ -22641,7 +22641,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H768" t="n">
         <v>8119</v>
@@ -22902,7 +22902,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H777" t="n">
         <v>7930</v>
@@ -22931,7 +22931,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>4.08850908279419</v>
+        <v>4.08850860595703</v>
       </c>
       <c r="H778" t="n">
         <v>10894</v>
@@ -23105,7 +23105,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G784" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H784" t="n">
         <v>10522</v>
@@ -23163,7 +23163,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G786" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H786" t="n">
         <v>1030</v>
@@ -23192,7 +23192,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G787" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>4.07934141159058</v>
+        <v>4.07934188842773</v>
       </c>
       <c r="H788" t="n">
         <v>5464</v>
@@ -23250,7 +23250,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G789" t="n">
-        <v>4.07934141159058</v>
+        <v>4.07934188842773</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -23337,7 +23337,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>4.04267358779907</v>
+        <v>4.04267311096191</v>
       </c>
       <c r="H792" t="n">
         <v>1205</v>
@@ -23482,7 +23482,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G797" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H797" t="n">
         <v>2403</v>
@@ -23511,7 +23511,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G798" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H798" t="n">
         <v>1860</v>
@@ -23598,7 +23598,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>3.91433453559875</v>
+        <v>3.91433477401733</v>
       </c>
       <c r="H801" t="n">
         <v>1035</v>
@@ -23743,7 +23743,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.86849904060364</v>
+        <v>3.86849927902222</v>
       </c>
       <c r="H806" t="n">
         <v>3833</v>
@@ -23772,7 +23772,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G807" t="n">
-        <v>3.88683319091797</v>
+        <v>3.88683342933655</v>
       </c>
       <c r="H807" t="n">
         <v>13265</v>
@@ -23801,7 +23801,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G808" t="n">
-        <v>3.88683319091797</v>
+        <v>3.88683342933655</v>
       </c>
       <c r="H808" t="n">
         <v>12349</v>
@@ -23946,7 +23946,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G813" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H813" t="n">
         <v>11042</v>
@@ -24004,7 +24004,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H815" t="n">
         <v>4760</v>
@@ -24033,7 +24033,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G816" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H816" t="n">
         <v>7780</v>
@@ -24120,7 +24120,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G819" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H819" t="n">
         <v>785</v>
@@ -24178,7 +24178,7 @@
         <v>4.75</v>
       </c>
       <c r="G821" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H821" t="n">
         <v>6878</v>
@@ -24294,7 +24294,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G825" t="n">
-        <v>4.51936054229736</v>
+        <v>4.51936006546021</v>
       </c>
       <c r="H825" t="n">
         <v>1867</v>
@@ -24352,7 +24352,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>4.51019334793091</v>
+        <v>4.51019382476807</v>
       </c>
       <c r="H827" t="n">
         <v>10424</v>
@@ -24410,7 +24410,7 @@
         <v>4.75</v>
       </c>
       <c r="G829" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H829" t="n">
         <v>5800</v>
@@ -24468,7 +24468,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.04267358779907</v>
+        <v>4.04267311096191</v>
       </c>
       <c r="H831" t="n">
         <v>16333</v>
@@ -24555,7 +24555,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>3.94183588027954</v>
+        <v>3.94183611869812</v>
       </c>
       <c r="H834" t="n">
         <v>25951</v>
@@ -24642,7 +24642,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H837" t="n">
         <v>21835</v>
@@ -24729,7 +24729,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G840" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H840" t="n">
         <v>34559</v>
@@ -24758,7 +24758,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H841" t="n">
         <v>225</v>
@@ -24845,7 +24845,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G844" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H844" t="n">
         <v>16368</v>
@@ -25193,7 +25193,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>4.96854639053345</v>
+        <v>4.96854686737061</v>
       </c>
       <c r="H856" t="n">
         <v>13143</v>
@@ -25309,7 +25309,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>5.1152195930481</v>
+        <v>5.11521911621094</v>
       </c>
       <c r="H860" t="n">
         <v>16237</v>
@@ -25367,7 +25367,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G862" t="n">
-        <v>5.13355350494385</v>
+        <v>5.13355398178101</v>
       </c>
       <c r="H862" t="n">
         <v>13036</v>
@@ -25396,7 +25396,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G863" t="n">
-        <v>5.1518874168396</v>
+        <v>5.15188789367676</v>
       </c>
       <c r="H863" t="n">
         <v>7153</v>
@@ -25454,7 +25454,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>5.00521516799927</v>
+        <v>5.00521469116211</v>
       </c>
       <c r="H865" t="n">
         <v>3756</v>
@@ -25686,7 +25686,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G873" t="n">
-        <v>5.39023113250732</v>
+        <v>5.39023160934448</v>
       </c>
       <c r="H873" t="n">
         <v>31741</v>
@@ -25715,7 +25715,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G874" t="n">
-        <v>5.39023113250732</v>
+        <v>5.39023160934448</v>
       </c>
       <c r="H874" t="n">
         <v>13377</v>
@@ -25831,7 +25831,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G878" t="n">
-        <v>5.61024045944214</v>
+        <v>5.6102409362793</v>
       </c>
       <c r="H878" t="n">
         <v>24852</v>
@@ -25947,7 +25947,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G882" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H882" t="n">
         <v>8738</v>
@@ -25976,7 +25976,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>5.88525247573853</v>
+        <v>5.88525295257568</v>
       </c>
       <c r="H883" t="n">
         <v>11732</v>
@@ -26121,7 +26121,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>5.94025468826294</v>
+        <v>5.9402551651001</v>
       </c>
       <c r="H888" t="n">
         <v>7733</v>
@@ -26266,7 +26266,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G893" t="n">
-        <v>5.83025074005127</v>
+        <v>5.83025026321411</v>
       </c>
       <c r="H893" t="n">
         <v>46103</v>
@@ -26324,7 +26324,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H895" t="n">
         <v>1658</v>
@@ -26382,7 +26382,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H897" t="n">
         <v>3856</v>
@@ -26469,7 +26469,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H900" t="n">
         <v>19114</v>
@@ -26498,7 +26498,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H901" t="n">
         <v>5834</v>
@@ -26527,7 +26527,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H902" t="n">
         <v>4663</v>
@@ -26643,7 +26643,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G906" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H906" t="n">
         <v>7547</v>
@@ -26759,7 +26759,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G910" t="n">
-        <v>6.19693326950073</v>
+        <v>6.19693279266357</v>
       </c>
       <c r="H910" t="n">
         <v>32257</v>
@@ -26817,7 +26817,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>6.38027429580688</v>
+        <v>6.38027381896973</v>
       </c>
       <c r="H912" t="n">
         <v>24783</v>
@@ -26846,7 +26846,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G913" t="n">
-        <v>6.28860378265381</v>
+        <v>6.28860330581665</v>
       </c>
       <c r="H913" t="n">
         <v>13157</v>
@@ -26991,7 +26991,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>6.47194480895996</v>
+        <v>6.4719443321228</v>
       </c>
       <c r="H918" t="n">
         <v>6002</v>
@@ -27049,7 +27049,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G920" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H920" t="n">
         <v>2787</v>
@@ -27078,7 +27078,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H921" t="n">
         <v>4737</v>
@@ -27107,7 +27107,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G922" t="n">
-        <v>6.58194875717163</v>
+        <v>6.58194923400879</v>
       </c>
       <c r="H922" t="n">
         <v>5358</v>
@@ -27165,7 +27165,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G924" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H924" t="n">
         <v>4250</v>
@@ -27252,7 +27252,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G927" t="n">
-        <v>6.61861705780029</v>
+        <v>6.61861753463745</v>
       </c>
       <c r="H927" t="n">
         <v>9701</v>
@@ -27339,7 +27339,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>6.58194875717163</v>
+        <v>6.58194923400879</v>
       </c>
       <c r="H930" t="n">
         <v>1400</v>
@@ -27368,7 +27368,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G931" t="n">
-        <v>6.61861705780029</v>
+        <v>6.61861753463745</v>
       </c>
       <c r="H931" t="n">
         <v>4392</v>
@@ -27542,7 +27542,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G937" t="n">
-        <v>6.54528093338013</v>
+        <v>6.54528045654297</v>
       </c>
       <c r="H937" t="n">
         <v>11503</v>
@@ -27600,7 +27600,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G939" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H939" t="n">
         <v>14602</v>
@@ -27658,7 +27658,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>6.85696077346802</v>
+        <v>6.85696125030518</v>
       </c>
       <c r="H941" t="n">
         <v>21995</v>
@@ -27890,7 +27890,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H949" t="n">
         <v>6250</v>
@@ -28093,7 +28093,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G956" t="n">
-        <v>6.78362464904785</v>
+        <v>6.78362417221069</v>
       </c>
       <c r="H956" t="n">
         <v>5975</v>
@@ -68438,6 +68438,64 @@
         <v>0</v>
       </c>
       <c r="I2347" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2348">
+      <c r="A2348" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2348" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2348" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D2348" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2348" t="n">
+        <v>2.32999992370605</v>
+      </c>
+      <c r="F2348" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G2348" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="H2348" t="n">
+        <v>7478</v>
+      </c>
+      <c r="I2348" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2349" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2349" t="n">
+        <v>2.39000010490417</v>
+      </c>
+      <c r="D2349" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E2349" t="n">
+        <v>2.32999992370605</v>
+      </c>
+      <c r="F2349" t="n">
+        <v>2.47000002861023</v>
+      </c>
+      <c r="G2349" t="n">
+        <v>2.47000002861023</v>
+      </c>
+      <c r="H2349" t="n">
+        <v>6495</v>
+      </c>
+      <c r="I2349" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2" t="n">
-        <v>9.40188121795654</v>
+        <v>9.40187931060791</v>
       </c>
       <c r="H2" t="n">
         <v>56600</v>
@@ -456,7 +456,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G3" t="n">
-        <v>9.44388961791992</v>
+        <v>9.44389057159424</v>
       </c>
       <c r="H3" t="n">
         <v>18800</v>
@@ -543,7 +543,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394115447998</v>
       </c>
       <c r="H6" t="n">
         <v>18000</v>
@@ -601,7 +601,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394115447998</v>
       </c>
       <c r="H8" t="n">
         <v>4800</v>
@@ -688,7 +688,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G11" t="n">
-        <v>9.737961769104</v>
+        <v>9.73796272277832</v>
       </c>
       <c r="H11" t="n">
         <v>7000</v>
@@ -717,7 +717,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G12" t="n">
-        <v>9.67074680328369</v>
+        <v>9.67074584960938</v>
       </c>
       <c r="H12" t="n">
         <v>1600</v>
@@ -746,7 +746,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.62033462524414</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H13" t="n">
         <v>1200</v>
@@ -775,7 +775,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>9.70435333251953</v>
+        <v>9.70435428619385</v>
       </c>
       <c r="H14" t="n">
         <v>21400</v>
@@ -862,7 +862,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H17" t="n">
         <v>248200</v>
@@ -1007,7 +1007,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G22" t="n">
-        <v>9.64554023742676</v>
+        <v>9.64553928375244</v>
       </c>
       <c r="H22" t="n">
         <v>3400</v>
@@ -1036,7 +1036,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>9.53631496429443</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H23" t="n">
         <v>800</v>
@@ -1065,7 +1065,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G24" t="n">
-        <v>9.40188121795654</v>
+        <v>9.40187931060791</v>
       </c>
       <c r="H24" t="n">
         <v>600</v>
@@ -1210,7 +1210,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G29" t="n">
-        <v>9.56151962280273</v>
+        <v>9.56152057647705</v>
       </c>
       <c r="H29" t="n">
         <v>6000</v>
@@ -1239,7 +1239,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G30" t="n">
-        <v>9.51950931549072</v>
+        <v>9.51950836181641</v>
       </c>
       <c r="H30" t="n">
         <v>2600</v>
@@ -1268,7 +1268,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G31" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H31" t="n">
         <v>4600</v>
@@ -1297,7 +1297,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H32" t="n">
         <v>1600</v>
@@ -1326,7 +1326,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G33" t="n">
-        <v>9.56992053985596</v>
+        <v>9.56992149353027</v>
       </c>
       <c r="H33" t="n">
         <v>1800</v>
@@ -1355,7 +1355,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G34" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H34" t="n">
         <v>14200</v>
@@ -1384,7 +1384,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H35" t="n">
         <v>800</v>
@@ -1413,7 +1413,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H36" t="n">
         <v>400</v>
@@ -1442,7 +1442,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G37" t="n">
-        <v>9.56992053985596</v>
+        <v>9.56992149353027</v>
       </c>
       <c r="H37" t="n">
         <v>3000</v>
@@ -1471,7 +1471,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>9.53631496429443</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H38" t="n">
         <v>2400</v>
@@ -1500,7 +1500,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G39" t="n">
-        <v>9.64554023742676</v>
+        <v>9.64553928375244</v>
       </c>
       <c r="H39" t="n">
         <v>800</v>
@@ -1529,7 +1529,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G40" t="n">
-        <v>9.737961769104</v>
+        <v>9.73796272277832</v>
       </c>
       <c r="H40" t="n">
         <v>21400</v>
@@ -1558,7 +1558,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G41" t="n">
-        <v>9.737961769104</v>
+        <v>9.73796272277832</v>
       </c>
       <c r="H41" t="n">
         <v>1400</v>
@@ -1848,7 +1848,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G51" t="n">
-        <v>10.1832695007324</v>
+        <v>10.1832704544067</v>
       </c>
       <c r="H51" t="n">
         <v>127800</v>
@@ -1964,7 +1964,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G55" t="n">
-        <v>9.85558986663818</v>
+        <v>9.8555908203125</v>
       </c>
       <c r="H55" t="n">
         <v>11800</v>
@@ -2109,7 +2109,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G60" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320339202881</v>
       </c>
       <c r="H60" t="n">
         <v>10600</v>
@@ -2138,7 +2138,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G61" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320339202881</v>
       </c>
       <c r="H61" t="n">
         <v>11200</v>
@@ -2167,7 +2167,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G62" t="n">
-        <v>9.99002265930176</v>
+        <v>9.99002361297607</v>
       </c>
       <c r="H62" t="n">
         <v>36400</v>
@@ -2196,7 +2196,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G63" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88919830322266</v>
       </c>
       <c r="H63" t="n">
         <v>14400</v>
@@ -2225,7 +2225,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G64" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88919830322266</v>
       </c>
       <c r="H64" t="n">
         <v>24000</v>
@@ -2283,7 +2283,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G66" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88919830322266</v>
       </c>
       <c r="H66" t="n">
         <v>16400</v>
@@ -2312,7 +2312,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G67" t="n">
-        <v>9.93961048126221</v>
+        <v>9.93960952758789</v>
       </c>
       <c r="H67" t="n">
         <v>18400</v>
@@ -2341,7 +2341,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G68" t="n">
-        <v>9.99002265930176</v>
+        <v>9.99002361297607</v>
       </c>
       <c r="H68" t="n">
         <v>13600</v>
@@ -2399,7 +2399,7 @@
         <v>11.75</v>
       </c>
       <c r="G70" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H70" t="n">
         <v>5200</v>
@@ -2428,7 +2428,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G71" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88919830322266</v>
       </c>
       <c r="H71" t="n">
         <v>64600</v>
@@ -2515,7 +2515,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G74" t="n">
-        <v>10.0656404495239</v>
+        <v>10.0656414031982</v>
       </c>
       <c r="H74" t="n">
         <v>7000</v>
@@ -2602,7 +2602,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G77" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320339202881</v>
       </c>
       <c r="H77" t="n">
         <v>58000</v>
@@ -2718,7 +2718,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G81" t="n">
-        <v>9.8976001739502</v>
+        <v>9.89760112762451</v>
       </c>
       <c r="H81" t="n">
         <v>18800</v>
@@ -2747,7 +2747,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G82" t="n">
-        <v>9.99002265930176</v>
+        <v>9.99002361297607</v>
       </c>
       <c r="H82" t="n">
         <v>4200</v>
@@ -2776,7 +2776,7 @@
         <v>11.75</v>
       </c>
       <c r="G83" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H83" t="n">
         <v>13000</v>
@@ -2834,7 +2834,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G85" t="n">
-        <v>9.90600395202637</v>
+        <v>9.90600204467773</v>
       </c>
       <c r="H85" t="n">
         <v>4200</v>
@@ -2892,7 +2892,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G87" t="n">
-        <v>9.8976001739502</v>
+        <v>9.89760112762451</v>
       </c>
       <c r="H87" t="n">
         <v>4400</v>
@@ -2921,7 +2921,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G88" t="n">
-        <v>9.90600395202637</v>
+        <v>9.90600204467773</v>
       </c>
       <c r="H88" t="n">
         <v>600</v>
@@ -2950,7 +2950,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H89" t="n">
         <v>22400</v>
@@ -2979,7 +2979,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H90" t="n">
         <v>2000</v>
@@ -3008,7 +3008,7 @@
         <v>11.75</v>
       </c>
       <c r="G91" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H91" t="n">
         <v>1000</v>
@@ -3037,7 +3037,7 @@
         <v>11.75</v>
       </c>
       <c r="G92" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H92" t="n">
         <v>3000</v>
@@ -3066,7 +3066,7 @@
         <v>11.75</v>
       </c>
       <c r="G93" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H93" t="n">
         <v>2600</v>
@@ -3124,7 +3124,7 @@
         <v>11.75</v>
       </c>
       <c r="G95" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H95" t="n">
         <v>7800</v>
@@ -3153,7 +3153,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H96" t="n">
         <v>2600</v>
@@ -3240,7 +3240,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G99" t="n">
-        <v>9.973219871521</v>
+        <v>9.97321891784668</v>
       </c>
       <c r="H99" t="n">
         <v>7400</v>
@@ -3269,7 +3269,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88919830322266</v>
       </c>
       <c r="H100" t="n">
         <v>36600</v>
@@ -3298,7 +3298,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G101" t="n">
-        <v>9.85558986663818</v>
+        <v>9.8555908203125</v>
       </c>
       <c r="H101" t="n">
         <v>3600</v>
@@ -3385,7 +3385,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G104" t="n">
-        <v>9.737961769104</v>
+        <v>9.73796272277832</v>
       </c>
       <c r="H104" t="n">
         <v>1800</v>
@@ -3501,7 +3501,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G108" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394115447998</v>
       </c>
       <c r="H108" t="n">
         <v>20400</v>
@@ -3530,7 +3530,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>9.62033462524414</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H109" t="n">
         <v>9400</v>
@@ -3588,7 +3588,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>9.62033462524414</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H111" t="n">
         <v>4600</v>
@@ -3617,7 +3617,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>9.53631496429443</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H112" t="n">
         <v>800</v>
@@ -3646,7 +3646,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G113" t="n">
-        <v>9.64554023742676</v>
+        <v>9.64553928375244</v>
       </c>
       <c r="H113" t="n">
         <v>2800</v>
@@ -3704,7 +3704,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G115" t="n">
-        <v>9.72956085205078</v>
+        <v>9.72955989837646</v>
       </c>
       <c r="H115" t="n">
         <v>6000</v>
@@ -3762,7 +3762,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H117" t="n">
         <v>16400</v>
@@ -3791,7 +3791,7 @@
         <v>11.75</v>
       </c>
       <c r="G118" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H118" t="n">
         <v>12000</v>
@@ -3820,7 +3820,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H119" t="n">
         <v>5400</v>
@@ -3878,7 +3878,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H121" t="n">
         <v>6200</v>
@@ -3907,7 +3907,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H122" t="n">
         <v>14000</v>
@@ -4052,7 +4052,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H127" t="n">
         <v>39200</v>
@@ -4139,7 +4139,7 @@
         <v>11.75</v>
       </c>
       <c r="G130" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H130" t="n">
         <v>3400</v>
@@ -4168,7 +4168,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H131" t="n">
         <v>5600</v>
@@ -4284,7 +4284,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H135" t="n">
         <v>5600</v>
@@ -4429,7 +4429,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H140" t="n">
         <v>9000</v>
@@ -4458,7 +4458,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H141" t="n">
         <v>1600</v>
@@ -4661,7 +4661,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G148" t="n">
-        <v>9.62033462524414</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H148" t="n">
         <v>3400</v>
@@ -4690,7 +4690,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H149" t="n">
         <v>5600</v>
@@ -4719,7 +4719,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>9.70435333251953</v>
+        <v>9.70435428619385</v>
       </c>
       <c r="H153" t="n">
         <v>19400</v>
@@ -4864,7 +4864,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G155" t="n">
-        <v>9.53631496429443</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H155" t="n">
         <v>27200</v>
@@ -4893,7 +4893,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>9.70435333251953</v>
+        <v>9.70435428619385</v>
       </c>
       <c r="H156" t="n">
         <v>200</v>
@@ -4980,7 +4980,7 @@
         <v>11</v>
       </c>
       <c r="G159" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H159" t="n">
         <v>14600</v>
@@ -5125,7 +5125,7 @@
         <v>11</v>
       </c>
       <c r="G164" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H164" t="n">
         <v>18800</v>
@@ -5154,7 +5154,7 @@
         <v>11</v>
       </c>
       <c r="G165" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>11</v>
       </c>
       <c r="G166" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H166" t="n">
         <v>400</v>
@@ -5241,7 +5241,7 @@
         <v>11</v>
       </c>
       <c r="G168" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H168" t="n">
         <v>1200</v>
@@ -5270,7 +5270,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>9.28425312042236</v>
+        <v>9.28425216674805</v>
       </c>
       <c r="H169" t="n">
         <v>200</v>
@@ -5357,7 +5357,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H172" t="n">
         <v>35400</v>
@@ -5415,7 +5415,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H174" t="n">
         <v>33600</v>
@@ -5502,7 +5502,7 @@
         <v>11</v>
       </c>
       <c r="G177" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H177" t="n">
         <v>5200</v>
@@ -5647,7 +5647,7 @@
         <v>11</v>
       </c>
       <c r="G182" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H182" t="n">
         <v>10000</v>
@@ -5705,7 +5705,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G184" t="n">
-        <v>9.11621189117432</v>
+        <v>9.1162109375</v>
       </c>
       <c r="H184" t="n">
         <v>7200</v>
@@ -5821,7 +5821,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>8.99018096923828</v>
+        <v>8.9901819229126</v>
       </c>
       <c r="H188" t="n">
         <v>5800</v>
@@ -5879,7 +5879,7 @@
         <v>10.75</v>
       </c>
       <c r="G190" t="n">
-        <v>9.03219223022461</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H190" t="n">
         <v>400</v>
@@ -5908,7 +5908,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>9.11621189117432</v>
+        <v>9.1162109375</v>
       </c>
       <c r="H191" t="n">
         <v>11600</v>
@@ -5937,7 +5937,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>9.11621189117432</v>
+        <v>9.1162109375</v>
       </c>
       <c r="H192" t="n">
         <v>400</v>
@@ -5966,7 +5966,7 @@
         <v>10.75</v>
       </c>
       <c r="G193" t="n">
-        <v>9.03219223022461</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H193" t="n">
         <v>400</v>
@@ -5995,7 +5995,7 @@
         <v>10.75</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03219223022461</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H194" t="n">
         <v>600</v>
@@ -6024,7 +6024,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>8.99018096923828</v>
+        <v>8.9901819229126</v>
       </c>
       <c r="H195" t="n">
         <v>200</v>
@@ -6053,7 +6053,7 @@
         <v>10.75</v>
       </c>
       <c r="G196" t="n">
-        <v>9.03219223022461</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H196" t="n">
         <v>10200</v>
@@ -6198,7 +6198,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G201" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H201" t="n">
         <v>3200</v>
@@ -6227,7 +6227,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G202" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H202" t="n">
         <v>2800</v>
@@ -6256,7 +6256,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G203" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H203" t="n">
         <v>3200</v>
@@ -6285,7 +6285,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G204" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H204" t="n">
         <v>3600</v>
@@ -6314,7 +6314,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G205" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H205" t="n">
         <v>8800</v>
@@ -6343,7 +6343,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G206" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H206" t="n">
         <v>23000</v>
@@ -6372,7 +6372,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G207" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H207" t="n">
         <v>3200</v>
@@ -6401,7 +6401,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>9.33020782470703</v>
+        <v>9.33020687103271</v>
       </c>
       <c r="H208" t="n">
         <v>20200</v>
@@ -6430,7 +6430,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G209" t="n">
-        <v>9.41619873046875</v>
+        <v>9.41619968414307</v>
       </c>
       <c r="H209" t="n">
         <v>200</v>
@@ -6459,7 +6459,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G210" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H210" t="n">
         <v>7400</v>
@@ -6488,7 +6488,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>9.33020782470703</v>
+        <v>9.33020687103271</v>
       </c>
       <c r="H211" t="n">
         <v>1000</v>
@@ -6517,7 +6517,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>9.41619873046875</v>
+        <v>9.41619968414307</v>
       </c>
       <c r="H212" t="n">
         <v>200</v>
@@ -6546,7 +6546,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>9.41619873046875</v>
+        <v>9.41619968414307</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G214" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H214" t="n">
         <v>6600</v>
@@ -6604,7 +6604,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>9.11522579193115</v>
+        <v>9.11522483825684</v>
       </c>
       <c r="H215" t="n">
         <v>18200</v>
@@ -6633,7 +6633,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>8.98623657226562</v>
+        <v>8.98623752593994</v>
       </c>
       <c r="H216" t="n">
         <v>7000</v>
@@ -6662,7 +6662,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G217" t="n">
-        <v>8.72825813293457</v>
+        <v>8.72825717926025</v>
       </c>
       <c r="H217" t="n">
         <v>31200</v>
@@ -6807,7 +6807,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G222" t="n">
-        <v>9.07222938537598</v>
+        <v>9.07222843170166</v>
       </c>
       <c r="H222" t="n">
         <v>8600</v>
@@ -6836,7 +6836,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G223" t="n">
-        <v>8.90024471282959</v>
+        <v>8.90024375915527</v>
       </c>
       <c r="H223" t="n">
         <v>20400</v>
@@ -6865,7 +6865,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H224" t="n">
         <v>3000</v>
@@ -6894,7 +6894,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G225" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>8.90024471282959</v>
+        <v>8.90024375915527</v>
       </c>
       <c r="H226" t="n">
         <v>1200</v>
@@ -6952,7 +6952,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>8.98623657226562</v>
+        <v>8.98623752593994</v>
       </c>
       <c r="H227" t="n">
         <v>2800</v>
@@ -7039,7 +7039,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>9.11522579193115</v>
+        <v>9.11522483825684</v>
       </c>
       <c r="H230" t="n">
         <v>64400</v>
@@ -7068,7 +7068,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>9.11522579193115</v>
+        <v>9.11522483825684</v>
       </c>
       <c r="H231" t="n">
         <v>5000</v>
@@ -7097,7 +7097,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G232" t="n">
-        <v>9.41619873046875</v>
+        <v>9.41619968414307</v>
       </c>
       <c r="H232" t="n">
         <v>2000</v>
@@ -7126,7 +7126,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>9.33020782470703</v>
+        <v>9.33020687103271</v>
       </c>
       <c r="H233" t="n">
         <v>11800</v>
@@ -7155,7 +7155,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G234" t="n">
-        <v>9.11522579193115</v>
+        <v>9.11522483825684</v>
       </c>
       <c r="H234" t="n">
         <v>6000</v>
@@ -7213,7 +7213,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G236" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H236" t="n">
         <v>9600</v>
@@ -7242,7 +7242,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G237" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H244" t="n">
         <v>19000</v>
@@ -7532,7 +7532,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H247" t="n">
         <v>1000</v>
@@ -7561,7 +7561,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G248" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H248" t="n">
         <v>600</v>
@@ -8025,7 +8025,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>9.07222938537598</v>
+        <v>9.07222843170166</v>
       </c>
       <c r="H264" t="n">
         <v>8000</v>
@@ -8112,7 +8112,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H267" t="n">
         <v>8000</v>
@@ -8141,7 +8141,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G268" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H268" t="n">
         <v>2200</v>
@@ -8170,7 +8170,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H269" t="n">
         <v>400</v>
@@ -8344,7 +8344,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H275" t="n">
         <v>2000</v>
@@ -8373,7 +8373,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G277" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G278" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G279" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G281" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H281" t="n">
         <v>400</v>
@@ -8547,7 +8547,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G282" t="n">
-        <v>8.51327705383301</v>
+        <v>8.51327610015869</v>
       </c>
       <c r="H282" t="n">
         <v>2000</v>
@@ -8576,7 +8576,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>8.72825813293457</v>
+        <v>8.72825717926025</v>
       </c>
       <c r="H283" t="n">
         <v>5000</v>
@@ -8605,7 +8605,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>8.72825813293457</v>
+        <v>8.72825717926025</v>
       </c>
       <c r="H284" t="n">
         <v>1000</v>
@@ -8750,7 +8750,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.25529956817627</v>
+        <v>8.25529861450195</v>
       </c>
       <c r="H289" t="n">
         <v>800</v>
@@ -8808,7 +8808,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G291" t="n">
-        <v>8.35848999023438</v>
+        <v>8.35849094390869</v>
       </c>
       <c r="H291" t="n">
         <v>6200</v>
@@ -8837,7 +8837,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G292" t="n">
-        <v>8.41008567810059</v>
+        <v>8.41008472442627</v>
       </c>
       <c r="H292" t="n">
         <v>3000</v>
@@ -8866,7 +8866,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G293" t="n">
-        <v>8.41008567810059</v>
+        <v>8.41008472442627</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         <v>9.5</v>
       </c>
       <c r="G296" t="n">
-        <v>8.1693058013916</v>
+        <v>8.16930675506592</v>
       </c>
       <c r="H296" t="n">
         <v>17200</v>
@@ -9156,7 +9156,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G303" t="n">
-        <v>8.53047466278076</v>
+        <v>8.53047561645508</v>
       </c>
       <c r="H303" t="n">
         <v>2000</v>
@@ -9185,7 +9185,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H304" t="n">
         <v>1200</v>
@@ -9272,7 +9272,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G307" t="n">
-        <v>8.03171730041504</v>
+        <v>8.03171825408936</v>
       </c>
       <c r="H307" t="n">
         <v>2000</v>
@@ -9330,7 +9330,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G309" t="n">
-        <v>8.03171730041504</v>
+        <v>8.03171825408936</v>
       </c>
       <c r="H309" t="n">
         <v>600</v>
@@ -9417,7 +9417,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>7.82533550262451</v>
+        <v>7.82533597946167</v>
       </c>
       <c r="H312" t="n">
         <v>1200</v>
@@ -9446,7 +9446,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>7.70494604110718</v>
+        <v>7.70494556427002</v>
       </c>
       <c r="H313" t="n">
         <v>4200</v>
@@ -9475,7 +9475,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H314" t="n">
         <v>23200</v>
@@ -9504,7 +9504,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H315" t="n">
         <v>14000</v>
@@ -9533,7 +9533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H317" t="n">
         <v>4200</v>
@@ -9591,7 +9591,7 @@
         <v>8.5</v>
       </c>
       <c r="G318" t="n">
-        <v>7.30937814712524</v>
+        <v>7.30937957763672</v>
       </c>
       <c r="H318" t="n">
         <v>1600</v>
@@ -9620,7 +9620,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G319" t="n">
-        <v>7.36097431182861</v>
+        <v>7.36097526550293</v>
       </c>
       <c r="H319" t="n">
         <v>2400</v>
@@ -9649,7 +9649,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G320" t="n">
-        <v>7.32657766342163</v>
+        <v>7.32657814025879</v>
       </c>
       <c r="H320" t="n">
         <v>400</v>
@@ -9678,7 +9678,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G321" t="n">
-        <v>7.32657766342163</v>
+        <v>7.32657814025879</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G323" t="n">
-        <v>6.99980545043945</v>
+        <v>6.99980592727661</v>
       </c>
       <c r="H323" t="n">
         <v>800</v>
@@ -9765,7 +9765,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G324" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H324" t="n">
         <v>3200</v>
@@ -9794,7 +9794,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>7.2061882019043</v>
+        <v>7.20618772506714</v>
       </c>
       <c r="H325" t="n">
         <v>3000</v>
@@ -9823,7 +9823,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G326" t="n">
-        <v>7.2061882019043</v>
+        <v>7.20618772506714</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G328" t="n">
-        <v>7.82533550262451</v>
+        <v>7.82533597946167</v>
       </c>
       <c r="H328" t="n">
         <v>600</v>
@@ -9910,7 +9910,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G329" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H329" t="n">
         <v>600</v>
@@ -10026,7 +10026,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>7.70494604110718</v>
+        <v>7.70494556427002</v>
       </c>
       <c r="H333" t="n">
         <v>600</v>
@@ -10055,7 +10055,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H334" t="n">
         <v>800</v>
@@ -10084,7 +10084,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G335" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G336" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H336" t="n">
         <v>1000</v>
@@ -10200,7 +10200,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H339" t="n">
         <v>400</v>
@@ -10258,7 +10258,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G341" t="n">
-        <v>7.13739395141602</v>
+        <v>7.13739347457886</v>
       </c>
       <c r="H341" t="n">
         <v>7000</v>
@@ -10316,7 +10316,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G343" t="n">
-        <v>7.06859922409058</v>
+        <v>7.06859970092773</v>
       </c>
       <c r="H343" t="n">
         <v>5200</v>
@@ -10374,7 +10374,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G345" t="n">
-        <v>6.99980545043945</v>
+        <v>6.99980592727661</v>
       </c>
       <c r="H345" t="n">
         <v>5400</v>
@@ -10519,7 +10519,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G350" t="n">
-        <v>6.99980545043945</v>
+        <v>6.99980592727661</v>
       </c>
       <c r="H350" t="n">
         <v>18548</v>
@@ -10548,7 +10548,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G351" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H351" t="n">
         <v>3182</v>
@@ -10577,7 +10577,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>6.9138126373291</v>
+        <v>6.91381216049194</v>
       </c>
       <c r="H352" t="n">
         <v>4342</v>
@@ -10606,7 +10606,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G353" t="n">
-        <v>6.70743036270142</v>
+        <v>6.70743083953857</v>
       </c>
       <c r="H353" t="n">
         <v>6730</v>
@@ -10664,7 +10664,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H355" t="n">
         <v>8049</v>
@@ -10780,7 +10780,7 @@
         <v>8</v>
       </c>
       <c r="G359" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H359" t="n">
         <v>140</v>
@@ -10867,7 +10867,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H362" t="n">
         <v>3100</v>
@@ -10954,7 +10954,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G365" t="n">
-        <v>6.79342269897461</v>
+        <v>6.79342317581177</v>
       </c>
       <c r="H365" t="n">
         <v>830</v>
@@ -11041,7 +11041,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H368" t="n">
         <v>200</v>
@@ -11157,7 +11157,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>7.13739395141602</v>
+        <v>7.13739347457886</v>
       </c>
       <c r="H372" t="n">
         <v>2867</v>
@@ -11215,7 +11215,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G374" t="n">
-        <v>6.75902605056763</v>
+        <v>6.75902557373047</v>
       </c>
       <c r="H374" t="n">
         <v>25405</v>
@@ -11244,7 +11244,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G375" t="n">
-        <v>6.79342269897461</v>
+        <v>6.79342317581177</v>
       </c>
       <c r="H375" t="n">
         <v>950</v>
@@ -11360,7 +11360,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H379" t="n">
         <v>1210</v>
@@ -11389,7 +11389,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H380" t="n">
         <v>1253</v>
@@ -11418,7 +11418,7 @@
         <v>8</v>
       </c>
       <c r="G381" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H381" t="n">
         <v>1532</v>
@@ -11447,7 +11447,7 @@
         <v>8</v>
       </c>
       <c r="G382" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H382" t="n">
         <v>291</v>
@@ -11505,7 +11505,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H384" t="n">
         <v>124</v>
@@ -11650,7 +11650,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>6.9138126373291</v>
+        <v>6.91381216049194</v>
       </c>
       <c r="H389" t="n">
         <v>7543</v>
@@ -11679,7 +11679,7 @@
         <v>8</v>
       </c>
       <c r="G390" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H390" t="n">
         <v>7347</v>
@@ -11708,7 +11708,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H391" t="n">
         <v>2600</v>
@@ -11766,7 +11766,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G393" t="n">
-        <v>6.69023132324219</v>
+        <v>6.69023180007935</v>
       </c>
       <c r="H393" t="n">
         <v>24134</v>
@@ -11795,7 +11795,7 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H394" t="n">
         <v>1786</v>
@@ -11853,7 +11853,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H396" t="n">
         <v>1510</v>
@@ -11882,7 +11882,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H397" t="n">
         <v>4250</v>
@@ -12027,7 +12027,7 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H402" t="n">
         <v>6710</v>
@@ -12056,7 +12056,7 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H403" t="n">
         <v>2710</v>
@@ -12085,7 +12085,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>6.79342269897461</v>
+        <v>6.79342317581177</v>
       </c>
       <c r="H404" t="n">
         <v>57</v>
@@ -12114,7 +12114,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G405" t="n">
-        <v>6.75902605056763</v>
+        <v>6.75902557373047</v>
       </c>
       <c r="H405" t="n">
         <v>3290</v>
@@ -12143,7 +12143,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G406" t="n">
-        <v>6.70743036270142</v>
+        <v>6.70743083953857</v>
       </c>
       <c r="H406" t="n">
         <v>4994</v>
@@ -12172,7 +12172,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>6.79342269897461</v>
+        <v>6.79342317581177</v>
       </c>
       <c r="H407" t="n">
         <v>20699</v>
@@ -12230,7 +12230,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>7.24058532714844</v>
+        <v>7.24058485031128</v>
       </c>
       <c r="H409" t="n">
         <v>12395</v>
@@ -12259,7 +12259,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G410" t="n">
-        <v>7.46416616439819</v>
+        <v>7.46416664123535</v>
       </c>
       <c r="H410" t="n">
         <v>32960</v>
@@ -12346,7 +12346,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H413" t="n">
         <v>3920</v>
@@ -12404,7 +12404,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G415" t="n">
-        <v>7.61895132064819</v>
+        <v>7.61895227432251</v>
       </c>
       <c r="H415" t="n">
         <v>5660</v>
@@ -12462,7 +12462,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G417" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H417" t="n">
         <v>1940</v>
@@ -12549,7 +12549,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>7.3437762260437</v>
+        <v>7.34377574920654</v>
       </c>
       <c r="H420" t="n">
         <v>4725</v>
@@ -12578,7 +12578,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>7.3437762260437</v>
+        <v>7.34377574920654</v>
       </c>
       <c r="H421" t="n">
         <v>1620</v>
@@ -12607,7 +12607,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G422" t="n">
-        <v>7.36097431182861</v>
+        <v>7.36097526550293</v>
       </c>
       <c r="H422" t="n">
         <v>1868</v>
@@ -12636,7 +12636,7 @@
         <v>8.5</v>
       </c>
       <c r="G423" t="n">
-        <v>7.30937814712524</v>
+        <v>7.30937957763672</v>
       </c>
       <c r="H423" t="n">
         <v>1963</v>
@@ -12665,7 +12665,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H424" t="n">
         <v>13987</v>
@@ -12694,7 +12694,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H425" t="n">
         <v>1500</v>
@@ -12723,7 +12723,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H426" t="n">
         <v>822</v>
@@ -12781,7 +12781,7 @@
         <v>8.5</v>
       </c>
       <c r="G428" t="n">
-        <v>7.30937814712524</v>
+        <v>7.30937957763672</v>
       </c>
       <c r="H428" t="n">
         <v>1002</v>
@@ -12839,7 +12839,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>7.13739395141602</v>
+        <v>7.13739347457886</v>
       </c>
       <c r="H430" t="n">
         <v>908</v>
@@ -12868,7 +12868,7 @@
         <v>8.5</v>
       </c>
       <c r="G431" t="n">
-        <v>7.30937814712524</v>
+        <v>7.30937957763672</v>
       </c>
       <c r="H431" t="n">
         <v>400</v>
@@ -12897,7 +12897,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H432" t="n">
         <v>7444</v>
@@ -12955,7 +12955,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H434" t="n">
         <v>1098</v>
@@ -12984,7 +12984,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G435" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H435" t="n">
         <v>1451</v>
@@ -13071,7 +13071,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H438" t="n">
         <v>5485</v>
@@ -13100,7 +13100,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H439" t="n">
         <v>572</v>
@@ -13129,7 +13129,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H440" t="n">
         <v>1662</v>
@@ -13158,7 +13158,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>7.78233909606934</v>
+        <v>7.78233861923218</v>
       </c>
       <c r="H442" t="n">
         <v>10</v>
@@ -13216,7 +13216,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H443" t="n">
         <v>4760</v>
@@ -13245,7 +13245,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H444" t="n">
         <v>800</v>
@@ -13274,7 +13274,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H445" t="n">
         <v>8557</v>
@@ -13303,7 +13303,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G446" t="n">
-        <v>7.43836688995361</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H446" t="n">
         <v>5102</v>
@@ -13332,7 +13332,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>7.43836688995361</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H447" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G449" t="n">
-        <v>7.43836688995361</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H449" t="n">
         <v>1237</v>
@@ -13419,7 +13419,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G450" t="n">
-        <v>7.43836688995361</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G451" t="n">
-        <v>7.43836688995361</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H451" t="n">
         <v>3000</v>
@@ -13477,7 +13477,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G452" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H452" t="n">
         <v>510</v>
@@ -13506,7 +13506,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G453" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H453" t="n">
         <v>2385</v>
@@ -13535,7 +13535,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G454" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H454" t="n">
         <v>200</v>
@@ -13564,7 +13564,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G455" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H455" t="n">
         <v>18119</v>
@@ -13593,7 +13593,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H456" t="n">
         <v>695</v>
@@ -13622,7 +13622,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G457" t="n">
-        <v>7.6442551612854</v>
+        <v>7.64425468444824</v>
       </c>
       <c r="H457" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G458" t="n">
-        <v>7.6442551612854</v>
+        <v>7.64425468444824</v>
       </c>
       <c r="H458" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>7.37759494781494</v>
+        <v>7.37759447097778</v>
       </c>
       <c r="H461" t="n">
         <v>6100</v>
@@ -13999,7 +13999,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G470" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H470" t="n">
         <v>3543</v>
@@ -14028,7 +14028,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>7.28870725631714</v>
+        <v>7.2887077331543</v>
       </c>
       <c r="H471" t="n">
         <v>30</v>
@@ -14115,7 +14115,7 @@
         <v>8.5</v>
       </c>
       <c r="G474" t="n">
-        <v>7.55536699295044</v>
+        <v>7.55536794662476</v>
       </c>
       <c r="H474" t="n">
         <v>3000</v>
@@ -14144,7 +14144,7 @@
         <v>8.5</v>
       </c>
       <c r="G475" t="n">
-        <v>7.55536699295044</v>
+        <v>7.55536794662476</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>8.5</v>
       </c>
       <c r="G476" t="n">
-        <v>7.55536699295044</v>
+        <v>7.55536794662476</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>7.37759494781494</v>
+        <v>7.37759447097778</v>
       </c>
       <c r="H477" t="n">
         <v>600</v>
@@ -14260,7 +14260,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G479" t="n">
-        <v>7.28870725631714</v>
+        <v>7.2887077331543</v>
       </c>
       <c r="H479" t="n">
         <v>3000</v>
@@ -14840,7 +14840,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G499" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H499" t="n">
         <v>21845</v>
@@ -14898,7 +14898,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H501" t="n">
         <v>40</v>
@@ -14927,7 +14927,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G502" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H502" t="n">
         <v>750</v>
@@ -14956,7 +14956,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G503" t="n">
-        <v>7.02204751968384</v>
+        <v>7.022047996521</v>
       </c>
       <c r="H503" t="n">
         <v>150</v>
@@ -15246,7 +15246,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G513" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H513" t="n">
         <v>115</v>
@@ -15275,7 +15275,7 @@
         <v>7.75</v>
       </c>
       <c r="G514" t="n">
-        <v>6.88871812820435</v>
+        <v>6.88871765136719</v>
       </c>
       <c r="H514" t="n">
         <v>1660</v>
@@ -15333,7 +15333,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>6.97760391235352</v>
+        <v>6.97760438919067</v>
       </c>
       <c r="H516" t="n">
         <v>192</v>
@@ -15362,7 +15362,7 @@
         <v>7.5</v>
       </c>
       <c r="G517" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H517" t="n">
         <v>2568</v>
@@ -15391,7 +15391,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G518" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H518" t="n">
         <v>2860</v>
@@ -15420,7 +15420,7 @@
         <v>7.5</v>
       </c>
       <c r="G519" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H519" t="n">
         <v>610</v>
@@ -15449,7 +15449,7 @@
         <v>7.5</v>
       </c>
       <c r="G520" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H520" t="n">
         <v>0</v>
@@ -15478,7 +15478,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G521" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H521" t="n">
         <v>300</v>
@@ -15507,7 +15507,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H522" t="n">
         <v>26</v>
@@ -15536,7 +15536,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H523" t="n">
         <v>16875</v>
@@ -15594,7 +15594,7 @@
         <v>7.5</v>
       </c>
       <c r="G525" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H525" t="n">
         <v>400</v>
@@ -15623,7 +15623,7 @@
         <v>7.5</v>
       </c>
       <c r="G526" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H526" t="n">
         <v>0</v>
@@ -15652,7 +15652,7 @@
         <v>7.5</v>
       </c>
       <c r="G527" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>7.5</v>
       </c>
       <c r="G528" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H528" t="n">
         <v>3103</v>
@@ -15710,7 +15710,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H529" t="n">
         <v>700</v>
@@ -15739,7 +15739,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G530" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -15826,7 +15826,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G533" t="n">
-        <v>6.71094417572021</v>
+        <v>6.71094465255737</v>
       </c>
       <c r="H533" t="n">
         <v>80</v>
@@ -15855,7 +15855,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.39984035491943</v>
+        <v>6.39984083175659</v>
       </c>
       <c r="H534" t="n">
         <v>2911</v>
@@ -15913,7 +15913,7 @@
         <v>7.25</v>
       </c>
       <c r="G536" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H536" t="n">
         <v>300</v>
@@ -15942,7 +15942,7 @@
         <v>7.25</v>
       </c>
       <c r="G537" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H537" t="n">
         <v>500</v>
@@ -15971,7 +15971,7 @@
         <v>7.25</v>
       </c>
       <c r="G538" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H538" t="n">
         <v>0</v>
@@ -16000,7 +16000,7 @@
         <v>7.25</v>
       </c>
       <c r="G539" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H539" t="n">
         <v>305</v>
@@ -16058,7 +16058,7 @@
         <v>7.25</v>
       </c>
       <c r="G541" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H541" t="n">
         <v>1320</v>
@@ -16087,7 +16087,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.39984035491943</v>
+        <v>6.39984083175659</v>
       </c>
       <c r="H542" t="n">
         <v>6172</v>
@@ -16116,7 +16116,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>6.39984035491943</v>
+        <v>6.39984083175659</v>
       </c>
       <c r="H543" t="n">
         <v>3219</v>
@@ -16174,7 +16174,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H545" t="n">
         <v>3438</v>
@@ -16232,7 +16232,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H547" t="n">
         <v>550</v>
@@ -16290,7 +16290,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H549" t="n">
         <v>450</v>
@@ -16377,7 +16377,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G552" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H552" t="n">
         <v>1717</v>
@@ -16406,7 +16406,7 @@
         <v>7.25</v>
       </c>
       <c r="G553" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H553" t="n">
         <v>343</v>
@@ -16493,7 +16493,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G556" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H556" t="n">
         <v>670</v>
@@ -16522,7 +16522,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G557" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H557" t="n">
         <v>3189</v>
@@ -16580,7 +16580,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G559" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H559" t="n">
         <v>7637</v>
@@ -16609,7 +16609,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H560" t="n">
         <v>3012</v>
@@ -16638,7 +16638,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16725,7 +16725,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H564" t="n">
         <v>300</v>
@@ -16754,7 +16754,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -16870,7 +16870,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G569" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H569" t="n">
         <v>6050</v>
@@ -16899,7 +16899,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H570" t="n">
         <v>3670</v>
@@ -16928,7 +16928,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G571" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G573" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H573" t="n">
         <v>4179</v>
@@ -17015,7 +17015,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G574" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H574" t="n">
         <v>2117</v>
@@ -17044,7 +17044,7 @@
         <v>7.25</v>
       </c>
       <c r="G575" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H575" t="n">
         <v>6238</v>
@@ -17073,7 +17073,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G576" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H576" t="n">
         <v>3710</v>
@@ -17102,7 +17102,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H577" t="n">
         <v>2610</v>
@@ -17131,7 +17131,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -17247,7 +17247,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G582" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H582" t="n">
         <v>2138</v>
@@ -17276,7 +17276,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G583" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H583" t="n">
         <v>18938</v>
@@ -17363,7 +17363,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G586" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H586" t="n">
         <v>2734</v>
@@ -17392,7 +17392,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H587" t="n">
         <v>3257</v>
@@ -17479,7 +17479,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G590" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H590" t="n">
         <v>8364</v>
@@ -17508,7 +17508,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H591" t="n">
         <v>200</v>
@@ -17537,7 +17537,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H592" t="n">
         <v>3684</v>
@@ -17566,7 +17566,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H593" t="n">
         <v>5400</v>
@@ -17624,7 +17624,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G595" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H595" t="n">
         <v>3897</v>
@@ -17682,7 +17682,7 @@
         <v>6.5</v>
       </c>
       <c r="G597" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H597" t="n">
         <v>12670</v>
@@ -17711,7 +17711,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H598" t="n">
         <v>8965</v>
@@ -17740,7 +17740,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G599" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H599" t="n">
         <v>11436</v>
@@ -17885,7 +17885,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H604" t="n">
         <v>52602</v>
@@ -17914,7 +17914,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G605" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H605" t="n">
         <v>2051</v>
@@ -17972,7 +17972,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G607" t="n">
-        <v>5.86652088165283</v>
+        <v>5.86652040481567</v>
       </c>
       <c r="H607" t="n">
         <v>17462</v>
@@ -18001,7 +18001,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H608" t="n">
         <v>23741</v>
@@ -18030,7 +18030,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G609" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H609" t="n">
         <v>3523</v>
@@ -18233,7 +18233,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G616" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H616" t="n">
         <v>3231</v>
@@ -18262,7 +18262,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G618" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H618" t="n">
         <v>2032</v>
@@ -18320,7 +18320,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G619" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H619" t="n">
         <v>50</v>
@@ -18349,7 +18349,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H620" t="n">
         <v>7613</v>
@@ -18378,7 +18378,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H621" t="n">
         <v>2570</v>
@@ -18407,7 +18407,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G622" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H622" t="n">
         <v>1100</v>
@@ -18436,7 +18436,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H623" t="n">
         <v>3777</v>
@@ -18465,7 +18465,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G624" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H624" t="n">
         <v>5586</v>
@@ -18494,7 +18494,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G625" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H625" t="n">
         <v>3300</v>
@@ -18523,7 +18523,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G626" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H626" t="n">
         <v>2368</v>
@@ -18552,7 +18552,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G627" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H627" t="n">
         <v>2744</v>
@@ -18581,7 +18581,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G628" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H628" t="n">
         <v>1005</v>
@@ -18610,7 +18610,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G629" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H629" t="n">
         <v>1200</v>
@@ -18639,7 +18639,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H630" t="n">
         <v>1307</v>
@@ -18668,7 +18668,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G631" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H631" t="n">
         <v>2750</v>
@@ -18726,7 +18726,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.86652088165283</v>
+        <v>5.86652040481567</v>
       </c>
       <c r="H633" t="n">
         <v>5366</v>
@@ -18755,7 +18755,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G634" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H634" t="n">
         <v>2000</v>
@@ -18784,7 +18784,7 @@
         <v>6.5</v>
       </c>
       <c r="G635" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H635" t="n">
         <v>12636</v>
@@ -18813,7 +18813,7 @@
         <v>6.5</v>
       </c>
       <c r="G636" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H636" t="n">
         <v>4185</v>
@@ -18842,7 +18842,7 @@
         <v>6.5</v>
       </c>
       <c r="G637" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H637" t="n">
         <v>0</v>
@@ -18871,7 +18871,7 @@
         <v>6.5</v>
       </c>
       <c r="G638" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H638" t="n">
         <v>3450</v>
@@ -18900,7 +18900,7 @@
         <v>6.5</v>
       </c>
       <c r="G639" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H639" t="n">
         <v>0</v>
@@ -18929,7 +18929,7 @@
         <v>6.5</v>
       </c>
       <c r="G640" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H640" t="n">
         <v>1550</v>
@@ -18958,7 +18958,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G641" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H641" t="n">
         <v>1959</v>
@@ -18987,7 +18987,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H642" t="n">
         <v>2879</v>
@@ -19045,7 +19045,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>5.6443042755127</v>
+        <v>5.64430379867554</v>
       </c>
       <c r="H644" t="n">
         <v>5286</v>
@@ -19074,7 +19074,7 @@
         <v>6.25</v>
       </c>
       <c r="G645" t="n">
-        <v>5.55541706085205</v>
+        <v>5.55541753768921</v>
       </c>
       <c r="H645" t="n">
         <v>3525</v>
@@ -19103,7 +19103,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.6443042755127</v>
+        <v>5.64430379867554</v>
       </c>
       <c r="H646" t="n">
         <v>297</v>
@@ -19132,7 +19132,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H647" t="n">
         <v>262</v>
@@ -19161,7 +19161,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H648" t="n">
         <v>2986</v>
@@ -19190,7 +19190,7 @@
         <v>6.5</v>
       </c>
       <c r="G649" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H649" t="n">
         <v>6789</v>
@@ -19248,7 +19248,7 @@
         <v>6.5</v>
       </c>
       <c r="G651" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H651" t="n">
         <v>1008</v>
@@ -19277,7 +19277,7 @@
         <v>6.5</v>
       </c>
       <c r="G652" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H652" t="n">
         <v>11094</v>
@@ -19306,7 +19306,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G653" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H653" t="n">
         <v>4753</v>
@@ -19335,7 +19335,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G654" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H654" t="n">
         <v>1310</v>
@@ -19683,7 +19683,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G666" t="n">
-        <v>4.35544729232788</v>
+        <v>4.35544681549072</v>
       </c>
       <c r="H666" t="n">
         <v>11395</v>
@@ -19712,7 +19712,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>4.26656055450439</v>
+        <v>4.26656103134155</v>
       </c>
       <c r="H667" t="n">
         <v>8251</v>
@@ -19741,7 +19741,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>4.07100963592529</v>
+        <v>4.07101011276245</v>
       </c>
       <c r="H668" t="n">
         <v>934</v>
@@ -19799,7 +19799,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G670" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H670" t="n">
         <v>10643</v>
@@ -19828,7 +19828,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G671" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -19857,7 +19857,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G672" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G673" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G674" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H674" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G675" t="n">
-        <v>3.8221275806427</v>
+        <v>3.82212734222412</v>
       </c>
       <c r="H675" t="n">
         <v>2991</v>
@@ -19973,7 +19973,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G676" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H676" t="n">
         <v>2454</v>
@@ -20002,7 +20002,7 @@
         <v>4.5</v>
       </c>
       <c r="G677" t="n">
-        <v>3.99990057945251</v>
+        <v>3.99990081787109</v>
       </c>
       <c r="H677" t="n">
         <v>2379</v>
@@ -20031,7 +20031,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G678" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H678" t="n">
         <v>6410</v>
@@ -20089,7 +20089,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G680" t="n">
-        <v>3.8576819896698</v>
+        <v>3.85768222808838</v>
       </c>
       <c r="H680" t="n">
         <v>4718</v>
@@ -20147,7 +20147,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G682" t="n">
-        <v>3.75101804733276</v>
+        <v>3.75101757049561</v>
       </c>
       <c r="H682" t="n">
         <v>2412</v>
@@ -20176,7 +20176,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G683" t="n">
-        <v>3.64435362815857</v>
+        <v>3.64435386657715</v>
       </c>
       <c r="H683" t="n">
         <v>1800</v>
@@ -20205,7 +20205,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G684" t="n">
-        <v>3.68879747390747</v>
+        <v>3.68879723548889</v>
       </c>
       <c r="H684" t="n">
         <v>1402</v>
@@ -20234,7 +20234,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G685" t="n">
-        <v>3.80434989929199</v>
+        <v>3.80435013771057</v>
       </c>
       <c r="H685" t="n">
         <v>3900</v>
@@ -20263,7 +20263,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G686" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H686" t="n">
         <v>4888</v>
@@ -20321,7 +20321,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>3.8576819896698</v>
+        <v>3.85768222808838</v>
       </c>
       <c r="H688" t="n">
         <v>1215</v>
@@ -20350,7 +20350,7 @@
         <v>4.5</v>
       </c>
       <c r="G689" t="n">
-        <v>3.99990057945251</v>
+        <v>3.99990081787109</v>
       </c>
       <c r="H689" t="n">
         <v>1891</v>
@@ -20408,7 +20408,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G691" t="n">
-        <v>3.98212337493896</v>
+        <v>3.98212313652039</v>
       </c>
       <c r="H691" t="n">
         <v>9728</v>
@@ -20495,7 +20495,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G694" t="n">
-        <v>3.8576819896698</v>
+        <v>3.85768222808838</v>
       </c>
       <c r="H694" t="n">
         <v>6301</v>
@@ -20524,7 +20524,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H695" t="n">
         <v>4540</v>
@@ -20553,7 +20553,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H696" t="n">
         <v>470</v>
@@ -20611,7 +20611,7 @@
         <v>4.5</v>
       </c>
       <c r="G698" t="n">
-        <v>3.99990057945251</v>
+        <v>3.99990081787109</v>
       </c>
       <c r="H698" t="n">
         <v>1703</v>
@@ -20640,7 +20640,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>3.98212337493896</v>
+        <v>3.98212313652039</v>
       </c>
       <c r="H699" t="n">
         <v>13560</v>
@@ -20669,7 +20669,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G700" t="n">
-        <v>3.98212337493896</v>
+        <v>3.98212313652039</v>
       </c>
       <c r="H700" t="n">
         <v>6239</v>
@@ -20698,7 +20698,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G701" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H701" t="n">
         <v>11088</v>
@@ -20756,7 +20756,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>3.76879501342773</v>
+        <v>3.76879477500916</v>
       </c>
       <c r="H703" t="n">
         <v>6306</v>
@@ -20785,7 +20785,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G704" t="n">
-        <v>3.90212535858154</v>
+        <v>3.90212512016296</v>
       </c>
       <c r="H704" t="n">
         <v>1895</v>
@@ -20814,7 +20814,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G705" t="n">
-        <v>3.88434743881226</v>
+        <v>3.88434791564941</v>
       </c>
       <c r="H705" t="n">
         <v>6050</v>
@@ -20843,7 +20843,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G706" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H706" t="n">
         <v>1629</v>
@@ -20872,7 +20872,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>3.88434743881226</v>
+        <v>3.88434791564941</v>
       </c>
       <c r="H707" t="n">
         <v>1037</v>
@@ -20901,7 +20901,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G708" t="n">
-        <v>3.83101558685303</v>
+        <v>3.83101606369019</v>
       </c>
       <c r="H708" t="n">
         <v>6323</v>
@@ -20930,7 +20930,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>3.83101558685303</v>
+        <v>3.83101606369019</v>
       </c>
       <c r="H709" t="n">
         <v>2542</v>
@@ -20959,7 +20959,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>3.71546292304993</v>
+        <v>3.71546316146851</v>
       </c>
       <c r="H710" t="n">
         <v>8368</v>
@@ -20988,7 +20988,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G711" t="n">
-        <v>3.76879501342773</v>
+        <v>3.76879477500916</v>
       </c>
       <c r="H711" t="n">
         <v>5939</v>
@@ -21017,7 +21017,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G712" t="n">
-        <v>3.75101804733276</v>
+        <v>3.75101757049561</v>
       </c>
       <c r="H712" t="n">
         <v>2662</v>
@@ -21046,7 +21046,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G713" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H713" t="n">
         <v>1264</v>
@@ -21075,7 +21075,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G714" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H714" t="n">
         <v>0</v>
@@ -21133,7 +21133,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G716" t="n">
-        <v>3.80434989929199</v>
+        <v>3.80435013771057</v>
       </c>
       <c r="H716" t="n">
         <v>685</v>
@@ -21162,7 +21162,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>3.88434743881226</v>
+        <v>3.88434791564941</v>
       </c>
       <c r="H717" t="n">
         <v>3887</v>
@@ -21278,7 +21278,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>4.13323068618774</v>
+        <v>4.13323020935059</v>
       </c>
       <c r="H721" t="n">
         <v>12913</v>
@@ -21452,7 +21452,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G727" t="n">
-        <v>4.09767627716064</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H727" t="n">
         <v>30466</v>
@@ -21539,7 +21539,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>4.38185453414917</v>
+        <v>4.38185501098633</v>
       </c>
       <c r="H730" t="n">
         <v>61399</v>
@@ -21568,7 +21568,7 @@
         <v>4.75</v>
       </c>
       <c r="G731" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H731" t="n">
         <v>16376</v>
@@ -21655,7 +21655,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G734" t="n">
-        <v>4.38185453414917</v>
+        <v>4.38185501098633</v>
       </c>
       <c r="H734" t="n">
         <v>34375</v>
@@ -21684,7 +21684,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G735" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H735" t="n">
         <v>17125</v>
@@ -21713,7 +21713,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G736" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H736" t="n">
         <v>9606</v>
@@ -21742,7 +21742,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G737" t="n">
-        <v>4.40935564041138</v>
+        <v>4.40935611724854</v>
       </c>
       <c r="H737" t="n">
         <v>2683</v>
@@ -21771,7 +21771,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>4.37268781661987</v>
+        <v>4.37268733978271</v>
       </c>
       <c r="H738" t="n">
         <v>600</v>
@@ -21800,7 +21800,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>4.37268781661987</v>
+        <v>4.37268733978271</v>
       </c>
       <c r="H739" t="n">
         <v>680</v>
@@ -21829,7 +21829,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G740" t="n">
-        <v>4.32685232162476</v>
+        <v>4.3268518447876</v>
       </c>
       <c r="H740" t="n">
         <v>7403</v>
@@ -21916,7 +21916,7 @@
         <v>4.75</v>
       </c>
       <c r="G743" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H743" t="n">
         <v>607</v>
@@ -21945,7 +21945,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G744" t="n">
-        <v>4.32685232162476</v>
+        <v>4.3268518447876</v>
       </c>
       <c r="H744" t="n">
         <v>11032</v>
@@ -22032,7 +22032,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G747" t="n">
-        <v>4.23518180847168</v>
+        <v>4.23518133163452</v>
       </c>
       <c r="H747" t="n">
         <v>2630</v>
@@ -22061,7 +22061,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>4.23518180847168</v>
+        <v>4.23518133163452</v>
       </c>
       <c r="H748" t="n">
         <v>1000</v>
@@ -22177,7 +22177,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G752" t="n">
-        <v>4.18934679031372</v>
+        <v>4.18934631347656</v>
       </c>
       <c r="H752" t="n">
         <v>1350</v>
@@ -22380,7 +22380,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G759" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H759" t="n">
         <v>3488</v>
@@ -22467,7 +22467,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.18934679031372</v>
+        <v>4.18934631347656</v>
       </c>
       <c r="H762" t="n">
         <v>4900</v>
@@ -22641,7 +22641,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H768" t="n">
         <v>8119</v>
@@ -22902,7 +22902,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>4.21684789657593</v>
+        <v>4.21684741973877</v>
       </c>
       <c r="H777" t="n">
         <v>7930</v>
@@ -22931,7 +22931,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>4.08850860595703</v>
+        <v>4.08850908279419</v>
       </c>
       <c r="H778" t="n">
         <v>10894</v>
@@ -23105,7 +23105,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G784" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H784" t="n">
         <v>10522</v>
@@ -23163,7 +23163,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G786" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H786" t="n">
         <v>1030</v>
@@ -23192,7 +23192,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G787" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>4.07934188842773</v>
+        <v>4.07934141159058</v>
       </c>
       <c r="H788" t="n">
         <v>5464</v>
@@ -23250,7 +23250,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G789" t="n">
-        <v>4.07934188842773</v>
+        <v>4.07934141159058</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -23337,7 +23337,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>4.04267311096191</v>
+        <v>4.04267358779907</v>
       </c>
       <c r="H792" t="n">
         <v>1205</v>
@@ -23482,7 +23482,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G797" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H797" t="n">
         <v>2403</v>
@@ -23511,7 +23511,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G798" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H798" t="n">
         <v>1860</v>
@@ -23598,7 +23598,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>3.91433477401733</v>
+        <v>3.91433453559875</v>
       </c>
       <c r="H801" t="n">
         <v>1035</v>
@@ -23743,7 +23743,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.86849927902222</v>
+        <v>3.86849904060364</v>
       </c>
       <c r="H806" t="n">
         <v>3833</v>
@@ -23772,7 +23772,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G807" t="n">
-        <v>3.88683342933655</v>
+        <v>3.88683319091797</v>
       </c>
       <c r="H807" t="n">
         <v>13265</v>
@@ -23801,7 +23801,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G808" t="n">
-        <v>3.88683342933655</v>
+        <v>3.88683319091797</v>
       </c>
       <c r="H808" t="n">
         <v>12349</v>
@@ -23946,7 +23946,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G813" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H813" t="n">
         <v>11042</v>
@@ -24004,7 +24004,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>4.37268781661987</v>
+        <v>4.37268733978271</v>
       </c>
       <c r="H815" t="n">
         <v>4760</v>
@@ -24033,7 +24033,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G816" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H816" t="n">
         <v>7780</v>
@@ -24120,7 +24120,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G819" t="n">
-        <v>4.32685232162476</v>
+        <v>4.3268518447876</v>
       </c>
       <c r="H819" t="n">
         <v>785</v>
@@ -24178,7 +24178,7 @@
         <v>4.75</v>
       </c>
       <c r="G821" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H821" t="n">
         <v>6878</v>
@@ -24294,7 +24294,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G825" t="n">
-        <v>4.51936006546021</v>
+        <v>4.51936054229736</v>
       </c>
       <c r="H825" t="n">
         <v>1867</v>
@@ -24352,7 +24352,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>4.51019382476807</v>
+        <v>4.51019334793091</v>
       </c>
       <c r="H827" t="n">
         <v>10424</v>
@@ -24410,7 +24410,7 @@
         <v>4.75</v>
       </c>
       <c r="G829" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H829" t="n">
         <v>5800</v>
@@ -24468,7 +24468,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.04267311096191</v>
+        <v>4.04267358779907</v>
       </c>
       <c r="H831" t="n">
         <v>16333</v>
@@ -24555,7 +24555,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>3.94183611869812</v>
+        <v>3.94183588027954</v>
       </c>
       <c r="H834" t="n">
         <v>25951</v>
@@ -24642,7 +24642,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>4.21684789657593</v>
+        <v>4.21684741973877</v>
       </c>
       <c r="H837" t="n">
         <v>21835</v>
@@ -24729,7 +24729,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G840" t="n">
-        <v>4.18934679031372</v>
+        <v>4.18934631347656</v>
       </c>
       <c r="H840" t="n">
         <v>34559</v>
@@ -24758,7 +24758,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>4.23518180847168</v>
+        <v>4.23518133163452</v>
       </c>
       <c r="H841" t="n">
         <v>225</v>
@@ -24845,7 +24845,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G844" t="n">
-        <v>4.21684789657593</v>
+        <v>4.21684741973877</v>
       </c>
       <c r="H844" t="n">
         <v>16368</v>
@@ -25193,7 +25193,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>4.96854686737061</v>
+        <v>4.96854639053345</v>
       </c>
       <c r="H856" t="n">
         <v>13143</v>
@@ -25309,7 +25309,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>5.11521911621094</v>
+        <v>5.1152195930481</v>
       </c>
       <c r="H860" t="n">
         <v>16237</v>
@@ -25367,7 +25367,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G862" t="n">
-        <v>5.13355398178101</v>
+        <v>5.13355350494385</v>
       </c>
       <c r="H862" t="n">
         <v>13036</v>
@@ -25396,7 +25396,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G863" t="n">
-        <v>5.15188789367676</v>
+        <v>5.1518874168396</v>
       </c>
       <c r="H863" t="n">
         <v>7153</v>
@@ -25454,7 +25454,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>5.00521469116211</v>
+        <v>5.00521516799927</v>
       </c>
       <c r="H865" t="n">
         <v>3756</v>
@@ -25686,7 +25686,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G873" t="n">
-        <v>5.39023160934448</v>
+        <v>5.39023113250732</v>
       </c>
       <c r="H873" t="n">
         <v>31741</v>
@@ -25715,7 +25715,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G874" t="n">
-        <v>5.39023160934448</v>
+        <v>5.39023113250732</v>
       </c>
       <c r="H874" t="n">
         <v>13377</v>
@@ -25831,7 +25831,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G878" t="n">
-        <v>5.6102409362793</v>
+        <v>5.61024045944214</v>
       </c>
       <c r="H878" t="n">
         <v>24852</v>
@@ -25947,7 +25947,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G882" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H882" t="n">
         <v>8738</v>
@@ -25976,7 +25976,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>5.88525295257568</v>
+        <v>5.88525247573853</v>
       </c>
       <c r="H883" t="n">
         <v>11732</v>
@@ -26121,7 +26121,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>5.9402551651001</v>
+        <v>5.94025468826294</v>
       </c>
       <c r="H888" t="n">
         <v>7733</v>
@@ -26266,7 +26266,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G893" t="n">
-        <v>5.83025026321411</v>
+        <v>5.83025074005127</v>
       </c>
       <c r="H893" t="n">
         <v>46103</v>
@@ -26324,7 +26324,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>5.92192077636719</v>
+        <v>5.92192125320435</v>
       </c>
       <c r="H895" t="n">
         <v>1658</v>
@@ -26382,7 +26382,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>5.92192077636719</v>
+        <v>5.92192125320435</v>
       </c>
       <c r="H897" t="n">
         <v>3856</v>
@@ -26469,7 +26469,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>5.92192077636719</v>
+        <v>5.92192125320435</v>
       </c>
       <c r="H900" t="n">
         <v>19114</v>
@@ -26498,7 +26498,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H901" t="n">
         <v>5834</v>
@@ -26527,7 +26527,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H902" t="n">
         <v>4663</v>
@@ -26643,7 +26643,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G906" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H906" t="n">
         <v>7547</v>
@@ -26759,7 +26759,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G910" t="n">
-        <v>6.19693279266357</v>
+        <v>6.19693326950073</v>
       </c>
       <c r="H910" t="n">
         <v>32257</v>
@@ -26817,7 +26817,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>6.38027381896973</v>
+        <v>6.38027429580688</v>
       </c>
       <c r="H912" t="n">
         <v>24783</v>
@@ -26846,7 +26846,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G913" t="n">
-        <v>6.28860330581665</v>
+        <v>6.28860378265381</v>
       </c>
       <c r="H913" t="n">
         <v>13157</v>
@@ -26991,7 +26991,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>6.4719443321228</v>
+        <v>6.47194480895996</v>
       </c>
       <c r="H918" t="n">
         <v>6002</v>
@@ -27049,7 +27049,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G920" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H920" t="n">
         <v>2787</v>
@@ -27078,7 +27078,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H921" t="n">
         <v>4737</v>
@@ -27107,7 +27107,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G922" t="n">
-        <v>6.58194923400879</v>
+        <v>6.58194875717163</v>
       </c>
       <c r="H922" t="n">
         <v>5358</v>
@@ -27165,7 +27165,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G924" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H924" t="n">
         <v>4250</v>
@@ -27252,7 +27252,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G927" t="n">
-        <v>6.61861753463745</v>
+        <v>6.61861705780029</v>
       </c>
       <c r="H927" t="n">
         <v>9701</v>
@@ -27339,7 +27339,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>6.58194923400879</v>
+        <v>6.58194875717163</v>
       </c>
       <c r="H930" t="n">
         <v>1400</v>
@@ -27368,7 +27368,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G931" t="n">
-        <v>6.61861753463745</v>
+        <v>6.61861705780029</v>
       </c>
       <c r="H931" t="n">
         <v>4392</v>
@@ -27542,7 +27542,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G937" t="n">
-        <v>6.54528045654297</v>
+        <v>6.54528093338013</v>
       </c>
       <c r="H937" t="n">
         <v>11503</v>
@@ -27600,7 +27600,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G939" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H939" t="n">
         <v>14602</v>
@@ -27658,7 +27658,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>6.85696125030518</v>
+        <v>6.85696077346802</v>
       </c>
       <c r="H941" t="n">
         <v>21995</v>
@@ -27890,7 +27890,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H949" t="n">
         <v>6250</v>
@@ -28093,7 +28093,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G956" t="n">
-        <v>6.78362417221069</v>
+        <v>6.78362464904785</v>
       </c>
       <c r="H956" t="n">
         <v>5975</v>
@@ -68493,9 +68493,38 @@
         <v>2.47000002861023</v>
       </c>
       <c r="H2349" t="n">
-        <v>6495</v>
+        <v>6520</v>
       </c>
       <c r="I2349" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2350" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2350" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="D2350" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="E2350" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="F2350" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="G2350" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="H2350" t="n">
+        <v>9241</v>
+      </c>
+      <c r="I2350" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2" t="n">
-        <v>9.40187931060791</v>
+        <v>9.40188026428223</v>
       </c>
       <c r="H2" t="n">
         <v>56600</v>
@@ -514,7 +514,7 @@
         <v>11.25</v>
       </c>
       <c r="G5" t="n">
-        <v>9.45229244232178</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H5" t="n">
         <v>13000</v>
@@ -688,7 +688,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G11" t="n">
-        <v>9.73796272277832</v>
+        <v>9.737961769104</v>
       </c>
       <c r="H11" t="n">
         <v>7000</v>
@@ -717,7 +717,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G12" t="n">
-        <v>9.67074584960938</v>
+        <v>9.67074680328369</v>
       </c>
       <c r="H12" t="n">
         <v>1600</v>
@@ -833,7 +833,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G16" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H16" t="n">
         <v>11400</v>
@@ -862,7 +862,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>9.52791213989258</v>
+        <v>9.52791118621826</v>
       </c>
       <c r="H17" t="n">
         <v>248200</v>
@@ -891,7 +891,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G18" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H18" t="n">
         <v>2600</v>
@@ -1036,7 +1036,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>9.5363130569458</v>
+        <v>9.53631401062012</v>
       </c>
       <c r="H23" t="n">
         <v>800</v>
@@ -1065,7 +1065,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G24" t="n">
-        <v>9.40187931060791</v>
+        <v>9.40188026428223</v>
       </c>
       <c r="H24" t="n">
         <v>600</v>
@@ -1094,7 +1094,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H25" t="n">
         <v>1600</v>
@@ -1123,7 +1123,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>11.25</v>
       </c>
       <c r="G28" t="n">
-        <v>9.45229244232178</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H28" t="n">
         <v>3600</v>
@@ -1239,7 +1239,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G30" t="n">
-        <v>9.51950836181641</v>
+        <v>9.51950931549072</v>
       </c>
       <c r="H30" t="n">
         <v>2600</v>
@@ -1268,7 +1268,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G31" t="n">
-        <v>9.52791213989258</v>
+        <v>9.52791118621826</v>
       </c>
       <c r="H31" t="n">
         <v>4600</v>
@@ -1297,7 +1297,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H32" t="n">
         <v>1600</v>
@@ -1326,7 +1326,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G33" t="n">
-        <v>9.56992149353027</v>
+        <v>9.56992244720459</v>
       </c>
       <c r="H33" t="n">
         <v>1800</v>
@@ -1355,7 +1355,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G34" t="n">
-        <v>9.52791213989258</v>
+        <v>9.52791118621826</v>
       </c>
       <c r="H34" t="n">
         <v>14200</v>
@@ -1384,7 +1384,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H35" t="n">
         <v>800</v>
@@ -1413,7 +1413,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H36" t="n">
         <v>400</v>
@@ -1442,7 +1442,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G37" t="n">
-        <v>9.56992149353027</v>
+        <v>9.56992244720459</v>
       </c>
       <c r="H37" t="n">
         <v>3000</v>
@@ -1471,7 +1471,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>9.5363130569458</v>
+        <v>9.53631401062012</v>
       </c>
       <c r="H38" t="n">
         <v>2400</v>
@@ -1529,7 +1529,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G40" t="n">
-        <v>9.73796272277832</v>
+        <v>9.737961769104</v>
       </c>
       <c r="H40" t="n">
         <v>21400</v>
@@ -1558,7 +1558,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G41" t="n">
-        <v>9.73796272277832</v>
+        <v>9.737961769104</v>
       </c>
       <c r="H41" t="n">
         <v>1400</v>
@@ -1674,7 +1674,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G45" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198333740234</v>
       </c>
       <c r="H45" t="n">
         <v>14000</v>
@@ -1819,7 +1819,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G50" t="n">
-        <v>9.76316833496094</v>
+        <v>9.76316738128662</v>
       </c>
       <c r="H50" t="n">
         <v>6600</v>
@@ -1848,7 +1848,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G51" t="n">
-        <v>10.1832704544067</v>
+        <v>10.1832695007324</v>
       </c>
       <c r="H51" t="n">
         <v>127800</v>
@@ -1877,7 +1877,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440391540527</v>
       </c>
       <c r="H52" t="n">
         <v>97800</v>
@@ -1906,7 +1906,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G53" t="n">
-        <v>9.77997303009033</v>
+        <v>9.77997207641602</v>
       </c>
       <c r="H53" t="n">
         <v>4200</v>
@@ -1935,7 +1935,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G54" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H54" t="n">
         <v>30200</v>
@@ -1993,7 +1993,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440391540527</v>
       </c>
       <c r="H56" t="n">
         <v>20400</v>
@@ -2022,7 +2022,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G57" t="n">
-        <v>9.9564151763916</v>
+        <v>9.95641613006592</v>
       </c>
       <c r="H57" t="n">
         <v>35400</v>
@@ -2051,7 +2051,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>9.9564151763916</v>
+        <v>9.95641613006592</v>
       </c>
       <c r="H58" t="n">
         <v>25000</v>
@@ -2109,7 +2109,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G60" t="n">
-        <v>10.0320339202881</v>
+        <v>10.0320320129395</v>
       </c>
       <c r="H60" t="n">
         <v>10600</v>
@@ -2138,7 +2138,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G61" t="n">
-        <v>10.0320339202881</v>
+        <v>10.0320320129395</v>
       </c>
       <c r="H61" t="n">
         <v>11200</v>
@@ -2254,7 +2254,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198333740234</v>
       </c>
       <c r="H65" t="n">
         <v>8600</v>
@@ -2312,7 +2312,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G67" t="n">
-        <v>9.93960952758789</v>
+        <v>9.93961143493652</v>
       </c>
       <c r="H67" t="n">
         <v>18400</v>
@@ -2370,7 +2370,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>9.9564151763916</v>
+        <v>9.95641613006592</v>
       </c>
       <c r="H69" t="n">
         <v>3200</v>
@@ -2399,7 +2399,7 @@
         <v>11.75</v>
       </c>
       <c r="G70" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H70" t="n">
         <v>5200</v>
@@ -2457,7 +2457,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440391540527</v>
       </c>
       <c r="H72" t="n">
         <v>73200</v>
@@ -2515,7 +2515,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G74" t="n">
-        <v>10.0656414031982</v>
+        <v>10.0656404495239</v>
       </c>
       <c r="H74" t="n">
         <v>7000</v>
@@ -2544,7 +2544,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>9.99842548370361</v>
+        <v>9.9984245300293</v>
       </c>
       <c r="H75" t="n">
         <v>26800</v>
@@ -2602,7 +2602,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G77" t="n">
-        <v>10.0320339202881</v>
+        <v>10.0320320129395</v>
       </c>
       <c r="H77" t="n">
         <v>58000</v>
@@ -2631,7 +2631,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>9.99842548370361</v>
+        <v>9.9984245300293</v>
       </c>
       <c r="H78" t="n">
         <v>14600</v>
@@ -2776,7 +2776,7 @@
         <v>11.75</v>
       </c>
       <c r="G83" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H83" t="n">
         <v>13000</v>
@@ -2805,7 +2805,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440391540527</v>
       </c>
       <c r="H84" t="n">
         <v>6200</v>
@@ -2834,7 +2834,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G85" t="n">
-        <v>9.90600204467773</v>
+        <v>9.90600299835205</v>
       </c>
       <c r="H85" t="n">
         <v>4200</v>
@@ -2863,7 +2863,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440391540527</v>
       </c>
       <c r="H86" t="n">
         <v>5400</v>
@@ -2921,7 +2921,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G88" t="n">
-        <v>9.90600204467773</v>
+        <v>9.90600299835205</v>
       </c>
       <c r="H88" t="n">
         <v>600</v>
@@ -2950,7 +2950,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H89" t="n">
         <v>22400</v>
@@ -2979,7 +2979,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H90" t="n">
         <v>2000</v>
@@ -3008,7 +3008,7 @@
         <v>11.75</v>
       </c>
       <c r="G91" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H91" t="n">
         <v>1000</v>
@@ -3037,7 +3037,7 @@
         <v>11.75</v>
       </c>
       <c r="G92" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H92" t="n">
         <v>3000</v>
@@ -3066,7 +3066,7 @@
         <v>11.75</v>
       </c>
       <c r="G93" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H93" t="n">
         <v>2600</v>
@@ -3095,7 +3095,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440391540527</v>
       </c>
       <c r="H94" t="n">
         <v>6000</v>
@@ -3124,7 +3124,7 @@
         <v>11.75</v>
       </c>
       <c r="G95" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H95" t="n">
         <v>7800</v>
@@ -3153,7 +3153,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H96" t="n">
         <v>2600</v>
@@ -3211,7 +3211,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G98" t="n">
-        <v>9.98162174224854</v>
+        <v>9.98162078857422</v>
       </c>
       <c r="H98" t="n">
         <v>13400</v>
@@ -3240,7 +3240,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G99" t="n">
-        <v>9.97321891784668</v>
+        <v>9.973219871521</v>
       </c>
       <c r="H99" t="n">
         <v>7400</v>
@@ -3327,7 +3327,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G102" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198333740234</v>
       </c>
       <c r="H102" t="n">
         <v>8200</v>
@@ -3356,7 +3356,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G103" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198333740234</v>
       </c>
       <c r="H103" t="n">
         <v>600</v>
@@ -3385,7 +3385,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G104" t="n">
-        <v>9.73796272277832</v>
+        <v>9.737961769104</v>
       </c>
       <c r="H104" t="n">
         <v>1800</v>
@@ -3414,7 +3414,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G105" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H105" t="n">
         <v>6400</v>
@@ -3443,7 +3443,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G106" t="n">
-        <v>9.62873554229736</v>
+        <v>9.62873458862305</v>
       </c>
       <c r="H106" t="n">
         <v>25400</v>
@@ -3472,7 +3472,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G107" t="n">
-        <v>9.62873554229736</v>
+        <v>9.62873458862305</v>
       </c>
       <c r="H107" t="n">
         <v>11600</v>
@@ -3617,7 +3617,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>9.5363130569458</v>
+        <v>9.53631401062012</v>
       </c>
       <c r="H112" t="n">
         <v>800</v>
@@ -3762,7 +3762,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H117" t="n">
         <v>16400</v>
@@ -3791,7 +3791,7 @@
         <v>11.75</v>
       </c>
       <c r="G118" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H118" t="n">
         <v>12000</v>
@@ -3820,7 +3820,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H119" t="n">
         <v>5400</v>
@@ -3878,7 +3878,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H121" t="n">
         <v>6200</v>
@@ -3907,7 +3907,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H122" t="n">
         <v>14000</v>
@@ -4052,7 +4052,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H127" t="n">
         <v>39200</v>
@@ -4139,7 +4139,7 @@
         <v>11.75</v>
       </c>
       <c r="G130" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H130" t="n">
         <v>3400</v>
@@ -4168,7 +4168,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H131" t="n">
         <v>5600</v>
@@ -4284,7 +4284,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H135" t="n">
         <v>5600</v>
@@ -4429,7 +4429,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H140" t="n">
         <v>9000</v>
@@ -4458,7 +4458,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H141" t="n">
         <v>1600</v>
@@ -4487,7 +4487,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H142" t="n">
         <v>12000</v>
@@ -4603,7 +4603,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H146" t="n">
         <v>2600</v>
@@ -4632,7 +4632,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H149" t="n">
         <v>5600</v>
@@ -4719,7 +4719,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G155" t="n">
-        <v>9.5363130569458</v>
+        <v>9.53631401062012</v>
       </c>
       <c r="H155" t="n">
         <v>27200</v>
@@ -4922,7 +4922,7 @@
         <v>11.25</v>
       </c>
       <c r="G157" t="n">
-        <v>9.45229244232178</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H157" t="n">
         <v>18800</v>
@@ -4980,7 +4980,7 @@
         <v>11</v>
       </c>
       <c r="G159" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H159" t="n">
         <v>14600</v>
@@ -5038,7 +5038,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G161" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H161" t="n">
         <v>5600</v>
@@ -5067,7 +5067,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H162" t="n">
         <v>6400</v>
@@ -5096,7 +5096,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>11</v>
       </c>
       <c r="G164" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H164" t="n">
         <v>18800</v>
@@ -5154,7 +5154,7 @@
         <v>11</v>
       </c>
       <c r="G165" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>11</v>
       </c>
       <c r="G166" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H166" t="n">
         <v>400</v>
@@ -5241,7 +5241,7 @@
         <v>11</v>
       </c>
       <c r="G168" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H168" t="n">
         <v>1200</v>
@@ -5270,7 +5270,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>9.28425216674805</v>
+        <v>9.28425312042236</v>
       </c>
       <c r="H169" t="n">
         <v>200</v>
@@ -5299,7 +5299,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G170" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H170" t="n">
         <v>1000</v>
@@ -5328,7 +5328,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G171" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H171" t="n">
         <v>2400</v>
@@ -5357,7 +5357,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H172" t="n">
         <v>35400</v>
@@ -5415,7 +5415,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H174" t="n">
         <v>33600</v>
@@ -5444,7 +5444,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H175" t="n">
         <v>1000</v>
@@ -5473,7 +5473,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G176" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H176" t="n">
         <v>18400</v>
@@ -5502,7 +5502,7 @@
         <v>11</v>
       </c>
       <c r="G177" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H177" t="n">
         <v>5200</v>
@@ -5560,7 +5560,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G179" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H179" t="n">
         <v>4000</v>
@@ -5589,7 +5589,7 @@
         <v>11.25</v>
       </c>
       <c r="G180" t="n">
-        <v>9.45229244232178</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H180" t="n">
         <v>12000</v>
@@ -5618,7 +5618,7 @@
         <v>11.25</v>
       </c>
       <c r="G181" t="n">
-        <v>9.45229244232178</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>11</v>
       </c>
       <c r="G182" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H182" t="n">
         <v>10000</v>
@@ -5676,7 +5676,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>9.15822124481201</v>
+        <v>9.15822219848633</v>
       </c>
       <c r="H183" t="n">
         <v>13600</v>
@@ -5821,7 +5821,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>8.9901819229126</v>
+        <v>8.99018096923828</v>
       </c>
       <c r="H188" t="n">
         <v>5800</v>
@@ -5879,7 +5879,7 @@
         <v>10.75</v>
       </c>
       <c r="G190" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H190" t="n">
         <v>400</v>
@@ -5966,7 +5966,7 @@
         <v>10.75</v>
       </c>
       <c r="G193" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H193" t="n">
         <v>400</v>
@@ -5995,7 +5995,7 @@
         <v>10.75</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H194" t="n">
         <v>600</v>
@@ -6024,7 +6024,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>8.9901819229126</v>
+        <v>8.99018096923828</v>
       </c>
       <c r="H195" t="n">
         <v>200</v>
@@ -6053,7 +6053,7 @@
         <v>10.75</v>
       </c>
       <c r="G196" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H196" t="n">
         <v>10200</v>
@@ -6082,7 +6082,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>9.15822124481201</v>
+        <v>9.15822219848633</v>
       </c>
       <c r="H197" t="n">
         <v>1000</v>
@@ -6111,7 +6111,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>9.15822124481201</v>
+        <v>9.15822219848633</v>
       </c>
       <c r="H198" t="n">
         <v>36800</v>
@@ -6169,7 +6169,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>9.15822124481201</v>
+        <v>9.15822219848633</v>
       </c>
       <c r="H200" t="n">
         <v>200</v>
@@ -6401,7 +6401,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>9.33020687103271</v>
+        <v>9.33020782470703</v>
       </c>
       <c r="H208" t="n">
         <v>20200</v>
@@ -6488,7 +6488,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>9.33020687103271</v>
+        <v>9.33020782470703</v>
       </c>
       <c r="H211" t="n">
         <v>1000</v>
@@ -6604,7 +6604,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>9.11522483825684</v>
+        <v>9.11522579193115</v>
       </c>
       <c r="H215" t="n">
         <v>18200</v>
@@ -6633,7 +6633,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>8.98623752593994</v>
+        <v>8.98623657226562</v>
       </c>
       <c r="H216" t="n">
         <v>7000</v>
@@ -6662,7 +6662,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G217" t="n">
-        <v>8.72825717926025</v>
+        <v>8.72825813293457</v>
       </c>
       <c r="H217" t="n">
         <v>31200</v>
@@ -6720,7 +6720,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H219" t="n">
         <v>10600</v>
@@ -6749,7 +6749,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H220" t="n">
         <v>7600</v>
@@ -6807,7 +6807,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G222" t="n">
-        <v>9.07222843170166</v>
+        <v>9.07223033905029</v>
       </c>
       <c r="H222" t="n">
         <v>8600</v>
@@ -6836,7 +6836,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G223" t="n">
-        <v>8.90024375915527</v>
+        <v>8.90024471282959</v>
       </c>
       <c r="H223" t="n">
         <v>20400</v>
@@ -6865,7 +6865,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H224" t="n">
         <v>3000</v>
@@ -6894,7 +6894,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G225" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>8.90024375915527</v>
+        <v>8.90024471282959</v>
       </c>
       <c r="H226" t="n">
         <v>1200</v>
@@ -6952,7 +6952,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>8.98623752593994</v>
+        <v>8.98623657226562</v>
       </c>
       <c r="H227" t="n">
         <v>2800</v>
@@ -6981,7 +6981,7 @@
         <v>10.5</v>
       </c>
       <c r="G228" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H228" t="n">
         <v>12000</v>
@@ -7039,7 +7039,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>9.11522483825684</v>
+        <v>9.11522579193115</v>
       </c>
       <c r="H230" t="n">
         <v>64400</v>
@@ -7068,7 +7068,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>9.11522483825684</v>
+        <v>9.11522579193115</v>
       </c>
       <c r="H231" t="n">
         <v>5000</v>
@@ -7126,7 +7126,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>9.33020687103271</v>
+        <v>9.33020782470703</v>
       </c>
       <c r="H233" t="n">
         <v>11800</v>
@@ -7155,7 +7155,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G234" t="n">
-        <v>9.11522483825684</v>
+        <v>9.11522579193115</v>
       </c>
       <c r="H234" t="n">
         <v>6000</v>
@@ -7271,7 +7271,7 @@
         <v>10.5</v>
       </c>
       <c r="G238" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H238" t="n">
         <v>3400</v>
@@ -7474,7 +7474,7 @@
         <v>11</v>
       </c>
       <c r="G245" t="n">
-        <v>9.45919704437256</v>
+        <v>9.45919609069824</v>
       </c>
       <c r="H245" t="n">
         <v>7000</v>
@@ -7503,7 +7503,7 @@
         <v>11</v>
       </c>
       <c r="G246" t="n">
-        <v>9.45919704437256</v>
+        <v>9.45919609069824</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>10.5</v>
       </c>
       <c r="G255" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H255" t="n">
         <v>1000</v>
@@ -7793,7 +7793,7 @@
         <v>10.5</v>
       </c>
       <c r="G256" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>10.5</v>
       </c>
       <c r="G257" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H257" t="n">
         <v>400</v>
@@ -7851,7 +7851,7 @@
         <v>10.5</v>
       </c>
       <c r="G258" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H259" t="n">
         <v>200</v>
@@ -7909,7 +7909,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H261" t="n">
         <v>800</v>
@@ -7967,7 +7967,7 @@
         <v>10.5</v>
       </c>
       <c r="G262" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H262" t="n">
         <v>800</v>
@@ -8025,7 +8025,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>9.07222843170166</v>
+        <v>9.07223033905029</v>
       </c>
       <c r="H264" t="n">
         <v>8000</v>
@@ -8112,7 +8112,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H267" t="n">
         <v>8000</v>
@@ -8141,7 +8141,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G268" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H268" t="n">
         <v>2200</v>
@@ -8170,7 +8170,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H269" t="n">
         <v>400</v>
@@ -8228,7 +8228,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>8.49607849121094</v>
+        <v>8.49607753753662</v>
       </c>
       <c r="H271" t="n">
         <v>9400</v>
@@ -8257,7 +8257,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G272" t="n">
-        <v>8.28969573974609</v>
+        <v>8.28969669342041</v>
       </c>
       <c r="H272" t="n">
         <v>9600</v>
@@ -8286,7 +8286,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G273" t="n">
-        <v>8.28969573974609</v>
+        <v>8.28969669342041</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>8.3412914276123</v>
+        <v>8.34129047393799</v>
       </c>
       <c r="H274" t="n">
         <v>4800</v>
@@ -8576,7 +8576,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>8.72825717926025</v>
+        <v>8.72825813293457</v>
       </c>
       <c r="H283" t="n">
         <v>5000</v>
@@ -8605,7 +8605,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>8.72825717926025</v>
+        <v>8.72825813293457</v>
       </c>
       <c r="H284" t="n">
         <v>1000</v>
@@ -8663,7 +8663,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>8.3412914276123</v>
+        <v>8.34129047393799</v>
       </c>
       <c r="H286" t="n">
         <v>10600</v>
@@ -8692,7 +8692,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>8.3412914276123</v>
+        <v>8.34129047393799</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G291" t="n">
-        <v>8.35849094390869</v>
+        <v>8.35848999023438</v>
       </c>
       <c r="H291" t="n">
         <v>6200</v>
@@ -8837,7 +8837,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G292" t="n">
-        <v>8.41008472442627</v>
+        <v>8.4100866317749</v>
       </c>
       <c r="H292" t="n">
         <v>3000</v>
@@ -8866,7 +8866,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G293" t="n">
-        <v>8.41008472442627</v>
+        <v>8.4100866317749</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -9156,7 +9156,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G303" t="n">
-        <v>8.53047561645508</v>
+        <v>8.53047466278076</v>
       </c>
       <c r="H303" t="n">
         <v>2000</v>
@@ -9214,7 +9214,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>8.3412914276123</v>
+        <v>8.34129047393799</v>
       </c>
       <c r="H305" t="n">
         <v>400</v>
@@ -9272,7 +9272,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G307" t="n">
-        <v>8.03171825408936</v>
+        <v>8.03171730041504</v>
       </c>
       <c r="H307" t="n">
         <v>2000</v>
@@ -9330,7 +9330,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G309" t="n">
-        <v>8.03171825408936</v>
+        <v>8.03171730041504</v>
       </c>
       <c r="H309" t="n">
         <v>600</v>
@@ -9359,7 +9359,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G310" t="n">
-        <v>7.87693071365356</v>
+        <v>7.87693023681641</v>
       </c>
       <c r="H310" t="n">
         <v>200</v>
@@ -9388,7 +9388,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>7.87693071365356</v>
+        <v>7.87693023681641</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>7.82533597946167</v>
+        <v>7.82533502578735</v>
       </c>
       <c r="H312" t="n">
         <v>1200</v>
@@ -9475,7 +9475,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H314" t="n">
         <v>23200</v>
@@ -9504,7 +9504,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H315" t="n">
         <v>14000</v>
@@ -9533,7 +9533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H317" t="n">
         <v>4200</v>
@@ -9591,7 +9591,7 @@
         <v>8.5</v>
       </c>
       <c r="G318" t="n">
-        <v>7.30937957763672</v>
+        <v>7.30937814712524</v>
       </c>
       <c r="H318" t="n">
         <v>1600</v>
@@ -9620,7 +9620,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G319" t="n">
-        <v>7.36097526550293</v>
+        <v>7.36097478866577</v>
       </c>
       <c r="H319" t="n">
         <v>2400</v>
@@ -9649,7 +9649,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G320" t="n">
-        <v>7.32657814025879</v>
+        <v>7.32657766342163</v>
       </c>
       <c r="H320" t="n">
         <v>400</v>
@@ -9678,7 +9678,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G321" t="n">
-        <v>7.32657814025879</v>
+        <v>7.32657766342163</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G322" t="n">
-        <v>7.18898916244507</v>
+        <v>7.18898868560791</v>
       </c>
       <c r="H322" t="n">
         <v>1400</v>
@@ -9736,7 +9736,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G323" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H323" t="n">
         <v>800</v>
@@ -9852,7 +9852,7 @@
         <v>9</v>
       </c>
       <c r="G327" t="n">
-        <v>7.73934316635132</v>
+        <v>7.73934268951416</v>
       </c>
       <c r="H327" t="n">
         <v>3600</v>
@@ -9881,7 +9881,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G328" t="n">
-        <v>7.82533597946167</v>
+        <v>7.82533502578735</v>
       </c>
       <c r="H328" t="n">
         <v>600</v>
@@ -9910,7 +9910,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G329" t="n">
-        <v>7.65334987640381</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H329" t="n">
         <v>600</v>
@@ -9939,7 +9939,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>7.48136472702026</v>
+        <v>7.48136425018311</v>
       </c>
       <c r="H330" t="n">
         <v>800</v>
@@ -10055,7 +10055,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>7.65334987640381</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H334" t="n">
         <v>800</v>
@@ -10084,7 +10084,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G335" t="n">
-        <v>7.65334987640381</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G336" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H336" t="n">
         <v>1000</v>
@@ -10142,7 +10142,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>7.41256999969482</v>
+        <v>7.41256952285767</v>
       </c>
       <c r="H337" t="n">
         <v>3600</v>
@@ -10171,7 +10171,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G338" t="n">
-        <v>7.53296041488647</v>
+        <v>7.53295993804932</v>
       </c>
       <c r="H338" t="n">
         <v>200</v>
@@ -10200,7 +10200,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H339" t="n">
         <v>400</v>
@@ -10258,7 +10258,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G341" t="n">
-        <v>7.13739347457886</v>
+        <v>7.13739395141602</v>
       </c>
       <c r="H341" t="n">
         <v>7000</v>
@@ -10316,7 +10316,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G343" t="n">
-        <v>7.06859970092773</v>
+        <v>7.06859922409058</v>
       </c>
       <c r="H343" t="n">
         <v>5200</v>
@@ -10374,7 +10374,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G345" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H345" t="n">
         <v>5400</v>
@@ -10519,7 +10519,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G350" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H350" t="n">
         <v>18548</v>
@@ -10548,7 +10548,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G351" t="n">
-        <v>6.94820928573608</v>
+        <v>6.94820976257324</v>
       </c>
       <c r="H351" t="n">
         <v>3182</v>
@@ -10577,7 +10577,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>6.91381216049194</v>
+        <v>6.9138126373291</v>
       </c>
       <c r="H352" t="n">
         <v>4342</v>
@@ -10606,7 +10606,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G353" t="n">
-        <v>6.70743083953857</v>
+        <v>6.70743036270142</v>
       </c>
       <c r="H353" t="n">
         <v>6730</v>
@@ -10664,7 +10664,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>6.94820928573608</v>
+        <v>6.94820976257324</v>
       </c>
       <c r="H355" t="n">
         <v>8049</v>
@@ -10780,7 +10780,7 @@
         <v>8</v>
       </c>
       <c r="G359" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H359" t="n">
         <v>140</v>
@@ -10867,7 +10867,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H362" t="n">
         <v>3100</v>
@@ -10954,7 +10954,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G365" t="n">
-        <v>6.79342317581177</v>
+        <v>6.79342269897461</v>
       </c>
       <c r="H365" t="n">
         <v>830</v>
@@ -11012,7 +11012,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G367" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260688781738</v>
       </c>
       <c r="H367" t="n">
         <v>3300</v>
@@ -11041,7 +11041,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H368" t="n">
         <v>200</v>
@@ -11070,7 +11070,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G369" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260688781738</v>
       </c>
       <c r="H369" t="n">
         <v>472</v>
@@ -11099,7 +11099,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260688781738</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G371" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260688781738</v>
       </c>
       <c r="H371" t="n">
         <v>1981</v>
@@ -11157,7 +11157,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>7.13739347457886</v>
+        <v>7.13739395141602</v>
       </c>
       <c r="H372" t="n">
         <v>2867</v>
@@ -11215,7 +11215,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G374" t="n">
-        <v>6.75902557373047</v>
+        <v>6.75902652740479</v>
       </c>
       <c r="H374" t="n">
         <v>25405</v>
@@ -11244,7 +11244,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G375" t="n">
-        <v>6.79342317581177</v>
+        <v>6.79342269897461</v>
       </c>
       <c r="H375" t="n">
         <v>950</v>
@@ -11302,7 +11302,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>6.84501886367798</v>
+        <v>6.84501838684082</v>
       </c>
       <c r="H377" t="n">
         <v>2353</v>
@@ -11331,7 +11331,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>6.84501886367798</v>
+        <v>6.84501838684082</v>
       </c>
       <c r="H378" t="n">
         <v>4149</v>
@@ -11418,7 +11418,7 @@
         <v>8</v>
       </c>
       <c r="G381" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H381" t="n">
         <v>1532</v>
@@ -11447,7 +11447,7 @@
         <v>8</v>
       </c>
       <c r="G382" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H382" t="n">
         <v>291</v>
@@ -11476,7 +11476,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G383" t="n">
-        <v>6.93101167678833</v>
+        <v>6.93101119995117</v>
       </c>
       <c r="H383" t="n">
         <v>4605</v>
@@ -11505,7 +11505,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>6.94820928573608</v>
+        <v>6.94820976257324</v>
       </c>
       <c r="H384" t="n">
         <v>124</v>
@@ -11650,7 +11650,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>6.91381216049194</v>
+        <v>6.9138126373291</v>
       </c>
       <c r="H389" t="n">
         <v>7543</v>
@@ -11679,7 +11679,7 @@
         <v>8</v>
       </c>
       <c r="G390" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H390" t="n">
         <v>7347</v>
@@ -11737,7 +11737,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>6.84501886367798</v>
+        <v>6.84501838684082</v>
       </c>
       <c r="H392" t="n">
         <v>2665</v>
@@ -11766,7 +11766,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G393" t="n">
-        <v>6.69023180007935</v>
+        <v>6.69023132324219</v>
       </c>
       <c r="H393" t="n">
         <v>24134</v>
@@ -11795,7 +11795,7 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H394" t="n">
         <v>1786</v>
@@ -11853,7 +11853,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>6.94820928573608</v>
+        <v>6.94820976257324</v>
       </c>
       <c r="H396" t="n">
         <v>1510</v>
@@ -11882,7 +11882,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>6.94820928573608</v>
+        <v>6.94820976257324</v>
       </c>
       <c r="H397" t="n">
         <v>4250</v>
@@ -11911,7 +11911,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>6.93101167678833</v>
+        <v>6.93101119995117</v>
       </c>
       <c r="H398" t="n">
         <v>2460</v>
@@ -12027,7 +12027,7 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H402" t="n">
         <v>6710</v>
@@ -12056,7 +12056,7 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H403" t="n">
         <v>2710</v>
@@ -12085,7 +12085,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>6.79342317581177</v>
+        <v>6.79342269897461</v>
       </c>
       <c r="H404" t="n">
         <v>57</v>
@@ -12114,7 +12114,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G405" t="n">
-        <v>6.75902557373047</v>
+        <v>6.75902652740479</v>
       </c>
       <c r="H405" t="n">
         <v>3290</v>
@@ -12143,7 +12143,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G406" t="n">
-        <v>6.70743083953857</v>
+        <v>6.70743036270142</v>
       </c>
       <c r="H406" t="n">
         <v>4994</v>
@@ -12172,7 +12172,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>6.79342317581177</v>
+        <v>6.79342269897461</v>
       </c>
       <c r="H407" t="n">
         <v>20699</v>
@@ -12259,7 +12259,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G410" t="n">
-        <v>7.46416664123535</v>
+        <v>7.46416616439819</v>
       </c>
       <c r="H410" t="n">
         <v>32960</v>
@@ -12288,7 +12288,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G411" t="n">
-        <v>7.53296041488647</v>
+        <v>7.53295993804932</v>
       </c>
       <c r="H411" t="n">
         <v>7212</v>
@@ -12317,7 +12317,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G412" t="n">
-        <v>7.48136472702026</v>
+        <v>7.48136425018311</v>
       </c>
       <c r="H412" t="n">
         <v>4587</v>
@@ -12346,7 +12346,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.65334987640381</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H413" t="n">
         <v>3920</v>
@@ -12404,7 +12404,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G415" t="n">
-        <v>7.61895227432251</v>
+        <v>7.61895179748535</v>
       </c>
       <c r="H415" t="n">
         <v>5660</v>
@@ -12462,7 +12462,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G417" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H417" t="n">
         <v>1940</v>
@@ -12491,7 +12491,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G418" t="n">
-        <v>7.53296041488647</v>
+        <v>7.53295993804932</v>
       </c>
       <c r="H418" t="n">
         <v>2536</v>
@@ -12520,7 +12520,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G419" t="n">
-        <v>7.41256999969482</v>
+        <v>7.41256952285767</v>
       </c>
       <c r="H419" t="n">
         <v>8008</v>
@@ -12549,7 +12549,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>7.34377574920654</v>
+        <v>7.34377670288086</v>
       </c>
       <c r="H420" t="n">
         <v>4725</v>
@@ -12578,7 +12578,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>7.34377574920654</v>
+        <v>7.34377670288086</v>
       </c>
       <c r="H421" t="n">
         <v>1620</v>
@@ -12607,7 +12607,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G422" t="n">
-        <v>7.36097526550293</v>
+        <v>7.36097478866577</v>
       </c>
       <c r="H422" t="n">
         <v>1868</v>
@@ -12636,7 +12636,7 @@
         <v>8.5</v>
       </c>
       <c r="G423" t="n">
-        <v>7.30937957763672</v>
+        <v>7.30937814712524</v>
       </c>
       <c r="H423" t="n">
         <v>1963</v>
@@ -12665,7 +12665,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>7.65334987640381</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H424" t="n">
         <v>13987</v>
@@ -12694,7 +12694,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H425" t="n">
         <v>1500</v>
@@ -12723,7 +12723,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H426" t="n">
         <v>822</v>
@@ -12752,7 +12752,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G427" t="n">
-        <v>7.42976903915405</v>
+        <v>7.42976856231689</v>
       </c>
       <c r="H427" t="n">
         <v>1502</v>
@@ -12781,7 +12781,7 @@
         <v>8.5</v>
       </c>
       <c r="G428" t="n">
-        <v>7.30937957763672</v>
+        <v>7.30937814712524</v>
       </c>
       <c r="H428" t="n">
         <v>1002</v>
@@ -12839,7 +12839,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>7.13739347457886</v>
+        <v>7.13739395141602</v>
       </c>
       <c r="H430" t="n">
         <v>908</v>
@@ -12868,7 +12868,7 @@
         <v>8.5</v>
       </c>
       <c r="G431" t="n">
-        <v>7.30937957763672</v>
+        <v>7.30937814712524</v>
       </c>
       <c r="H431" t="n">
         <v>400</v>
@@ -12897,7 +12897,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H432" t="n">
         <v>7444</v>
@@ -12926,7 +12926,7 @@
         <v>9</v>
       </c>
       <c r="G433" t="n">
-        <v>7.73934316635132</v>
+        <v>7.73934268951416</v>
       </c>
       <c r="H433" t="n">
         <v>12673</v>
@@ -12984,7 +12984,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G435" t="n">
-        <v>7.65334987640381</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H435" t="n">
         <v>1451</v>
@@ -13013,7 +13013,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>7.48136472702026</v>
+        <v>7.48136425018311</v>
       </c>
       <c r="H436" t="n">
         <v>2489</v>
@@ -13071,7 +13071,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H438" t="n">
         <v>5485</v>
@@ -13100,7 +13100,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H439" t="n">
         <v>572</v>
@@ -13187,7 +13187,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>7.78233861923218</v>
+        <v>7.78233909606934</v>
       </c>
       <c r="H442" t="n">
         <v>10</v>
@@ -13245,7 +13245,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H444" t="n">
         <v>800</v>
@@ -13274,7 +13274,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H445" t="n">
         <v>8557</v>
@@ -13303,7 +13303,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G446" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H446" t="n">
         <v>5102</v>
@@ -13332,7 +13332,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H447" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G449" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H449" t="n">
         <v>1237</v>
@@ -13419,7 +13419,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G450" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G451" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836736679077</v>
       </c>
       <c r="H451" t="n">
         <v>3000</v>
@@ -13477,7 +13477,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G452" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H452" t="n">
         <v>510</v>
@@ -13506,7 +13506,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G453" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H453" t="n">
         <v>2385</v>
@@ -13535,7 +13535,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G454" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H454" t="n">
         <v>200</v>
@@ -13564,7 +13564,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G455" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H455" t="n">
         <v>18119</v>
@@ -13593,7 +13593,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537239074707</v>
       </c>
       <c r="H456" t="n">
         <v>695</v>
@@ -13622,7 +13622,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G457" t="n">
-        <v>7.64425468444824</v>
+        <v>7.6442551612854</v>
       </c>
       <c r="H457" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G458" t="n">
-        <v>7.64425468444824</v>
+        <v>7.6442551612854</v>
       </c>
       <c r="H458" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>7.37759447097778</v>
+        <v>7.37759494781494</v>
       </c>
       <c r="H461" t="n">
         <v>6100</v>
@@ -13999,7 +13999,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G470" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H470" t="n">
         <v>3543</v>
@@ -14028,7 +14028,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>7.2887077331543</v>
+        <v>7.28870725631714</v>
       </c>
       <c r="H471" t="n">
         <v>30</v>
@@ -14115,7 +14115,7 @@
         <v>8.5</v>
       </c>
       <c r="G474" t="n">
-        <v>7.55536794662476</v>
+        <v>7.55536699295044</v>
       </c>
       <c r="H474" t="n">
         <v>3000</v>
@@ -14144,7 +14144,7 @@
         <v>8.5</v>
       </c>
       <c r="G475" t="n">
-        <v>7.55536794662476</v>
+        <v>7.55536699295044</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>8.5</v>
       </c>
       <c r="G476" t="n">
-        <v>7.55536794662476</v>
+        <v>7.55536699295044</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>7.37759447097778</v>
+        <v>7.37759494781494</v>
       </c>
       <c r="H477" t="n">
         <v>600</v>
@@ -14260,7 +14260,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G479" t="n">
-        <v>7.2887077331543</v>
+        <v>7.28870725631714</v>
       </c>
       <c r="H479" t="n">
         <v>3000</v>
@@ -14840,7 +14840,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G499" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H499" t="n">
         <v>21845</v>
@@ -14898,7 +14898,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H501" t="n">
         <v>40</v>
@@ -14927,7 +14927,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G502" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H502" t="n">
         <v>750</v>
@@ -14956,7 +14956,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G503" t="n">
-        <v>7.022047996521</v>
+        <v>7.02204751968384</v>
       </c>
       <c r="H503" t="n">
         <v>150</v>
@@ -15246,7 +15246,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G513" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H513" t="n">
         <v>115</v>
@@ -15275,7 +15275,7 @@
         <v>7.75</v>
       </c>
       <c r="G514" t="n">
-        <v>6.88871765136719</v>
+        <v>6.88871812820435</v>
       </c>
       <c r="H514" t="n">
         <v>1660</v>
@@ -15333,7 +15333,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>6.97760438919067</v>
+        <v>6.97760391235352</v>
       </c>
       <c r="H516" t="n">
         <v>192</v>
@@ -15362,7 +15362,7 @@
         <v>7.5</v>
       </c>
       <c r="G517" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H517" t="n">
         <v>2568</v>
@@ -15391,7 +15391,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G518" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H518" t="n">
         <v>2860</v>
@@ -15420,7 +15420,7 @@
         <v>7.5</v>
       </c>
       <c r="G519" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H519" t="n">
         <v>610</v>
@@ -15449,7 +15449,7 @@
         <v>7.5</v>
       </c>
       <c r="G520" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H520" t="n">
         <v>0</v>
@@ -15478,7 +15478,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G521" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H521" t="n">
         <v>300</v>
@@ -15507,7 +15507,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H522" t="n">
         <v>26</v>
@@ -15536,7 +15536,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H523" t="n">
         <v>16875</v>
@@ -15594,7 +15594,7 @@
         <v>7.5</v>
       </c>
       <c r="G525" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H525" t="n">
         <v>400</v>
@@ -15623,7 +15623,7 @@
         <v>7.5</v>
       </c>
       <c r="G526" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H526" t="n">
         <v>0</v>
@@ -15652,7 +15652,7 @@
         <v>7.5</v>
       </c>
       <c r="G527" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>7.5</v>
       </c>
       <c r="G528" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H528" t="n">
         <v>3103</v>
@@ -15710,7 +15710,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H529" t="n">
         <v>700</v>
@@ -15739,7 +15739,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G530" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -15826,7 +15826,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G533" t="n">
-        <v>6.71094465255737</v>
+        <v>6.71094417572021</v>
       </c>
       <c r="H533" t="n">
         <v>80</v>
@@ -15855,7 +15855,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.39984083175659</v>
+        <v>6.39984035491943</v>
       </c>
       <c r="H534" t="n">
         <v>2911</v>
@@ -15913,7 +15913,7 @@
         <v>7.25</v>
       </c>
       <c r="G536" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H536" t="n">
         <v>300</v>
@@ -15942,7 +15942,7 @@
         <v>7.25</v>
       </c>
       <c r="G537" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H537" t="n">
         <v>500</v>
@@ -15971,7 +15971,7 @@
         <v>7.25</v>
       </c>
       <c r="G538" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H538" t="n">
         <v>0</v>
@@ -16000,7 +16000,7 @@
         <v>7.25</v>
       </c>
       <c r="G539" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H539" t="n">
         <v>305</v>
@@ -16058,7 +16058,7 @@
         <v>7.25</v>
       </c>
       <c r="G541" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H541" t="n">
         <v>1320</v>
@@ -16087,7 +16087,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.39984083175659</v>
+        <v>6.39984035491943</v>
       </c>
       <c r="H542" t="n">
         <v>6172</v>
@@ -16116,7 +16116,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>6.39984083175659</v>
+        <v>6.39984035491943</v>
       </c>
       <c r="H543" t="n">
         <v>3219</v>
@@ -16174,7 +16174,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H545" t="n">
         <v>3438</v>
@@ -16232,7 +16232,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H547" t="n">
         <v>550</v>
@@ -16290,7 +16290,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H549" t="n">
         <v>450</v>
@@ -16377,7 +16377,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G552" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H552" t="n">
         <v>1717</v>
@@ -16406,7 +16406,7 @@
         <v>7.25</v>
       </c>
       <c r="G553" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H553" t="n">
         <v>343</v>
@@ -16493,7 +16493,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G556" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H556" t="n">
         <v>670</v>
@@ -16522,7 +16522,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G557" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H557" t="n">
         <v>3189</v>
@@ -16580,7 +16580,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G559" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H559" t="n">
         <v>7637</v>
@@ -16609,7 +16609,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H560" t="n">
         <v>3012</v>
@@ -16638,7 +16638,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16725,7 +16725,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H564" t="n">
         <v>300</v>
@@ -16754,7 +16754,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -16870,7 +16870,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G569" t="n">
-        <v>5.95540714263916</v>
+        <v>5.95540761947632</v>
       </c>
       <c r="H569" t="n">
         <v>6050</v>
@@ -16899,7 +16899,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H570" t="n">
         <v>3670</v>
@@ -16928,7 +16928,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G571" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G573" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H573" t="n">
         <v>4179</v>
@@ -17015,7 +17015,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G574" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H574" t="n">
         <v>2117</v>
@@ -17044,7 +17044,7 @@
         <v>7.25</v>
       </c>
       <c r="G575" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H575" t="n">
         <v>6238</v>
@@ -17073,7 +17073,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G576" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H576" t="n">
         <v>3710</v>
@@ -17102,7 +17102,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H577" t="n">
         <v>2610</v>
@@ -17131,7 +17131,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -17247,7 +17247,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G582" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H582" t="n">
         <v>2138</v>
@@ -17276,7 +17276,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G583" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H583" t="n">
         <v>18938</v>
@@ -17363,7 +17363,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G586" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H586" t="n">
         <v>2734</v>
@@ -17392,7 +17392,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H587" t="n">
         <v>3257</v>
@@ -17479,7 +17479,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G590" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H590" t="n">
         <v>8364</v>
@@ -17508,7 +17508,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>6.13318109512329</v>
+        <v>6.13318061828613</v>
       </c>
       <c r="H591" t="n">
         <v>200</v>
@@ -17537,7 +17537,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H592" t="n">
         <v>3684</v>
@@ -17566,7 +17566,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H593" t="n">
         <v>5400</v>
@@ -17624,7 +17624,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G595" t="n">
-        <v>5.95540714263916</v>
+        <v>5.95540761947632</v>
       </c>
       <c r="H595" t="n">
         <v>3897</v>
@@ -17682,7 +17682,7 @@
         <v>6.5</v>
       </c>
       <c r="G597" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H597" t="n">
         <v>12670</v>
@@ -17711,7 +17711,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H598" t="n">
         <v>8965</v>
@@ -17740,7 +17740,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G599" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H599" t="n">
         <v>11436</v>
@@ -17885,7 +17885,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H604" t="n">
         <v>52602</v>
@@ -17914,7 +17914,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G605" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H605" t="n">
         <v>2051</v>
@@ -17972,7 +17972,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G607" t="n">
-        <v>5.86652040481567</v>
+        <v>5.86652088165283</v>
       </c>
       <c r="H607" t="n">
         <v>17462</v>
@@ -18001,7 +18001,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>5.95540714263916</v>
+        <v>5.95540761947632</v>
       </c>
       <c r="H608" t="n">
         <v>23741</v>
@@ -18030,7 +18030,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G609" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H609" t="n">
         <v>3523</v>
@@ -18233,7 +18233,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G616" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H616" t="n">
         <v>3231</v>
@@ -18262,7 +18262,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G618" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H618" t="n">
         <v>2032</v>
@@ -18320,7 +18320,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G619" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H619" t="n">
         <v>50</v>
@@ -18349,7 +18349,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H620" t="n">
         <v>7613</v>
@@ -18378,7 +18378,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H621" t="n">
         <v>2570</v>
@@ -18407,7 +18407,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G622" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H622" t="n">
         <v>1100</v>
@@ -18436,7 +18436,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H623" t="n">
         <v>3777</v>
@@ -18465,7 +18465,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G624" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H624" t="n">
         <v>5586</v>
@@ -18494,7 +18494,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G625" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H625" t="n">
         <v>3300</v>
@@ -18523,7 +18523,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G626" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H626" t="n">
         <v>2368</v>
@@ -18552,7 +18552,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G627" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H627" t="n">
         <v>2744</v>
@@ -18581,7 +18581,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G628" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H628" t="n">
         <v>1005</v>
@@ -18610,7 +18610,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G629" t="n">
-        <v>5.95540714263916</v>
+        <v>5.95540761947632</v>
       </c>
       <c r="H629" t="n">
         <v>1200</v>
@@ -18639,7 +18639,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H630" t="n">
         <v>1307</v>
@@ -18668,7 +18668,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G631" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H631" t="n">
         <v>2750</v>
@@ -18726,7 +18726,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.86652040481567</v>
+        <v>5.86652088165283</v>
       </c>
       <c r="H633" t="n">
         <v>5366</v>
@@ -18755,7 +18755,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G634" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H634" t="n">
         <v>2000</v>
@@ -18784,7 +18784,7 @@
         <v>6.5</v>
       </c>
       <c r="G635" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H635" t="n">
         <v>12636</v>
@@ -18813,7 +18813,7 @@
         <v>6.5</v>
       </c>
       <c r="G636" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H636" t="n">
         <v>4185</v>
@@ -18842,7 +18842,7 @@
         <v>6.5</v>
       </c>
       <c r="G637" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H637" t="n">
         <v>0</v>
@@ -18871,7 +18871,7 @@
         <v>6.5</v>
       </c>
       <c r="G638" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H638" t="n">
         <v>3450</v>
@@ -18900,7 +18900,7 @@
         <v>6.5</v>
       </c>
       <c r="G639" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H639" t="n">
         <v>0</v>
@@ -18929,7 +18929,7 @@
         <v>6.5</v>
       </c>
       <c r="G640" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H640" t="n">
         <v>1550</v>
@@ -18958,7 +18958,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G641" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H641" t="n">
         <v>1959</v>
@@ -18987,7 +18987,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H642" t="n">
         <v>2879</v>
@@ -19045,7 +19045,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>5.64430379867554</v>
+        <v>5.6443042755127</v>
       </c>
       <c r="H644" t="n">
         <v>5286</v>
@@ -19074,7 +19074,7 @@
         <v>6.25</v>
       </c>
       <c r="G645" t="n">
-        <v>5.55541753768921</v>
+        <v>5.55541706085205</v>
       </c>
       <c r="H645" t="n">
         <v>3525</v>
@@ -19103,7 +19103,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.64430379867554</v>
+        <v>5.6443042755127</v>
       </c>
       <c r="H646" t="n">
         <v>297</v>
@@ -19132,7 +19132,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H647" t="n">
         <v>262</v>
@@ -19161,7 +19161,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H648" t="n">
         <v>2986</v>
@@ -19190,7 +19190,7 @@
         <v>6.5</v>
       </c>
       <c r="G649" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H649" t="n">
         <v>6789</v>
@@ -19248,7 +19248,7 @@
         <v>6.5</v>
       </c>
       <c r="G651" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H651" t="n">
         <v>1008</v>
@@ -19277,7 +19277,7 @@
         <v>6.5</v>
       </c>
       <c r="G652" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H652" t="n">
         <v>11094</v>
@@ -19306,7 +19306,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G653" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H653" t="n">
         <v>4753</v>
@@ -19335,7 +19335,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G654" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H654" t="n">
         <v>1310</v>
@@ -19683,7 +19683,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G666" t="n">
-        <v>4.35544681549072</v>
+        <v>4.35544729232788</v>
       </c>
       <c r="H666" t="n">
         <v>11395</v>
@@ -19712,7 +19712,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>4.26656103134155</v>
+        <v>4.26656055450439</v>
       </c>
       <c r="H667" t="n">
         <v>8251</v>
@@ -19741,7 +19741,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>4.07101011276245</v>
+        <v>4.07100963592529</v>
       </c>
       <c r="H668" t="n">
         <v>934</v>
@@ -19799,7 +19799,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G670" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H670" t="n">
         <v>10643</v>
@@ -19828,7 +19828,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G671" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -19857,7 +19857,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G672" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G673" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G674" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H674" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G675" t="n">
-        <v>3.82212734222412</v>
+        <v>3.8221275806427</v>
       </c>
       <c r="H675" t="n">
         <v>2991</v>
@@ -19973,7 +19973,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G676" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H676" t="n">
         <v>2454</v>
@@ -20002,7 +20002,7 @@
         <v>4.5</v>
       </c>
       <c r="G677" t="n">
-        <v>3.99990081787109</v>
+        <v>3.99990057945251</v>
       </c>
       <c r="H677" t="n">
         <v>2379</v>
@@ -20031,7 +20031,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G678" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H678" t="n">
         <v>6410</v>
@@ -20089,7 +20089,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G680" t="n">
-        <v>3.85768222808838</v>
+        <v>3.8576819896698</v>
       </c>
       <c r="H680" t="n">
         <v>4718</v>
@@ -20147,7 +20147,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G682" t="n">
-        <v>3.75101757049561</v>
+        <v>3.75101804733276</v>
       </c>
       <c r="H682" t="n">
         <v>2412</v>
@@ -20176,7 +20176,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G683" t="n">
-        <v>3.64435386657715</v>
+        <v>3.64435362815857</v>
       </c>
       <c r="H683" t="n">
         <v>1800</v>
@@ -20205,7 +20205,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G684" t="n">
-        <v>3.68879723548889</v>
+        <v>3.68879747390747</v>
       </c>
       <c r="H684" t="n">
         <v>1402</v>
@@ -20234,7 +20234,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G685" t="n">
-        <v>3.80435013771057</v>
+        <v>3.80434989929199</v>
       </c>
       <c r="H685" t="n">
         <v>3900</v>
@@ -20263,7 +20263,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G686" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H686" t="n">
         <v>4888</v>
@@ -20321,7 +20321,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>3.85768222808838</v>
+        <v>3.8576819896698</v>
       </c>
       <c r="H688" t="n">
         <v>1215</v>
@@ -20350,7 +20350,7 @@
         <v>4.5</v>
       </c>
       <c r="G689" t="n">
-        <v>3.99990081787109</v>
+        <v>3.99990057945251</v>
       </c>
       <c r="H689" t="n">
         <v>1891</v>
@@ -20408,7 +20408,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G691" t="n">
-        <v>3.98212313652039</v>
+        <v>3.98212337493896</v>
       </c>
       <c r="H691" t="n">
         <v>9728</v>
@@ -20495,7 +20495,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G694" t="n">
-        <v>3.85768222808838</v>
+        <v>3.8576819896698</v>
       </c>
       <c r="H694" t="n">
         <v>6301</v>
@@ -20524,7 +20524,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H695" t="n">
         <v>4540</v>
@@ -20553,7 +20553,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H696" t="n">
         <v>470</v>
@@ -20611,7 +20611,7 @@
         <v>4.5</v>
       </c>
       <c r="G698" t="n">
-        <v>3.99990081787109</v>
+        <v>3.99990057945251</v>
       </c>
       <c r="H698" t="n">
         <v>1703</v>
@@ -20640,7 +20640,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>3.98212313652039</v>
+        <v>3.98212337493896</v>
       </c>
       <c r="H699" t="n">
         <v>13560</v>
@@ -20669,7 +20669,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G700" t="n">
-        <v>3.98212313652039</v>
+        <v>3.98212337493896</v>
       </c>
       <c r="H700" t="n">
         <v>6239</v>
@@ -20698,7 +20698,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G701" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H701" t="n">
         <v>11088</v>
@@ -20756,7 +20756,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>3.76879477500916</v>
+        <v>3.76879501342773</v>
       </c>
       <c r="H703" t="n">
         <v>6306</v>
@@ -20785,7 +20785,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G704" t="n">
-        <v>3.90212512016296</v>
+        <v>3.90212535858154</v>
       </c>
       <c r="H704" t="n">
         <v>1895</v>
@@ -20814,7 +20814,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G705" t="n">
-        <v>3.88434791564941</v>
+        <v>3.88434743881226</v>
       </c>
       <c r="H705" t="n">
         <v>6050</v>
@@ -20843,7 +20843,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G706" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H706" t="n">
         <v>1629</v>
@@ -20872,7 +20872,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>3.88434791564941</v>
+        <v>3.88434743881226</v>
       </c>
       <c r="H707" t="n">
         <v>1037</v>
@@ -20901,7 +20901,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G708" t="n">
-        <v>3.83101606369019</v>
+        <v>3.83101558685303</v>
       </c>
       <c r="H708" t="n">
         <v>6323</v>
@@ -20930,7 +20930,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>3.83101606369019</v>
+        <v>3.83101558685303</v>
       </c>
       <c r="H709" t="n">
         <v>2542</v>
@@ -20959,7 +20959,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>3.71546316146851</v>
+        <v>3.71546292304993</v>
       </c>
       <c r="H710" t="n">
         <v>8368</v>
@@ -20988,7 +20988,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G711" t="n">
-        <v>3.76879477500916</v>
+        <v>3.76879501342773</v>
       </c>
       <c r="H711" t="n">
         <v>5939</v>
@@ -21017,7 +21017,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G712" t="n">
-        <v>3.75101757049561</v>
+        <v>3.75101804733276</v>
       </c>
       <c r="H712" t="n">
         <v>2662</v>
@@ -21046,7 +21046,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G713" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H713" t="n">
         <v>1264</v>
@@ -21075,7 +21075,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G714" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H714" t="n">
         <v>0</v>
@@ -21133,7 +21133,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G716" t="n">
-        <v>3.80435013771057</v>
+        <v>3.80434989929199</v>
       </c>
       <c r="H716" t="n">
         <v>685</v>
@@ -21162,7 +21162,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>3.88434791564941</v>
+        <v>3.88434743881226</v>
       </c>
       <c r="H717" t="n">
         <v>3887</v>
@@ -21278,7 +21278,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>4.13323020935059</v>
+        <v>4.13323068618774</v>
       </c>
       <c r="H721" t="n">
         <v>12913</v>
@@ -21452,7 +21452,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G727" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767627716064</v>
       </c>
       <c r="H727" t="n">
         <v>30466</v>
@@ -21539,7 +21539,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>4.38185501098633</v>
+        <v>4.38185453414917</v>
       </c>
       <c r="H730" t="n">
         <v>61399</v>
@@ -21568,7 +21568,7 @@
         <v>4.75</v>
       </c>
       <c r="G731" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H731" t="n">
         <v>16376</v>
@@ -21655,7 +21655,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G734" t="n">
-        <v>4.38185501098633</v>
+        <v>4.38185453414917</v>
       </c>
       <c r="H734" t="n">
         <v>34375</v>
@@ -21684,7 +21684,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G735" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H735" t="n">
         <v>17125</v>
@@ -21713,7 +21713,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G736" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H736" t="n">
         <v>9606</v>
@@ -21742,7 +21742,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G737" t="n">
-        <v>4.40935611724854</v>
+        <v>4.40935564041138</v>
       </c>
       <c r="H737" t="n">
         <v>2683</v>
@@ -21771,7 +21771,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H738" t="n">
         <v>600</v>
@@ -21800,7 +21800,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H739" t="n">
         <v>680</v>
@@ -21829,7 +21829,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G740" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H740" t="n">
         <v>7403</v>
@@ -21916,7 +21916,7 @@
         <v>4.75</v>
       </c>
       <c r="G743" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H743" t="n">
         <v>607</v>
@@ -21945,7 +21945,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G744" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H744" t="n">
         <v>11032</v>
@@ -22032,7 +22032,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G747" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H747" t="n">
         <v>2630</v>
@@ -22061,7 +22061,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H748" t="n">
         <v>1000</v>
@@ -22177,7 +22177,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G752" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H752" t="n">
         <v>1350</v>
@@ -22380,7 +22380,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G759" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H759" t="n">
         <v>3488</v>
@@ -22467,7 +22467,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H762" t="n">
         <v>4900</v>
@@ -22641,7 +22641,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H768" t="n">
         <v>8119</v>
@@ -22902,7 +22902,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H777" t="n">
         <v>7930</v>
@@ -22931,7 +22931,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>4.08850908279419</v>
+        <v>4.08850860595703</v>
       </c>
       <c r="H778" t="n">
         <v>10894</v>
@@ -23105,7 +23105,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G784" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H784" t="n">
         <v>10522</v>
@@ -23163,7 +23163,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G786" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H786" t="n">
         <v>1030</v>
@@ -23192,7 +23192,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G787" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>4.07934141159058</v>
+        <v>4.07934188842773</v>
       </c>
       <c r="H788" t="n">
         <v>5464</v>
@@ -23250,7 +23250,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G789" t="n">
-        <v>4.07934141159058</v>
+        <v>4.07934188842773</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -23337,7 +23337,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>4.04267358779907</v>
+        <v>4.04267311096191</v>
       </c>
       <c r="H792" t="n">
         <v>1205</v>
@@ -23482,7 +23482,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G797" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H797" t="n">
         <v>2403</v>
@@ -23511,7 +23511,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G798" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H798" t="n">
         <v>1860</v>
@@ -23598,7 +23598,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>3.91433453559875</v>
+        <v>3.91433477401733</v>
       </c>
       <c r="H801" t="n">
         <v>1035</v>
@@ -23743,7 +23743,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.86849904060364</v>
+        <v>3.86849927902222</v>
       </c>
       <c r="H806" t="n">
         <v>3833</v>
@@ -23772,7 +23772,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G807" t="n">
-        <v>3.88683319091797</v>
+        <v>3.88683342933655</v>
       </c>
       <c r="H807" t="n">
         <v>13265</v>
@@ -23801,7 +23801,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G808" t="n">
-        <v>3.88683319091797</v>
+        <v>3.88683342933655</v>
       </c>
       <c r="H808" t="n">
         <v>12349</v>
@@ -23946,7 +23946,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G813" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H813" t="n">
         <v>11042</v>
@@ -24004,7 +24004,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H815" t="n">
         <v>4760</v>
@@ -24033,7 +24033,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G816" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H816" t="n">
         <v>7780</v>
@@ -24120,7 +24120,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G819" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H819" t="n">
         <v>785</v>
@@ -24178,7 +24178,7 @@
         <v>4.75</v>
       </c>
       <c r="G821" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H821" t="n">
         <v>6878</v>
@@ -24294,7 +24294,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G825" t="n">
-        <v>4.51936054229736</v>
+        <v>4.51936006546021</v>
       </c>
       <c r="H825" t="n">
         <v>1867</v>
@@ -24352,7 +24352,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>4.51019334793091</v>
+        <v>4.51019382476807</v>
       </c>
       <c r="H827" t="n">
         <v>10424</v>
@@ -24410,7 +24410,7 @@
         <v>4.75</v>
       </c>
       <c r="G829" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H829" t="n">
         <v>5800</v>
@@ -24468,7 +24468,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.04267358779907</v>
+        <v>4.04267311096191</v>
       </c>
       <c r="H831" t="n">
         <v>16333</v>
@@ -24555,7 +24555,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>3.94183588027954</v>
+        <v>3.94183611869812</v>
       </c>
       <c r="H834" t="n">
         <v>25951</v>
@@ -24642,7 +24642,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H837" t="n">
         <v>21835</v>
@@ -24729,7 +24729,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G840" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H840" t="n">
         <v>34559</v>
@@ -24758,7 +24758,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H841" t="n">
         <v>225</v>
@@ -24845,7 +24845,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G844" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H844" t="n">
         <v>16368</v>
@@ -25193,7 +25193,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>4.96854639053345</v>
+        <v>4.96854686737061</v>
       </c>
       <c r="H856" t="n">
         <v>13143</v>
@@ -25309,7 +25309,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>5.1152195930481</v>
+        <v>5.11521911621094</v>
       </c>
       <c r="H860" t="n">
         <v>16237</v>
@@ -25367,7 +25367,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G862" t="n">
-        <v>5.13355350494385</v>
+        <v>5.13355398178101</v>
       </c>
       <c r="H862" t="n">
         <v>13036</v>
@@ -25396,7 +25396,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G863" t="n">
-        <v>5.1518874168396</v>
+        <v>5.15188789367676</v>
       </c>
       <c r="H863" t="n">
         <v>7153</v>
@@ -25454,7 +25454,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>5.00521516799927</v>
+        <v>5.00521469116211</v>
       </c>
       <c r="H865" t="n">
         <v>3756</v>
@@ -25686,7 +25686,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G873" t="n">
-        <v>5.39023113250732</v>
+        <v>5.39023160934448</v>
       </c>
       <c r="H873" t="n">
         <v>31741</v>
@@ -25715,7 +25715,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G874" t="n">
-        <v>5.39023113250732</v>
+        <v>5.39023160934448</v>
       </c>
       <c r="H874" t="n">
         <v>13377</v>
@@ -25831,7 +25831,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G878" t="n">
-        <v>5.61024045944214</v>
+        <v>5.6102409362793</v>
       </c>
       <c r="H878" t="n">
         <v>24852</v>
@@ -25947,7 +25947,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G882" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H882" t="n">
         <v>8738</v>
@@ -25976,7 +25976,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>5.88525247573853</v>
+        <v>5.88525295257568</v>
       </c>
       <c r="H883" t="n">
         <v>11732</v>
@@ -26121,7 +26121,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>5.94025468826294</v>
+        <v>5.9402551651001</v>
       </c>
       <c r="H888" t="n">
         <v>7733</v>
@@ -26266,7 +26266,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G893" t="n">
-        <v>5.83025074005127</v>
+        <v>5.83025026321411</v>
       </c>
       <c r="H893" t="n">
         <v>46103</v>
@@ -26324,7 +26324,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H895" t="n">
         <v>1658</v>
@@ -26382,7 +26382,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H897" t="n">
         <v>3856</v>
@@ -26469,7 +26469,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H900" t="n">
         <v>19114</v>
@@ -26498,7 +26498,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H901" t="n">
         <v>5834</v>
@@ -26527,7 +26527,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H902" t="n">
         <v>4663</v>
@@ -26643,7 +26643,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G906" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H906" t="n">
         <v>7547</v>
@@ -26759,7 +26759,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G910" t="n">
-        <v>6.19693326950073</v>
+        <v>6.19693279266357</v>
       </c>
       <c r="H910" t="n">
         <v>32257</v>
@@ -26817,7 +26817,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>6.38027429580688</v>
+        <v>6.38027381896973</v>
       </c>
       <c r="H912" t="n">
         <v>24783</v>
@@ -26846,7 +26846,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G913" t="n">
-        <v>6.28860378265381</v>
+        <v>6.28860330581665</v>
       </c>
       <c r="H913" t="n">
         <v>13157</v>
@@ -26991,7 +26991,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>6.47194480895996</v>
+        <v>6.4719443321228</v>
       </c>
       <c r="H918" t="n">
         <v>6002</v>
@@ -27049,7 +27049,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G920" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H920" t="n">
         <v>2787</v>
@@ -27078,7 +27078,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H921" t="n">
         <v>4737</v>
@@ -27107,7 +27107,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G922" t="n">
-        <v>6.58194875717163</v>
+        <v>6.58194923400879</v>
       </c>
       <c r="H922" t="n">
         <v>5358</v>
@@ -27165,7 +27165,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G924" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H924" t="n">
         <v>4250</v>
@@ -27252,7 +27252,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G927" t="n">
-        <v>6.61861705780029</v>
+        <v>6.61861753463745</v>
       </c>
       <c r="H927" t="n">
         <v>9701</v>
@@ -27339,7 +27339,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>6.58194875717163</v>
+        <v>6.58194923400879</v>
       </c>
       <c r="H930" t="n">
         <v>1400</v>
@@ -27368,7 +27368,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G931" t="n">
-        <v>6.61861705780029</v>
+        <v>6.61861753463745</v>
       </c>
       <c r="H931" t="n">
         <v>4392</v>
@@ -27542,7 +27542,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G937" t="n">
-        <v>6.54528093338013</v>
+        <v>6.54528045654297</v>
       </c>
       <c r="H937" t="n">
         <v>11503</v>
@@ -27600,7 +27600,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G939" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H939" t="n">
         <v>14602</v>
@@ -27658,7 +27658,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>6.85696077346802</v>
+        <v>6.85696125030518</v>
       </c>
       <c r="H941" t="n">
         <v>21995</v>
@@ -27890,7 +27890,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H949" t="n">
         <v>6250</v>
@@ -28093,7 +28093,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G956" t="n">
-        <v>6.78362464904785</v>
+        <v>6.78362417221069</v>
       </c>
       <c r="H956" t="n">
         <v>5975</v>
@@ -68525,6 +68525,35 @@
         <v>9241</v>
       </c>
       <c r="I2350" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2351" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2351" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D2351" t="n">
+        <v>2.58999991416931</v>
+      </c>
+      <c r="E2351" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F2351" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="G2351" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="H2351" t="n">
+        <v>81646</v>
+      </c>
+      <c r="I2351" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2" t="n">
-        <v>9.40188026428223</v>
+        <v>9.40188121795654</v>
       </c>
       <c r="H2" t="n">
         <v>56600</v>
@@ -456,7 +456,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G3" t="n">
-        <v>9.44389057159424</v>
+        <v>9.44389152526855</v>
       </c>
       <c r="H3" t="n">
         <v>18800</v>
@@ -572,7 +572,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>9.57832336425781</v>
+        <v>9.5783224105835</v>
       </c>
       <c r="H7" t="n">
         <v>14800</v>
@@ -659,7 +659,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>9.57832336425781</v>
+        <v>9.5783224105835</v>
       </c>
       <c r="H10" t="n">
         <v>4000</v>
@@ -862,7 +862,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H17" t="n">
         <v>248200</v>
@@ -920,7 +920,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>9.57832336425781</v>
+        <v>9.5783224105835</v>
       </c>
       <c r="H19" t="n">
         <v>2400</v>
@@ -1065,7 +1065,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G24" t="n">
-        <v>9.40188026428223</v>
+        <v>9.40188121795654</v>
       </c>
       <c r="H24" t="n">
         <v>600</v>
@@ -1094,7 +1094,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H25" t="n">
         <v>1600</v>
@@ -1123,7 +1123,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G30" t="n">
-        <v>9.51950931549072</v>
+        <v>9.51951026916504</v>
       </c>
       <c r="H30" t="n">
         <v>2600</v>
@@ -1268,7 +1268,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G31" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H31" t="n">
         <v>4600</v>
@@ -1297,7 +1297,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H32" t="n">
         <v>1600</v>
@@ -1355,7 +1355,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G34" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H34" t="n">
         <v>14200</v>
@@ -1384,7 +1384,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H35" t="n">
         <v>800</v>
@@ -1413,7 +1413,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H36" t="n">
         <v>400</v>
@@ -1674,7 +1674,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G45" t="n">
-        <v>9.82198333740234</v>
+        <v>9.82198238372803</v>
       </c>
       <c r="H45" t="n">
         <v>14000</v>
@@ -1703,7 +1703,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>9.77157020568848</v>
+        <v>9.77157115936279</v>
       </c>
       <c r="H46" t="n">
         <v>47600</v>
@@ -1790,7 +1790,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G49" t="n">
-        <v>9.77157020568848</v>
+        <v>9.77157115936279</v>
       </c>
       <c r="H49" t="n">
         <v>37000</v>
@@ -1877,7 +1877,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>9.91440391540527</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H52" t="n">
         <v>97800</v>
@@ -1993,7 +1993,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>9.91440391540527</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H56" t="n">
         <v>20400</v>
@@ -2109,7 +2109,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G60" t="n">
-        <v>10.0320320129395</v>
+        <v>10.0320329666138</v>
       </c>
       <c r="H60" t="n">
         <v>10600</v>
@@ -2138,7 +2138,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G61" t="n">
-        <v>10.0320320129395</v>
+        <v>10.0320329666138</v>
       </c>
       <c r="H61" t="n">
         <v>11200</v>
@@ -2196,7 +2196,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G63" t="n">
-        <v>9.88919830322266</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H63" t="n">
         <v>14400</v>
@@ -2225,7 +2225,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G64" t="n">
-        <v>9.88919830322266</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H64" t="n">
         <v>24000</v>
@@ -2254,7 +2254,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>9.82198333740234</v>
+        <v>9.82198238372803</v>
       </c>
       <c r="H65" t="n">
         <v>8600</v>
@@ -2283,7 +2283,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G66" t="n">
-        <v>9.88919830322266</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H66" t="n">
         <v>16400</v>
@@ -2312,7 +2312,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G67" t="n">
-        <v>9.93961143493652</v>
+        <v>9.93961048126221</v>
       </c>
       <c r="H67" t="n">
         <v>18400</v>
@@ -2399,7 +2399,7 @@
         <v>11.75</v>
       </c>
       <c r="G70" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239646911621</v>
       </c>
       <c r="H70" t="n">
         <v>5200</v>
@@ -2428,7 +2428,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G71" t="n">
-        <v>9.88919830322266</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H71" t="n">
         <v>64600</v>
@@ -2457,7 +2457,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>9.91440391540527</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H72" t="n">
         <v>73200</v>
@@ -2544,7 +2544,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>9.9984245300293</v>
+        <v>9.99842548370361</v>
       </c>
       <c r="H75" t="n">
         <v>26800</v>
@@ -2573,7 +2573,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G76" t="n">
-        <v>10.0488386154175</v>
+        <v>10.0488376617432</v>
       </c>
       <c r="H76" t="n">
         <v>116000</v>
@@ -2602,7 +2602,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G77" t="n">
-        <v>10.0320320129395</v>
+        <v>10.0320329666138</v>
       </c>
       <c r="H77" t="n">
         <v>58000</v>
@@ -2631,7 +2631,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>9.9984245300293</v>
+        <v>9.99842548370361</v>
       </c>
       <c r="H78" t="n">
         <v>14600</v>
@@ -2689,7 +2689,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G80" t="n">
-        <v>10.0488386154175</v>
+        <v>10.0488376617432</v>
       </c>
       <c r="H80" t="n">
         <v>12400</v>
@@ -2776,7 +2776,7 @@
         <v>11.75</v>
       </c>
       <c r="G83" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239646911621</v>
       </c>
       <c r="H83" t="n">
         <v>13000</v>
@@ -2805,7 +2805,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.91440391540527</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H84" t="n">
         <v>6200</v>
@@ -2863,7 +2863,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>9.91440391540527</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H86" t="n">
         <v>5400</v>
@@ -2950,7 +2950,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H89" t="n">
         <v>22400</v>
@@ -2979,7 +2979,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H90" t="n">
         <v>2000</v>
@@ -3008,7 +3008,7 @@
         <v>11.75</v>
       </c>
       <c r="G91" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239646911621</v>
       </c>
       <c r="H91" t="n">
         <v>1000</v>
@@ -3037,7 +3037,7 @@
         <v>11.75</v>
       </c>
       <c r="G92" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239646911621</v>
       </c>
       <c r="H92" t="n">
         <v>3000</v>
@@ -3066,7 +3066,7 @@
         <v>11.75</v>
       </c>
       <c r="G93" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239646911621</v>
       </c>
       <c r="H93" t="n">
         <v>2600</v>
@@ -3095,7 +3095,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>9.91440391540527</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H94" t="n">
         <v>6000</v>
@@ -3124,7 +3124,7 @@
         <v>11.75</v>
       </c>
       <c r="G95" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239646911621</v>
       </c>
       <c r="H95" t="n">
         <v>7800</v>
@@ -3153,7 +3153,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H96" t="n">
         <v>2600</v>
@@ -3182,7 +3182,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G97" t="n">
-        <v>10.0488386154175</v>
+        <v>10.0488376617432</v>
       </c>
       <c r="H97" t="n">
         <v>14800</v>
@@ -3269,7 +3269,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>9.88919830322266</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H100" t="n">
         <v>36600</v>
@@ -3327,7 +3327,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G102" t="n">
-        <v>9.82198333740234</v>
+        <v>9.82198238372803</v>
       </c>
       <c r="H102" t="n">
         <v>8200</v>
@@ -3356,7 +3356,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G103" t="n">
-        <v>9.82198333740234</v>
+        <v>9.82198238372803</v>
       </c>
       <c r="H103" t="n">
         <v>600</v>
@@ -3443,7 +3443,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G106" t="n">
-        <v>9.62873458862305</v>
+        <v>9.62873554229736</v>
       </c>
       <c r="H106" t="n">
         <v>25400</v>
@@ -3472,7 +3472,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G107" t="n">
-        <v>9.62873458862305</v>
+        <v>9.62873554229736</v>
       </c>
       <c r="H107" t="n">
         <v>11600</v>
@@ -3762,7 +3762,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H117" t="n">
         <v>16400</v>
@@ -3791,7 +3791,7 @@
         <v>11.75</v>
       </c>
       <c r="G118" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239646911621</v>
       </c>
       <c r="H118" t="n">
         <v>12000</v>
@@ -3820,7 +3820,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H119" t="n">
         <v>5400</v>
@@ -3878,7 +3878,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H121" t="n">
         <v>6200</v>
@@ -3907,7 +3907,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H122" t="n">
         <v>14000</v>
@@ -4052,7 +4052,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H127" t="n">
         <v>39200</v>
@@ -4139,7 +4139,7 @@
         <v>11.75</v>
       </c>
       <c r="G130" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239646911621</v>
       </c>
       <c r="H130" t="n">
         <v>3400</v>
@@ -4168,7 +4168,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H131" t="n">
         <v>5600</v>
@@ -4284,7 +4284,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H135" t="n">
         <v>5600</v>
@@ -4400,7 +4400,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G139" t="n">
-        <v>9.57832336425781</v>
+        <v>9.5783224105835</v>
       </c>
       <c r="H139" t="n">
         <v>8000</v>
@@ -4429,7 +4429,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H140" t="n">
         <v>9000</v>
@@ -4458,7 +4458,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H141" t="n">
         <v>1600</v>
@@ -4690,7 +4690,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H149" t="n">
         <v>5600</v>
@@ -4719,7 +4719,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>9.57832336425781</v>
+        <v>9.5783224105835</v>
       </c>
       <c r="H151" t="n">
         <v>2000</v>
@@ -4777,7 +4777,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>9.57832336425781</v>
+        <v>9.5783224105835</v>
       </c>
       <c r="H152" t="n">
         <v>800</v>
@@ -4980,7 +4980,7 @@
         <v>11</v>
       </c>
       <c r="G159" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H159" t="n">
         <v>14600</v>
@@ -5125,7 +5125,7 @@
         <v>11</v>
       </c>
       <c r="G164" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H164" t="n">
         <v>18800</v>
@@ -5154,7 +5154,7 @@
         <v>11</v>
       </c>
       <c r="G165" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>11</v>
       </c>
       <c r="G166" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H166" t="n">
         <v>400</v>
@@ -5241,7 +5241,7 @@
         <v>11</v>
       </c>
       <c r="G168" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H168" t="n">
         <v>1200</v>
@@ -5270,7 +5270,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>9.28425312042236</v>
+        <v>9.28425407409668</v>
       </c>
       <c r="H169" t="n">
         <v>200</v>
@@ -5328,7 +5328,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G171" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H171" t="n">
         <v>2400</v>
@@ -5357,7 +5357,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H172" t="n">
         <v>35400</v>
@@ -5386,7 +5386,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>9.57832336425781</v>
+        <v>9.5783224105835</v>
       </c>
       <c r="H173" t="n">
         <v>3000</v>
@@ -5415,7 +5415,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H174" t="n">
         <v>33600</v>
@@ -5444,7 +5444,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H175" t="n">
         <v>1000</v>
@@ -5473,7 +5473,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G176" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H176" t="n">
         <v>18400</v>
@@ -5502,7 +5502,7 @@
         <v>11</v>
       </c>
       <c r="G177" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H177" t="n">
         <v>5200</v>
@@ -5647,7 +5647,7 @@
         <v>11</v>
       </c>
       <c r="G182" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H182" t="n">
         <v>10000</v>
@@ -5676,7 +5676,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>9.15822219848633</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H183" t="n">
         <v>13600</v>
@@ -5734,7 +5734,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G185" t="n">
-        <v>9.0742015838623</v>
+        <v>9.07420063018799</v>
       </c>
       <c r="H185" t="n">
         <v>5800</v>
@@ -5850,7 +5850,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G189" t="n">
-        <v>9.0742015838623</v>
+        <v>9.07420063018799</v>
       </c>
       <c r="H189" t="n">
         <v>3000</v>
@@ -5879,7 +5879,7 @@
         <v>10.75</v>
       </c>
       <c r="G190" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H190" t="n">
         <v>400</v>
@@ -5966,7 +5966,7 @@
         <v>10.75</v>
       </c>
       <c r="G193" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H193" t="n">
         <v>400</v>
@@ -5995,7 +5995,7 @@
         <v>10.75</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H194" t="n">
         <v>600</v>
@@ -6053,7 +6053,7 @@
         <v>10.75</v>
       </c>
       <c r="G196" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H196" t="n">
         <v>10200</v>
@@ -6082,7 +6082,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>9.15822219848633</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H197" t="n">
         <v>1000</v>
@@ -6111,7 +6111,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>9.15822219848633</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H198" t="n">
         <v>36800</v>
@@ -6140,7 +6140,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>9.0742015838623</v>
+        <v>9.07420063018799</v>
       </c>
       <c r="H199" t="n">
         <v>14800</v>
@@ -6169,7 +6169,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>9.15822219848633</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H200" t="n">
         <v>200</v>
@@ -6198,7 +6198,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G201" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H201" t="n">
         <v>3200</v>
@@ -6227,7 +6227,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G202" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H202" t="n">
         <v>2800</v>
@@ -6256,7 +6256,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G203" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H203" t="n">
         <v>3200</v>
@@ -6285,7 +6285,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G204" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H204" t="n">
         <v>3600</v>
@@ -6314,7 +6314,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G205" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H205" t="n">
         <v>8800</v>
@@ -6343,7 +6343,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G206" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H206" t="n">
         <v>23000</v>
@@ -6372,7 +6372,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G207" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H207" t="n">
         <v>3200</v>
@@ -6459,7 +6459,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G210" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H210" t="n">
         <v>7400</v>
@@ -6575,7 +6575,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G214" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H214" t="n">
         <v>6600</v>
@@ -6807,7 +6807,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G222" t="n">
-        <v>9.07223033905029</v>
+        <v>9.07222938537598</v>
       </c>
       <c r="H222" t="n">
         <v>8600</v>
@@ -6836,7 +6836,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G223" t="n">
-        <v>8.90024471282959</v>
+        <v>8.90024566650391</v>
       </c>
       <c r="H223" t="n">
         <v>20400</v>
@@ -6923,7 +6923,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>8.90024471282959</v>
+        <v>8.90024566650391</v>
       </c>
       <c r="H226" t="n">
         <v>1200</v>
@@ -6981,7 +6981,7 @@
         <v>10.5</v>
       </c>
       <c r="G228" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H228" t="n">
         <v>12000</v>
@@ -7213,7 +7213,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G236" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H236" t="n">
         <v>9600</v>
@@ -7242,7 +7242,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G237" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>10.5</v>
       </c>
       <c r="G238" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H238" t="n">
         <v>3400</v>
@@ -7445,7 +7445,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H244" t="n">
         <v>19000</v>
@@ -7532,7 +7532,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H247" t="n">
         <v>1000</v>
@@ -7561,7 +7561,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G248" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H248" t="n">
         <v>600</v>
@@ -7764,7 +7764,7 @@
         <v>10.5</v>
       </c>
       <c r="G255" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H255" t="n">
         <v>1000</v>
@@ -7793,7 +7793,7 @@
         <v>10.5</v>
       </c>
       <c r="G256" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>10.5</v>
       </c>
       <c r="G257" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H257" t="n">
         <v>400</v>
@@ -7851,7 +7851,7 @@
         <v>10.5</v>
       </c>
       <c r="G258" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>10.5</v>
       </c>
       <c r="G262" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H262" t="n">
         <v>800</v>
@@ -8025,7 +8025,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>9.07223033905029</v>
+        <v>9.07222938537598</v>
       </c>
       <c r="H264" t="n">
         <v>8000</v>
@@ -8228,7 +8228,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>8.49607753753662</v>
+        <v>8.49607849121094</v>
       </c>
       <c r="H271" t="n">
         <v>9400</v>
@@ -8547,7 +8547,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G282" t="n">
-        <v>8.51327610015869</v>
+        <v>8.51327705383301</v>
       </c>
       <c r="H282" t="n">
         <v>2000</v>
@@ -8837,7 +8837,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G292" t="n">
-        <v>8.4100866317749</v>
+        <v>8.41008567810059</v>
       </c>
       <c r="H292" t="n">
         <v>3000</v>
@@ -8866,7 +8866,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G293" t="n">
-        <v>8.4100866317749</v>
+        <v>8.41008567810059</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         <v>9.5</v>
       </c>
       <c r="G296" t="n">
-        <v>8.16930675506592</v>
+        <v>8.1693058013916</v>
       </c>
       <c r="H296" t="n">
         <v>17200</v>
@@ -9359,7 +9359,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G310" t="n">
-        <v>7.87693023681641</v>
+        <v>7.87693119049072</v>
       </c>
       <c r="H310" t="n">
         <v>200</v>
@@ -9388,7 +9388,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>7.87693023681641</v>
+        <v>7.87693119049072</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>8.5</v>
       </c>
       <c r="G318" t="n">
-        <v>7.30937814712524</v>
+        <v>7.3093786239624</v>
       </c>
       <c r="H318" t="n">
         <v>1600</v>
@@ -9707,7 +9707,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G322" t="n">
-        <v>7.18898868560791</v>
+        <v>7.18898916244507</v>
       </c>
       <c r="H322" t="n">
         <v>1400</v>
@@ -9852,7 +9852,7 @@
         <v>9</v>
       </c>
       <c r="G327" t="n">
-        <v>7.73934268951416</v>
+        <v>7.739342212677</v>
       </c>
       <c r="H327" t="n">
         <v>3600</v>
@@ -9910,7 +9910,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G329" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65335035324097</v>
       </c>
       <c r="H329" t="n">
         <v>600</v>
@@ -9939,7 +9939,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>7.48136425018311</v>
+        <v>7.48136377334595</v>
       </c>
       <c r="H330" t="n">
         <v>800</v>
@@ -10055,7 +10055,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65335035324097</v>
       </c>
       <c r="H334" t="n">
         <v>800</v>
@@ -10084,7 +10084,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G335" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65335035324097</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G340" t="n">
-        <v>7.29218006134033</v>
+        <v>7.29218053817749</v>
       </c>
       <c r="H340" t="n">
         <v>2800</v>
@@ -10287,7 +10287,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G342" t="n">
-        <v>7.08579778671265</v>
+        <v>7.0857982635498</v>
       </c>
       <c r="H342" t="n">
         <v>6600</v>
@@ -10316,7 +10316,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G343" t="n">
-        <v>7.06859922409058</v>
+        <v>7.06859970092773</v>
       </c>
       <c r="H343" t="n">
         <v>5200</v>
@@ -10490,7 +10490,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G349" t="n">
-        <v>7.08579778671265</v>
+        <v>7.0857982635498</v>
       </c>
       <c r="H349" t="n">
         <v>3522</v>
@@ -10780,7 +10780,7 @@
         <v>8</v>
       </c>
       <c r="G359" t="n">
-        <v>6.87941551208496</v>
+        <v>6.87941598892212</v>
       </c>
       <c r="H359" t="n">
         <v>140</v>
@@ -10867,7 +10867,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="n">
-        <v>6.87941551208496</v>
+        <v>6.87941598892212</v>
       </c>
       <c r="H362" t="n">
         <v>3100</v>
@@ -11041,7 +11041,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>6.87941551208496</v>
+        <v>6.87941598892212</v>
       </c>
       <c r="H368" t="n">
         <v>200</v>
@@ -11186,7 +11186,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>7.05140066146851</v>
+        <v>7.05140113830566</v>
       </c>
       <c r="H373" t="n">
         <v>354</v>
@@ -11215,7 +11215,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G374" t="n">
-        <v>6.75902652740479</v>
+        <v>6.75902605056763</v>
       </c>
       <c r="H374" t="n">
         <v>25405</v>
@@ -11418,7 +11418,7 @@
         <v>8</v>
       </c>
       <c r="G381" t="n">
-        <v>6.87941551208496</v>
+        <v>6.87941598892212</v>
       </c>
       <c r="H381" t="n">
         <v>1532</v>
@@ -11447,7 +11447,7 @@
         <v>8</v>
       </c>
       <c r="G382" t="n">
-        <v>6.87941551208496</v>
+        <v>6.87941598892212</v>
       </c>
       <c r="H382" t="n">
         <v>291</v>
@@ -11476,7 +11476,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G383" t="n">
-        <v>6.93101119995117</v>
+        <v>6.93101167678833</v>
       </c>
       <c r="H383" t="n">
         <v>4605</v>
@@ -11679,7 +11679,7 @@
         <v>8</v>
       </c>
       <c r="G390" t="n">
-        <v>6.87941551208496</v>
+        <v>6.87941598892212</v>
       </c>
       <c r="H390" t="n">
         <v>7347</v>
@@ -11766,7 +11766,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G393" t="n">
-        <v>6.69023132324219</v>
+        <v>6.69023180007935</v>
       </c>
       <c r="H393" t="n">
         <v>24134</v>
@@ -11795,7 +11795,7 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>6.87941551208496</v>
+        <v>6.87941598892212</v>
       </c>
       <c r="H394" t="n">
         <v>1786</v>
@@ -11911,7 +11911,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>6.93101119995117</v>
+        <v>6.93101167678833</v>
       </c>
       <c r="H398" t="n">
         <v>2460</v>
@@ -11969,7 +11969,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G400" t="n">
-        <v>7.01700401306152</v>
+        <v>7.01700353622437</v>
       </c>
       <c r="H400" t="n">
         <v>4830</v>
@@ -11998,7 +11998,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G401" t="n">
-        <v>7.01700401306152</v>
+        <v>7.01700353622437</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -12027,7 +12027,7 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>6.87941551208496</v>
+        <v>6.87941598892212</v>
       </c>
       <c r="H402" t="n">
         <v>6710</v>
@@ -12056,7 +12056,7 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>6.87941551208496</v>
+        <v>6.87941598892212</v>
       </c>
       <c r="H403" t="n">
         <v>2710</v>
@@ -12114,7 +12114,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G405" t="n">
-        <v>6.75902652740479</v>
+        <v>6.75902605056763</v>
       </c>
       <c r="H405" t="n">
         <v>3290</v>
@@ -12259,7 +12259,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G410" t="n">
-        <v>7.46416616439819</v>
+        <v>7.46416568756104</v>
       </c>
       <c r="H410" t="n">
         <v>32960</v>
@@ -12317,7 +12317,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G412" t="n">
-        <v>7.48136425018311</v>
+        <v>7.48136377334595</v>
       </c>
       <c r="H412" t="n">
         <v>4587</v>
@@ -12346,7 +12346,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65335035324097</v>
       </c>
       <c r="H413" t="n">
         <v>3920</v>
@@ -12404,7 +12404,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G415" t="n">
-        <v>7.61895179748535</v>
+        <v>7.61895227432251</v>
       </c>
       <c r="H415" t="n">
         <v>5660</v>
@@ -12636,7 +12636,7 @@
         <v>8.5</v>
       </c>
       <c r="G423" t="n">
-        <v>7.30937814712524</v>
+        <v>7.3093786239624</v>
       </c>
       <c r="H423" t="n">
         <v>1963</v>
@@ -12665,7 +12665,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65335035324097</v>
       </c>
       <c r="H424" t="n">
         <v>13987</v>
@@ -12781,7 +12781,7 @@
         <v>8.5</v>
       </c>
       <c r="G428" t="n">
-        <v>7.30937814712524</v>
+        <v>7.3093786239624</v>
       </c>
       <c r="H428" t="n">
         <v>1002</v>
@@ -12810,7 +12810,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G429" t="n">
-        <v>7.29218006134033</v>
+        <v>7.29218053817749</v>
       </c>
       <c r="H429" t="n">
         <v>314</v>
@@ -12868,7 +12868,7 @@
         <v>8.5</v>
       </c>
       <c r="G431" t="n">
-        <v>7.30937814712524</v>
+        <v>7.3093786239624</v>
       </c>
       <c r="H431" t="n">
         <v>400</v>
@@ -12926,7 +12926,7 @@
         <v>9</v>
       </c>
       <c r="G433" t="n">
-        <v>7.73934268951416</v>
+        <v>7.739342212677</v>
       </c>
       <c r="H433" t="n">
         <v>12673</v>
@@ -12984,7 +12984,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G435" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65335035324097</v>
       </c>
       <c r="H435" t="n">
         <v>1451</v>
@@ -13013,7 +13013,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>7.48136425018311</v>
+        <v>7.48136377334595</v>
       </c>
       <c r="H436" t="n">
         <v>2489</v>
@@ -13187,7 +13187,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>7.78233909606934</v>
+        <v>7.78234004974365</v>
       </c>
       <c r="H442" t="n">
         <v>10</v>
@@ -13303,7 +13303,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G446" t="n">
-        <v>7.43836736679077</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H446" t="n">
         <v>5102</v>
@@ -13332,7 +13332,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>7.43836736679077</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H447" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G449" t="n">
-        <v>7.43836736679077</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H449" t="n">
         <v>1237</v>
@@ -13419,7 +13419,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G450" t="n">
-        <v>7.43836736679077</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G451" t="n">
-        <v>7.43836736679077</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H451" t="n">
         <v>3000</v>
@@ -13941,7 +13941,7 @@
         <v>8</v>
       </c>
       <c r="G468" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H468" t="n">
         <v>56</v>
@@ -13970,7 +13970,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G469" t="n">
-        <v>7.15537786483765</v>
+        <v>7.15537738800049</v>
       </c>
       <c r="H469" t="n">
         <v>1420</v>
@@ -14028,7 +14028,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>7.28870725631714</v>
+        <v>7.2887077331543</v>
       </c>
       <c r="H471" t="n">
         <v>30</v>
@@ -14115,7 +14115,7 @@
         <v>8.5</v>
       </c>
       <c r="G474" t="n">
-        <v>7.55536699295044</v>
+        <v>7.5553674697876</v>
       </c>
       <c r="H474" t="n">
         <v>3000</v>
@@ -14144,7 +14144,7 @@
         <v>8.5</v>
       </c>
       <c r="G475" t="n">
-        <v>7.55536699295044</v>
+        <v>7.5553674697876</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>8.5</v>
       </c>
       <c r="G476" t="n">
-        <v>7.55536699295044</v>
+        <v>7.5553674697876</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14260,7 +14260,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G479" t="n">
-        <v>7.28870725631714</v>
+        <v>7.2887077331543</v>
       </c>
       <c r="H479" t="n">
         <v>3000</v>
@@ -14289,7 +14289,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G480" t="n">
-        <v>7.46648073196411</v>
+        <v>7.46648025512695</v>
       </c>
       <c r="H480" t="n">
         <v>10</v>
@@ -14318,7 +14318,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G481" t="n">
-        <v>7.46648073196411</v>
+        <v>7.46648025512695</v>
       </c>
       <c r="H481" t="n">
         <v>0</v>
@@ -14347,7 +14347,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G482" t="n">
-        <v>7.46648073196411</v>
+        <v>7.46648025512695</v>
       </c>
       <c r="H482" t="n">
         <v>0</v>
@@ -14666,7 +14666,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G493" t="n">
-        <v>7.46648073196411</v>
+        <v>7.46648025512695</v>
       </c>
       <c r="H493" t="n">
         <v>2584</v>
@@ -14811,7 +14811,7 @@
         <v>8</v>
       </c>
       <c r="G498" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H498" t="n">
         <v>2910</v>
@@ -14869,7 +14869,7 @@
         <v>8</v>
       </c>
       <c r="G500" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H500" t="n">
         <v>225</v>
@@ -14985,7 +14985,7 @@
         <v>8</v>
       </c>
       <c r="G504" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H504" t="n">
         <v>20</v>
@@ -15014,7 +15014,7 @@
         <v>8</v>
       </c>
       <c r="G505" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H505" t="n">
         <v>2776</v>
@@ -15043,7 +15043,7 @@
         <v>8</v>
       </c>
       <c r="G506" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>8</v>
       </c>
       <c r="G509" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H509" t="n">
         <v>422</v>
@@ -15188,7 +15188,7 @@
         <v>8</v>
       </c>
       <c r="G511" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H511" t="n">
         <v>200</v>
@@ -15217,7 +15217,7 @@
         <v>8</v>
       </c>
       <c r="G512" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H512" t="n">
         <v>0</v>
@@ -15275,7 +15275,7 @@
         <v>7.75</v>
       </c>
       <c r="G514" t="n">
-        <v>6.88871812820435</v>
+        <v>6.88871765136719</v>
       </c>
       <c r="H514" t="n">
         <v>1660</v>
@@ -15304,7 +15304,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G515" t="n">
-        <v>7.15537786483765</v>
+        <v>7.15537738800049</v>
       </c>
       <c r="H515" t="n">
         <v>10</v>
@@ -15333,7 +15333,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>6.97760391235352</v>
+        <v>6.97760438919067</v>
       </c>
       <c r="H516" t="n">
         <v>192</v>
@@ -15391,7 +15391,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G518" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761383056641</v>
       </c>
       <c r="H518" t="n">
         <v>2860</v>
@@ -15478,7 +15478,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G521" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761383056641</v>
       </c>
       <c r="H521" t="n">
         <v>300</v>
@@ -15507,7 +15507,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761383056641</v>
       </c>
       <c r="H522" t="n">
         <v>26</v>
@@ -15536,7 +15536,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761383056641</v>
       </c>
       <c r="H523" t="n">
         <v>16875</v>
@@ -15710,7 +15710,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761383056641</v>
       </c>
       <c r="H529" t="n">
         <v>700</v>
@@ -15739,7 +15739,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G530" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761383056641</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -15768,7 +15768,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>6.53317070007324</v>
+        <v>6.5331711769104</v>
       </c>
       <c r="H531" t="n">
         <v>1</v>
@@ -15855,7 +15855,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.39984035491943</v>
+        <v>6.39984083175659</v>
       </c>
       <c r="H534" t="n">
         <v>2911</v>
@@ -15884,7 +15884,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>6.53317070007324</v>
+        <v>6.5331711769104</v>
       </c>
       <c r="H535" t="n">
         <v>1925</v>
@@ -16087,7 +16087,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.39984035491943</v>
+        <v>6.39984083175659</v>
       </c>
       <c r="H542" t="n">
         <v>6172</v>
@@ -16116,7 +16116,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>6.39984035491943</v>
+        <v>6.39984083175659</v>
       </c>
       <c r="H543" t="n">
         <v>3219</v>
@@ -16174,7 +16174,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761383056641</v>
       </c>
       <c r="H545" t="n">
         <v>3438</v>
@@ -16232,7 +16232,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761383056641</v>
       </c>
       <c r="H547" t="n">
         <v>550</v>
@@ -16261,7 +16261,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G548" t="n">
-        <v>6.53317070007324</v>
+        <v>6.5331711769104</v>
       </c>
       <c r="H548" t="n">
         <v>147</v>
@@ -16290,7 +16290,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761383056641</v>
       </c>
       <c r="H549" t="n">
         <v>450</v>
@@ -16319,7 +16319,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G550" t="n">
-        <v>6.53317070007324</v>
+        <v>6.5331711769104</v>
       </c>
       <c r="H550" t="n">
         <v>976</v>
@@ -16348,7 +16348,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G551" t="n">
-        <v>6.53317070007324</v>
+        <v>6.5331711769104</v>
       </c>
       <c r="H551" t="n">
         <v>1277</v>
@@ -16377,7 +16377,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G552" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H552" t="n">
         <v>1717</v>
@@ -16493,7 +16493,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G556" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H556" t="n">
         <v>670</v>
@@ -16522,7 +16522,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G557" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H557" t="n">
         <v>3189</v>
@@ -16580,7 +16580,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G559" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H559" t="n">
         <v>7637</v>
@@ -16609,7 +16609,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H560" t="n">
         <v>3012</v>
@@ -16638,7 +16638,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16725,7 +16725,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H564" t="n">
         <v>300</v>
@@ -16754,7 +16754,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -17363,7 +17363,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G586" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H586" t="n">
         <v>2734</v>
@@ -17392,7 +17392,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H587" t="n">
         <v>3257</v>
@@ -17479,7 +17479,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G590" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H590" t="n">
         <v>8364</v>
@@ -17508,7 +17508,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>6.13318061828613</v>
+        <v>6.13318109512329</v>
       </c>
       <c r="H591" t="n">
         <v>200</v>
@@ -17537,7 +17537,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H592" t="n">
         <v>3684</v>
@@ -17653,7 +17653,7 @@
         <v>6.75</v>
       </c>
       <c r="G596" t="n">
-        <v>5.99985122680664</v>
+        <v>5.99985074996948</v>
       </c>
       <c r="H596" t="n">
         <v>10250</v>
@@ -17711,7 +17711,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H598" t="n">
         <v>8965</v>
@@ -17740,7 +17740,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G599" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H599" t="n">
         <v>11436</v>
@@ -17914,7 +17914,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G605" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H605" t="n">
         <v>2051</v>
@@ -17943,7 +17943,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G606" t="n">
-        <v>5.82207727432251</v>
+        <v>5.82207775115967</v>
       </c>
       <c r="H606" t="n">
         <v>6520</v>
@@ -18233,7 +18233,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G616" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H616" t="n">
         <v>3231</v>
@@ -18262,7 +18262,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G618" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H618" t="n">
         <v>2032</v>
@@ -18320,7 +18320,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G619" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H619" t="n">
         <v>50</v>
@@ -18349,7 +18349,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H620" t="n">
         <v>7613</v>
@@ -18697,7 +18697,7 @@
         <v>6.75</v>
       </c>
       <c r="G632" t="n">
-        <v>5.99985122680664</v>
+        <v>5.99985074996948</v>
       </c>
       <c r="H632" t="n">
         <v>7978</v>
@@ -18755,7 +18755,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G634" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H634" t="n">
         <v>2000</v>
@@ -18987,7 +18987,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H642" t="n">
         <v>2879</v>
@@ -19074,7 +19074,7 @@
         <v>6.25</v>
       </c>
       <c r="G645" t="n">
-        <v>5.55541706085205</v>
+        <v>5.55541753768921</v>
       </c>
       <c r="H645" t="n">
         <v>3525</v>
@@ -19306,7 +19306,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G653" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H653" t="n">
         <v>4753</v>
@@ -19567,7 +19567,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G662" t="n">
-        <v>5.37764453887939</v>
+        <v>5.37764406204224</v>
       </c>
       <c r="H662" t="n">
         <v>1</v>
@@ -19741,7 +19741,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>4.07100963592529</v>
+        <v>4.07101011276245</v>
       </c>
       <c r="H668" t="n">
         <v>934</v>
@@ -20002,7 +20002,7 @@
         <v>4.5</v>
       </c>
       <c r="G677" t="n">
-        <v>3.99990057945251</v>
+        <v>3.99990034103394</v>
       </c>
       <c r="H677" t="n">
         <v>2379</v>
@@ -20060,7 +20060,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.8932363986969</v>
+        <v>3.89323663711548</v>
       </c>
       <c r="H679" t="n">
         <v>5101</v>
@@ -20089,7 +20089,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G680" t="n">
-        <v>3.8576819896698</v>
+        <v>3.85768175125122</v>
       </c>
       <c r="H680" t="n">
         <v>4718</v>
@@ -20118,7 +20118,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>3.73324036598206</v>
+        <v>3.73324012756348</v>
       </c>
       <c r="H681" t="n">
         <v>1886</v>
@@ -20147,7 +20147,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G682" t="n">
-        <v>3.75101804733276</v>
+        <v>3.75101780891418</v>
       </c>
       <c r="H682" t="n">
         <v>2412</v>
@@ -20176,7 +20176,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G683" t="n">
-        <v>3.64435362815857</v>
+        <v>3.64435386657715</v>
       </c>
       <c r="H683" t="n">
         <v>1800</v>
@@ -20321,7 +20321,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>3.8576819896698</v>
+        <v>3.85768175125122</v>
       </c>
       <c r="H688" t="n">
         <v>1215</v>
@@ -20350,7 +20350,7 @@
         <v>4.5</v>
       </c>
       <c r="G689" t="n">
-        <v>3.99990057945251</v>
+        <v>3.99990034103394</v>
       </c>
       <c r="H689" t="n">
         <v>1891</v>
@@ -20437,7 +20437,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>3.96434593200684</v>
+        <v>3.96434569358826</v>
       </c>
       <c r="H692" t="n">
         <v>7551</v>
@@ -20495,7 +20495,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G694" t="n">
-        <v>3.8576819896698</v>
+        <v>3.85768175125122</v>
       </c>
       <c r="H694" t="n">
         <v>6301</v>
@@ -20582,7 +20582,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G697" t="n">
-        <v>3.95545697212219</v>
+        <v>3.95545744895935</v>
       </c>
       <c r="H697" t="n">
         <v>9501</v>
@@ -20611,7 +20611,7 @@
         <v>4.5</v>
       </c>
       <c r="G698" t="n">
-        <v>3.99990057945251</v>
+        <v>3.99990034103394</v>
       </c>
       <c r="H698" t="n">
         <v>1703</v>
@@ -20727,7 +20727,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G702" t="n">
-        <v>3.8932363986969</v>
+        <v>3.89323663711548</v>
       </c>
       <c r="H702" t="n">
         <v>8208</v>
@@ -20756,7 +20756,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>3.76879501342773</v>
+        <v>3.76879525184631</v>
       </c>
       <c r="H703" t="n">
         <v>6306</v>
@@ -20785,7 +20785,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G704" t="n">
-        <v>3.90212535858154</v>
+        <v>3.90212512016296</v>
       </c>
       <c r="H704" t="n">
         <v>1895</v>
@@ -20959,7 +20959,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>3.71546292304993</v>
+        <v>3.71546316146851</v>
       </c>
       <c r="H710" t="n">
         <v>8368</v>
@@ -20988,7 +20988,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G711" t="n">
-        <v>3.76879501342773</v>
+        <v>3.76879525184631</v>
       </c>
       <c r="H711" t="n">
         <v>5939</v>
@@ -21017,7 +21017,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G712" t="n">
-        <v>3.75101804733276</v>
+        <v>3.75101780891418</v>
       </c>
       <c r="H712" t="n">
         <v>2662</v>
@@ -21191,7 +21191,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G718" t="n">
-        <v>3.8932363986969</v>
+        <v>3.89323663711548</v>
       </c>
       <c r="H718" t="n">
         <v>38481</v>
@@ -21452,7 +21452,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G727" t="n">
-        <v>4.09767627716064</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H727" t="n">
         <v>30466</v>
@@ -68554,6 +68554,35 @@
         <v>81646</v>
       </c>
       <c r="I2351" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2352" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2352" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D2352" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="E2352" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F2352" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="G2352" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="H2352" t="n">
+        <v>13877</v>
+      </c>
+      <c r="I2352" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2" t="n">
-        <v>9.40188121795654</v>
+        <v>9.40188026428223</v>
       </c>
       <c r="H2" t="n">
         <v>56600</v>
@@ -456,7 +456,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G3" t="n">
-        <v>9.44389152526855</v>
+        <v>9.44388961791992</v>
       </c>
       <c r="H3" t="n">
         <v>18800</v>
@@ -543,7 +543,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.65394115447998</v>
+        <v>9.6539421081543</v>
       </c>
       <c r="H6" t="n">
         <v>18000</v>
@@ -572,7 +572,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>9.5783224105835</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H7" t="n">
         <v>14800</v>
@@ -601,7 +601,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.65394115447998</v>
+        <v>9.6539421081543</v>
       </c>
       <c r="H8" t="n">
         <v>4800</v>
@@ -630,7 +630,7 @@
         <v>11.5</v>
       </c>
       <c r="G9" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H9" t="n">
         <v>2200</v>
@@ -659,7 +659,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>9.5783224105835</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H10" t="n">
         <v>4000</v>
@@ -688,7 +688,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G11" t="n">
-        <v>9.737961769104</v>
+        <v>9.73796272277832</v>
       </c>
       <c r="H11" t="n">
         <v>7000</v>
@@ -746,7 +746,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033271789551</v>
       </c>
       <c r="H13" t="n">
         <v>1200</v>
@@ -804,7 +804,7 @@
         <v>11.5</v>
       </c>
       <c r="G15" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H15" t="n">
         <v>13400</v>
@@ -862,7 +862,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>9.52791213989258</v>
+        <v>9.52791118621826</v>
       </c>
       <c r="H17" t="n">
         <v>248200</v>
@@ -920,7 +920,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>9.5783224105835</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H19" t="n">
         <v>2400</v>
@@ -949,7 +949,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G20" t="n">
-        <v>9.61193180084229</v>
+        <v>9.61193084716797</v>
       </c>
       <c r="H20" t="n">
         <v>2200</v>
@@ -978,7 +978,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>9.61193180084229</v>
+        <v>9.61193084716797</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>9.53631401062012</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H23" t="n">
         <v>800</v>
@@ -1065,7 +1065,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G24" t="n">
-        <v>9.40188121795654</v>
+        <v>9.40188026428223</v>
       </c>
       <c r="H24" t="n">
         <v>600</v>
@@ -1210,7 +1210,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G29" t="n">
-        <v>9.56152057647705</v>
+        <v>9.56151962280273</v>
       </c>
       <c r="H29" t="n">
         <v>6000</v>
@@ -1239,7 +1239,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G30" t="n">
-        <v>9.51951026916504</v>
+        <v>9.51950931549072</v>
       </c>
       <c r="H30" t="n">
         <v>2600</v>
@@ -1268,7 +1268,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G31" t="n">
-        <v>9.52791213989258</v>
+        <v>9.52791118621826</v>
       </c>
       <c r="H31" t="n">
         <v>4600</v>
@@ -1297,7 +1297,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H32" t="n">
         <v>1600</v>
@@ -1326,7 +1326,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G33" t="n">
-        <v>9.56992244720459</v>
+        <v>9.56992149353027</v>
       </c>
       <c r="H33" t="n">
         <v>1800</v>
@@ -1355,7 +1355,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G34" t="n">
-        <v>9.52791213989258</v>
+        <v>9.52791118621826</v>
       </c>
       <c r="H34" t="n">
         <v>14200</v>
@@ -1384,7 +1384,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H35" t="n">
         <v>800</v>
@@ -1413,7 +1413,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H36" t="n">
         <v>400</v>
@@ -1442,7 +1442,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G37" t="n">
-        <v>9.56992244720459</v>
+        <v>9.56992149353027</v>
       </c>
       <c r="H37" t="n">
         <v>3000</v>
@@ -1471,7 +1471,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>9.53631401062012</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H38" t="n">
         <v>2400</v>
@@ -1529,7 +1529,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G40" t="n">
-        <v>9.737961769104</v>
+        <v>9.73796272277832</v>
       </c>
       <c r="H40" t="n">
         <v>21400</v>
@@ -1558,7 +1558,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G41" t="n">
-        <v>9.737961769104</v>
+        <v>9.73796272277832</v>
       </c>
       <c r="H41" t="n">
         <v>1400</v>
@@ -1674,7 +1674,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G45" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198333740234</v>
       </c>
       <c r="H45" t="n">
         <v>14000</v>
@@ -1732,7 +1732,7 @@
         <v>11.5</v>
       </c>
       <c r="G47" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H47" t="n">
         <v>11200</v>
@@ -1819,7 +1819,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G50" t="n">
-        <v>9.76316738128662</v>
+        <v>9.76316928863525</v>
       </c>
       <c r="H50" t="n">
         <v>6600</v>
@@ -1848,7 +1848,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G51" t="n">
-        <v>10.1832695007324</v>
+        <v>10.1832714080811</v>
       </c>
       <c r="H51" t="n">
         <v>127800</v>
@@ -1877,7 +1877,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H52" t="n">
         <v>97800</v>
@@ -1906,7 +1906,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G53" t="n">
-        <v>9.77997207641602</v>
+        <v>9.77997303009033</v>
       </c>
       <c r="H53" t="n">
         <v>4200</v>
@@ -1993,7 +1993,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H56" t="n">
         <v>20400</v>
@@ -2022,7 +2022,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G57" t="n">
-        <v>9.95641613006592</v>
+        <v>9.9564151763916</v>
       </c>
       <c r="H57" t="n">
         <v>35400</v>
@@ -2051,7 +2051,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>9.95641613006592</v>
+        <v>9.9564151763916</v>
       </c>
       <c r="H58" t="n">
         <v>25000</v>
@@ -2167,7 +2167,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G62" t="n">
-        <v>9.99002361297607</v>
+        <v>9.99002456665039</v>
       </c>
       <c r="H62" t="n">
         <v>36400</v>
@@ -2254,7 +2254,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198333740234</v>
       </c>
       <c r="H65" t="n">
         <v>8600</v>
@@ -2312,7 +2312,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G67" t="n">
-        <v>9.93961048126221</v>
+        <v>9.93961143493652</v>
       </c>
       <c r="H67" t="n">
         <v>18400</v>
@@ -2341,7 +2341,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G68" t="n">
-        <v>9.99002361297607</v>
+        <v>9.99002456665039</v>
       </c>
       <c r="H68" t="n">
         <v>13600</v>
@@ -2370,7 +2370,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>9.95641613006592</v>
+        <v>9.9564151763916</v>
       </c>
       <c r="H69" t="n">
         <v>3200</v>
@@ -2399,7 +2399,7 @@
         <v>11.75</v>
       </c>
       <c r="G70" t="n">
-        <v>9.87239646911621</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H70" t="n">
         <v>5200</v>
@@ -2457,7 +2457,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H72" t="n">
         <v>73200</v>
@@ -2486,7 +2486,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G73" t="n">
-        <v>10.057240486145</v>
+        <v>10.0572395324707</v>
       </c>
       <c r="H73" t="n">
         <v>150000</v>
@@ -2573,7 +2573,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G76" t="n">
-        <v>10.0488376617432</v>
+        <v>10.0488367080688</v>
       </c>
       <c r="H76" t="n">
         <v>116000</v>
@@ -2689,7 +2689,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G80" t="n">
-        <v>10.0488376617432</v>
+        <v>10.0488367080688</v>
       </c>
       <c r="H80" t="n">
         <v>12400</v>
@@ -2747,7 +2747,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G82" t="n">
-        <v>9.99002361297607</v>
+        <v>9.99002456665039</v>
       </c>
       <c r="H82" t="n">
         <v>4200</v>
@@ -2776,7 +2776,7 @@
         <v>11.75</v>
       </c>
       <c r="G83" t="n">
-        <v>9.87239646911621</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H83" t="n">
         <v>13000</v>
@@ -2805,7 +2805,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H84" t="n">
         <v>6200</v>
@@ -2834,7 +2834,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G85" t="n">
-        <v>9.90600299835205</v>
+        <v>9.90600395202637</v>
       </c>
       <c r="H85" t="n">
         <v>4200</v>
@@ -2863,7 +2863,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H86" t="n">
         <v>5400</v>
@@ -2921,7 +2921,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G88" t="n">
-        <v>9.90600299835205</v>
+        <v>9.90600395202637</v>
       </c>
       <c r="H88" t="n">
         <v>600</v>
@@ -2950,7 +2950,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H89" t="n">
         <v>22400</v>
@@ -2979,7 +2979,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H90" t="n">
         <v>2000</v>
@@ -3008,7 +3008,7 @@
         <v>11.75</v>
       </c>
       <c r="G91" t="n">
-        <v>9.87239646911621</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H91" t="n">
         <v>1000</v>
@@ -3037,7 +3037,7 @@
         <v>11.75</v>
       </c>
       <c r="G92" t="n">
-        <v>9.87239646911621</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H92" t="n">
         <v>3000</v>
@@ -3066,7 +3066,7 @@
         <v>11.75</v>
       </c>
       <c r="G93" t="n">
-        <v>9.87239646911621</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H93" t="n">
         <v>2600</v>
@@ -3095,7 +3095,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H94" t="n">
         <v>6000</v>
@@ -3124,7 +3124,7 @@
         <v>11.75</v>
       </c>
       <c r="G95" t="n">
-        <v>9.87239646911621</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H95" t="n">
         <v>7800</v>
@@ -3153,7 +3153,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H96" t="n">
         <v>2600</v>
@@ -3182,7 +3182,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G97" t="n">
-        <v>10.0488376617432</v>
+        <v>10.0488367080688</v>
       </c>
       <c r="H97" t="n">
         <v>14800</v>
@@ -3211,7 +3211,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G98" t="n">
-        <v>9.98162078857422</v>
+        <v>9.98162174224854</v>
       </c>
       <c r="H98" t="n">
         <v>13400</v>
@@ -3240,7 +3240,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G99" t="n">
-        <v>9.973219871521</v>
+        <v>9.97321891784668</v>
       </c>
       <c r="H99" t="n">
         <v>7400</v>
@@ -3327,7 +3327,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G102" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198333740234</v>
       </c>
       <c r="H102" t="n">
         <v>8200</v>
@@ -3356,7 +3356,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G103" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198333740234</v>
       </c>
       <c r="H103" t="n">
         <v>600</v>
@@ -3385,7 +3385,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G104" t="n">
-        <v>9.737961769104</v>
+        <v>9.73796272277832</v>
       </c>
       <c r="H104" t="n">
         <v>1800</v>
@@ -3501,7 +3501,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G108" t="n">
-        <v>9.65394115447998</v>
+        <v>9.6539421081543</v>
       </c>
       <c r="H108" t="n">
         <v>20400</v>
@@ -3530,7 +3530,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033271789551</v>
       </c>
       <c r="H109" t="n">
         <v>9400</v>
@@ -3559,7 +3559,7 @@
         <v>11.5</v>
       </c>
       <c r="G110" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H110" t="n">
         <v>6400</v>
@@ -3588,7 +3588,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033271789551</v>
       </c>
       <c r="H111" t="n">
         <v>4600</v>
@@ -3617,7 +3617,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>9.53631401062012</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H112" t="n">
         <v>800</v>
@@ -3675,7 +3675,7 @@
         <v>11.5</v>
       </c>
       <c r="G114" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H114" t="n">
         <v>21600</v>
@@ -3704,7 +3704,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G115" t="n">
-        <v>9.72955989837646</v>
+        <v>9.72956085205078</v>
       </c>
       <c r="H115" t="n">
         <v>6000</v>
@@ -3762,7 +3762,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H117" t="n">
         <v>16400</v>
@@ -3791,7 +3791,7 @@
         <v>11.75</v>
       </c>
       <c r="G118" t="n">
-        <v>9.87239646911621</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H118" t="n">
         <v>12000</v>
@@ -3820,7 +3820,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H119" t="n">
         <v>5400</v>
@@ -3878,7 +3878,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H121" t="n">
         <v>6200</v>
@@ -3907,7 +3907,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H122" t="n">
         <v>14000</v>
@@ -4052,7 +4052,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H127" t="n">
         <v>39200</v>
@@ -4139,7 +4139,7 @@
         <v>11.75</v>
       </c>
       <c r="G130" t="n">
-        <v>9.87239646911621</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H130" t="n">
         <v>3400</v>
@@ -4168,7 +4168,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H131" t="n">
         <v>5600</v>
@@ -4284,7 +4284,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H135" t="n">
         <v>5600</v>
@@ -4313,7 +4313,7 @@
         <v>11.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H136" t="n">
         <v>9600</v>
@@ -4342,7 +4342,7 @@
         <v>11.5</v>
       </c>
       <c r="G137" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H137" t="n">
         <v>5800</v>
@@ -4400,7 +4400,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G139" t="n">
-        <v>9.5783224105835</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H139" t="n">
         <v>8000</v>
@@ -4429,7 +4429,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H140" t="n">
         <v>9000</v>
@@ -4458,7 +4458,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H141" t="n">
         <v>1600</v>
@@ -4487,7 +4487,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H142" t="n">
         <v>12000</v>
@@ -4603,7 +4603,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H146" t="n">
         <v>2600</v>
@@ -4632,7 +4632,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G148" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033271789551</v>
       </c>
       <c r="H148" t="n">
         <v>3400</v>
@@ -4690,7 +4690,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H149" t="n">
         <v>5600</v>
@@ -4719,7 +4719,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>9.5783224105835</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H151" t="n">
         <v>2000</v>
@@ -4777,7 +4777,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>9.5783224105835</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H152" t="n">
         <v>800</v>
@@ -4835,7 +4835,7 @@
         <v>11.5</v>
       </c>
       <c r="G154" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H154" t="n">
         <v>1000</v>
@@ -4864,7 +4864,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G155" t="n">
-        <v>9.53631401062012</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H155" t="n">
         <v>27200</v>
@@ -4980,7 +4980,7 @@
         <v>11</v>
       </c>
       <c r="G159" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H159" t="n">
         <v>14600</v>
@@ -5038,7 +5038,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G161" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H161" t="n">
         <v>5600</v>
@@ -5067,7 +5067,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H162" t="n">
         <v>6400</v>
@@ -5096,7 +5096,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>11</v>
       </c>
       <c r="G164" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H164" t="n">
         <v>18800</v>
@@ -5154,7 +5154,7 @@
         <v>11</v>
       </c>
       <c r="G165" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>11</v>
       </c>
       <c r="G166" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H166" t="n">
         <v>400</v>
@@ -5241,7 +5241,7 @@
         <v>11</v>
       </c>
       <c r="G168" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H168" t="n">
         <v>1200</v>
@@ -5270,7 +5270,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>9.28425407409668</v>
+        <v>9.28425312042236</v>
       </c>
       <c r="H169" t="n">
         <v>200</v>
@@ -5299,7 +5299,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G170" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H170" t="n">
         <v>1000</v>
@@ -5357,7 +5357,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H172" t="n">
         <v>35400</v>
@@ -5386,7 +5386,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>9.5783224105835</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H173" t="n">
         <v>3000</v>
@@ -5415,7 +5415,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H174" t="n">
         <v>33600</v>
@@ -5502,7 +5502,7 @@
         <v>11</v>
       </c>
       <c r="G177" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H177" t="n">
         <v>5200</v>
@@ -5560,7 +5560,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G179" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H179" t="n">
         <v>4000</v>
@@ -5647,7 +5647,7 @@
         <v>11</v>
       </c>
       <c r="G182" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H182" t="n">
         <v>10000</v>
@@ -5705,7 +5705,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G184" t="n">
-        <v>9.1162109375</v>
+        <v>9.11621189117432</v>
       </c>
       <c r="H184" t="n">
         <v>7200</v>
@@ -5879,7 +5879,7 @@
         <v>10.75</v>
       </c>
       <c r="G190" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H190" t="n">
         <v>400</v>
@@ -5908,7 +5908,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>9.1162109375</v>
+        <v>9.11621189117432</v>
       </c>
       <c r="H191" t="n">
         <v>11600</v>
@@ -5937,7 +5937,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>9.1162109375</v>
+        <v>9.11621189117432</v>
       </c>
       <c r="H192" t="n">
         <v>400</v>
@@ -5966,7 +5966,7 @@
         <v>10.75</v>
       </c>
       <c r="G193" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H193" t="n">
         <v>400</v>
@@ -5995,7 +5995,7 @@
         <v>10.75</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H194" t="n">
         <v>600</v>
@@ -6053,7 +6053,7 @@
         <v>10.75</v>
       </c>
       <c r="G196" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H196" t="n">
         <v>10200</v>
@@ -6836,7 +6836,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G223" t="n">
-        <v>8.90024566650391</v>
+        <v>8.90024471282959</v>
       </c>
       <c r="H223" t="n">
         <v>20400</v>
@@ -6865,7 +6865,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H224" t="n">
         <v>3000</v>
@@ -6894,7 +6894,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G225" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>8.90024566650391</v>
+        <v>8.90024471282959</v>
       </c>
       <c r="H226" t="n">
         <v>1200</v>
@@ -8112,7 +8112,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H267" t="n">
         <v>8000</v>
@@ -8141,7 +8141,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G268" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H268" t="n">
         <v>2200</v>
@@ -8170,7 +8170,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H269" t="n">
         <v>400</v>
@@ -8257,7 +8257,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G272" t="n">
-        <v>8.28969669342041</v>
+        <v>8.28969573974609</v>
       </c>
       <c r="H272" t="n">
         <v>9600</v>
@@ -8286,7 +8286,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G273" t="n">
-        <v>8.28969669342041</v>
+        <v>8.28969573974609</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G282" t="n">
-        <v>8.51327705383301</v>
+        <v>8.51327610015869</v>
       </c>
       <c r="H282" t="n">
         <v>2000</v>
@@ -8721,7 +8721,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G288" t="n">
-        <v>8.22090148925781</v>
+        <v>8.22090244293213</v>
       </c>
       <c r="H288" t="n">
         <v>2600</v>
@@ -8953,7 +8953,7 @@
         <v>9.5</v>
       </c>
       <c r="G296" t="n">
-        <v>8.1693058013916</v>
+        <v>8.16930484771729</v>
       </c>
       <c r="H296" t="n">
         <v>17200</v>
@@ -9156,7 +9156,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G303" t="n">
-        <v>8.53047466278076</v>
+        <v>8.53047561645508</v>
       </c>
       <c r="H303" t="n">
         <v>2000</v>
@@ -9562,7 +9562,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H317" t="n">
         <v>4200</v>
@@ -9620,7 +9620,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G319" t="n">
-        <v>7.36097478866577</v>
+        <v>7.36097526550293</v>
       </c>
       <c r="H319" t="n">
         <v>2400</v>
@@ -9707,7 +9707,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G322" t="n">
-        <v>7.18898916244507</v>
+        <v>7.18898963928223</v>
       </c>
       <c r="H322" t="n">
         <v>1400</v>
@@ -9736,7 +9736,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G323" t="n">
-        <v>6.99980545043945</v>
+        <v>6.99980592727661</v>
       </c>
       <c r="H323" t="n">
         <v>800</v>
@@ -9765,7 +9765,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G324" t="n">
-        <v>6.86221742630005</v>
+        <v>6.86221694946289</v>
       </c>
       <c r="H324" t="n">
         <v>3200</v>
@@ -9910,7 +9910,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G329" t="n">
-        <v>7.65335035324097</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H329" t="n">
         <v>600</v>
@@ -10055,7 +10055,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>7.65335035324097</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H334" t="n">
         <v>800</v>
@@ -10084,7 +10084,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G335" t="n">
-        <v>7.65335035324097</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G336" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H336" t="n">
         <v>1000</v>
@@ -10142,7 +10142,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>7.41256952285767</v>
+        <v>7.41256999969482</v>
       </c>
       <c r="H337" t="n">
         <v>3600</v>
@@ -10200,7 +10200,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H339" t="n">
         <v>400</v>
@@ -10229,7 +10229,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G340" t="n">
-        <v>7.29218053817749</v>
+        <v>7.29218006134033</v>
       </c>
       <c r="H340" t="n">
         <v>2800</v>
@@ -10374,7 +10374,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G345" t="n">
-        <v>6.99980545043945</v>
+        <v>6.99980592727661</v>
       </c>
       <c r="H345" t="n">
         <v>5400</v>
@@ -10519,7 +10519,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G350" t="n">
-        <v>6.99980545043945</v>
+        <v>6.99980592727661</v>
       </c>
       <c r="H350" t="n">
         <v>18548</v>
@@ -10809,7 +10809,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>6.7418270111084</v>
+        <v>6.74182748794556</v>
       </c>
       <c r="H360" t="n">
         <v>3952</v>
@@ -10838,7 +10838,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>6.7418270111084</v>
+        <v>6.74182748794556</v>
       </c>
       <c r="H361" t="n">
         <v>4250</v>
@@ -10896,7 +10896,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>6.7418270111084</v>
+        <v>6.74182748794556</v>
       </c>
       <c r="H363" t="n">
         <v>6700</v>
@@ -10925,7 +10925,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G364" t="n">
-        <v>6.63863611221313</v>
+        <v>6.63863563537598</v>
       </c>
       <c r="H364" t="n">
         <v>1200</v>
@@ -10954,7 +10954,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G365" t="n">
-        <v>6.79342269897461</v>
+        <v>6.79342317581177</v>
       </c>
       <c r="H365" t="n">
         <v>830</v>
@@ -11244,7 +11244,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G375" t="n">
-        <v>6.79342269897461</v>
+        <v>6.79342317581177</v>
       </c>
       <c r="H375" t="n">
         <v>950</v>
@@ -11360,7 +11360,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>6.86221742630005</v>
+        <v>6.86221694946289</v>
       </c>
       <c r="H379" t="n">
         <v>1210</v>
@@ -11389,7 +11389,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>6.86221742630005</v>
+        <v>6.86221694946289</v>
       </c>
       <c r="H380" t="n">
         <v>1253</v>
@@ -11708,7 +11708,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>6.86221742630005</v>
+        <v>6.86221694946289</v>
       </c>
       <c r="H391" t="n">
         <v>2600</v>
@@ -12085,7 +12085,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>6.79342269897461</v>
+        <v>6.79342317581177</v>
       </c>
       <c r="H404" t="n">
         <v>57</v>
@@ -12172,7 +12172,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>6.79342269897461</v>
+        <v>6.79342317581177</v>
       </c>
       <c r="H407" t="n">
         <v>20699</v>
@@ -12259,7 +12259,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G410" t="n">
-        <v>7.46416568756104</v>
+        <v>7.46416616439819</v>
       </c>
       <c r="H410" t="n">
         <v>32960</v>
@@ -12346,7 +12346,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.65335035324097</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H413" t="n">
         <v>3920</v>
@@ -12520,7 +12520,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G419" t="n">
-        <v>7.41256952285767</v>
+        <v>7.41256999969482</v>
       </c>
       <c r="H419" t="n">
         <v>8008</v>
@@ -12549,7 +12549,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>7.34377670288086</v>
+        <v>7.3437762260437</v>
       </c>
       <c r="H420" t="n">
         <v>4725</v>
@@ -12578,7 +12578,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>7.34377670288086</v>
+        <v>7.3437762260437</v>
       </c>
       <c r="H421" t="n">
         <v>1620</v>
@@ -12607,7 +12607,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G422" t="n">
-        <v>7.36097478866577</v>
+        <v>7.36097526550293</v>
       </c>
       <c r="H422" t="n">
         <v>1868</v>
@@ -12665,7 +12665,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>7.65335035324097</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H424" t="n">
         <v>13987</v>
@@ -12810,7 +12810,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G429" t="n">
-        <v>7.29218053817749</v>
+        <v>7.29218006134033</v>
       </c>
       <c r="H429" t="n">
         <v>314</v>
@@ -12984,7 +12984,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G435" t="n">
-        <v>7.65335035324097</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H435" t="n">
         <v>1451</v>
@@ -13187,7 +13187,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>7.78234004974365</v>
+        <v>7.78233909606934</v>
       </c>
       <c r="H442" t="n">
         <v>10</v>
@@ -13303,7 +13303,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G446" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836832046509</v>
       </c>
       <c r="H446" t="n">
         <v>5102</v>
@@ -13332,7 +13332,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836832046509</v>
       </c>
       <c r="H447" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G449" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836832046509</v>
       </c>
       <c r="H449" t="n">
         <v>1237</v>
@@ -13419,7 +13419,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G450" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836832046509</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G451" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836832046509</v>
       </c>
       <c r="H451" t="n">
         <v>3000</v>
@@ -13477,7 +13477,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G452" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H452" t="n">
         <v>510</v>
@@ -13506,7 +13506,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G453" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H453" t="n">
         <v>2385</v>
@@ -13535,7 +13535,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G454" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H454" t="n">
         <v>200</v>
@@ -13564,7 +13564,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G455" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H455" t="n">
         <v>18119</v>
@@ -13593,7 +13593,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>7.39537239074707</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H456" t="n">
         <v>695</v>
@@ -13622,7 +13622,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G457" t="n">
-        <v>7.6442551612854</v>
+        <v>7.64425468444824</v>
       </c>
       <c r="H457" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G458" t="n">
-        <v>7.6442551612854</v>
+        <v>7.64425468444824</v>
       </c>
       <c r="H458" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>8.25</v>
       </c>
       <c r="G459" t="n">
-        <v>7.33315086364746</v>
+        <v>7.33315134048462</v>
       </c>
       <c r="H459" t="n">
         <v>6911</v>
@@ -13709,7 +13709,7 @@
         <v>8.25</v>
       </c>
       <c r="G460" t="n">
-        <v>7.33315086364746</v>
+        <v>7.33315134048462</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>8.25</v>
       </c>
       <c r="G467" t="n">
-        <v>7.33315086364746</v>
+        <v>7.33315134048462</v>
       </c>
       <c r="H467" t="n">
         <v>402</v>
@@ -13970,7 +13970,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G469" t="n">
-        <v>7.15537738800049</v>
+        <v>7.15537786483765</v>
       </c>
       <c r="H469" t="n">
         <v>1420</v>
@@ -14231,7 +14231,7 @@
         <v>8.25</v>
       </c>
       <c r="G478" t="n">
-        <v>7.33315086364746</v>
+        <v>7.33315134048462</v>
       </c>
       <c r="H478" t="n">
         <v>1858</v>
@@ -14695,7 +14695,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>7.59981107711792</v>
+        <v>7.59981155395508</v>
       </c>
       <c r="H494" t="n">
         <v>2906</v>
@@ -14956,7 +14956,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G503" t="n">
-        <v>7.02204751968384</v>
+        <v>7.022047996521</v>
       </c>
       <c r="H503" t="n">
         <v>150</v>
@@ -15304,7 +15304,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G515" t="n">
-        <v>7.15537738800049</v>
+        <v>7.15537786483765</v>
       </c>
       <c r="H515" t="n">
         <v>10</v>
@@ -15391,7 +15391,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G518" t="n">
-        <v>6.57761383056641</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H518" t="n">
         <v>2860</v>
@@ -15478,7 +15478,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G521" t="n">
-        <v>6.57761383056641</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H521" t="n">
         <v>300</v>
@@ -15507,7 +15507,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>6.57761383056641</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H522" t="n">
         <v>26</v>
@@ -15536,7 +15536,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>6.57761383056641</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H523" t="n">
         <v>16875</v>
@@ -15710,7 +15710,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>6.57761383056641</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H529" t="n">
         <v>700</v>
@@ -15739,7 +15739,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G530" t="n">
-        <v>6.57761383056641</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -15826,7 +15826,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G533" t="n">
-        <v>6.71094417572021</v>
+        <v>6.71094465255737</v>
       </c>
       <c r="H533" t="n">
         <v>80</v>
@@ -15913,7 +15913,7 @@
         <v>7.25</v>
       </c>
       <c r="G536" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H536" t="n">
         <v>300</v>
@@ -15942,7 +15942,7 @@
         <v>7.25</v>
       </c>
       <c r="G537" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H537" t="n">
         <v>500</v>
@@ -15971,7 +15971,7 @@
         <v>7.25</v>
       </c>
       <c r="G538" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H538" t="n">
         <v>0</v>
@@ -16000,7 +16000,7 @@
         <v>7.25</v>
       </c>
       <c r="G539" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H539" t="n">
         <v>305</v>
@@ -16058,7 +16058,7 @@
         <v>7.25</v>
       </c>
       <c r="G541" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H541" t="n">
         <v>1320</v>
@@ -16174,7 +16174,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>6.57761383056641</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H545" t="n">
         <v>3438</v>
@@ -16232,7 +16232,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>6.57761383056641</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H547" t="n">
         <v>550</v>
@@ -16290,7 +16290,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>6.57761383056641</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H549" t="n">
         <v>450</v>
@@ -16406,7 +16406,7 @@
         <v>7.25</v>
       </c>
       <c r="G553" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H553" t="n">
         <v>343</v>
@@ -17044,7 +17044,7 @@
         <v>7.25</v>
       </c>
       <c r="G575" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H575" t="n">
         <v>6238</v>
@@ -19625,7 +19625,7 @@
         <v>5.75</v>
       </c>
       <c r="G664" t="n">
-        <v>5.11098432540894</v>
+        <v>5.11098384857178</v>
       </c>
       <c r="H664" t="n">
         <v>8131</v>
@@ -19799,7 +19799,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G670" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H670" t="n">
         <v>10643</v>
@@ -19828,7 +19828,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G671" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -19857,7 +19857,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G672" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G673" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G674" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H674" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G675" t="n">
-        <v>3.8221275806427</v>
+        <v>3.82212734222412</v>
       </c>
       <c r="H675" t="n">
         <v>2991</v>
@@ -20089,7 +20089,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G680" t="n">
-        <v>3.85768175125122</v>
+        <v>3.8576819896698</v>
       </c>
       <c r="H680" t="n">
         <v>4718</v>
@@ -20147,7 +20147,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G682" t="n">
-        <v>3.75101780891418</v>
+        <v>3.75101757049561</v>
       </c>
       <c r="H682" t="n">
         <v>2412</v>
@@ -20234,7 +20234,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G685" t="n">
-        <v>3.80434989929199</v>
+        <v>3.80435013771057</v>
       </c>
       <c r="H685" t="n">
         <v>3900</v>
@@ -20321,7 +20321,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>3.85768175125122</v>
+        <v>3.8576819896698</v>
       </c>
       <c r="H688" t="n">
         <v>1215</v>
@@ -20379,7 +20379,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G690" t="n">
-        <v>4.08878755569458</v>
+        <v>4.08878707885742</v>
       </c>
       <c r="H690" t="n">
         <v>5209</v>
@@ -20437,7 +20437,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>3.96434569358826</v>
+        <v>3.96434617042542</v>
       </c>
       <c r="H692" t="n">
         <v>7551</v>
@@ -20495,7 +20495,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G694" t="n">
-        <v>3.85768175125122</v>
+        <v>3.8576819896698</v>
       </c>
       <c r="H694" t="n">
         <v>6301</v>
@@ -20582,7 +20582,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G697" t="n">
-        <v>3.95545744895935</v>
+        <v>3.95545697212219</v>
       </c>
       <c r="H697" t="n">
         <v>9501</v>
@@ -20756,7 +20756,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>3.76879525184631</v>
+        <v>3.76879501342773</v>
       </c>
       <c r="H703" t="n">
         <v>6306</v>
@@ -20901,7 +20901,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G708" t="n">
-        <v>3.83101558685303</v>
+        <v>3.83101582527161</v>
       </c>
       <c r="H708" t="n">
         <v>6323</v>
@@ -20930,7 +20930,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>3.83101558685303</v>
+        <v>3.83101582527161</v>
       </c>
       <c r="H709" t="n">
         <v>2542</v>
@@ -20959,7 +20959,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>3.71546316146851</v>
+        <v>3.71546339988708</v>
       </c>
       <c r="H710" t="n">
         <v>8368</v>
@@ -20988,7 +20988,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G711" t="n">
-        <v>3.76879525184631</v>
+        <v>3.76879501342773</v>
       </c>
       <c r="H711" t="n">
         <v>5939</v>
@@ -21017,7 +21017,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G712" t="n">
-        <v>3.75101780891418</v>
+        <v>3.75101757049561</v>
       </c>
       <c r="H712" t="n">
         <v>2662</v>
@@ -21133,7 +21133,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G716" t="n">
-        <v>3.80434989929199</v>
+        <v>3.80435013771057</v>
       </c>
       <c r="H716" t="n">
         <v>685</v>
@@ -21220,7 +21220,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G719" t="n">
-        <v>4.08878755569458</v>
+        <v>4.08878707885742</v>
       </c>
       <c r="H719" t="n">
         <v>10718</v>
@@ -21249,7 +21249,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G720" t="n">
-        <v>4.06212139129639</v>
+        <v>4.06212091445923</v>
       </c>
       <c r="H720" t="n">
         <v>15398</v>
@@ -21307,7 +21307,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G722" t="n">
-        <v>4.10656452178955</v>
+        <v>4.10656404495239</v>
       </c>
       <c r="H722" t="n">
         <v>4518</v>
@@ -21336,7 +21336,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G723" t="n">
-        <v>4.10656452178955</v>
+        <v>4.10656404495239</v>
       </c>
       <c r="H723" t="n">
         <v>30910</v>
@@ -21452,7 +21452,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G727" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767627716064</v>
       </c>
       <c r="H727" t="n">
         <v>30466</v>
@@ -21539,7 +21539,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>4.38185453414917</v>
+        <v>4.38185501098633</v>
       </c>
       <c r="H730" t="n">
         <v>61399</v>
@@ -21568,7 +21568,7 @@
         <v>4.75</v>
       </c>
       <c r="G731" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H731" t="n">
         <v>16376</v>
@@ -21655,7 +21655,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G734" t="n">
-        <v>4.38185453414917</v>
+        <v>4.38185501098633</v>
       </c>
       <c r="H734" t="n">
         <v>34375</v>
@@ -21684,7 +21684,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G735" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H735" t="n">
         <v>17125</v>
@@ -21713,7 +21713,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G736" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H736" t="n">
         <v>9606</v>
@@ -21742,7 +21742,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G737" t="n">
-        <v>4.40935564041138</v>
+        <v>4.40935611724854</v>
       </c>
       <c r="H737" t="n">
         <v>2683</v>
@@ -21771,7 +21771,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>4.37268781661987</v>
+        <v>4.37268733978271</v>
       </c>
       <c r="H738" t="n">
         <v>600</v>
@@ -21800,7 +21800,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>4.37268781661987</v>
+        <v>4.37268733978271</v>
       </c>
       <c r="H739" t="n">
         <v>680</v>
@@ -21829,7 +21829,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G740" t="n">
-        <v>4.32685232162476</v>
+        <v>4.3268518447876</v>
       </c>
       <c r="H740" t="n">
         <v>7403</v>
@@ -21916,7 +21916,7 @@
         <v>4.75</v>
       </c>
       <c r="G743" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H743" t="n">
         <v>607</v>
@@ -21945,7 +21945,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G744" t="n">
-        <v>4.32685232162476</v>
+        <v>4.3268518447876</v>
       </c>
       <c r="H744" t="n">
         <v>11032</v>
@@ -22032,7 +22032,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G747" t="n">
-        <v>4.23518180847168</v>
+        <v>4.23518133163452</v>
       </c>
       <c r="H747" t="n">
         <v>2630</v>
@@ -22061,7 +22061,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>4.23518180847168</v>
+        <v>4.23518133163452</v>
       </c>
       <c r="H748" t="n">
         <v>1000</v>
@@ -22177,7 +22177,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G752" t="n">
-        <v>4.18934679031372</v>
+        <v>4.18934631347656</v>
       </c>
       <c r="H752" t="n">
         <v>1350</v>
@@ -22380,7 +22380,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G759" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H759" t="n">
         <v>3488</v>
@@ -22467,7 +22467,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.18934679031372</v>
+        <v>4.18934631347656</v>
       </c>
       <c r="H762" t="n">
         <v>4900</v>
@@ -22641,7 +22641,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H768" t="n">
         <v>8119</v>
@@ -22902,7 +22902,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>4.21684789657593</v>
+        <v>4.21684741973877</v>
       </c>
       <c r="H777" t="n">
         <v>7930</v>
@@ -22931,7 +22931,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>4.08850860595703</v>
+        <v>4.08850908279419</v>
       </c>
       <c r="H778" t="n">
         <v>10894</v>
@@ -23105,7 +23105,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G784" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H784" t="n">
         <v>10522</v>
@@ -23163,7 +23163,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G786" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H786" t="n">
         <v>1030</v>
@@ -23192,7 +23192,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G787" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>4.07934188842773</v>
+        <v>4.07934141159058</v>
       </c>
       <c r="H788" t="n">
         <v>5464</v>
@@ -23250,7 +23250,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G789" t="n">
-        <v>4.07934188842773</v>
+        <v>4.07934141159058</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -23337,7 +23337,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>4.04267311096191</v>
+        <v>4.04267358779907</v>
       </c>
       <c r="H792" t="n">
         <v>1205</v>
@@ -23482,7 +23482,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G797" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H797" t="n">
         <v>2403</v>
@@ -23511,7 +23511,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G798" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H798" t="n">
         <v>1860</v>
@@ -23598,7 +23598,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>3.91433477401733</v>
+        <v>3.91433453559875</v>
       </c>
       <c r="H801" t="n">
         <v>1035</v>
@@ -23743,7 +23743,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.86849927902222</v>
+        <v>3.86849904060364</v>
       </c>
       <c r="H806" t="n">
         <v>3833</v>
@@ -23772,7 +23772,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G807" t="n">
-        <v>3.88683342933655</v>
+        <v>3.88683319091797</v>
       </c>
       <c r="H807" t="n">
         <v>13265</v>
@@ -23801,7 +23801,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G808" t="n">
-        <v>3.88683342933655</v>
+        <v>3.88683319091797</v>
       </c>
       <c r="H808" t="n">
         <v>12349</v>
@@ -23946,7 +23946,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G813" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H813" t="n">
         <v>11042</v>
@@ -24004,7 +24004,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>4.37268781661987</v>
+        <v>4.37268733978271</v>
       </c>
       <c r="H815" t="n">
         <v>4760</v>
@@ -24033,7 +24033,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G816" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H816" t="n">
         <v>7780</v>
@@ -24120,7 +24120,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G819" t="n">
-        <v>4.32685232162476</v>
+        <v>4.3268518447876</v>
       </c>
       <c r="H819" t="n">
         <v>785</v>
@@ -24178,7 +24178,7 @@
         <v>4.75</v>
       </c>
       <c r="G821" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H821" t="n">
         <v>6878</v>
@@ -24294,7 +24294,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G825" t="n">
-        <v>4.51936006546021</v>
+        <v>4.51936054229736</v>
       </c>
       <c r="H825" t="n">
         <v>1867</v>
@@ -24352,7 +24352,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>4.51019382476807</v>
+        <v>4.51019334793091</v>
       </c>
       <c r="H827" t="n">
         <v>10424</v>
@@ -24410,7 +24410,7 @@
         <v>4.75</v>
       </c>
       <c r="G829" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H829" t="n">
         <v>5800</v>
@@ -24468,7 +24468,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.04267311096191</v>
+        <v>4.04267358779907</v>
       </c>
       <c r="H831" t="n">
         <v>16333</v>
@@ -24555,7 +24555,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>3.94183611869812</v>
+        <v>3.94183588027954</v>
       </c>
       <c r="H834" t="n">
         <v>25951</v>
@@ -24642,7 +24642,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>4.21684789657593</v>
+        <v>4.21684741973877</v>
       </c>
       <c r="H837" t="n">
         <v>21835</v>
@@ -24729,7 +24729,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G840" t="n">
-        <v>4.18934679031372</v>
+        <v>4.18934631347656</v>
       </c>
       <c r="H840" t="n">
         <v>34559</v>
@@ -24758,7 +24758,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>4.23518180847168</v>
+        <v>4.23518133163452</v>
       </c>
       <c r="H841" t="n">
         <v>225</v>
@@ -24845,7 +24845,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G844" t="n">
-        <v>4.21684789657593</v>
+        <v>4.21684741973877</v>
       </c>
       <c r="H844" t="n">
         <v>16368</v>
@@ -25193,7 +25193,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>4.96854686737061</v>
+        <v>4.96854639053345</v>
       </c>
       <c r="H856" t="n">
         <v>13143</v>
@@ -25309,7 +25309,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>5.11521911621094</v>
+        <v>5.1152195930481</v>
       </c>
       <c r="H860" t="n">
         <v>16237</v>
@@ -25367,7 +25367,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G862" t="n">
-        <v>5.13355398178101</v>
+        <v>5.13355350494385</v>
       </c>
       <c r="H862" t="n">
         <v>13036</v>
@@ -25396,7 +25396,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G863" t="n">
-        <v>5.15188789367676</v>
+        <v>5.1518874168396</v>
       </c>
       <c r="H863" t="n">
         <v>7153</v>
@@ -25454,7 +25454,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>5.00521469116211</v>
+        <v>5.00521516799927</v>
       </c>
       <c r="H865" t="n">
         <v>3756</v>
@@ -25686,7 +25686,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G873" t="n">
-        <v>5.39023160934448</v>
+        <v>5.39023113250732</v>
       </c>
       <c r="H873" t="n">
         <v>31741</v>
@@ -25715,7 +25715,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G874" t="n">
-        <v>5.39023160934448</v>
+        <v>5.39023113250732</v>
       </c>
       <c r="H874" t="n">
         <v>13377</v>
@@ -25831,7 +25831,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G878" t="n">
-        <v>5.6102409362793</v>
+        <v>5.61024045944214</v>
       </c>
       <c r="H878" t="n">
         <v>24852</v>
@@ -25947,7 +25947,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G882" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H882" t="n">
         <v>8738</v>
@@ -25976,7 +25976,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>5.88525295257568</v>
+        <v>5.88525247573853</v>
       </c>
       <c r="H883" t="n">
         <v>11732</v>
@@ -26121,7 +26121,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>5.9402551651001</v>
+        <v>5.94025468826294</v>
       </c>
       <c r="H888" t="n">
         <v>7733</v>
@@ -26266,7 +26266,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G893" t="n">
-        <v>5.83025026321411</v>
+        <v>5.83025074005127</v>
       </c>
       <c r="H893" t="n">
         <v>46103</v>
@@ -26324,7 +26324,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>5.92192077636719</v>
+        <v>5.92192125320435</v>
       </c>
       <c r="H895" t="n">
         <v>1658</v>
@@ -26382,7 +26382,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>5.92192077636719</v>
+        <v>5.92192125320435</v>
       </c>
       <c r="H897" t="n">
         <v>3856</v>
@@ -26469,7 +26469,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>5.92192077636719</v>
+        <v>5.92192125320435</v>
       </c>
       <c r="H900" t="n">
         <v>19114</v>
@@ -26498,7 +26498,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H901" t="n">
         <v>5834</v>
@@ -26527,7 +26527,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H902" t="n">
         <v>4663</v>
@@ -26643,7 +26643,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G906" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H906" t="n">
         <v>7547</v>
@@ -26759,7 +26759,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G910" t="n">
-        <v>6.19693279266357</v>
+        <v>6.19693326950073</v>
       </c>
       <c r="H910" t="n">
         <v>32257</v>
@@ -26817,7 +26817,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>6.38027381896973</v>
+        <v>6.38027429580688</v>
       </c>
       <c r="H912" t="n">
         <v>24783</v>
@@ -26846,7 +26846,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G913" t="n">
-        <v>6.28860330581665</v>
+        <v>6.28860378265381</v>
       </c>
       <c r="H913" t="n">
         <v>13157</v>
@@ -26991,7 +26991,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>6.4719443321228</v>
+        <v>6.47194480895996</v>
       </c>
       <c r="H918" t="n">
         <v>6002</v>
@@ -27049,7 +27049,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G920" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H920" t="n">
         <v>2787</v>
@@ -27078,7 +27078,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H921" t="n">
         <v>4737</v>
@@ -27107,7 +27107,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G922" t="n">
-        <v>6.58194923400879</v>
+        <v>6.58194875717163</v>
       </c>
       <c r="H922" t="n">
         <v>5358</v>
@@ -27165,7 +27165,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G924" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H924" t="n">
         <v>4250</v>
@@ -27252,7 +27252,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G927" t="n">
-        <v>6.61861753463745</v>
+        <v>6.61861705780029</v>
       </c>
       <c r="H927" t="n">
         <v>9701</v>
@@ -27339,7 +27339,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>6.58194923400879</v>
+        <v>6.58194875717163</v>
       </c>
       <c r="H930" t="n">
         <v>1400</v>
@@ -27368,7 +27368,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G931" t="n">
-        <v>6.61861753463745</v>
+        <v>6.61861705780029</v>
       </c>
       <c r="H931" t="n">
         <v>4392</v>
@@ -27542,7 +27542,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G937" t="n">
-        <v>6.54528045654297</v>
+        <v>6.54528093338013</v>
       </c>
       <c r="H937" t="n">
         <v>11503</v>
@@ -27600,7 +27600,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G939" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H939" t="n">
         <v>14602</v>
@@ -27658,7 +27658,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>6.85696125030518</v>
+        <v>6.85696077346802</v>
       </c>
       <c r="H941" t="n">
         <v>21995</v>
@@ -27890,7 +27890,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H949" t="n">
         <v>6250</v>
@@ -28093,7 +28093,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G956" t="n">
-        <v>6.78362417221069</v>
+        <v>6.78362464904785</v>
       </c>
       <c r="H956" t="n">
         <v>5975</v>
@@ -68583,6 +68583,35 @@
         <v>13877</v>
       </c>
       <c r="I2352" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2353">
+      <c r="A2353" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2353" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2353" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="D2353" t="n">
+        <v>2.30999994277954</v>
+      </c>
+      <c r="E2353" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F2353" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="G2353" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="H2353" t="n">
+        <v>3192</v>
+      </c>
+      <c r="I2353" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -456,7 +456,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G3" t="n">
-        <v>9.44388961791992</v>
+        <v>9.44389057159424</v>
       </c>
       <c r="H3" t="n">
         <v>18800</v>
@@ -485,7 +485,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.41868495941162</v>
+        <v>9.41868591308594</v>
       </c>
       <c r="H4" t="n">
         <v>41600</v>
@@ -543,7 +543,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394115447998</v>
       </c>
       <c r="H6" t="n">
         <v>18000</v>
@@ -601,7 +601,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394115447998</v>
       </c>
       <c r="H8" t="n">
         <v>4800</v>
@@ -630,7 +630,7 @@
         <v>11.5</v>
       </c>
       <c r="G9" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H9" t="n">
         <v>2200</v>
@@ -717,7 +717,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G12" t="n">
-        <v>9.67074680328369</v>
+        <v>9.67074584960938</v>
       </c>
       <c r="H12" t="n">
         <v>1600</v>
@@ -746,7 +746,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.62033271789551</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H13" t="n">
         <v>1200</v>
@@ -804,7 +804,7 @@
         <v>11.5</v>
       </c>
       <c r="G15" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H15" t="n">
         <v>13400</v>
@@ -833,7 +833,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G16" t="n">
-        <v>9.63713836669922</v>
+        <v>9.6371374130249</v>
       </c>
       <c r="H16" t="n">
         <v>11400</v>
@@ -862,7 +862,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H17" t="n">
         <v>248200</v>
@@ -891,7 +891,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G18" t="n">
-        <v>9.63713836669922</v>
+        <v>9.6371374130249</v>
       </c>
       <c r="H18" t="n">
         <v>2600</v>
@@ -949,7 +949,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G20" t="n">
-        <v>9.61193084716797</v>
+        <v>9.61193180084229</v>
       </c>
       <c r="H20" t="n">
         <v>2200</v>
@@ -978,7 +978,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>9.61193084716797</v>
+        <v>9.61193180084229</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G29" t="n">
-        <v>9.56151962280273</v>
+        <v>9.56152057647705</v>
       </c>
       <c r="H29" t="n">
         <v>6000</v>
@@ -1239,7 +1239,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G30" t="n">
-        <v>9.51950931549072</v>
+        <v>9.51950836181641</v>
       </c>
       <c r="H30" t="n">
         <v>2600</v>
@@ -1268,7 +1268,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G31" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H31" t="n">
         <v>4600</v>
@@ -1297,7 +1297,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H32" t="n">
         <v>1600</v>
@@ -1355,7 +1355,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G34" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H34" t="n">
         <v>14200</v>
@@ -1384,7 +1384,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H35" t="n">
         <v>800</v>
@@ -1413,7 +1413,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H36" t="n">
         <v>400</v>
@@ -1587,7 +1587,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G42" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H42" t="n">
         <v>7000</v>
@@ -1616,7 +1616,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H43" t="n">
         <v>2000</v>
@@ -1645,7 +1645,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H44" t="n">
         <v>4400</v>
@@ -1674,7 +1674,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G45" t="n">
-        <v>9.82198333740234</v>
+        <v>9.82198238372803</v>
       </c>
       <c r="H45" t="n">
         <v>14000</v>
@@ -1703,7 +1703,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>9.77157115936279</v>
+        <v>9.77157020568848</v>
       </c>
       <c r="H46" t="n">
         <v>47600</v>
@@ -1732,7 +1732,7 @@
         <v>11.5</v>
       </c>
       <c r="G47" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H47" t="n">
         <v>11200</v>
@@ -1761,7 +1761,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H48" t="n">
         <v>8800</v>
@@ -1790,7 +1790,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G49" t="n">
-        <v>9.77157115936279</v>
+        <v>9.77157020568848</v>
       </c>
       <c r="H49" t="n">
         <v>37000</v>
@@ -1877,7 +1877,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440677642822</v>
       </c>
       <c r="H52" t="n">
         <v>97800</v>
@@ -1935,7 +1935,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G54" t="n">
-        <v>9.63713836669922</v>
+        <v>9.6371374130249</v>
       </c>
       <c r="H54" t="n">
         <v>30200</v>
@@ -1993,7 +1993,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440677642822</v>
       </c>
       <c r="H56" t="n">
         <v>20400</v>
@@ -2109,7 +2109,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G60" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320339202881</v>
       </c>
       <c r="H60" t="n">
         <v>10600</v>
@@ -2138,7 +2138,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G61" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320339202881</v>
       </c>
       <c r="H61" t="n">
         <v>11200</v>
@@ -2167,7 +2167,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G62" t="n">
-        <v>9.99002456665039</v>
+        <v>9.99002361297607</v>
       </c>
       <c r="H62" t="n">
         <v>36400</v>
@@ -2254,7 +2254,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>9.82198333740234</v>
+        <v>9.82198238372803</v>
       </c>
       <c r="H65" t="n">
         <v>8600</v>
@@ -2312,7 +2312,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G67" t="n">
-        <v>9.93961143493652</v>
+        <v>9.93961048126221</v>
       </c>
       <c r="H67" t="n">
         <v>18400</v>
@@ -2341,7 +2341,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G68" t="n">
-        <v>9.99002456665039</v>
+        <v>9.99002361297607</v>
       </c>
       <c r="H68" t="n">
         <v>13600</v>
@@ -2457,7 +2457,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440677642822</v>
       </c>
       <c r="H72" t="n">
         <v>73200</v>
@@ -2486,7 +2486,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G73" t="n">
-        <v>10.0572395324707</v>
+        <v>10.057240486145</v>
       </c>
       <c r="H73" t="n">
         <v>150000</v>
@@ -2515,7 +2515,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G74" t="n">
-        <v>10.0656404495239</v>
+        <v>10.0656414031982</v>
       </c>
       <c r="H74" t="n">
         <v>7000</v>
@@ -2573,7 +2573,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G76" t="n">
-        <v>10.0488367080688</v>
+        <v>10.0488386154175</v>
       </c>
       <c r="H76" t="n">
         <v>116000</v>
@@ -2602,7 +2602,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G77" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320339202881</v>
       </c>
       <c r="H77" t="n">
         <v>58000</v>
@@ -2689,7 +2689,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G80" t="n">
-        <v>10.0488367080688</v>
+        <v>10.0488386154175</v>
       </c>
       <c r="H80" t="n">
         <v>12400</v>
@@ -2747,7 +2747,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G82" t="n">
-        <v>9.99002456665039</v>
+        <v>9.99002361297607</v>
       </c>
       <c r="H82" t="n">
         <v>4200</v>
@@ -2805,7 +2805,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440677642822</v>
       </c>
       <c r="H84" t="n">
         <v>6200</v>
@@ -2834,7 +2834,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G85" t="n">
-        <v>9.90600395202637</v>
+        <v>9.90600299835205</v>
       </c>
       <c r="H85" t="n">
         <v>4200</v>
@@ -2863,7 +2863,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440677642822</v>
       </c>
       <c r="H86" t="n">
         <v>5400</v>
@@ -2921,7 +2921,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G88" t="n">
-        <v>9.90600395202637</v>
+        <v>9.90600299835205</v>
       </c>
       <c r="H88" t="n">
         <v>600</v>
@@ -3095,7 +3095,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440677642822</v>
       </c>
       <c r="H94" t="n">
         <v>6000</v>
@@ -3182,7 +3182,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G97" t="n">
-        <v>10.0488367080688</v>
+        <v>10.0488386154175</v>
       </c>
       <c r="H97" t="n">
         <v>14800</v>
@@ -3327,7 +3327,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G102" t="n">
-        <v>9.82198333740234</v>
+        <v>9.82198238372803</v>
       </c>
       <c r="H102" t="n">
         <v>8200</v>
@@ -3356,7 +3356,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G103" t="n">
-        <v>9.82198333740234</v>
+        <v>9.82198238372803</v>
       </c>
       <c r="H103" t="n">
         <v>600</v>
@@ -3414,7 +3414,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G105" t="n">
-        <v>9.63713836669922</v>
+        <v>9.6371374130249</v>
       </c>
       <c r="H105" t="n">
         <v>6400</v>
@@ -3501,7 +3501,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G108" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394115447998</v>
       </c>
       <c r="H108" t="n">
         <v>20400</v>
@@ -3530,7 +3530,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>9.62033271789551</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H109" t="n">
         <v>9400</v>
@@ -3559,7 +3559,7 @@
         <v>11.5</v>
       </c>
       <c r="G110" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H110" t="n">
         <v>6400</v>
@@ -3588,7 +3588,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>9.62033271789551</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H111" t="n">
         <v>4600</v>
@@ -3675,7 +3675,7 @@
         <v>11.5</v>
       </c>
       <c r="G114" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H114" t="n">
         <v>21600</v>
@@ -3733,7 +3733,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H116" t="n">
         <v>4600</v>
@@ -3849,7 +3849,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837299346924</v>
       </c>
       <c r="H120" t="n">
         <v>4800</v>
@@ -3936,7 +3936,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G123" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837299346924</v>
       </c>
       <c r="H123" t="n">
         <v>15800</v>
@@ -3965,7 +3965,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H124" t="n">
         <v>14200</v>
@@ -3994,7 +3994,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H125" t="n">
         <v>8000</v>
@@ -4023,7 +4023,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H126" t="n">
         <v>24600</v>
@@ -4081,7 +4081,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837299346924</v>
       </c>
       <c r="H128" t="n">
         <v>20000</v>
@@ -4110,7 +4110,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837299346924</v>
       </c>
       <c r="H129" t="n">
         <v>1600</v>
@@ -4197,7 +4197,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G132" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837299346924</v>
       </c>
       <c r="H132" t="n">
         <v>11400</v>
@@ -4226,7 +4226,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G133" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837299346924</v>
       </c>
       <c r="H133" t="n">
         <v>9800</v>
@@ -4255,7 +4255,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H134" t="n">
         <v>3400</v>
@@ -4313,7 +4313,7 @@
         <v>11.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H136" t="n">
         <v>9600</v>
@@ -4342,7 +4342,7 @@
         <v>11.5</v>
       </c>
       <c r="G137" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H137" t="n">
         <v>5800</v>
@@ -4371,7 +4371,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837299346924</v>
       </c>
       <c r="H138" t="n">
         <v>50800</v>
@@ -4429,7 +4429,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H140" t="n">
         <v>9000</v>
@@ -4458,7 +4458,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H141" t="n">
         <v>1600</v>
@@ -4661,7 +4661,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G148" t="n">
-        <v>9.62033271789551</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H148" t="n">
         <v>3400</v>
@@ -4690,7 +4690,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H149" t="n">
         <v>5600</v>
@@ -4719,7 +4719,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>11.5</v>
       </c>
       <c r="G154" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H154" t="n">
         <v>1000</v>
@@ -4980,7 +4980,7 @@
         <v>11</v>
       </c>
       <c r="G159" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H159" t="n">
         <v>14600</v>
@@ -5125,7 +5125,7 @@
         <v>11</v>
       </c>
       <c r="G164" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H164" t="n">
         <v>18800</v>
@@ -5154,7 +5154,7 @@
         <v>11</v>
       </c>
       <c r="G165" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>11</v>
       </c>
       <c r="G166" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H166" t="n">
         <v>400</v>
@@ -5241,7 +5241,7 @@
         <v>11</v>
       </c>
       <c r="G168" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H168" t="n">
         <v>1200</v>
@@ -5270,7 +5270,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>9.28425312042236</v>
+        <v>9.28425216674805</v>
       </c>
       <c r="H169" t="n">
         <v>200</v>
@@ -5357,7 +5357,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H172" t="n">
         <v>35400</v>
@@ -5415,7 +5415,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H174" t="n">
         <v>33600</v>
@@ -5502,7 +5502,7 @@
         <v>11</v>
       </c>
       <c r="G177" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H177" t="n">
         <v>5200</v>
@@ -5647,7 +5647,7 @@
         <v>11</v>
       </c>
       <c r="G182" t="n">
-        <v>9.24224185943604</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H182" t="n">
         <v>10000</v>
@@ -5734,7 +5734,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G185" t="n">
-        <v>9.07420063018799</v>
+        <v>9.0742015838623</v>
       </c>
       <c r="H185" t="n">
         <v>5800</v>
@@ -5850,7 +5850,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G189" t="n">
-        <v>9.07420063018799</v>
+        <v>9.0742015838623</v>
       </c>
       <c r="H189" t="n">
         <v>3000</v>
@@ -5879,7 +5879,7 @@
         <v>10.75</v>
       </c>
       <c r="G190" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H190" t="n">
         <v>400</v>
@@ -5966,7 +5966,7 @@
         <v>10.75</v>
       </c>
       <c r="G193" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H193" t="n">
         <v>400</v>
@@ -5995,7 +5995,7 @@
         <v>10.75</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H194" t="n">
         <v>600</v>
@@ -6053,7 +6053,7 @@
         <v>10.75</v>
       </c>
       <c r="G196" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H196" t="n">
         <v>10200</v>
@@ -6140,7 +6140,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>9.07420063018799</v>
+        <v>9.0742015838623</v>
       </c>
       <c r="H199" t="n">
         <v>14800</v>
@@ -6198,7 +6198,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G201" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H201" t="n">
         <v>3200</v>
@@ -6227,7 +6227,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G202" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H202" t="n">
         <v>2800</v>
@@ -6256,7 +6256,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G203" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H203" t="n">
         <v>3200</v>
@@ -6285,7 +6285,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G204" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H204" t="n">
         <v>3600</v>
@@ -6314,7 +6314,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G205" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H205" t="n">
         <v>8800</v>
@@ -6343,7 +6343,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G206" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H206" t="n">
         <v>23000</v>
@@ -6372,7 +6372,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G207" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H207" t="n">
         <v>3200</v>
@@ -6459,7 +6459,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G210" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H210" t="n">
         <v>7400</v>
@@ -6575,7 +6575,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G214" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H214" t="n">
         <v>6600</v>
@@ -6662,7 +6662,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G217" t="n">
-        <v>8.72825813293457</v>
+        <v>8.72825717926025</v>
       </c>
       <c r="H217" t="n">
         <v>31200</v>
@@ -6720,7 +6720,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H219" t="n">
         <v>10600</v>
@@ -6749,7 +6749,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H220" t="n">
         <v>7600</v>
@@ -7213,7 +7213,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G236" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H236" t="n">
         <v>9600</v>
@@ -7242,7 +7242,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G237" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H244" t="n">
         <v>19000</v>
@@ -7474,7 +7474,7 @@
         <v>11</v>
       </c>
       <c r="G245" t="n">
-        <v>9.45919609069824</v>
+        <v>9.45919704437256</v>
       </c>
       <c r="H245" t="n">
         <v>7000</v>
@@ -7503,7 +7503,7 @@
         <v>11</v>
       </c>
       <c r="G246" t="n">
-        <v>9.45919609069824</v>
+        <v>9.45919704437256</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H247" t="n">
         <v>1000</v>
@@ -7561,7 +7561,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G248" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H248" t="n">
         <v>600</v>
@@ -7880,7 +7880,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H259" t="n">
         <v>200</v>
@@ -7909,7 +7909,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H261" t="n">
         <v>800</v>
@@ -8228,7 +8228,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>8.49607849121094</v>
+        <v>8.49607753753662</v>
       </c>
       <c r="H271" t="n">
         <v>9400</v>
@@ -8315,7 +8315,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H274" t="n">
         <v>4800</v>
@@ -8576,7 +8576,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>8.72825813293457</v>
+        <v>8.72825717926025</v>
       </c>
       <c r="H283" t="n">
         <v>5000</v>
@@ -8605,7 +8605,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>8.72825813293457</v>
+        <v>8.72825717926025</v>
       </c>
       <c r="H284" t="n">
         <v>1000</v>
@@ -8663,7 +8663,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H286" t="n">
         <v>10600</v>
@@ -8692,7 +8692,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.25529861450195</v>
+        <v>8.25529956817627</v>
       </c>
       <c r="H289" t="n">
         <v>800</v>
@@ -8779,7 +8779,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G290" t="n">
-        <v>8.32409286499023</v>
+        <v>8.32409381866455</v>
       </c>
       <c r="H290" t="n">
         <v>24800</v>
@@ -8895,7 +8895,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G294" t="n">
-        <v>8.32409286499023</v>
+        <v>8.32409381866455</v>
       </c>
       <c r="H294" t="n">
         <v>13000</v>
@@ -8924,7 +8924,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G295" t="n">
-        <v>8.32409286499023</v>
+        <v>8.32409381866455</v>
       </c>
       <c r="H295" t="n">
         <v>5000</v>
@@ -8953,7 +8953,7 @@
         <v>9.5</v>
       </c>
       <c r="G296" t="n">
-        <v>8.16930484771729</v>
+        <v>8.1693058013916</v>
       </c>
       <c r="H296" t="n">
         <v>17200</v>
@@ -9156,7 +9156,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G303" t="n">
-        <v>8.53047561645508</v>
+        <v>8.53047466278076</v>
       </c>
       <c r="H303" t="n">
         <v>2000</v>
@@ -9214,7 +9214,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H305" t="n">
         <v>400</v>
@@ -9272,7 +9272,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G307" t="n">
-        <v>8.03171730041504</v>
+        <v>8.03171825408936</v>
       </c>
       <c r="H307" t="n">
         <v>2000</v>
@@ -9330,7 +9330,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G309" t="n">
-        <v>8.03171730041504</v>
+        <v>8.03171825408936</v>
       </c>
       <c r="H309" t="n">
         <v>600</v>
@@ -9359,7 +9359,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G310" t="n">
-        <v>7.87693119049072</v>
+        <v>7.87693071365356</v>
       </c>
       <c r="H310" t="n">
         <v>200</v>
@@ -9388,7 +9388,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>7.87693119049072</v>
+        <v>7.87693071365356</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>7.82533502578735</v>
+        <v>7.82533645629883</v>
       </c>
       <c r="H312" t="n">
         <v>1200</v>
@@ -9446,7 +9446,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>7.70494556427002</v>
+        <v>7.70494508743286</v>
       </c>
       <c r="H313" t="n">
         <v>4200</v>
@@ -9591,7 +9591,7 @@
         <v>8.5</v>
       </c>
       <c r="G318" t="n">
-        <v>7.3093786239624</v>
+        <v>7.30937957763672</v>
       </c>
       <c r="H318" t="n">
         <v>1600</v>
@@ -9620,7 +9620,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G319" t="n">
-        <v>7.36097526550293</v>
+        <v>7.36097478866577</v>
       </c>
       <c r="H319" t="n">
         <v>2400</v>
@@ -9649,7 +9649,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G320" t="n">
-        <v>7.32657766342163</v>
+        <v>7.32657814025879</v>
       </c>
       <c r="H320" t="n">
         <v>400</v>
@@ -9678,7 +9678,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G321" t="n">
-        <v>7.32657766342163</v>
+        <v>7.32657814025879</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G322" t="n">
-        <v>7.18898963928223</v>
+        <v>7.18898916244507</v>
       </c>
       <c r="H322" t="n">
         <v>1400</v>
@@ -9765,7 +9765,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G324" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H324" t="n">
         <v>3200</v>
@@ -9794,7 +9794,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>7.20618772506714</v>
+        <v>7.2061882019043</v>
       </c>
       <c r="H325" t="n">
         <v>3000</v>
@@ -9823,7 +9823,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G326" t="n">
-        <v>7.20618772506714</v>
+        <v>7.2061882019043</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>9</v>
       </c>
       <c r="G327" t="n">
-        <v>7.739342212677</v>
+        <v>7.73934316635132</v>
       </c>
       <c r="H327" t="n">
         <v>3600</v>
@@ -9881,7 +9881,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G328" t="n">
-        <v>7.82533502578735</v>
+        <v>7.82533645629883</v>
       </c>
       <c r="H328" t="n">
         <v>600</v>
@@ -9939,7 +9939,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>7.48136377334595</v>
+        <v>7.48136472702026</v>
       </c>
       <c r="H330" t="n">
         <v>800</v>
@@ -10026,7 +10026,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>7.70494556427002</v>
+        <v>7.70494508743286</v>
       </c>
       <c r="H333" t="n">
         <v>600</v>
@@ -10171,7 +10171,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G338" t="n">
-        <v>7.53295993804932</v>
+        <v>7.53296089172363</v>
       </c>
       <c r="H338" t="n">
         <v>200</v>
@@ -10229,7 +10229,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G340" t="n">
-        <v>7.29218006134033</v>
+        <v>7.29217958450317</v>
       </c>
       <c r="H340" t="n">
         <v>2800</v>
@@ -10287,7 +10287,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G342" t="n">
-        <v>7.0857982635498</v>
+        <v>7.08579778671265</v>
       </c>
       <c r="H342" t="n">
         <v>6600</v>
@@ -10345,7 +10345,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G344" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H344" t="n">
         <v>17800</v>
@@ -10403,7 +10403,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G346" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H346" t="n">
         <v>4600</v>
@@ -10432,7 +10432,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G347" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G348" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H348" t="n">
         <v>3370</v>
@@ -10490,7 +10490,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G349" t="n">
-        <v>7.0857982635498</v>
+        <v>7.08579778671265</v>
       </c>
       <c r="H349" t="n">
         <v>3522</v>
@@ -10693,7 +10693,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G356" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H356" t="n">
         <v>5700</v>
@@ -10722,7 +10722,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G357" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H357" t="n">
         <v>15150</v>
@@ -10751,7 +10751,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G358" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>8</v>
       </c>
       <c r="G359" t="n">
-        <v>6.87941598892212</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H359" t="n">
         <v>140</v>
@@ -10809,7 +10809,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>6.74182748794556</v>
+        <v>6.7418270111084</v>
       </c>
       <c r="H360" t="n">
         <v>3952</v>
@@ -10838,7 +10838,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>6.74182748794556</v>
+        <v>6.7418270111084</v>
       </c>
       <c r="H361" t="n">
         <v>4250</v>
@@ -10867,7 +10867,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="n">
-        <v>6.87941598892212</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H362" t="n">
         <v>3100</v>
@@ -10896,7 +10896,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>6.74182748794556</v>
+        <v>6.7418270111084</v>
       </c>
       <c r="H363" t="n">
         <v>6700</v>
@@ -10925,7 +10925,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G364" t="n">
-        <v>6.63863563537598</v>
+        <v>6.63863611221313</v>
       </c>
       <c r="H364" t="n">
         <v>1200</v>
@@ -11012,7 +11012,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G367" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H367" t="n">
         <v>3300</v>
@@ -11041,7 +11041,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>6.87941598892212</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H368" t="n">
         <v>200</v>
@@ -11070,7 +11070,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G369" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H369" t="n">
         <v>472</v>
@@ -11099,7 +11099,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G371" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H371" t="n">
         <v>1981</v>
@@ -11186,7 +11186,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>7.05140113830566</v>
+        <v>7.05140018463135</v>
       </c>
       <c r="H373" t="n">
         <v>354</v>
@@ -11215,7 +11215,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G374" t="n">
-        <v>6.75902605056763</v>
+        <v>6.75902557373047</v>
       </c>
       <c r="H374" t="n">
         <v>25405</v>
@@ -11302,7 +11302,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>6.84501838684082</v>
+        <v>6.84501886367798</v>
       </c>
       <c r="H377" t="n">
         <v>2353</v>
@@ -11331,7 +11331,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>6.84501838684082</v>
+        <v>6.84501886367798</v>
       </c>
       <c r="H378" t="n">
         <v>4149</v>
@@ -11360,7 +11360,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H379" t="n">
         <v>1210</v>
@@ -11389,7 +11389,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H380" t="n">
         <v>1253</v>
@@ -11418,7 +11418,7 @@
         <v>8</v>
       </c>
       <c r="G381" t="n">
-        <v>6.87941598892212</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H381" t="n">
         <v>1532</v>
@@ -11447,7 +11447,7 @@
         <v>8</v>
       </c>
       <c r="G382" t="n">
-        <v>6.87941598892212</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H382" t="n">
         <v>291</v>
@@ -11534,7 +11534,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G385" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H385" t="n">
         <v>10</v>
@@ -11563,7 +11563,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G386" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G387" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G388" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H388" t="n">
         <v>3115</v>
@@ -11679,7 +11679,7 @@
         <v>8</v>
       </c>
       <c r="G390" t="n">
-        <v>6.87941598892212</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H390" t="n">
         <v>7347</v>
@@ -11708,7 +11708,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H391" t="n">
         <v>2600</v>
@@ -11737,7 +11737,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>6.84501838684082</v>
+        <v>6.84501886367798</v>
       </c>
       <c r="H392" t="n">
         <v>2665</v>
@@ -11795,7 +11795,7 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>6.87941598892212</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H394" t="n">
         <v>1786</v>
@@ -11824,7 +11824,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G395" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H395" t="n">
         <v>9230</v>
@@ -11969,7 +11969,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G400" t="n">
-        <v>7.01700353622437</v>
+        <v>7.01700401306152</v>
       </c>
       <c r="H400" t="n">
         <v>4830</v>
@@ -11998,7 +11998,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G401" t="n">
-        <v>7.01700353622437</v>
+        <v>7.01700401306152</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -12027,7 +12027,7 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>6.87941598892212</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H402" t="n">
         <v>6710</v>
@@ -12056,7 +12056,7 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>6.87941598892212</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H403" t="n">
         <v>2710</v>
@@ -12114,7 +12114,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G405" t="n">
-        <v>6.75902605056763</v>
+        <v>6.75902557373047</v>
       </c>
       <c r="H405" t="n">
         <v>3290</v>
@@ -12201,7 +12201,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G408" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H408" t="n">
         <v>66943</v>
@@ -12230,7 +12230,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>7.24058485031128</v>
+        <v>7.24058532714844</v>
       </c>
       <c r="H409" t="n">
         <v>12395</v>
@@ -12259,7 +12259,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G410" t="n">
-        <v>7.46416616439819</v>
+        <v>7.46416664123535</v>
       </c>
       <c r="H410" t="n">
         <v>32960</v>
@@ -12288,7 +12288,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G411" t="n">
-        <v>7.53295993804932</v>
+        <v>7.53296089172363</v>
       </c>
       <c r="H411" t="n">
         <v>7212</v>
@@ -12317,7 +12317,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G412" t="n">
-        <v>7.48136377334595</v>
+        <v>7.48136472702026</v>
       </c>
       <c r="H412" t="n">
         <v>4587</v>
@@ -12375,7 +12375,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G414" t="n">
-        <v>7.44696760177612</v>
+        <v>7.44696807861328</v>
       </c>
       <c r="H414" t="n">
         <v>2400</v>
@@ -12491,7 +12491,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G418" t="n">
-        <v>7.53295993804932</v>
+        <v>7.53296089172363</v>
       </c>
       <c r="H418" t="n">
         <v>2536</v>
@@ -12607,7 +12607,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G422" t="n">
-        <v>7.36097526550293</v>
+        <v>7.36097478866577</v>
       </c>
       <c r="H422" t="n">
         <v>1868</v>
@@ -12636,7 +12636,7 @@
         <v>8.5</v>
       </c>
       <c r="G423" t="n">
-        <v>7.3093786239624</v>
+        <v>7.30937957763672</v>
       </c>
       <c r="H423" t="n">
         <v>1963</v>
@@ -12752,7 +12752,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G427" t="n">
-        <v>7.42976856231689</v>
+        <v>7.42976903915405</v>
       </c>
       <c r="H427" t="n">
         <v>1502</v>
@@ -12781,7 +12781,7 @@
         <v>8.5</v>
       </c>
       <c r="G428" t="n">
-        <v>7.3093786239624</v>
+        <v>7.30937957763672</v>
       </c>
       <c r="H428" t="n">
         <v>1002</v>
@@ -12810,7 +12810,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G429" t="n">
-        <v>7.29218006134033</v>
+        <v>7.29217958450317</v>
       </c>
       <c r="H429" t="n">
         <v>314</v>
@@ -12868,7 +12868,7 @@
         <v>8.5</v>
       </c>
       <c r="G431" t="n">
-        <v>7.3093786239624</v>
+        <v>7.30937957763672</v>
       </c>
       <c r="H431" t="n">
         <v>400</v>
@@ -12926,7 +12926,7 @@
         <v>9</v>
       </c>
       <c r="G433" t="n">
-        <v>7.739342212677</v>
+        <v>7.73934316635132</v>
       </c>
       <c r="H433" t="n">
         <v>12673</v>
@@ -12955,7 +12955,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H434" t="n">
         <v>1098</v>
@@ -13013,7 +13013,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>7.48136377334595</v>
+        <v>7.48136472702026</v>
       </c>
       <c r="H436" t="n">
         <v>2489</v>
@@ -13129,7 +13129,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H440" t="n">
         <v>1662</v>
@@ -13158,7 +13158,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H443" t="n">
         <v>4760</v>
@@ -13303,7 +13303,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G446" t="n">
-        <v>7.43836832046509</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H446" t="n">
         <v>5102</v>
@@ -13332,7 +13332,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>7.43836832046509</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H447" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G449" t="n">
-        <v>7.43836832046509</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H449" t="n">
         <v>1237</v>
@@ -13419,7 +13419,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G450" t="n">
-        <v>7.43836832046509</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G451" t="n">
-        <v>7.43836832046509</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H451" t="n">
         <v>3000</v>
@@ -13680,7 +13680,7 @@
         <v>8.25</v>
       </c>
       <c r="G459" t="n">
-        <v>7.33315134048462</v>
+        <v>7.33315086364746</v>
       </c>
       <c r="H459" t="n">
         <v>6911</v>
@@ -13709,7 +13709,7 @@
         <v>8.25</v>
       </c>
       <c r="G460" t="n">
-        <v>7.33315134048462</v>
+        <v>7.33315086364746</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>7.37759494781494</v>
+        <v>7.37759447097778</v>
       </c>
       <c r="H461" t="n">
         <v>6100</v>
@@ -13912,7 +13912,7 @@
         <v>8.25</v>
       </c>
       <c r="G467" t="n">
-        <v>7.33315134048462</v>
+        <v>7.33315086364746</v>
       </c>
       <c r="H467" t="n">
         <v>402</v>
@@ -13941,7 +13941,7 @@
         <v>8</v>
       </c>
       <c r="G468" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H468" t="n">
         <v>56</v>
@@ -13970,7 +13970,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G469" t="n">
-        <v>7.15537786483765</v>
+        <v>7.1553783416748</v>
       </c>
       <c r="H469" t="n">
         <v>1420</v>
@@ -13999,7 +13999,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G470" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H470" t="n">
         <v>3543</v>
@@ -14028,7 +14028,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>7.2887077331543</v>
+        <v>7.28870725631714</v>
       </c>
       <c r="H471" t="n">
         <v>30</v>
@@ -14115,7 +14115,7 @@
         <v>8.5</v>
       </c>
       <c r="G474" t="n">
-        <v>7.5553674697876</v>
+        <v>7.55536794662476</v>
       </c>
       <c r="H474" t="n">
         <v>3000</v>
@@ -14144,7 +14144,7 @@
         <v>8.5</v>
       </c>
       <c r="G475" t="n">
-        <v>7.5553674697876</v>
+        <v>7.55536794662476</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>8.5</v>
       </c>
       <c r="G476" t="n">
-        <v>7.5553674697876</v>
+        <v>7.55536794662476</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>7.37759494781494</v>
+        <v>7.37759447097778</v>
       </c>
       <c r="H477" t="n">
         <v>600</v>
@@ -14231,7 +14231,7 @@
         <v>8.25</v>
       </c>
       <c r="G478" t="n">
-        <v>7.33315134048462</v>
+        <v>7.33315086364746</v>
       </c>
       <c r="H478" t="n">
         <v>1858</v>
@@ -14260,7 +14260,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G479" t="n">
-        <v>7.2887077331543</v>
+        <v>7.28870725631714</v>
       </c>
       <c r="H479" t="n">
         <v>3000</v>
@@ -14289,7 +14289,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G480" t="n">
-        <v>7.46648025512695</v>
+        <v>7.46648120880127</v>
       </c>
       <c r="H480" t="n">
         <v>10</v>
@@ -14318,7 +14318,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G481" t="n">
-        <v>7.46648025512695</v>
+        <v>7.46648120880127</v>
       </c>
       <c r="H481" t="n">
         <v>0</v>
@@ -14347,7 +14347,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G482" t="n">
-        <v>7.46648025512695</v>
+        <v>7.46648120880127</v>
       </c>
       <c r="H482" t="n">
         <v>0</v>
@@ -14666,7 +14666,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G493" t="n">
-        <v>7.46648025512695</v>
+        <v>7.46648120880127</v>
       </c>
       <c r="H493" t="n">
         <v>2584</v>
@@ -14695,7 +14695,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>7.59981155395508</v>
+        <v>7.59981107711792</v>
       </c>
       <c r="H494" t="n">
         <v>2906</v>
@@ -14811,7 +14811,7 @@
         <v>8</v>
       </c>
       <c r="G498" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H498" t="n">
         <v>2910</v>
@@ -14840,7 +14840,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G499" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H499" t="n">
         <v>21845</v>
@@ -14869,7 +14869,7 @@
         <v>8</v>
       </c>
       <c r="G500" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H500" t="n">
         <v>225</v>
@@ -14898,7 +14898,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H501" t="n">
         <v>40</v>
@@ -14927,7 +14927,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G502" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H502" t="n">
         <v>750</v>
@@ -14985,7 +14985,7 @@
         <v>8</v>
       </c>
       <c r="G504" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H504" t="n">
         <v>20</v>
@@ -15014,7 +15014,7 @@
         <v>8</v>
       </c>
       <c r="G505" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H505" t="n">
         <v>2776</v>
@@ -15043,7 +15043,7 @@
         <v>8</v>
       </c>
       <c r="G506" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>8</v>
       </c>
       <c r="G509" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H509" t="n">
         <v>422</v>
@@ -15188,7 +15188,7 @@
         <v>8</v>
       </c>
       <c r="G511" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H511" t="n">
         <v>200</v>
@@ -15217,7 +15217,7 @@
         <v>8</v>
       </c>
       <c r="G512" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H512" t="n">
         <v>0</v>
@@ -15246,7 +15246,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G513" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H513" t="n">
         <v>115</v>
@@ -15275,7 +15275,7 @@
         <v>7.75</v>
       </c>
       <c r="G514" t="n">
-        <v>6.88871765136719</v>
+        <v>6.88871812820435</v>
       </c>
       <c r="H514" t="n">
         <v>1660</v>
@@ -15304,7 +15304,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G515" t="n">
-        <v>7.15537786483765</v>
+        <v>7.1553783416748</v>
       </c>
       <c r="H515" t="n">
         <v>10</v>
@@ -15333,7 +15333,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>6.97760438919067</v>
+        <v>6.97760391235352</v>
       </c>
       <c r="H516" t="n">
         <v>192</v>
@@ -15391,7 +15391,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G518" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H518" t="n">
         <v>2860</v>
@@ -15478,7 +15478,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G521" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H521" t="n">
         <v>300</v>
@@ -15507,7 +15507,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H522" t="n">
         <v>26</v>
@@ -15536,7 +15536,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H523" t="n">
         <v>16875</v>
@@ -15710,7 +15710,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H529" t="n">
         <v>700</v>
@@ -15739,7 +15739,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G530" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -15768,7 +15768,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H531" t="n">
         <v>1</v>
@@ -15855,7 +15855,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.39984083175659</v>
+        <v>6.39984035491943</v>
       </c>
       <c r="H534" t="n">
         <v>2911</v>
@@ -15884,7 +15884,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H535" t="n">
         <v>1925</v>
@@ -16087,7 +16087,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.39984083175659</v>
+        <v>6.39984035491943</v>
       </c>
       <c r="H542" t="n">
         <v>6172</v>
@@ -16116,7 +16116,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>6.39984083175659</v>
+        <v>6.39984035491943</v>
       </c>
       <c r="H543" t="n">
         <v>3219</v>
@@ -16174,7 +16174,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H545" t="n">
         <v>3438</v>
@@ -16232,7 +16232,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H547" t="n">
         <v>550</v>
@@ -16261,7 +16261,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G548" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H548" t="n">
         <v>147</v>
@@ -16290,7 +16290,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H549" t="n">
         <v>450</v>
@@ -16319,7 +16319,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G550" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H550" t="n">
         <v>976</v>
@@ -16348,7 +16348,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G551" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H551" t="n">
         <v>1277</v>
@@ -16377,7 +16377,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G552" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H552" t="n">
         <v>1717</v>
@@ -16493,7 +16493,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G556" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H556" t="n">
         <v>670</v>
@@ -16870,7 +16870,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G569" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H569" t="n">
         <v>6050</v>
@@ -16899,7 +16899,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H570" t="n">
         <v>3670</v>
@@ -16928,7 +16928,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G571" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G572" t="n">
-        <v>6.17762422561646</v>
+        <v>6.1776237487793</v>
       </c>
       <c r="H572" t="n">
         <v>12462</v>
@@ -17363,7 +17363,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G586" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H586" t="n">
         <v>2734</v>
@@ -17392,7 +17392,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H587" t="n">
         <v>3257</v>
@@ -17537,7 +17537,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H592" t="n">
         <v>3684</v>
@@ -17624,7 +17624,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G595" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H595" t="n">
         <v>3897</v>
@@ -17653,7 +17653,7 @@
         <v>6.75</v>
       </c>
       <c r="G596" t="n">
-        <v>5.99985074996948</v>
+        <v>5.99985122680664</v>
       </c>
       <c r="H596" t="n">
         <v>10250</v>
@@ -17711,7 +17711,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H598" t="n">
         <v>8965</v>
@@ -17740,7 +17740,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G599" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H599" t="n">
         <v>11436</v>
@@ -17769,7 +17769,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G600" t="n">
-        <v>5.59986114501953</v>
+        <v>5.59986066818237</v>
       </c>
       <c r="H600" t="n">
         <v>44660</v>
@@ -17798,7 +17798,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G601" t="n">
-        <v>5.59986114501953</v>
+        <v>5.59986066818237</v>
       </c>
       <c r="H601" t="n">
         <v>43295</v>
@@ -17827,7 +17827,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G602" t="n">
-        <v>5.59986114501953</v>
+        <v>5.59986066818237</v>
       </c>
       <c r="H602" t="n">
         <v>9860</v>
@@ -17885,7 +17885,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H604" t="n">
         <v>52602</v>
@@ -17914,7 +17914,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G605" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H605" t="n">
         <v>2051</v>
@@ -17943,7 +17943,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G606" t="n">
-        <v>5.82207775115967</v>
+        <v>5.82207727432251</v>
       </c>
       <c r="H606" t="n">
         <v>6520</v>
@@ -18001,7 +18001,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H608" t="n">
         <v>23741</v>
@@ -18030,7 +18030,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G609" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H609" t="n">
         <v>3523</v>
@@ -18233,7 +18233,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G616" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H616" t="n">
         <v>3231</v>
@@ -18262,7 +18262,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G618" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H618" t="n">
         <v>2032</v>
@@ -18320,7 +18320,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G619" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H619" t="n">
         <v>50</v>
@@ -18349,7 +18349,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H620" t="n">
         <v>7613</v>
@@ -18378,7 +18378,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H621" t="n">
         <v>2570</v>
@@ -18407,7 +18407,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G622" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H622" t="n">
         <v>1100</v>
@@ -18436,7 +18436,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H623" t="n">
         <v>3777</v>
@@ -18465,7 +18465,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G624" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H624" t="n">
         <v>5586</v>
@@ -18494,7 +18494,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G625" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H625" t="n">
         <v>3300</v>
@@ -18523,7 +18523,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G626" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H626" t="n">
         <v>2368</v>
@@ -18552,7 +18552,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G627" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H627" t="n">
         <v>2744</v>
@@ -18581,7 +18581,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G628" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H628" t="n">
         <v>1005</v>
@@ -18610,7 +18610,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G629" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H629" t="n">
         <v>1200</v>
@@ -18639,7 +18639,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H630" t="n">
         <v>1307</v>
@@ -18668,7 +18668,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G631" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H631" t="n">
         <v>2750</v>
@@ -18697,7 +18697,7 @@
         <v>6.75</v>
       </c>
       <c r="G632" t="n">
-        <v>5.99985074996948</v>
+        <v>5.99985122680664</v>
       </c>
       <c r="H632" t="n">
         <v>7978</v>
@@ -18755,7 +18755,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G634" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H634" t="n">
         <v>2000</v>
@@ -18958,7 +18958,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G641" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H641" t="n">
         <v>1959</v>
@@ -18987,7 +18987,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H642" t="n">
         <v>2879</v>
@@ -19016,7 +19016,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G643" t="n">
-        <v>5.59986114501953</v>
+        <v>5.59986066818237</v>
       </c>
       <c r="H643" t="n">
         <v>4049</v>
@@ -19132,7 +19132,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H647" t="n">
         <v>262</v>
@@ -19161,7 +19161,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H648" t="n">
         <v>2986</v>
@@ -19306,7 +19306,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G653" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H653" t="n">
         <v>4753</v>
@@ -19335,7 +19335,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G654" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H654" t="n">
         <v>1310</v>
@@ -19393,7 +19393,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G656" t="n">
-        <v>5.59986114501953</v>
+        <v>5.59986066818237</v>
       </c>
       <c r="H656" t="n">
         <v>2652</v>
@@ -19625,7 +19625,7 @@
         <v>5.75</v>
       </c>
       <c r="G664" t="n">
-        <v>5.11098384857178</v>
+        <v>5.11098432540894</v>
       </c>
       <c r="H664" t="n">
         <v>8131</v>
@@ -19799,7 +19799,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G670" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H670" t="n">
         <v>10643</v>
@@ -19828,7 +19828,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G671" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -19857,7 +19857,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G672" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G673" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G674" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H674" t="n">
         <v>0</v>
@@ -19973,7 +19973,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G676" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H676" t="n">
         <v>2454</v>
@@ -20002,7 +20002,7 @@
         <v>4.5</v>
       </c>
       <c r="G677" t="n">
-        <v>3.99990034103394</v>
+        <v>3.99990105628967</v>
       </c>
       <c r="H677" t="n">
         <v>2379</v>
@@ -20031,7 +20031,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G678" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H678" t="n">
         <v>6410</v>
@@ -20060,7 +20060,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.89323663711548</v>
+        <v>3.8932363986969</v>
       </c>
       <c r="H679" t="n">
         <v>5101</v>
@@ -20089,7 +20089,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G680" t="n">
-        <v>3.8576819896698</v>
+        <v>3.85768222808838</v>
       </c>
       <c r="H680" t="n">
         <v>4718</v>
@@ -20118,7 +20118,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>3.73324012756348</v>
+        <v>3.73324060440063</v>
       </c>
       <c r="H681" t="n">
         <v>1886</v>
@@ -20176,7 +20176,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G683" t="n">
-        <v>3.64435386657715</v>
+        <v>3.64435362815857</v>
       </c>
       <c r="H683" t="n">
         <v>1800</v>
@@ -20205,7 +20205,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G684" t="n">
-        <v>3.68879747390747</v>
+        <v>3.68879723548889</v>
       </c>
       <c r="H684" t="n">
         <v>1402</v>
@@ -20321,7 +20321,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>3.8576819896698</v>
+        <v>3.85768222808838</v>
       </c>
       <c r="H688" t="n">
         <v>1215</v>
@@ -20350,7 +20350,7 @@
         <v>4.5</v>
       </c>
       <c r="G689" t="n">
-        <v>3.99990034103394</v>
+        <v>3.99990105628967</v>
       </c>
       <c r="H689" t="n">
         <v>1891</v>
@@ -20408,7 +20408,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G691" t="n">
-        <v>3.98212337493896</v>
+        <v>3.98212313652039</v>
       </c>
       <c r="H691" t="n">
         <v>9728</v>
@@ -20437,7 +20437,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>3.96434617042542</v>
+        <v>3.96434593200684</v>
       </c>
       <c r="H692" t="n">
         <v>7551</v>
@@ -20495,7 +20495,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G694" t="n">
-        <v>3.8576819896698</v>
+        <v>3.85768222808838</v>
       </c>
       <c r="H694" t="n">
         <v>6301</v>
@@ -20611,7 +20611,7 @@
         <v>4.5</v>
       </c>
       <c r="G698" t="n">
-        <v>3.99990034103394</v>
+        <v>3.99990105628967</v>
       </c>
       <c r="H698" t="n">
         <v>1703</v>
@@ -20640,7 +20640,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>3.98212337493896</v>
+        <v>3.98212313652039</v>
       </c>
       <c r="H699" t="n">
         <v>13560</v>
@@ -20669,7 +20669,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G700" t="n">
-        <v>3.98212337493896</v>
+        <v>3.98212313652039</v>
       </c>
       <c r="H700" t="n">
         <v>6239</v>
@@ -20727,7 +20727,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G702" t="n">
-        <v>3.89323663711548</v>
+        <v>3.8932363986969</v>
       </c>
       <c r="H702" t="n">
         <v>8208</v>
@@ -20756,7 +20756,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>3.76879501342773</v>
+        <v>3.76879477500916</v>
       </c>
       <c r="H703" t="n">
         <v>6306</v>
@@ -20785,7 +20785,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G704" t="n">
-        <v>3.90212512016296</v>
+        <v>3.90212488174438</v>
       </c>
       <c r="H704" t="n">
         <v>1895</v>
@@ -20814,7 +20814,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G705" t="n">
-        <v>3.88434743881226</v>
+        <v>3.88434791564941</v>
       </c>
       <c r="H705" t="n">
         <v>6050</v>
@@ -20843,7 +20843,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G706" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H706" t="n">
         <v>1629</v>
@@ -20872,7 +20872,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>3.88434743881226</v>
+        <v>3.88434791564941</v>
       </c>
       <c r="H707" t="n">
         <v>1037</v>
@@ -20901,7 +20901,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G708" t="n">
-        <v>3.83101582527161</v>
+        <v>3.83101558685303</v>
       </c>
       <c r="H708" t="n">
         <v>6323</v>
@@ -20930,7 +20930,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>3.83101582527161</v>
+        <v>3.83101558685303</v>
       </c>
       <c r="H709" t="n">
         <v>2542</v>
@@ -20959,7 +20959,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>3.71546339988708</v>
+        <v>3.71546316146851</v>
       </c>
       <c r="H710" t="n">
         <v>8368</v>
@@ -20988,7 +20988,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G711" t="n">
-        <v>3.76879501342773</v>
+        <v>3.76879477500916</v>
       </c>
       <c r="H711" t="n">
         <v>5939</v>
@@ -21046,7 +21046,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G713" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H713" t="n">
         <v>1264</v>
@@ -21075,7 +21075,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G714" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H714" t="n">
         <v>0</v>
@@ -21104,7 +21104,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G715" t="n">
-        <v>3.81323838233948</v>
+        <v>3.81323862075806</v>
       </c>
       <c r="H715" t="n">
         <v>611</v>
@@ -21162,7 +21162,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>3.88434743881226</v>
+        <v>3.88434791564941</v>
       </c>
       <c r="H717" t="n">
         <v>3887</v>
@@ -21191,7 +21191,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G718" t="n">
-        <v>3.89323663711548</v>
+        <v>3.8932363986969</v>
       </c>
       <c r="H718" t="n">
         <v>38481</v>
@@ -21307,7 +21307,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G722" t="n">
-        <v>4.10656404495239</v>
+        <v>4.10656452178955</v>
       </c>
       <c r="H722" t="n">
         <v>4518</v>
@@ -21336,7 +21336,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G723" t="n">
-        <v>4.10656404495239</v>
+        <v>4.10656452178955</v>
       </c>
       <c r="H723" t="n">
         <v>30910</v>
@@ -21539,7 +21539,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>4.38185501098633</v>
+        <v>4.38185453414917</v>
       </c>
       <c r="H730" t="n">
         <v>61399</v>
@@ -21568,7 +21568,7 @@
         <v>4.75</v>
       </c>
       <c r="G731" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H731" t="n">
         <v>16376</v>
@@ -21655,7 +21655,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G734" t="n">
-        <v>4.38185501098633</v>
+        <v>4.38185453414917</v>
       </c>
       <c r="H734" t="n">
         <v>34375</v>
@@ -21684,7 +21684,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G735" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H735" t="n">
         <v>17125</v>
@@ -21713,7 +21713,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G736" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H736" t="n">
         <v>9606</v>
@@ -21742,7 +21742,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G737" t="n">
-        <v>4.40935611724854</v>
+        <v>4.40935564041138</v>
       </c>
       <c r="H737" t="n">
         <v>2683</v>
@@ -21771,7 +21771,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H738" t="n">
         <v>600</v>
@@ -21800,7 +21800,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H739" t="n">
         <v>680</v>
@@ -21829,7 +21829,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G740" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H740" t="n">
         <v>7403</v>
@@ -21916,7 +21916,7 @@
         <v>4.75</v>
       </c>
       <c r="G743" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H743" t="n">
         <v>607</v>
@@ -21945,7 +21945,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G744" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H744" t="n">
         <v>11032</v>
@@ -22032,7 +22032,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G747" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H747" t="n">
         <v>2630</v>
@@ -22061,7 +22061,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H748" t="n">
         <v>1000</v>
@@ -22177,7 +22177,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G752" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H752" t="n">
         <v>1350</v>
@@ -22380,7 +22380,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G759" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H759" t="n">
         <v>3488</v>
@@ -22467,7 +22467,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H762" t="n">
         <v>4900</v>
@@ -22641,7 +22641,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H768" t="n">
         <v>8119</v>
@@ -22902,7 +22902,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H777" t="n">
         <v>7930</v>
@@ -22931,7 +22931,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>4.08850908279419</v>
+        <v>4.08850860595703</v>
       </c>
       <c r="H778" t="n">
         <v>10894</v>
@@ -23105,7 +23105,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G784" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H784" t="n">
         <v>10522</v>
@@ -23163,7 +23163,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G786" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H786" t="n">
         <v>1030</v>
@@ -23192,7 +23192,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G787" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>4.07934141159058</v>
+        <v>4.07934188842773</v>
       </c>
       <c r="H788" t="n">
         <v>5464</v>
@@ -23250,7 +23250,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G789" t="n">
-        <v>4.07934141159058</v>
+        <v>4.07934188842773</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -23337,7 +23337,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>4.04267358779907</v>
+        <v>4.04267311096191</v>
       </c>
       <c r="H792" t="n">
         <v>1205</v>
@@ -23482,7 +23482,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G797" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H797" t="n">
         <v>2403</v>
@@ -23511,7 +23511,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G798" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H798" t="n">
         <v>1860</v>
@@ -23598,7 +23598,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>3.91433453559875</v>
+        <v>3.91433477401733</v>
       </c>
       <c r="H801" t="n">
         <v>1035</v>
@@ -23743,7 +23743,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.86849904060364</v>
+        <v>3.86849927902222</v>
       </c>
       <c r="H806" t="n">
         <v>3833</v>
@@ -23772,7 +23772,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G807" t="n">
-        <v>3.88683319091797</v>
+        <v>3.88683342933655</v>
       </c>
       <c r="H807" t="n">
         <v>13265</v>
@@ -23801,7 +23801,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G808" t="n">
-        <v>3.88683319091797</v>
+        <v>3.88683342933655</v>
       </c>
       <c r="H808" t="n">
         <v>12349</v>
@@ -23946,7 +23946,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G813" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H813" t="n">
         <v>11042</v>
@@ -24004,7 +24004,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H815" t="n">
         <v>4760</v>
@@ -24033,7 +24033,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G816" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H816" t="n">
         <v>7780</v>
@@ -24120,7 +24120,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G819" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H819" t="n">
         <v>785</v>
@@ -24178,7 +24178,7 @@
         <v>4.75</v>
       </c>
       <c r="G821" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H821" t="n">
         <v>6878</v>
@@ -24294,7 +24294,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G825" t="n">
-        <v>4.51936054229736</v>
+        <v>4.51936006546021</v>
       </c>
       <c r="H825" t="n">
         <v>1867</v>
@@ -24352,7 +24352,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>4.51019334793091</v>
+        <v>4.51019382476807</v>
       </c>
       <c r="H827" t="n">
         <v>10424</v>
@@ -24410,7 +24410,7 @@
         <v>4.75</v>
       </c>
       <c r="G829" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H829" t="n">
         <v>5800</v>
@@ -24468,7 +24468,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.04267358779907</v>
+        <v>4.04267311096191</v>
       </c>
       <c r="H831" t="n">
         <v>16333</v>
@@ -24555,7 +24555,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>3.94183588027954</v>
+        <v>3.94183611869812</v>
       </c>
       <c r="H834" t="n">
         <v>25951</v>
@@ -24642,7 +24642,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H837" t="n">
         <v>21835</v>
@@ -24729,7 +24729,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G840" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H840" t="n">
         <v>34559</v>
@@ -24758,7 +24758,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H841" t="n">
         <v>225</v>
@@ -24845,7 +24845,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G844" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H844" t="n">
         <v>16368</v>
@@ -25193,7 +25193,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>4.96854639053345</v>
+        <v>4.96854686737061</v>
       </c>
       <c r="H856" t="n">
         <v>13143</v>
@@ -25309,7 +25309,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>5.1152195930481</v>
+        <v>5.11521911621094</v>
       </c>
       <c r="H860" t="n">
         <v>16237</v>
@@ -25367,7 +25367,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G862" t="n">
-        <v>5.13355350494385</v>
+        <v>5.13355398178101</v>
       </c>
       <c r="H862" t="n">
         <v>13036</v>
@@ -25396,7 +25396,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G863" t="n">
-        <v>5.1518874168396</v>
+        <v>5.15188789367676</v>
       </c>
       <c r="H863" t="n">
         <v>7153</v>
@@ -25454,7 +25454,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>5.00521516799927</v>
+        <v>5.00521469116211</v>
       </c>
       <c r="H865" t="n">
         <v>3756</v>
@@ -25686,7 +25686,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G873" t="n">
-        <v>5.39023113250732</v>
+        <v>5.39023160934448</v>
       </c>
       <c r="H873" t="n">
         <v>31741</v>
@@ -25715,7 +25715,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G874" t="n">
-        <v>5.39023113250732</v>
+        <v>5.39023160934448</v>
       </c>
       <c r="H874" t="n">
         <v>13377</v>
@@ -25831,7 +25831,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G878" t="n">
-        <v>5.61024045944214</v>
+        <v>5.6102409362793</v>
       </c>
       <c r="H878" t="n">
         <v>24852</v>
@@ -25947,7 +25947,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G882" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H882" t="n">
         <v>8738</v>
@@ -25976,7 +25976,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>5.88525247573853</v>
+        <v>5.88525295257568</v>
       </c>
       <c r="H883" t="n">
         <v>11732</v>
@@ -26121,7 +26121,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>5.94025468826294</v>
+        <v>5.9402551651001</v>
       </c>
       <c r="H888" t="n">
         <v>7733</v>
@@ -26266,7 +26266,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G893" t="n">
-        <v>5.83025074005127</v>
+        <v>5.83025026321411</v>
       </c>
       <c r="H893" t="n">
         <v>46103</v>
@@ -26324,7 +26324,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H895" t="n">
         <v>1658</v>
@@ -26382,7 +26382,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H897" t="n">
         <v>3856</v>
@@ -26469,7 +26469,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H900" t="n">
         <v>19114</v>
@@ -26498,7 +26498,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H901" t="n">
         <v>5834</v>
@@ -26527,7 +26527,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H902" t="n">
         <v>4663</v>
@@ -26643,7 +26643,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G906" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H906" t="n">
         <v>7547</v>
@@ -26759,7 +26759,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G910" t="n">
-        <v>6.19693326950073</v>
+        <v>6.19693279266357</v>
       </c>
       <c r="H910" t="n">
         <v>32257</v>
@@ -26817,7 +26817,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>6.38027429580688</v>
+        <v>6.38027381896973</v>
       </c>
       <c r="H912" t="n">
         <v>24783</v>
@@ -26846,7 +26846,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G913" t="n">
-        <v>6.28860378265381</v>
+        <v>6.28860330581665</v>
       </c>
       <c r="H913" t="n">
         <v>13157</v>
@@ -26991,7 +26991,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>6.47194480895996</v>
+        <v>6.4719443321228</v>
       </c>
       <c r="H918" t="n">
         <v>6002</v>
@@ -27049,7 +27049,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G920" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H920" t="n">
         <v>2787</v>
@@ -27078,7 +27078,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H921" t="n">
         <v>4737</v>
@@ -27107,7 +27107,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G922" t="n">
-        <v>6.58194875717163</v>
+        <v>6.58194923400879</v>
       </c>
       <c r="H922" t="n">
         <v>5358</v>
@@ -27165,7 +27165,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G924" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H924" t="n">
         <v>4250</v>
@@ -27252,7 +27252,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G927" t="n">
-        <v>6.61861705780029</v>
+        <v>6.61861753463745</v>
       </c>
       <c r="H927" t="n">
         <v>9701</v>
@@ -27339,7 +27339,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>6.58194875717163</v>
+        <v>6.58194923400879</v>
       </c>
       <c r="H930" t="n">
         <v>1400</v>
@@ -27368,7 +27368,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G931" t="n">
-        <v>6.61861705780029</v>
+        <v>6.61861753463745</v>
       </c>
       <c r="H931" t="n">
         <v>4392</v>
@@ -27542,7 +27542,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G937" t="n">
-        <v>6.54528093338013</v>
+        <v>6.54528045654297</v>
       </c>
       <c r="H937" t="n">
         <v>11503</v>
@@ -27600,7 +27600,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G939" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H939" t="n">
         <v>14602</v>
@@ -27658,7 +27658,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>6.85696077346802</v>
+        <v>6.85696125030518</v>
       </c>
       <c r="H941" t="n">
         <v>21995</v>
@@ -27890,7 +27890,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H949" t="n">
         <v>6250</v>
@@ -28093,7 +28093,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G956" t="n">
-        <v>6.78362464904785</v>
+        <v>6.78362417221069</v>
       </c>
       <c r="H956" t="n">
         <v>5975</v>
@@ -68612,6 +68612,35 @@
         <v>3192</v>
       </c>
       <c r="I2353" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2354" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2354" t="n">
+        <v>2.32999992370605</v>
+      </c>
+      <c r="D2354" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="E2354" t="n">
+        <v>2.28999996185303</v>
+      </c>
+      <c r="F2354" t="n">
+        <v>2.30999994277954</v>
+      </c>
+      <c r="G2354" t="n">
+        <v>2.30999994277954</v>
+      </c>
+      <c r="H2354" t="n">
+        <v>3088</v>
+      </c>
+      <c r="I2354" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -456,7 +456,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G3" t="n">
-        <v>9.44389057159424</v>
+        <v>9.44389152526855</v>
       </c>
       <c r="H3" t="n">
         <v>18800</v>
@@ -485,7 +485,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.41868591308594</v>
+        <v>9.41868495941162</v>
       </c>
       <c r="H4" t="n">
         <v>41600</v>
@@ -514,7 +514,7 @@
         <v>11.25</v>
       </c>
       <c r="G5" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229244232178</v>
       </c>
       <c r="H5" t="n">
         <v>13000</v>
@@ -543,7 +543,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.65394115447998</v>
+        <v>9.6539421081543</v>
       </c>
       <c r="H6" t="n">
         <v>18000</v>
@@ -601,7 +601,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.65394115447998</v>
+        <v>9.6539421081543</v>
       </c>
       <c r="H8" t="n">
         <v>4800</v>
@@ -717,7 +717,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G12" t="n">
-        <v>9.67074584960938</v>
+        <v>9.67074680328369</v>
       </c>
       <c r="H12" t="n">
         <v>1600</v>
@@ -833,7 +833,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G16" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H16" t="n">
         <v>11400</v>
@@ -891,7 +891,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G18" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H18" t="n">
         <v>2600</v>
@@ -1007,7 +1007,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G22" t="n">
-        <v>9.64553928375244</v>
+        <v>9.64553833007812</v>
       </c>
       <c r="H22" t="n">
         <v>3400</v>
@@ -1036,7 +1036,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>9.5363130569458</v>
+        <v>9.53631401062012</v>
       </c>
       <c r="H23" t="n">
         <v>800</v>
@@ -1181,7 +1181,7 @@
         <v>11.25</v>
       </c>
       <c r="G28" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229244232178</v>
       </c>
       <c r="H28" t="n">
         <v>3600</v>
@@ -1210,7 +1210,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G29" t="n">
-        <v>9.56152057647705</v>
+        <v>9.56151962280273</v>
       </c>
       <c r="H29" t="n">
         <v>6000</v>
@@ -1297,7 +1297,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H32" t="n">
         <v>1600</v>
@@ -1384,7 +1384,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H35" t="n">
         <v>800</v>
@@ -1413,7 +1413,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H36" t="n">
         <v>400</v>
@@ -1471,7 +1471,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>9.5363130569458</v>
+        <v>9.53631401062012</v>
       </c>
       <c r="H38" t="n">
         <v>2400</v>
@@ -1500,7 +1500,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G39" t="n">
-        <v>9.64553928375244</v>
+        <v>9.64553833007812</v>
       </c>
       <c r="H39" t="n">
         <v>800</v>
@@ -1587,7 +1587,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G42" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H42" t="n">
         <v>7000</v>
@@ -1616,7 +1616,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H43" t="n">
         <v>2000</v>
@@ -1645,7 +1645,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H44" t="n">
         <v>4400</v>
@@ -1761,7 +1761,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H48" t="n">
         <v>8800</v>
@@ -1819,7 +1819,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G50" t="n">
-        <v>9.76316928863525</v>
+        <v>9.76316833496094</v>
       </c>
       <c r="H50" t="n">
         <v>6600</v>
@@ -1848,7 +1848,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G51" t="n">
-        <v>10.1832714080811</v>
+        <v>10.1832695007324</v>
       </c>
       <c r="H51" t="n">
         <v>127800</v>
@@ -1877,7 +1877,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>9.91440677642822</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H52" t="n">
         <v>97800</v>
@@ -1935,7 +1935,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G54" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H54" t="n">
         <v>30200</v>
@@ -1964,7 +1964,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G55" t="n">
-        <v>9.8555908203125</v>
+        <v>9.85558986663818</v>
       </c>
       <c r="H55" t="n">
         <v>11800</v>
@@ -1993,7 +1993,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>9.91440677642822</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H56" t="n">
         <v>20400</v>
@@ -2312,7 +2312,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G67" t="n">
-        <v>9.93961048126221</v>
+        <v>9.93960952758789</v>
       </c>
       <c r="H67" t="n">
         <v>18400</v>
@@ -2399,7 +2399,7 @@
         <v>11.75</v>
       </c>
       <c r="G70" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H70" t="n">
         <v>5200</v>
@@ -2457,7 +2457,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>9.91440677642822</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H72" t="n">
         <v>73200</v>
@@ -2573,7 +2573,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G76" t="n">
-        <v>10.0488386154175</v>
+        <v>10.0488367080688</v>
       </c>
       <c r="H76" t="n">
         <v>116000</v>
@@ -2689,7 +2689,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G80" t="n">
-        <v>10.0488386154175</v>
+        <v>10.0488367080688</v>
       </c>
       <c r="H80" t="n">
         <v>12400</v>
@@ -2718,7 +2718,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G81" t="n">
-        <v>9.89760112762451</v>
+        <v>9.8976001739502</v>
       </c>
       <c r="H81" t="n">
         <v>18800</v>
@@ -2776,7 +2776,7 @@
         <v>11.75</v>
       </c>
       <c r="G83" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H83" t="n">
         <v>13000</v>
@@ -2805,7 +2805,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.91440677642822</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H84" t="n">
         <v>6200</v>
@@ -2863,7 +2863,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>9.91440677642822</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H86" t="n">
         <v>5400</v>
@@ -2892,7 +2892,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G87" t="n">
-        <v>9.89760112762451</v>
+        <v>9.8976001739502</v>
       </c>
       <c r="H87" t="n">
         <v>4400</v>
@@ -2950,7 +2950,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H89" t="n">
         <v>22400</v>
@@ -2979,7 +2979,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H90" t="n">
         <v>2000</v>
@@ -3008,7 +3008,7 @@
         <v>11.75</v>
       </c>
       <c r="G91" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H91" t="n">
         <v>1000</v>
@@ -3037,7 +3037,7 @@
         <v>11.75</v>
       </c>
       <c r="G92" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H92" t="n">
         <v>3000</v>
@@ -3066,7 +3066,7 @@
         <v>11.75</v>
       </c>
       <c r="G93" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H93" t="n">
         <v>2600</v>
@@ -3095,7 +3095,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>9.91440677642822</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H94" t="n">
         <v>6000</v>
@@ -3124,7 +3124,7 @@
         <v>11.75</v>
       </c>
       <c r="G95" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H95" t="n">
         <v>7800</v>
@@ -3153,7 +3153,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H96" t="n">
         <v>2600</v>
@@ -3182,7 +3182,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G97" t="n">
-        <v>10.0488386154175</v>
+        <v>10.0488367080688</v>
       </c>
       <c r="H97" t="n">
         <v>14800</v>
@@ -3298,7 +3298,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G101" t="n">
-        <v>9.8555908203125</v>
+        <v>9.85558986663818</v>
       </c>
       <c r="H101" t="n">
         <v>3600</v>
@@ -3414,7 +3414,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G105" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H105" t="n">
         <v>6400</v>
@@ -3501,7 +3501,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G108" t="n">
-        <v>9.65394115447998</v>
+        <v>9.6539421081543</v>
       </c>
       <c r="H108" t="n">
         <v>20400</v>
@@ -3617,7 +3617,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>9.5363130569458</v>
+        <v>9.53631401062012</v>
       </c>
       <c r="H112" t="n">
         <v>800</v>
@@ -3646,7 +3646,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G113" t="n">
-        <v>9.64553928375244</v>
+        <v>9.64553833007812</v>
       </c>
       <c r="H113" t="n">
         <v>2800</v>
@@ -3704,7 +3704,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G115" t="n">
-        <v>9.72956085205078</v>
+        <v>9.72955894470215</v>
       </c>
       <c r="H115" t="n">
         <v>6000</v>
@@ -3733,7 +3733,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H116" t="n">
         <v>4600</v>
@@ -3762,7 +3762,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H117" t="n">
         <v>16400</v>
@@ -3791,7 +3791,7 @@
         <v>11.75</v>
       </c>
       <c r="G118" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H118" t="n">
         <v>12000</v>
@@ -3820,7 +3820,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H119" t="n">
         <v>5400</v>
@@ -3849,7 +3849,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>9.78837299346924</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H120" t="n">
         <v>4800</v>
@@ -3878,7 +3878,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H121" t="n">
         <v>6200</v>
@@ -3907,7 +3907,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H122" t="n">
         <v>14000</v>
@@ -3936,7 +3936,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G123" t="n">
-        <v>9.78837299346924</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H123" t="n">
         <v>15800</v>
@@ -3965,7 +3965,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H124" t="n">
         <v>14200</v>
@@ -3994,7 +3994,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H125" t="n">
         <v>8000</v>
@@ -4023,7 +4023,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H126" t="n">
         <v>24600</v>
@@ -4052,7 +4052,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H127" t="n">
         <v>39200</v>
@@ -4081,7 +4081,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>9.78837299346924</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H128" t="n">
         <v>20000</v>
@@ -4110,7 +4110,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>9.78837299346924</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H129" t="n">
         <v>1600</v>
@@ -4139,7 +4139,7 @@
         <v>11.75</v>
       </c>
       <c r="G130" t="n">
-        <v>9.87239551544189</v>
+        <v>9.87239456176758</v>
       </c>
       <c r="H130" t="n">
         <v>3400</v>
@@ -4168,7 +4168,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H131" t="n">
         <v>5600</v>
@@ -4197,7 +4197,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G132" t="n">
-        <v>9.78837299346924</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H132" t="n">
         <v>11400</v>
@@ -4226,7 +4226,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G133" t="n">
-        <v>9.78837299346924</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H133" t="n">
         <v>9800</v>
@@ -4255,7 +4255,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H134" t="n">
         <v>3400</v>
@@ -4284,7 +4284,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H135" t="n">
         <v>5600</v>
@@ -4371,7 +4371,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>9.78837299346924</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H138" t="n">
         <v>50800</v>
@@ -4429,7 +4429,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H140" t="n">
         <v>9000</v>
@@ -4458,7 +4458,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H141" t="n">
         <v>1600</v>
@@ -4690,7 +4690,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H149" t="n">
         <v>5600</v>
@@ -4719,7 +4719,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G155" t="n">
-        <v>9.5363130569458</v>
+        <v>9.53631401062012</v>
       </c>
       <c r="H155" t="n">
         <v>27200</v>
@@ -4922,7 +4922,7 @@
         <v>11.25</v>
       </c>
       <c r="G157" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229244232178</v>
       </c>
       <c r="H157" t="n">
         <v>18800</v>
@@ -4980,7 +4980,7 @@
         <v>11</v>
       </c>
       <c r="G159" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224090576172</v>
       </c>
       <c r="H159" t="n">
         <v>14600</v>
@@ -5125,7 +5125,7 @@
         <v>11</v>
       </c>
       <c r="G164" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224090576172</v>
       </c>
       <c r="H164" t="n">
         <v>18800</v>
@@ -5154,7 +5154,7 @@
         <v>11</v>
       </c>
       <c r="G165" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224090576172</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>11</v>
       </c>
       <c r="G166" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224090576172</v>
       </c>
       <c r="H166" t="n">
         <v>400</v>
@@ -5241,7 +5241,7 @@
         <v>11</v>
       </c>
       <c r="G168" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224090576172</v>
       </c>
       <c r="H168" t="n">
         <v>1200</v>
@@ -5357,7 +5357,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H172" t="n">
         <v>35400</v>
@@ -5415,7 +5415,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>9.49430465698242</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H174" t="n">
         <v>33600</v>
@@ -5502,7 +5502,7 @@
         <v>11</v>
       </c>
       <c r="G177" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224090576172</v>
       </c>
       <c r="H177" t="n">
         <v>5200</v>
@@ -5589,7 +5589,7 @@
         <v>11.25</v>
       </c>
       <c r="G180" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229244232178</v>
       </c>
       <c r="H180" t="n">
         <v>12000</v>
@@ -5618,7 +5618,7 @@
         <v>11.25</v>
       </c>
       <c r="G181" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229244232178</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>11</v>
       </c>
       <c r="G182" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224090576172</v>
       </c>
       <c r="H182" t="n">
         <v>10000</v>
@@ -5676,7 +5676,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>9.15822124481201</v>
+        <v>9.1582202911377</v>
       </c>
       <c r="H183" t="n">
         <v>13600</v>
@@ -5705,7 +5705,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G184" t="n">
-        <v>9.11621189117432</v>
+        <v>9.1162109375</v>
       </c>
       <c r="H184" t="n">
         <v>7200</v>
@@ -5763,7 +5763,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G186" t="n">
-        <v>8.94816970825195</v>
+        <v>8.94817066192627</v>
       </c>
       <c r="H186" t="n">
         <v>25800</v>
@@ -5792,7 +5792,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>8.94816970825195</v>
+        <v>8.94817066192627</v>
       </c>
       <c r="H187" t="n">
         <v>600</v>
@@ -5879,7 +5879,7 @@
         <v>10.75</v>
       </c>
       <c r="G190" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H190" t="n">
         <v>400</v>
@@ -5908,7 +5908,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>9.11621189117432</v>
+        <v>9.1162109375</v>
       </c>
       <c r="H191" t="n">
         <v>11600</v>
@@ -5937,7 +5937,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>9.11621189117432</v>
+        <v>9.1162109375</v>
       </c>
       <c r="H192" t="n">
         <v>400</v>
@@ -5966,7 +5966,7 @@
         <v>10.75</v>
       </c>
       <c r="G193" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H193" t="n">
         <v>400</v>
@@ -5995,7 +5995,7 @@
         <v>10.75</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H194" t="n">
         <v>600</v>
@@ -6053,7 +6053,7 @@
         <v>10.75</v>
       </c>
       <c r="G196" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H196" t="n">
         <v>10200</v>
@@ -6082,7 +6082,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>9.15822124481201</v>
+        <v>9.1582202911377</v>
       </c>
       <c r="H197" t="n">
         <v>1000</v>
@@ -6111,7 +6111,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>9.15822124481201</v>
+        <v>9.1582202911377</v>
       </c>
       <c r="H198" t="n">
         <v>36800</v>
@@ -6169,7 +6169,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>9.15822124481201</v>
+        <v>9.1582202911377</v>
       </c>
       <c r="H200" t="n">
         <v>200</v>
@@ -6401,7 +6401,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>9.33020782470703</v>
+        <v>9.33020687103271</v>
       </c>
       <c r="H208" t="n">
         <v>20200</v>
@@ -6488,7 +6488,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>9.33020782470703</v>
+        <v>9.33020687103271</v>
       </c>
       <c r="H211" t="n">
         <v>1000</v>
@@ -6604,7 +6604,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>9.11522579193115</v>
+        <v>9.11522483825684</v>
       </c>
       <c r="H215" t="n">
         <v>18200</v>
@@ -6807,7 +6807,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G222" t="n">
-        <v>9.07222938537598</v>
+        <v>9.07222843170166</v>
       </c>
       <c r="H222" t="n">
         <v>8600</v>
@@ -6836,7 +6836,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G223" t="n">
-        <v>8.90024471282959</v>
+        <v>8.90024375915527</v>
       </c>
       <c r="H223" t="n">
         <v>20400</v>
@@ -6923,7 +6923,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>8.90024471282959</v>
+        <v>8.90024375915527</v>
       </c>
       <c r="H226" t="n">
         <v>1200</v>
@@ -7039,7 +7039,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>9.11522579193115</v>
+        <v>9.11522483825684</v>
       </c>
       <c r="H230" t="n">
         <v>64400</v>
@@ -7068,7 +7068,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>9.11522579193115</v>
+        <v>9.11522483825684</v>
       </c>
       <c r="H231" t="n">
         <v>5000</v>
@@ -7126,7 +7126,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>9.33020782470703</v>
+        <v>9.33020687103271</v>
       </c>
       <c r="H233" t="n">
         <v>11800</v>
@@ -7155,7 +7155,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G234" t="n">
-        <v>9.11522579193115</v>
+        <v>9.11522483825684</v>
       </c>
       <c r="H234" t="n">
         <v>6000</v>
@@ -7184,7 +7184,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G235" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H235" t="n">
         <v>3800</v>
@@ -7358,7 +7358,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H241" t="n">
         <v>2000</v>
@@ -7416,7 +7416,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G243" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H243" t="n">
         <v>2400</v>
@@ -7474,7 +7474,7 @@
         <v>11</v>
       </c>
       <c r="G245" t="n">
-        <v>9.45919704437256</v>
+        <v>9.45919609069824</v>
       </c>
       <c r="H245" t="n">
         <v>7000</v>
@@ -7503,7 +7503,7 @@
         <v>11</v>
       </c>
       <c r="G246" t="n">
-        <v>9.45919704437256</v>
+        <v>9.45919609069824</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G249" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H249" t="n">
         <v>1400</v>
@@ -7619,7 +7619,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G250" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H250" t="n">
         <v>4200</v>
@@ -7648,7 +7648,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H251" t="n">
         <v>4800</v>
@@ -7677,7 +7677,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G252" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H252" t="n">
         <v>1200</v>
@@ -7706,7 +7706,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H253" t="n">
         <v>2000</v>
@@ -7735,7 +7735,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G254" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>9.07222938537598</v>
+        <v>9.07222843170166</v>
       </c>
       <c r="H264" t="n">
         <v>8000</v>
@@ -8199,7 +8199,7 @@
         <v>10</v>
       </c>
       <c r="G270" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H270" t="n">
         <v>200</v>
@@ -8228,7 +8228,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>8.49607753753662</v>
+        <v>8.49607849121094</v>
       </c>
       <c r="H271" t="n">
         <v>9400</v>
@@ -8634,7 +8634,7 @@
         <v>10</v>
       </c>
       <c r="G285" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H285" t="n">
         <v>2200</v>
@@ -8750,7 +8750,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.25529956817627</v>
+        <v>8.25529861450195</v>
       </c>
       <c r="H289" t="n">
         <v>800</v>
@@ -8779,7 +8779,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G290" t="n">
-        <v>8.32409381866455</v>
+        <v>8.32409286499023</v>
       </c>
       <c r="H290" t="n">
         <v>24800</v>
@@ -8837,7 +8837,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G292" t="n">
-        <v>8.41008567810059</v>
+        <v>8.41008472442627</v>
       </c>
       <c r="H292" t="n">
         <v>3000</v>
@@ -8866,7 +8866,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G293" t="n">
-        <v>8.41008567810059</v>
+        <v>8.41008472442627</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G294" t="n">
-        <v>8.32409381866455</v>
+        <v>8.32409286499023</v>
       </c>
       <c r="H294" t="n">
         <v>13000</v>
@@ -8924,7 +8924,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G295" t="n">
-        <v>8.32409381866455</v>
+        <v>8.32409286499023</v>
       </c>
       <c r="H295" t="n">
         <v>5000</v>
@@ -8953,7 +8953,7 @@
         <v>9.5</v>
       </c>
       <c r="G296" t="n">
-        <v>8.1693058013916</v>
+        <v>8.16930675506592</v>
       </c>
       <c r="H296" t="n">
         <v>17200</v>
@@ -9040,7 +9040,7 @@
         <v>10</v>
       </c>
       <c r="G299" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H299" t="n">
         <v>3600</v>
@@ -9069,7 +9069,7 @@
         <v>10</v>
       </c>
       <c r="G300" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>10</v>
       </c>
       <c r="G301" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>10</v>
       </c>
       <c r="G302" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -9156,7 +9156,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G303" t="n">
-        <v>8.53047466278076</v>
+        <v>8.53047561645508</v>
       </c>
       <c r="H303" t="n">
         <v>2000</v>
@@ -9359,7 +9359,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G310" t="n">
-        <v>7.87693071365356</v>
+        <v>7.87693023681641</v>
       </c>
       <c r="H310" t="n">
         <v>200</v>
@@ -9388,7 +9388,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>7.87693071365356</v>
+        <v>7.87693023681641</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>7.82533645629883</v>
+        <v>7.82533597946167</v>
       </c>
       <c r="H312" t="n">
         <v>1200</v>
@@ -9446,7 +9446,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>7.70494508743286</v>
+        <v>7.70494556427002</v>
       </c>
       <c r="H313" t="n">
         <v>4200</v>
@@ -9475,7 +9475,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H314" t="n">
         <v>23200</v>
@@ -9504,7 +9504,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H315" t="n">
         <v>14000</v>
@@ -9533,7 +9533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>8.5</v>
       </c>
       <c r="G318" t="n">
-        <v>7.30937957763672</v>
+        <v>7.30937910079956</v>
       </c>
       <c r="H318" t="n">
         <v>1600</v>
@@ -9620,7 +9620,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G319" t="n">
-        <v>7.36097478866577</v>
+        <v>7.36097526550293</v>
       </c>
       <c r="H319" t="n">
         <v>2400</v>
@@ -9707,7 +9707,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G322" t="n">
-        <v>7.18898916244507</v>
+        <v>7.18898868560791</v>
       </c>
       <c r="H322" t="n">
         <v>1400</v>
@@ -9736,7 +9736,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G323" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H323" t="n">
         <v>800</v>
@@ -9794,7 +9794,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>7.2061882019043</v>
+        <v>7.20618724822998</v>
       </c>
       <c r="H325" t="n">
         <v>3000</v>
@@ -9823,7 +9823,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G326" t="n">
-        <v>7.2061882019043</v>
+        <v>7.20618724822998</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G328" t="n">
-        <v>7.82533645629883</v>
+        <v>7.82533597946167</v>
       </c>
       <c r="H328" t="n">
         <v>600</v>
@@ -9910,7 +9910,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G329" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H329" t="n">
         <v>600</v>
@@ -9968,7 +9968,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G331" t="n">
-        <v>7.72214317321777</v>
+        <v>7.72214412689209</v>
       </c>
       <c r="H331" t="n">
         <v>1800</v>
@@ -9997,7 +9997,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G332" t="n">
-        <v>7.72214317321777</v>
+        <v>7.72214412689209</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>7.70494508743286</v>
+        <v>7.70494556427002</v>
       </c>
       <c r="H333" t="n">
         <v>600</v>
@@ -10055,7 +10055,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H334" t="n">
         <v>800</v>
@@ -10084,7 +10084,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G335" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G338" t="n">
-        <v>7.53296089172363</v>
+        <v>7.53295946121216</v>
       </c>
       <c r="H338" t="n">
         <v>200</v>
@@ -10229,7 +10229,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G340" t="n">
-        <v>7.29217958450317</v>
+        <v>7.29218006134033</v>
       </c>
       <c r="H340" t="n">
         <v>2800</v>
@@ -10345,7 +10345,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G344" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H344" t="n">
         <v>17800</v>
@@ -10374,7 +10374,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G345" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H345" t="n">
         <v>5400</v>
@@ -10403,7 +10403,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G346" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H346" t="n">
         <v>4600</v>
@@ -10432,7 +10432,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G347" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G348" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H348" t="n">
         <v>3370</v>
@@ -10519,7 +10519,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G350" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H350" t="n">
         <v>18548</v>
@@ -10548,7 +10548,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G351" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H351" t="n">
         <v>3182</v>
@@ -10664,7 +10664,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H355" t="n">
         <v>8049</v>
@@ -10693,7 +10693,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G356" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H356" t="n">
         <v>5700</v>
@@ -10722,7 +10722,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G357" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H357" t="n">
         <v>15150</v>
@@ -10751,7 +10751,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G358" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>8</v>
       </c>
       <c r="G359" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H359" t="n">
         <v>140</v>
@@ -10809,7 +10809,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>6.7418270111084</v>
+        <v>6.74182748794556</v>
       </c>
       <c r="H360" t="n">
         <v>3952</v>
@@ -10838,7 +10838,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>6.7418270111084</v>
+        <v>6.74182748794556</v>
       </c>
       <c r="H361" t="n">
         <v>4250</v>
@@ -10867,7 +10867,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H362" t="n">
         <v>3100</v>
@@ -10896,7 +10896,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>6.7418270111084</v>
+        <v>6.74182748794556</v>
       </c>
       <c r="H363" t="n">
         <v>6700</v>
@@ -11041,7 +11041,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H368" t="n">
         <v>200</v>
@@ -11186,7 +11186,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>7.05140018463135</v>
+        <v>7.05140113830566</v>
       </c>
       <c r="H373" t="n">
         <v>354</v>
@@ -11302,7 +11302,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>6.84501886367798</v>
+        <v>6.84501838684082</v>
       </c>
       <c r="H377" t="n">
         <v>2353</v>
@@ -11331,7 +11331,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>6.84501886367798</v>
+        <v>6.84501838684082</v>
       </c>
       <c r="H378" t="n">
         <v>4149</v>
@@ -11418,7 +11418,7 @@
         <v>8</v>
       </c>
       <c r="G381" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H381" t="n">
         <v>1532</v>
@@ -11447,7 +11447,7 @@
         <v>8</v>
       </c>
       <c r="G382" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H382" t="n">
         <v>291</v>
@@ -11505,7 +11505,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H384" t="n">
         <v>124</v>
@@ -11534,7 +11534,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G385" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H385" t="n">
         <v>10</v>
@@ -11563,7 +11563,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G386" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G387" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G388" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H388" t="n">
         <v>3115</v>
@@ -11679,7 +11679,7 @@
         <v>8</v>
       </c>
       <c r="G390" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H390" t="n">
         <v>7347</v>
@@ -11737,7 +11737,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>6.84501886367798</v>
+        <v>6.84501838684082</v>
       </c>
       <c r="H392" t="n">
         <v>2665</v>
@@ -11795,7 +11795,7 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H394" t="n">
         <v>1786</v>
@@ -11824,7 +11824,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G395" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H395" t="n">
         <v>9230</v>
@@ -11853,7 +11853,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H396" t="n">
         <v>1510</v>
@@ -11882,7 +11882,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H397" t="n">
         <v>4250</v>
@@ -11969,7 +11969,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G400" t="n">
-        <v>7.01700401306152</v>
+        <v>7.01700353622437</v>
       </c>
       <c r="H400" t="n">
         <v>4830</v>
@@ -11998,7 +11998,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G401" t="n">
-        <v>7.01700401306152</v>
+        <v>7.01700353622437</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -12027,7 +12027,7 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H402" t="n">
         <v>6710</v>
@@ -12056,7 +12056,7 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H403" t="n">
         <v>2710</v>
@@ -12201,7 +12201,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G408" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H408" t="n">
         <v>66943</v>
@@ -12230,7 +12230,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>7.24058532714844</v>
+        <v>7.24058485031128</v>
       </c>
       <c r="H409" t="n">
         <v>12395</v>
@@ -12288,7 +12288,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G411" t="n">
-        <v>7.53296089172363</v>
+        <v>7.53295946121216</v>
       </c>
       <c r="H411" t="n">
         <v>7212</v>
@@ -12346,7 +12346,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H413" t="n">
         <v>3920</v>
@@ -12375,7 +12375,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G414" t="n">
-        <v>7.44696807861328</v>
+        <v>7.44696712493896</v>
       </c>
       <c r="H414" t="n">
         <v>2400</v>
@@ -12433,7 +12433,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G416" t="n">
-        <v>7.72214317321777</v>
+        <v>7.72214412689209</v>
       </c>
       <c r="H416" t="n">
         <v>11289</v>
@@ -12462,7 +12462,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G417" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H417" t="n">
         <v>1940</v>
@@ -12491,7 +12491,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G418" t="n">
-        <v>7.53296089172363</v>
+        <v>7.53295946121216</v>
       </c>
       <c r="H418" t="n">
         <v>2536</v>
@@ -12549,7 +12549,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>7.3437762260437</v>
+        <v>7.34377574920654</v>
       </c>
       <c r="H420" t="n">
         <v>4725</v>
@@ -12578,7 +12578,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>7.3437762260437</v>
+        <v>7.34377574920654</v>
       </c>
       <c r="H421" t="n">
         <v>1620</v>
@@ -12607,7 +12607,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G422" t="n">
-        <v>7.36097478866577</v>
+        <v>7.36097526550293</v>
       </c>
       <c r="H422" t="n">
         <v>1868</v>
@@ -12636,7 +12636,7 @@
         <v>8.5</v>
       </c>
       <c r="G423" t="n">
-        <v>7.30937957763672</v>
+        <v>7.30937910079956</v>
       </c>
       <c r="H423" t="n">
         <v>1963</v>
@@ -12665,7 +12665,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H424" t="n">
         <v>13987</v>
@@ -12694,7 +12694,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H425" t="n">
         <v>1500</v>
@@ -12723,7 +12723,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H426" t="n">
         <v>822</v>
@@ -12781,7 +12781,7 @@
         <v>8.5</v>
       </c>
       <c r="G428" t="n">
-        <v>7.30937957763672</v>
+        <v>7.30937910079956</v>
       </c>
       <c r="H428" t="n">
         <v>1002</v>
@@ -12810,7 +12810,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G429" t="n">
-        <v>7.29217958450317</v>
+        <v>7.29218006134033</v>
       </c>
       <c r="H429" t="n">
         <v>314</v>
@@ -12868,7 +12868,7 @@
         <v>8.5</v>
       </c>
       <c r="G431" t="n">
-        <v>7.30937957763672</v>
+        <v>7.30937910079956</v>
       </c>
       <c r="H431" t="n">
         <v>400</v>
@@ -12897,7 +12897,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H432" t="n">
         <v>7444</v>
@@ -12955,7 +12955,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H434" t="n">
         <v>1098</v>
@@ -12984,7 +12984,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G435" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H435" t="n">
         <v>1451</v>
@@ -13042,7 +13042,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G437" t="n">
-        <v>7.61035346984863</v>
+        <v>7.61035442352295</v>
       </c>
       <c r="H437" t="n">
         <v>5810</v>
@@ -13071,7 +13071,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H438" t="n">
         <v>5485</v>
@@ -13100,7 +13100,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H439" t="n">
         <v>572</v>
@@ -13129,7 +13129,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H440" t="n">
         <v>1662</v>
@@ -13158,7 +13158,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>7.78233909606934</v>
+        <v>7.78233861923218</v>
       </c>
       <c r="H442" t="n">
         <v>10</v>
@@ -13216,7 +13216,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H443" t="n">
         <v>4760</v>
@@ -13245,7 +13245,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H444" t="n">
         <v>800</v>
@@ -13274,7 +13274,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H445" t="n">
         <v>8557</v>
@@ -13970,7 +13970,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G469" t="n">
-        <v>7.1553783416748</v>
+        <v>7.15537786483765</v>
       </c>
       <c r="H469" t="n">
         <v>1420</v>
@@ -14028,7 +14028,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>7.28870725631714</v>
+        <v>7.2887077331543</v>
       </c>
       <c r="H471" t="n">
         <v>30</v>
@@ -14260,7 +14260,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G479" t="n">
-        <v>7.28870725631714</v>
+        <v>7.2887077331543</v>
       </c>
       <c r="H479" t="n">
         <v>3000</v>
@@ -14289,7 +14289,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G480" t="n">
-        <v>7.46648120880127</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H480" t="n">
         <v>10</v>
@@ -14318,7 +14318,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G481" t="n">
-        <v>7.46648120880127</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H481" t="n">
         <v>0</v>
@@ -14347,7 +14347,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G482" t="n">
-        <v>7.46648120880127</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H482" t="n">
         <v>0</v>
@@ -14666,7 +14666,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G493" t="n">
-        <v>7.46648120880127</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H493" t="n">
         <v>2584</v>
@@ -15275,7 +15275,7 @@
         <v>7.75</v>
       </c>
       <c r="G514" t="n">
-        <v>6.88871812820435</v>
+        <v>6.88871765136719</v>
       </c>
       <c r="H514" t="n">
         <v>1660</v>
@@ -15304,7 +15304,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G515" t="n">
-        <v>7.1553783416748</v>
+        <v>7.15537786483765</v>
       </c>
       <c r="H515" t="n">
         <v>10</v>
@@ -15333,7 +15333,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>6.97760391235352</v>
+        <v>6.97760438919067</v>
       </c>
       <c r="H516" t="n">
         <v>192</v>
@@ -15362,7 +15362,7 @@
         <v>7.5</v>
       </c>
       <c r="G517" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H517" t="n">
         <v>2568</v>
@@ -15420,7 +15420,7 @@
         <v>7.5</v>
       </c>
       <c r="G519" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H519" t="n">
         <v>610</v>
@@ -15449,7 +15449,7 @@
         <v>7.5</v>
       </c>
       <c r="G520" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H520" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>7.5</v>
       </c>
       <c r="G525" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H525" t="n">
         <v>400</v>
@@ -15623,7 +15623,7 @@
         <v>7.5</v>
       </c>
       <c r="G526" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H526" t="n">
         <v>0</v>
@@ -15652,7 +15652,7 @@
         <v>7.5</v>
       </c>
       <c r="G527" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>7.5</v>
       </c>
       <c r="G528" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H528" t="n">
         <v>3103</v>
@@ -15855,7 +15855,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.39984035491943</v>
+        <v>6.39984083175659</v>
       </c>
       <c r="H534" t="n">
         <v>2911</v>
@@ -16087,7 +16087,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.39984035491943</v>
+        <v>6.39984083175659</v>
       </c>
       <c r="H542" t="n">
         <v>6172</v>
@@ -16116,7 +16116,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>6.39984035491943</v>
+        <v>6.39984083175659</v>
       </c>
       <c r="H543" t="n">
         <v>3219</v>
@@ -16377,7 +16377,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G552" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H552" t="n">
         <v>1717</v>
@@ -16493,7 +16493,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G556" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H556" t="n">
         <v>670</v>
@@ -16957,7 +16957,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G572" t="n">
-        <v>6.1776237487793</v>
+        <v>6.17762422561646</v>
       </c>
       <c r="H572" t="n">
         <v>12462</v>
@@ -16986,7 +16986,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G573" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H573" t="n">
         <v>4179</v>
@@ -17015,7 +17015,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G574" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H574" t="n">
         <v>2117</v>
@@ -17073,7 +17073,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G576" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H576" t="n">
         <v>3710</v>
@@ -17102,7 +17102,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H577" t="n">
         <v>2610</v>
@@ -17131,7 +17131,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -17247,7 +17247,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G582" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H582" t="n">
         <v>2138</v>
@@ -17276,7 +17276,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G583" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H583" t="n">
         <v>18938</v>
@@ -17363,7 +17363,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G586" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H586" t="n">
         <v>2734</v>
@@ -17392,7 +17392,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H587" t="n">
         <v>3257</v>
@@ -17537,7 +17537,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H592" t="n">
         <v>3684</v>
@@ -17566,7 +17566,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H593" t="n">
         <v>5400</v>
@@ -17682,7 +17682,7 @@
         <v>6.5</v>
       </c>
       <c r="G597" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H597" t="n">
         <v>12670</v>
@@ -17711,7 +17711,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H598" t="n">
         <v>8965</v>
@@ -17740,7 +17740,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G599" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H599" t="n">
         <v>11436</v>
@@ -17769,7 +17769,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G600" t="n">
-        <v>5.59986066818237</v>
+        <v>5.59986114501953</v>
       </c>
       <c r="H600" t="n">
         <v>44660</v>
@@ -17798,7 +17798,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G601" t="n">
-        <v>5.59986066818237</v>
+        <v>5.59986114501953</v>
       </c>
       <c r="H601" t="n">
         <v>43295</v>
@@ -17827,7 +17827,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G602" t="n">
-        <v>5.59986066818237</v>
+        <v>5.59986114501953</v>
       </c>
       <c r="H602" t="n">
         <v>9860</v>
@@ -17914,7 +17914,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G605" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H605" t="n">
         <v>2051</v>
@@ -17972,7 +17972,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G607" t="n">
-        <v>5.86652088165283</v>
+        <v>5.86652040481567</v>
       </c>
       <c r="H607" t="n">
         <v>17462</v>
@@ -18233,7 +18233,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G616" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H616" t="n">
         <v>3231</v>
@@ -18262,7 +18262,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G618" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H618" t="n">
         <v>2032</v>
@@ -18320,7 +18320,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G619" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H619" t="n">
         <v>50</v>
@@ -18349,7 +18349,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H620" t="n">
         <v>7613</v>
@@ -18726,7 +18726,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.86652088165283</v>
+        <v>5.86652040481567</v>
       </c>
       <c r="H633" t="n">
         <v>5366</v>
@@ -18755,7 +18755,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G634" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H634" t="n">
         <v>2000</v>
@@ -18784,7 +18784,7 @@
         <v>6.5</v>
       </c>
       <c r="G635" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H635" t="n">
         <v>12636</v>
@@ -18813,7 +18813,7 @@
         <v>6.5</v>
       </c>
       <c r="G636" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H636" t="n">
         <v>4185</v>
@@ -18842,7 +18842,7 @@
         <v>6.5</v>
       </c>
       <c r="G637" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H637" t="n">
         <v>0</v>
@@ -18871,7 +18871,7 @@
         <v>6.5</v>
       </c>
       <c r="G638" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H638" t="n">
         <v>3450</v>
@@ -18900,7 +18900,7 @@
         <v>6.5</v>
       </c>
       <c r="G639" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H639" t="n">
         <v>0</v>
@@ -18929,7 +18929,7 @@
         <v>6.5</v>
       </c>
       <c r="G640" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H640" t="n">
         <v>1550</v>
@@ -18987,7 +18987,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H642" t="n">
         <v>2879</v>
@@ -19016,7 +19016,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G643" t="n">
-        <v>5.59986066818237</v>
+        <v>5.59986114501953</v>
       </c>
       <c r="H643" t="n">
         <v>4049</v>
@@ -19045,7 +19045,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>5.6443042755127</v>
+        <v>5.64430379867554</v>
       </c>
       <c r="H644" t="n">
         <v>5286</v>
@@ -19103,7 +19103,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.6443042755127</v>
+        <v>5.64430379867554</v>
       </c>
       <c r="H646" t="n">
         <v>297</v>
@@ -19190,7 +19190,7 @@
         <v>6.5</v>
       </c>
       <c r="G649" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H649" t="n">
         <v>6789</v>
@@ -19248,7 +19248,7 @@
         <v>6.5</v>
       </c>
       <c r="G651" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H651" t="n">
         <v>1008</v>
@@ -19277,7 +19277,7 @@
         <v>6.5</v>
       </c>
       <c r="G652" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H652" t="n">
         <v>11094</v>
@@ -19306,7 +19306,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G653" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H653" t="n">
         <v>4753</v>
@@ -19393,7 +19393,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G656" t="n">
-        <v>5.59986066818237</v>
+        <v>5.59986114501953</v>
       </c>
       <c r="H656" t="n">
         <v>2652</v>
@@ -19567,7 +19567,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G662" t="n">
-        <v>5.37764406204224</v>
+        <v>5.37764453887939</v>
       </c>
       <c r="H662" t="n">
         <v>1</v>
@@ -19683,7 +19683,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G666" t="n">
-        <v>4.35544729232788</v>
+        <v>4.35544681549072</v>
       </c>
       <c r="H666" t="n">
         <v>11395</v>
@@ -19712,7 +19712,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>4.26656055450439</v>
+        <v>4.26656103134155</v>
       </c>
       <c r="H667" t="n">
         <v>8251</v>
@@ -19799,7 +19799,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G670" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H670" t="n">
         <v>10643</v>
@@ -19828,7 +19828,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G671" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -19857,7 +19857,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G672" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G673" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G674" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H674" t="n">
         <v>0</v>
@@ -20002,7 +20002,7 @@
         <v>4.5</v>
       </c>
       <c r="G677" t="n">
-        <v>3.99990105628967</v>
+        <v>3.99990081787109</v>
       </c>
       <c r="H677" t="n">
         <v>2379</v>
@@ -20118,7 +20118,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>3.73324060440063</v>
+        <v>3.73324036598206</v>
       </c>
       <c r="H681" t="n">
         <v>1886</v>
@@ -20176,7 +20176,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G683" t="n">
-        <v>3.64435362815857</v>
+        <v>3.64435386657715</v>
       </c>
       <c r="H683" t="n">
         <v>1800</v>
@@ -20263,7 +20263,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G686" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H686" t="n">
         <v>4888</v>
@@ -20350,7 +20350,7 @@
         <v>4.5</v>
       </c>
       <c r="G689" t="n">
-        <v>3.99990105628967</v>
+        <v>3.99990081787109</v>
       </c>
       <c r="H689" t="n">
         <v>1891</v>
@@ -20379,7 +20379,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G690" t="n">
-        <v>4.08878707885742</v>
+        <v>4.08878755569458</v>
       </c>
       <c r="H690" t="n">
         <v>5209</v>
@@ -20524,7 +20524,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H695" t="n">
         <v>4540</v>
@@ -20553,7 +20553,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H696" t="n">
         <v>470</v>
@@ -20611,7 +20611,7 @@
         <v>4.5</v>
       </c>
       <c r="G698" t="n">
-        <v>3.99990105628967</v>
+        <v>3.99990081787109</v>
       </c>
       <c r="H698" t="n">
         <v>1703</v>
@@ -20698,7 +20698,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G701" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H701" t="n">
         <v>11088</v>
@@ -20785,7 +20785,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G704" t="n">
-        <v>3.90212488174438</v>
+        <v>3.90212512016296</v>
       </c>
       <c r="H704" t="n">
         <v>1895</v>
@@ -20901,7 +20901,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G708" t="n">
-        <v>3.83101558685303</v>
+        <v>3.83101606369019</v>
       </c>
       <c r="H708" t="n">
         <v>6323</v>
@@ -20930,7 +20930,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>3.83101558685303</v>
+        <v>3.83101606369019</v>
       </c>
       <c r="H709" t="n">
         <v>2542</v>
@@ -21104,7 +21104,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G715" t="n">
-        <v>3.81323862075806</v>
+        <v>3.81323838233948</v>
       </c>
       <c r="H715" t="n">
         <v>611</v>
@@ -21220,7 +21220,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G719" t="n">
-        <v>4.08878707885742</v>
+        <v>4.08878755569458</v>
       </c>
       <c r="H719" t="n">
         <v>10718</v>
@@ -21249,7 +21249,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G720" t="n">
-        <v>4.06212091445923</v>
+        <v>4.06212139129639</v>
       </c>
       <c r="H720" t="n">
         <v>15398</v>
@@ -21278,7 +21278,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>4.13323068618774</v>
+        <v>4.13323020935059</v>
       </c>
       <c r="H721" t="n">
         <v>12913</v>
@@ -21452,7 +21452,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G727" t="n">
-        <v>4.09767627716064</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H727" t="n">
         <v>30466</v>
@@ -21539,7 +21539,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>4.38185453414917</v>
+        <v>4.38185501098633</v>
       </c>
       <c r="H730" t="n">
         <v>61399</v>
@@ -21568,7 +21568,7 @@
         <v>4.75</v>
       </c>
       <c r="G731" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H731" t="n">
         <v>16376</v>
@@ -21655,7 +21655,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G734" t="n">
-        <v>4.38185453414917</v>
+        <v>4.38185501098633</v>
       </c>
       <c r="H734" t="n">
         <v>34375</v>
@@ -21684,7 +21684,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G735" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H735" t="n">
         <v>17125</v>
@@ -21713,7 +21713,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G736" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H736" t="n">
         <v>9606</v>
@@ -21742,7 +21742,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G737" t="n">
-        <v>4.40935564041138</v>
+        <v>4.40935611724854</v>
       </c>
       <c r="H737" t="n">
         <v>2683</v>
@@ -21771,7 +21771,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>4.37268781661987</v>
+        <v>4.37268733978271</v>
       </c>
       <c r="H738" t="n">
         <v>600</v>
@@ -21800,7 +21800,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>4.37268781661987</v>
+        <v>4.37268733978271</v>
       </c>
       <c r="H739" t="n">
         <v>680</v>
@@ -21829,7 +21829,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G740" t="n">
-        <v>4.32685232162476</v>
+        <v>4.3268518447876</v>
       </c>
       <c r="H740" t="n">
         <v>7403</v>
@@ -21916,7 +21916,7 @@
         <v>4.75</v>
       </c>
       <c r="G743" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H743" t="n">
         <v>607</v>
@@ -21945,7 +21945,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G744" t="n">
-        <v>4.32685232162476</v>
+        <v>4.3268518447876</v>
       </c>
       <c r="H744" t="n">
         <v>11032</v>
@@ -22032,7 +22032,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G747" t="n">
-        <v>4.23518180847168</v>
+        <v>4.23518133163452</v>
       </c>
       <c r="H747" t="n">
         <v>2630</v>
@@ -22061,7 +22061,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>4.23518180847168</v>
+        <v>4.23518133163452</v>
       </c>
       <c r="H748" t="n">
         <v>1000</v>
@@ -22177,7 +22177,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G752" t="n">
-        <v>4.18934679031372</v>
+        <v>4.18934631347656</v>
       </c>
       <c r="H752" t="n">
         <v>1350</v>
@@ -22380,7 +22380,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G759" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H759" t="n">
         <v>3488</v>
@@ -22467,7 +22467,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.18934679031372</v>
+        <v>4.18934631347656</v>
       </c>
       <c r="H762" t="n">
         <v>4900</v>
@@ -22641,7 +22641,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H768" t="n">
         <v>8119</v>
@@ -22902,7 +22902,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>4.21684789657593</v>
+        <v>4.21684741973877</v>
       </c>
       <c r="H777" t="n">
         <v>7930</v>
@@ -22931,7 +22931,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>4.08850860595703</v>
+        <v>4.08850908279419</v>
       </c>
       <c r="H778" t="n">
         <v>10894</v>
@@ -23105,7 +23105,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G784" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H784" t="n">
         <v>10522</v>
@@ -23163,7 +23163,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G786" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H786" t="n">
         <v>1030</v>
@@ -23192,7 +23192,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G787" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>4.07934188842773</v>
+        <v>4.07934141159058</v>
       </c>
       <c r="H788" t="n">
         <v>5464</v>
@@ -23250,7 +23250,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G789" t="n">
-        <v>4.07934188842773</v>
+        <v>4.07934141159058</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -23337,7 +23337,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>4.04267311096191</v>
+        <v>4.04267358779907</v>
       </c>
       <c r="H792" t="n">
         <v>1205</v>
@@ -23482,7 +23482,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G797" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H797" t="n">
         <v>2403</v>
@@ -23511,7 +23511,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G798" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H798" t="n">
         <v>1860</v>
@@ -23598,7 +23598,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>3.91433477401733</v>
+        <v>3.91433453559875</v>
       </c>
       <c r="H801" t="n">
         <v>1035</v>
@@ -23743,7 +23743,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.86849927902222</v>
+        <v>3.86849904060364</v>
       </c>
       <c r="H806" t="n">
         <v>3833</v>
@@ -23772,7 +23772,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G807" t="n">
-        <v>3.88683342933655</v>
+        <v>3.88683319091797</v>
       </c>
       <c r="H807" t="n">
         <v>13265</v>
@@ -23801,7 +23801,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G808" t="n">
-        <v>3.88683342933655</v>
+        <v>3.88683319091797</v>
       </c>
       <c r="H808" t="n">
         <v>12349</v>
@@ -23946,7 +23946,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G813" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H813" t="n">
         <v>11042</v>
@@ -24004,7 +24004,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>4.37268781661987</v>
+        <v>4.37268733978271</v>
       </c>
       <c r="H815" t="n">
         <v>4760</v>
@@ -24033,7 +24033,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G816" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H816" t="n">
         <v>7780</v>
@@ -24120,7 +24120,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G819" t="n">
-        <v>4.32685232162476</v>
+        <v>4.3268518447876</v>
       </c>
       <c r="H819" t="n">
         <v>785</v>
@@ -24178,7 +24178,7 @@
         <v>4.75</v>
       </c>
       <c r="G821" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H821" t="n">
         <v>6878</v>
@@ -24294,7 +24294,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G825" t="n">
-        <v>4.51936006546021</v>
+        <v>4.51936054229736</v>
       </c>
       <c r="H825" t="n">
         <v>1867</v>
@@ -24352,7 +24352,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>4.51019382476807</v>
+        <v>4.51019334793091</v>
       </c>
       <c r="H827" t="n">
         <v>10424</v>
@@ -24410,7 +24410,7 @@
         <v>4.75</v>
       </c>
       <c r="G829" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H829" t="n">
         <v>5800</v>
@@ -24468,7 +24468,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.04267311096191</v>
+        <v>4.04267358779907</v>
       </c>
       <c r="H831" t="n">
         <v>16333</v>
@@ -24555,7 +24555,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>3.94183611869812</v>
+        <v>3.94183588027954</v>
       </c>
       <c r="H834" t="n">
         <v>25951</v>
@@ -24642,7 +24642,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>4.21684789657593</v>
+        <v>4.21684741973877</v>
       </c>
       <c r="H837" t="n">
         <v>21835</v>
@@ -24729,7 +24729,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G840" t="n">
-        <v>4.18934679031372</v>
+        <v>4.18934631347656</v>
       </c>
       <c r="H840" t="n">
         <v>34559</v>
@@ -24758,7 +24758,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>4.23518180847168</v>
+        <v>4.23518133163452</v>
       </c>
       <c r="H841" t="n">
         <v>225</v>
@@ -24845,7 +24845,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G844" t="n">
-        <v>4.21684789657593</v>
+        <v>4.21684741973877</v>
       </c>
       <c r="H844" t="n">
         <v>16368</v>
@@ -25193,7 +25193,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>4.96854686737061</v>
+        <v>4.96854639053345</v>
       </c>
       <c r="H856" t="n">
         <v>13143</v>
@@ -25309,7 +25309,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>5.11521911621094</v>
+        <v>5.1152195930481</v>
       </c>
       <c r="H860" t="n">
         <v>16237</v>
@@ -25367,7 +25367,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G862" t="n">
-        <v>5.13355398178101</v>
+        <v>5.13355350494385</v>
       </c>
       <c r="H862" t="n">
         <v>13036</v>
@@ -25396,7 +25396,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G863" t="n">
-        <v>5.15188789367676</v>
+        <v>5.1518874168396</v>
       </c>
       <c r="H863" t="n">
         <v>7153</v>
@@ -25454,7 +25454,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>5.00521469116211</v>
+        <v>5.00521516799927</v>
       </c>
       <c r="H865" t="n">
         <v>3756</v>
@@ -25686,7 +25686,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G873" t="n">
-        <v>5.39023160934448</v>
+        <v>5.39023113250732</v>
       </c>
       <c r="H873" t="n">
         <v>31741</v>
@@ -25715,7 +25715,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G874" t="n">
-        <v>5.39023160934448</v>
+        <v>5.39023113250732</v>
       </c>
       <c r="H874" t="n">
         <v>13377</v>
@@ -25831,7 +25831,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G878" t="n">
-        <v>5.6102409362793</v>
+        <v>5.61024045944214</v>
       </c>
       <c r="H878" t="n">
         <v>24852</v>
@@ -25947,7 +25947,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G882" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H882" t="n">
         <v>8738</v>
@@ -25976,7 +25976,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>5.88525295257568</v>
+        <v>5.88525247573853</v>
       </c>
       <c r="H883" t="n">
         <v>11732</v>
@@ -26121,7 +26121,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>5.9402551651001</v>
+        <v>5.94025468826294</v>
       </c>
       <c r="H888" t="n">
         <v>7733</v>
@@ -26266,7 +26266,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G893" t="n">
-        <v>5.83025026321411</v>
+        <v>5.83025074005127</v>
       </c>
       <c r="H893" t="n">
         <v>46103</v>
@@ -26324,7 +26324,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>5.92192077636719</v>
+        <v>5.92192125320435</v>
       </c>
       <c r="H895" t="n">
         <v>1658</v>
@@ -26382,7 +26382,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>5.92192077636719</v>
+        <v>5.92192125320435</v>
       </c>
       <c r="H897" t="n">
         <v>3856</v>
@@ -26469,7 +26469,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>5.92192077636719</v>
+        <v>5.92192125320435</v>
       </c>
       <c r="H900" t="n">
         <v>19114</v>
@@ -26498,7 +26498,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H901" t="n">
         <v>5834</v>
@@ -26527,7 +26527,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H902" t="n">
         <v>4663</v>
@@ -26643,7 +26643,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G906" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H906" t="n">
         <v>7547</v>
@@ -26759,7 +26759,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G910" t="n">
-        <v>6.19693279266357</v>
+        <v>6.19693326950073</v>
       </c>
       <c r="H910" t="n">
         <v>32257</v>
@@ -26817,7 +26817,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>6.38027381896973</v>
+        <v>6.38027429580688</v>
       </c>
       <c r="H912" t="n">
         <v>24783</v>
@@ -26846,7 +26846,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G913" t="n">
-        <v>6.28860330581665</v>
+        <v>6.28860378265381</v>
       </c>
       <c r="H913" t="n">
         <v>13157</v>
@@ -26991,7 +26991,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>6.4719443321228</v>
+        <v>6.47194480895996</v>
       </c>
       <c r="H918" t="n">
         <v>6002</v>
@@ -27049,7 +27049,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G920" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H920" t="n">
         <v>2787</v>
@@ -27078,7 +27078,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H921" t="n">
         <v>4737</v>
@@ -27107,7 +27107,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G922" t="n">
-        <v>6.58194923400879</v>
+        <v>6.58194875717163</v>
       </c>
       <c r="H922" t="n">
         <v>5358</v>
@@ -27165,7 +27165,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G924" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H924" t="n">
         <v>4250</v>
@@ -27252,7 +27252,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G927" t="n">
-        <v>6.61861753463745</v>
+        <v>6.61861705780029</v>
       </c>
       <c r="H927" t="n">
         <v>9701</v>
@@ -27339,7 +27339,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>6.58194923400879</v>
+        <v>6.58194875717163</v>
       </c>
       <c r="H930" t="n">
         <v>1400</v>
@@ -27368,7 +27368,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G931" t="n">
-        <v>6.61861753463745</v>
+        <v>6.61861705780029</v>
       </c>
       <c r="H931" t="n">
         <v>4392</v>
@@ -27542,7 +27542,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G937" t="n">
-        <v>6.54528045654297</v>
+        <v>6.54528093338013</v>
       </c>
       <c r="H937" t="n">
         <v>11503</v>
@@ -27600,7 +27600,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G939" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H939" t="n">
         <v>14602</v>
@@ -27658,7 +27658,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>6.85696125030518</v>
+        <v>6.85696077346802</v>
       </c>
       <c r="H941" t="n">
         <v>21995</v>
@@ -27890,7 +27890,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H949" t="n">
         <v>6250</v>
@@ -28093,7 +28093,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G956" t="n">
-        <v>6.78362417221069</v>
+        <v>6.78362464904785</v>
       </c>
       <c r="H956" t="n">
         <v>5975</v>
@@ -68641,6 +68641,35 @@
         <v>3088</v>
       </c>
       <c r="I2354" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2355" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2355" t="n">
+        <v>2.30999994277954</v>
+      </c>
+      <c r="D2355" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="E2355" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F2355" t="n">
+        <v>2.32999992370605</v>
+      </c>
+      <c r="G2355" t="n">
+        <v>2.32999992370605</v>
+      </c>
+      <c r="H2355" t="n">
+        <v>1759</v>
+      </c>
+      <c r="I2355" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2" t="n">
-        <v>9.40188026428223</v>
+        <v>9.40188121795654</v>
       </c>
       <c r="H2" t="n">
         <v>56600</v>
@@ -456,7 +456,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G3" t="n">
-        <v>9.44389152526855</v>
+        <v>9.44389057159424</v>
       </c>
       <c r="H3" t="n">
         <v>18800</v>
@@ -514,7 +514,7 @@
         <v>11.25</v>
       </c>
       <c r="G5" t="n">
-        <v>9.45229244232178</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H5" t="n">
         <v>13000</v>
@@ -543,7 +543,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394115447998</v>
       </c>
       <c r="H6" t="n">
         <v>18000</v>
@@ -601,7 +601,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394115447998</v>
       </c>
       <c r="H8" t="n">
         <v>4800</v>
@@ -746,7 +746,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033462524414</v>
       </c>
       <c r="H13" t="n">
         <v>1200</v>
@@ -833,7 +833,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G16" t="n">
-        <v>9.63713836669922</v>
+        <v>9.6371374130249</v>
       </c>
       <c r="H16" t="n">
         <v>11400</v>
@@ -862,7 +862,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>9.52791213989258</v>
+        <v>9.52791118621826</v>
       </c>
       <c r="H17" t="n">
         <v>248200</v>
@@ -891,7 +891,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G18" t="n">
-        <v>9.63713836669922</v>
+        <v>9.6371374130249</v>
       </c>
       <c r="H18" t="n">
         <v>2600</v>
@@ -949,7 +949,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G20" t="n">
-        <v>9.61193180084229</v>
+        <v>9.61193084716797</v>
       </c>
       <c r="H20" t="n">
         <v>2200</v>
@@ -978,7 +978,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>9.61193180084229</v>
+        <v>9.61193084716797</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G22" t="n">
-        <v>9.64553833007812</v>
+        <v>9.64553928375244</v>
       </c>
       <c r="H22" t="n">
         <v>3400</v>
@@ -1065,7 +1065,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G24" t="n">
-        <v>9.40188026428223</v>
+        <v>9.40188121795654</v>
       </c>
       <c r="H24" t="n">
         <v>600</v>
@@ -1181,7 +1181,7 @@
         <v>11.25</v>
       </c>
       <c r="G28" t="n">
-        <v>9.45229244232178</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H28" t="n">
         <v>3600</v>
@@ -1239,7 +1239,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G30" t="n">
-        <v>9.51950836181641</v>
+        <v>9.51950931549072</v>
       </c>
       <c r="H30" t="n">
         <v>2600</v>
@@ -1268,7 +1268,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G31" t="n">
-        <v>9.52791213989258</v>
+        <v>9.52791118621826</v>
       </c>
       <c r="H31" t="n">
         <v>4600</v>
@@ -1326,7 +1326,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G33" t="n">
-        <v>9.56992149353027</v>
+        <v>9.56992244720459</v>
       </c>
       <c r="H33" t="n">
         <v>1800</v>
@@ -1355,7 +1355,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G34" t="n">
-        <v>9.52791213989258</v>
+        <v>9.52791118621826</v>
       </c>
       <c r="H34" t="n">
         <v>14200</v>
@@ -1442,7 +1442,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G37" t="n">
-        <v>9.56992149353027</v>
+        <v>9.56992244720459</v>
       </c>
       <c r="H37" t="n">
         <v>3000</v>
@@ -1500,7 +1500,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G39" t="n">
-        <v>9.64553833007812</v>
+        <v>9.64553928375244</v>
       </c>
       <c r="H39" t="n">
         <v>800</v>
@@ -1587,7 +1587,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G42" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H42" t="n">
         <v>7000</v>
@@ -1616,7 +1616,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H43" t="n">
         <v>2000</v>
@@ -1645,7 +1645,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H44" t="n">
         <v>4400</v>
@@ -1674,7 +1674,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G45" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198143005371</v>
       </c>
       <c r="H45" t="n">
         <v>14000</v>
@@ -1761,7 +1761,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H48" t="n">
         <v>8800</v>
@@ -1848,7 +1848,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G51" t="n">
-        <v>10.1832695007324</v>
+        <v>10.1832704544067</v>
       </c>
       <c r="H51" t="n">
         <v>127800</v>
@@ -1877,7 +1877,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H52" t="n">
         <v>97800</v>
@@ -1906,7 +1906,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G53" t="n">
-        <v>9.77997303009033</v>
+        <v>9.77997207641602</v>
       </c>
       <c r="H53" t="n">
         <v>4200</v>
@@ -1935,7 +1935,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G54" t="n">
-        <v>9.63713836669922</v>
+        <v>9.6371374130249</v>
       </c>
       <c r="H54" t="n">
         <v>30200</v>
@@ -1964,7 +1964,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G55" t="n">
-        <v>9.85558986663818</v>
+        <v>9.8555908203125</v>
       </c>
       <c r="H55" t="n">
         <v>11800</v>
@@ -1993,7 +1993,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H56" t="n">
         <v>20400</v>
@@ -2080,7 +2080,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>10.0404357910156</v>
+        <v>10.0404348373413</v>
       </c>
       <c r="H59" t="n">
         <v>61400</v>
@@ -2109,7 +2109,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G60" t="n">
-        <v>10.0320339202881</v>
+        <v>10.0320329666138</v>
       </c>
       <c r="H60" t="n">
         <v>10600</v>
@@ -2138,7 +2138,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G61" t="n">
-        <v>10.0320339202881</v>
+        <v>10.0320329666138</v>
       </c>
       <c r="H61" t="n">
         <v>11200</v>
@@ -2254,7 +2254,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198143005371</v>
       </c>
       <c r="H65" t="n">
         <v>8600</v>
@@ -2312,7 +2312,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G67" t="n">
-        <v>9.93960952758789</v>
+        <v>9.93961048126221</v>
       </c>
       <c r="H67" t="n">
         <v>18400</v>
@@ -2399,7 +2399,7 @@
         <v>11.75</v>
       </c>
       <c r="G70" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H70" t="n">
         <v>5200</v>
@@ -2457,7 +2457,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H72" t="n">
         <v>73200</v>
@@ -2515,7 +2515,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G74" t="n">
-        <v>10.0656414031982</v>
+        <v>10.0656404495239</v>
       </c>
       <c r="H74" t="n">
         <v>7000</v>
@@ -2573,7 +2573,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G76" t="n">
-        <v>10.0488367080688</v>
+        <v>10.0488386154175</v>
       </c>
       <c r="H76" t="n">
         <v>116000</v>
@@ -2602,7 +2602,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G77" t="n">
-        <v>10.0320339202881</v>
+        <v>10.0320329666138</v>
       </c>
       <c r="H77" t="n">
         <v>58000</v>
@@ -2660,7 +2660,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G79" t="n">
-        <v>10.0404357910156</v>
+        <v>10.0404348373413</v>
       </c>
       <c r="H79" t="n">
         <v>13600</v>
@@ -2689,7 +2689,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G80" t="n">
-        <v>10.0488367080688</v>
+        <v>10.0488386154175</v>
       </c>
       <c r="H80" t="n">
         <v>12400</v>
@@ -2776,7 +2776,7 @@
         <v>11.75</v>
       </c>
       <c r="G83" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H83" t="n">
         <v>13000</v>
@@ -2805,7 +2805,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H84" t="n">
         <v>6200</v>
@@ -2863,7 +2863,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H86" t="n">
         <v>5400</v>
@@ -3008,7 +3008,7 @@
         <v>11.75</v>
       </c>
       <c r="G91" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H91" t="n">
         <v>1000</v>
@@ -3037,7 +3037,7 @@
         <v>11.75</v>
       </c>
       <c r="G92" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H92" t="n">
         <v>3000</v>
@@ -3066,7 +3066,7 @@
         <v>11.75</v>
       </c>
       <c r="G93" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H93" t="n">
         <v>2600</v>
@@ -3095,7 +3095,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>9.91440582275391</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H94" t="n">
         <v>6000</v>
@@ -3124,7 +3124,7 @@
         <v>11.75</v>
       </c>
       <c r="G95" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H95" t="n">
         <v>7800</v>
@@ -3182,7 +3182,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G97" t="n">
-        <v>10.0488367080688</v>
+        <v>10.0488386154175</v>
       </c>
       <c r="H97" t="n">
         <v>14800</v>
@@ -3240,7 +3240,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G99" t="n">
-        <v>9.97321891784668</v>
+        <v>9.973219871521</v>
       </c>
       <c r="H99" t="n">
         <v>7400</v>
@@ -3298,7 +3298,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G101" t="n">
-        <v>9.85558986663818</v>
+        <v>9.8555908203125</v>
       </c>
       <c r="H101" t="n">
         <v>3600</v>
@@ -3327,7 +3327,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G102" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198143005371</v>
       </c>
       <c r="H102" t="n">
         <v>8200</v>
@@ -3356,7 +3356,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G103" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198143005371</v>
       </c>
       <c r="H103" t="n">
         <v>600</v>
@@ -3414,7 +3414,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G105" t="n">
-        <v>9.63713836669922</v>
+        <v>9.6371374130249</v>
       </c>
       <c r="H105" t="n">
         <v>6400</v>
@@ -3501,7 +3501,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G108" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394115447998</v>
       </c>
       <c r="H108" t="n">
         <v>20400</v>
@@ -3530,7 +3530,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033462524414</v>
       </c>
       <c r="H109" t="n">
         <v>9400</v>
@@ -3588,7 +3588,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033462524414</v>
       </c>
       <c r="H111" t="n">
         <v>4600</v>
@@ -3646,7 +3646,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G113" t="n">
-        <v>9.64553833007812</v>
+        <v>9.64553928375244</v>
       </c>
       <c r="H113" t="n">
         <v>2800</v>
@@ -3704,7 +3704,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G115" t="n">
-        <v>9.72955894470215</v>
+        <v>9.72955989837646</v>
       </c>
       <c r="H115" t="n">
         <v>6000</v>
@@ -3733,7 +3733,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H116" t="n">
         <v>4600</v>
@@ -3791,7 +3791,7 @@
         <v>11.75</v>
       </c>
       <c r="G118" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H118" t="n">
         <v>12000</v>
@@ -3965,7 +3965,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H124" t="n">
         <v>14200</v>
@@ -3994,7 +3994,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H125" t="n">
         <v>8000</v>
@@ -4023,7 +4023,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H126" t="n">
         <v>24600</v>
@@ -4139,7 +4139,7 @@
         <v>11.75</v>
       </c>
       <c r="G130" t="n">
-        <v>9.87239456176758</v>
+        <v>9.87239551544189</v>
       </c>
       <c r="H130" t="n">
         <v>3400</v>
@@ -4255,7 +4255,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636554718018</v>
       </c>
       <c r="H134" t="n">
         <v>3400</v>
@@ -4487,7 +4487,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H142" t="n">
         <v>12000</v>
@@ -4603,7 +4603,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H146" t="n">
         <v>2600</v>
@@ -4632,7 +4632,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G148" t="n">
-        <v>9.62033367156982</v>
+        <v>9.62033462524414</v>
       </c>
       <c r="H148" t="n">
         <v>3400</v>
@@ -4922,7 +4922,7 @@
         <v>11.25</v>
       </c>
       <c r="G157" t="n">
-        <v>9.45229244232178</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H157" t="n">
         <v>18800</v>
@@ -4980,7 +4980,7 @@
         <v>11</v>
       </c>
       <c r="G159" t="n">
-        <v>9.24224090576172</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H159" t="n">
         <v>14600</v>
@@ -5038,7 +5038,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G161" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H161" t="n">
         <v>5600</v>
@@ -5067,7 +5067,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H162" t="n">
         <v>6400</v>
@@ -5096,7 +5096,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>11</v>
       </c>
       <c r="G164" t="n">
-        <v>9.24224090576172</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H164" t="n">
         <v>18800</v>
@@ -5154,7 +5154,7 @@
         <v>11</v>
       </c>
       <c r="G165" t="n">
-        <v>9.24224090576172</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>11</v>
       </c>
       <c r="G166" t="n">
-        <v>9.24224090576172</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H166" t="n">
         <v>400</v>
@@ -5241,7 +5241,7 @@
         <v>11</v>
       </c>
       <c r="G168" t="n">
-        <v>9.24224090576172</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H168" t="n">
         <v>1200</v>
@@ -5270,7 +5270,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>9.28425216674805</v>
+        <v>9.28425312042236</v>
       </c>
       <c r="H169" t="n">
         <v>200</v>
@@ -5299,7 +5299,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G170" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H170" t="n">
         <v>1000</v>
@@ -5502,7 +5502,7 @@
         <v>11</v>
       </c>
       <c r="G177" t="n">
-        <v>9.24224090576172</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H177" t="n">
         <v>5200</v>
@@ -5560,7 +5560,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G179" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827278137207</v>
       </c>
       <c r="H179" t="n">
         <v>4000</v>
@@ -5589,7 +5589,7 @@
         <v>11.25</v>
       </c>
       <c r="G180" t="n">
-        <v>9.45229244232178</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H180" t="n">
         <v>12000</v>
@@ -5618,7 +5618,7 @@
         <v>11.25</v>
       </c>
       <c r="G181" t="n">
-        <v>9.45229244232178</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>11</v>
       </c>
       <c r="G182" t="n">
-        <v>9.24224090576172</v>
+        <v>9.24224281311035</v>
       </c>
       <c r="H182" t="n">
         <v>10000</v>
@@ -5676,7 +5676,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>9.1582202911377</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H183" t="n">
         <v>13600</v>
@@ -5705,7 +5705,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G184" t="n">
-        <v>9.1162109375</v>
+        <v>9.11621189117432</v>
       </c>
       <c r="H184" t="n">
         <v>7200</v>
@@ -5763,7 +5763,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G186" t="n">
-        <v>8.94817066192627</v>
+        <v>8.94816970825195</v>
       </c>
       <c r="H186" t="n">
         <v>25800</v>
@@ -5792,7 +5792,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>8.94817066192627</v>
+        <v>8.94816970825195</v>
       </c>
       <c r="H187" t="n">
         <v>600</v>
@@ -5908,7 +5908,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>9.1162109375</v>
+        <v>9.11621189117432</v>
       </c>
       <c r="H191" t="n">
         <v>11600</v>
@@ -5937,7 +5937,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>9.1162109375</v>
+        <v>9.11621189117432</v>
       </c>
       <c r="H192" t="n">
         <v>400</v>
@@ -6082,7 +6082,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>9.1582202911377</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H197" t="n">
         <v>1000</v>
@@ -6111,7 +6111,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>9.1582202911377</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H198" t="n">
         <v>36800</v>
@@ -6169,7 +6169,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>9.1582202911377</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H200" t="n">
         <v>200</v>
@@ -6198,7 +6198,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G201" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H201" t="n">
         <v>3200</v>
@@ -6227,7 +6227,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G202" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H202" t="n">
         <v>2800</v>
@@ -6256,7 +6256,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G203" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H203" t="n">
         <v>3200</v>
@@ -6285,7 +6285,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G204" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H204" t="n">
         <v>3600</v>
@@ -6314,7 +6314,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G205" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H205" t="n">
         <v>8800</v>
@@ -6343,7 +6343,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G206" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H206" t="n">
         <v>23000</v>
@@ -6372,7 +6372,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G207" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H207" t="n">
         <v>3200</v>
@@ -6401,7 +6401,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>9.33020687103271</v>
+        <v>9.33020782470703</v>
       </c>
       <c r="H208" t="n">
         <v>20200</v>
@@ -6459,7 +6459,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G210" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H210" t="n">
         <v>7400</v>
@@ -6488,7 +6488,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>9.33020687103271</v>
+        <v>9.33020782470703</v>
       </c>
       <c r="H211" t="n">
         <v>1000</v>
@@ -6575,7 +6575,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G214" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H214" t="n">
         <v>6600</v>
@@ -6604,7 +6604,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>9.11522483825684</v>
+        <v>9.11522579193115</v>
       </c>
       <c r="H215" t="n">
         <v>18200</v>
@@ -6662,7 +6662,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G217" t="n">
-        <v>8.72825717926025</v>
+        <v>8.72825813293457</v>
       </c>
       <c r="H217" t="n">
         <v>31200</v>
@@ -6720,7 +6720,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H219" t="n">
         <v>10600</v>
@@ -6749,7 +6749,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H220" t="n">
         <v>7600</v>
@@ -6807,7 +6807,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G222" t="n">
-        <v>9.07222843170166</v>
+        <v>9.07223033905029</v>
       </c>
       <c r="H222" t="n">
         <v>8600</v>
@@ -6836,7 +6836,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G223" t="n">
-        <v>8.90024375915527</v>
+        <v>8.90024471282959</v>
       </c>
       <c r="H223" t="n">
         <v>20400</v>
@@ -6865,7 +6865,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H224" t="n">
         <v>3000</v>
@@ -6894,7 +6894,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G225" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>8.90024375915527</v>
+        <v>8.90024471282959</v>
       </c>
       <c r="H226" t="n">
         <v>1200</v>
@@ -7039,7 +7039,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>9.11522483825684</v>
+        <v>9.11522579193115</v>
       </c>
       <c r="H230" t="n">
         <v>64400</v>
@@ -7068,7 +7068,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>9.11522483825684</v>
+        <v>9.11522579193115</v>
       </c>
       <c r="H231" t="n">
         <v>5000</v>
@@ -7126,7 +7126,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>9.33020687103271</v>
+        <v>9.33020782470703</v>
       </c>
       <c r="H233" t="n">
         <v>11800</v>
@@ -7155,7 +7155,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G234" t="n">
-        <v>9.11522483825684</v>
+        <v>9.11522579193115</v>
       </c>
       <c r="H234" t="n">
         <v>6000</v>
@@ -7184,7 +7184,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G235" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H235" t="n">
         <v>3800</v>
@@ -7213,7 +7213,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G236" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H236" t="n">
         <v>9600</v>
@@ -7242,7 +7242,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G237" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H241" t="n">
         <v>2000</v>
@@ -7416,7 +7416,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G243" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H243" t="n">
         <v>2400</v>
@@ -7445,7 +7445,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H244" t="n">
         <v>19000</v>
@@ -7532,7 +7532,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H247" t="n">
         <v>1000</v>
@@ -7561,7 +7561,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G248" t="n">
-        <v>9.28721141815186</v>
+        <v>9.28721046447754</v>
       </c>
       <c r="H248" t="n">
         <v>600</v>
@@ -7590,7 +7590,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G249" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H249" t="n">
         <v>1400</v>
@@ -7619,7 +7619,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G250" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H250" t="n">
         <v>4200</v>
@@ -7648,7 +7648,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H251" t="n">
         <v>4800</v>
@@ -7677,7 +7677,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G252" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H252" t="n">
         <v>1200</v>
@@ -7706,7 +7706,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H253" t="n">
         <v>2000</v>
@@ -7735,7 +7735,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G254" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H259" t="n">
         <v>200</v>
@@ -7909,7 +7909,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H261" t="n">
         <v>800</v>
@@ -8025,7 +8025,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>9.07222843170166</v>
+        <v>9.07223033905029</v>
       </c>
       <c r="H264" t="n">
         <v>8000</v>
@@ -8112,7 +8112,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H267" t="n">
         <v>8000</v>
@@ -8141,7 +8141,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G268" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H268" t="n">
         <v>2200</v>
@@ -8170,7 +8170,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>8.77125453948975</v>
+        <v>8.77125549316406</v>
       </c>
       <c r="H269" t="n">
         <v>400</v>
@@ -8199,7 +8199,7 @@
         <v>10</v>
       </c>
       <c r="G270" t="n">
-        <v>8.59926891326904</v>
+        <v>8.59926986694336</v>
       </c>
       <c r="H270" t="n">
         <v>200</v>
@@ -8228,7 +8228,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>8.49607849121094</v>
+        <v>8.49607753753662</v>
       </c>
       <c r="H271" t="n">
         <v>9400</v>
@@ -8315,7 +8315,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>8.3412914276123</v>
+        <v>8.34129047393799</v>
       </c>
       <c r="H274" t="n">
         <v>4800</v>
@@ -8576,7 +8576,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>8.72825717926025</v>
+        <v>8.72825813293457</v>
       </c>
       <c r="H283" t="n">
         <v>5000</v>
@@ -8605,7 +8605,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>8.72825717926025</v>
+        <v>8.72825813293457</v>
       </c>
       <c r="H284" t="n">
         <v>1000</v>
@@ -8634,7 +8634,7 @@
         <v>10</v>
       </c>
       <c r="G285" t="n">
-        <v>8.59926891326904</v>
+        <v>8.59926986694336</v>
       </c>
       <c r="H285" t="n">
         <v>2200</v>
@@ -8663,7 +8663,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>8.3412914276123</v>
+        <v>8.34129047393799</v>
       </c>
       <c r="H286" t="n">
         <v>10600</v>
@@ -8692,7 +8692,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>8.3412914276123</v>
+        <v>8.34129047393799</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G288" t="n">
-        <v>8.22090244293213</v>
+        <v>8.22090148925781</v>
       </c>
       <c r="H288" t="n">
         <v>2600</v>
@@ -8779,7 +8779,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G290" t="n">
-        <v>8.32409286499023</v>
+        <v>8.32409381866455</v>
       </c>
       <c r="H290" t="n">
         <v>24800</v>
@@ -8837,7 +8837,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G292" t="n">
-        <v>8.41008472442627</v>
+        <v>8.41008567810059</v>
       </c>
       <c r="H292" t="n">
         <v>3000</v>
@@ -8866,7 +8866,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G293" t="n">
-        <v>8.41008472442627</v>
+        <v>8.41008567810059</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G294" t="n">
-        <v>8.32409286499023</v>
+        <v>8.32409381866455</v>
       </c>
       <c r="H294" t="n">
         <v>13000</v>
@@ -8924,7 +8924,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G295" t="n">
-        <v>8.32409286499023</v>
+        <v>8.32409381866455</v>
       </c>
       <c r="H295" t="n">
         <v>5000</v>
@@ -8953,7 +8953,7 @@
         <v>9.5</v>
       </c>
       <c r="G296" t="n">
-        <v>8.16930675506592</v>
+        <v>8.1693058013916</v>
       </c>
       <c r="H296" t="n">
         <v>17200</v>
@@ -9040,7 +9040,7 @@
         <v>10</v>
       </c>
       <c r="G299" t="n">
-        <v>8.59926891326904</v>
+        <v>8.59926986694336</v>
       </c>
       <c r="H299" t="n">
         <v>3600</v>
@@ -9069,7 +9069,7 @@
         <v>10</v>
       </c>
       <c r="G300" t="n">
-        <v>8.59926891326904</v>
+        <v>8.59926986694336</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>10</v>
       </c>
       <c r="G301" t="n">
-        <v>8.59926891326904</v>
+        <v>8.59926986694336</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>10</v>
       </c>
       <c r="G302" t="n">
-        <v>8.59926891326904</v>
+        <v>8.59926986694336</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>8.3412914276123</v>
+        <v>8.34129047393799</v>
       </c>
       <c r="H305" t="n">
         <v>400</v>
@@ -9359,7 +9359,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G310" t="n">
-        <v>7.87693023681641</v>
+        <v>7.87693119049072</v>
       </c>
       <c r="H310" t="n">
         <v>200</v>
@@ -9388,7 +9388,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>7.87693023681641</v>
+        <v>7.87693119049072</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>7.82533597946167</v>
+        <v>7.82533502578735</v>
       </c>
       <c r="H312" t="n">
         <v>1200</v>
@@ -9446,7 +9446,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>7.70494556427002</v>
+        <v>7.70494508743286</v>
       </c>
       <c r="H313" t="n">
         <v>4200</v>
@@ -9475,7 +9475,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H314" t="n">
         <v>23200</v>
@@ -9504,7 +9504,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H315" t="n">
         <v>14000</v>
@@ -9533,7 +9533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G322" t="n">
-        <v>7.18898868560791</v>
+        <v>7.18898916244507</v>
       </c>
       <c r="H322" t="n">
         <v>1400</v>
@@ -9736,7 +9736,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G323" t="n">
-        <v>6.99980545043945</v>
+        <v>6.99980592727661</v>
       </c>
       <c r="H323" t="n">
         <v>800</v>
@@ -9794,7 +9794,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>7.20618724822998</v>
+        <v>7.20618772506714</v>
       </c>
       <c r="H325" t="n">
         <v>3000</v>
@@ -9823,7 +9823,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G326" t="n">
-        <v>7.20618724822998</v>
+        <v>7.20618772506714</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>9</v>
       </c>
       <c r="G327" t="n">
-        <v>7.73934316635132</v>
+        <v>7.73934364318848</v>
       </c>
       <c r="H327" t="n">
         <v>3600</v>
@@ -9881,7 +9881,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G328" t="n">
-        <v>7.82533597946167</v>
+        <v>7.82533502578735</v>
       </c>
       <c r="H328" t="n">
         <v>600</v>
@@ -9910,7 +9910,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G329" t="n">
-        <v>7.65334987640381</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H329" t="n">
         <v>600</v>
@@ -9939,7 +9939,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>7.48136472702026</v>
+        <v>7.48136425018311</v>
       </c>
       <c r="H330" t="n">
         <v>800</v>
@@ -9968,7 +9968,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G331" t="n">
-        <v>7.72214412689209</v>
+        <v>7.72214317321777</v>
       </c>
       <c r="H331" t="n">
         <v>1800</v>
@@ -9997,7 +9997,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G332" t="n">
-        <v>7.72214412689209</v>
+        <v>7.72214317321777</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>7.70494556427002</v>
+        <v>7.70494508743286</v>
       </c>
       <c r="H333" t="n">
         <v>600</v>
@@ -10055,7 +10055,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>7.65334987640381</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H334" t="n">
         <v>800</v>
@@ -10084,7 +10084,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G335" t="n">
-        <v>7.65334987640381</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>7.41256999969482</v>
+        <v>7.41256952285767</v>
       </c>
       <c r="H337" t="n">
         <v>3600</v>
@@ -10171,7 +10171,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G338" t="n">
-        <v>7.53295946121216</v>
+        <v>7.53295993804932</v>
       </c>
       <c r="H338" t="n">
         <v>200</v>
@@ -10229,7 +10229,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G340" t="n">
-        <v>7.29218006134033</v>
+        <v>7.29217958450317</v>
       </c>
       <c r="H340" t="n">
         <v>2800</v>
@@ -10258,7 +10258,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G341" t="n">
-        <v>7.13739395141602</v>
+        <v>7.13739347457886</v>
       </c>
       <c r="H341" t="n">
         <v>7000</v>
@@ -10374,7 +10374,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G345" t="n">
-        <v>6.99980545043945</v>
+        <v>6.99980592727661</v>
       </c>
       <c r="H345" t="n">
         <v>5400</v>
@@ -10519,7 +10519,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G350" t="n">
-        <v>6.99980545043945</v>
+        <v>6.99980592727661</v>
       </c>
       <c r="H350" t="n">
         <v>18548</v>
@@ -10548,7 +10548,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G351" t="n">
-        <v>6.94820928573608</v>
+        <v>6.94820976257324</v>
       </c>
       <c r="H351" t="n">
         <v>3182</v>
@@ -10577,7 +10577,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>6.9138126373291</v>
+        <v>6.91381216049194</v>
       </c>
       <c r="H352" t="n">
         <v>4342</v>
@@ -10664,7 +10664,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>6.94820928573608</v>
+        <v>6.94820976257324</v>
       </c>
       <c r="H355" t="n">
         <v>8049</v>
@@ -10780,7 +10780,7 @@
         <v>8</v>
       </c>
       <c r="G359" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H359" t="n">
         <v>140</v>
@@ -10867,7 +10867,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H362" t="n">
         <v>3100</v>
@@ -11012,7 +11012,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G367" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260688781738</v>
       </c>
       <c r="H367" t="n">
         <v>3300</v>
@@ -11041,7 +11041,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H368" t="n">
         <v>200</v>
@@ -11070,7 +11070,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G369" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260688781738</v>
       </c>
       <c r="H369" t="n">
         <v>472</v>
@@ -11099,7 +11099,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260688781738</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G371" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260688781738</v>
       </c>
       <c r="H371" t="n">
         <v>1981</v>
@@ -11157,7 +11157,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>7.13739395141602</v>
+        <v>7.13739347457886</v>
       </c>
       <c r="H372" t="n">
         <v>2867</v>
@@ -11186,7 +11186,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>7.05140113830566</v>
+        <v>7.05140066146851</v>
       </c>
       <c r="H373" t="n">
         <v>354</v>
@@ -11215,7 +11215,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G374" t="n">
-        <v>6.75902557373047</v>
+        <v>6.75902605056763</v>
       </c>
       <c r="H374" t="n">
         <v>25405</v>
@@ -11302,7 +11302,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>6.84501838684082</v>
+        <v>6.84501886367798</v>
       </c>
       <c r="H377" t="n">
         <v>2353</v>
@@ -11331,7 +11331,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>6.84501838684082</v>
+        <v>6.84501886367798</v>
       </c>
       <c r="H378" t="n">
         <v>4149</v>
@@ -11418,7 +11418,7 @@
         <v>8</v>
       </c>
       <c r="G381" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H381" t="n">
         <v>1532</v>
@@ -11447,7 +11447,7 @@
         <v>8</v>
       </c>
       <c r="G382" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H382" t="n">
         <v>291</v>
@@ -11476,7 +11476,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G383" t="n">
-        <v>6.93101167678833</v>
+        <v>6.93101119995117</v>
       </c>
       <c r="H383" t="n">
         <v>4605</v>
@@ -11505,7 +11505,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>6.94820928573608</v>
+        <v>6.94820976257324</v>
       </c>
       <c r="H384" t="n">
         <v>124</v>
@@ -11650,7 +11650,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>6.9138126373291</v>
+        <v>6.91381216049194</v>
       </c>
       <c r="H389" t="n">
         <v>7543</v>
@@ -11679,7 +11679,7 @@
         <v>8</v>
       </c>
       <c r="G390" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H390" t="n">
         <v>7347</v>
@@ -11737,7 +11737,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>6.84501838684082</v>
+        <v>6.84501886367798</v>
       </c>
       <c r="H392" t="n">
         <v>2665</v>
@@ -11795,7 +11795,7 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H394" t="n">
         <v>1786</v>
@@ -11853,7 +11853,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>6.94820928573608</v>
+        <v>6.94820976257324</v>
       </c>
       <c r="H396" t="n">
         <v>1510</v>
@@ -11882,7 +11882,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>6.94820928573608</v>
+        <v>6.94820976257324</v>
       </c>
       <c r="H397" t="n">
         <v>4250</v>
@@ -11911,7 +11911,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>6.93101167678833</v>
+        <v>6.93101119995117</v>
       </c>
       <c r="H398" t="n">
         <v>2460</v>
@@ -12027,7 +12027,7 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H402" t="n">
         <v>6710</v>
@@ -12056,7 +12056,7 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>6.8794150352478</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H403" t="n">
         <v>2710</v>
@@ -12114,7 +12114,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G405" t="n">
-        <v>6.75902557373047</v>
+        <v>6.75902605056763</v>
       </c>
       <c r="H405" t="n">
         <v>3290</v>
@@ -12288,7 +12288,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G411" t="n">
-        <v>7.53295946121216</v>
+        <v>7.53295993804932</v>
       </c>
       <c r="H411" t="n">
         <v>7212</v>
@@ -12317,7 +12317,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G412" t="n">
-        <v>7.48136472702026</v>
+        <v>7.48136425018311</v>
       </c>
       <c r="H412" t="n">
         <v>4587</v>
@@ -12346,7 +12346,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.65334987640381</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H413" t="n">
         <v>3920</v>
@@ -12375,7 +12375,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G414" t="n">
-        <v>7.44696712493896</v>
+        <v>7.44696760177612</v>
       </c>
       <c r="H414" t="n">
         <v>2400</v>
@@ -12404,7 +12404,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G415" t="n">
-        <v>7.61895227432251</v>
+        <v>7.61895275115967</v>
       </c>
       <c r="H415" t="n">
         <v>5660</v>
@@ -12433,7 +12433,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G416" t="n">
-        <v>7.72214412689209</v>
+        <v>7.72214317321777</v>
       </c>
       <c r="H416" t="n">
         <v>11289</v>
@@ -12462,7 +12462,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G417" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H417" t="n">
         <v>1940</v>
@@ -12491,7 +12491,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G418" t="n">
-        <v>7.53295946121216</v>
+        <v>7.53295993804932</v>
       </c>
       <c r="H418" t="n">
         <v>2536</v>
@@ -12520,7 +12520,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G419" t="n">
-        <v>7.41256999969482</v>
+        <v>7.41256952285767</v>
       </c>
       <c r="H419" t="n">
         <v>8008</v>
@@ -12549,7 +12549,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>7.34377574920654</v>
+        <v>7.34377670288086</v>
       </c>
       <c r="H420" t="n">
         <v>4725</v>
@@ -12578,7 +12578,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>7.34377574920654</v>
+        <v>7.34377670288086</v>
       </c>
       <c r="H421" t="n">
         <v>1620</v>
@@ -12665,7 +12665,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>7.65334987640381</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H424" t="n">
         <v>13987</v>
@@ -12694,7 +12694,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H425" t="n">
         <v>1500</v>
@@ -12723,7 +12723,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H426" t="n">
         <v>822</v>
@@ -12752,7 +12752,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G427" t="n">
-        <v>7.42976903915405</v>
+        <v>7.42976856231689</v>
       </c>
       <c r="H427" t="n">
         <v>1502</v>
@@ -12810,7 +12810,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G429" t="n">
-        <v>7.29218006134033</v>
+        <v>7.29217958450317</v>
       </c>
       <c r="H429" t="n">
         <v>314</v>
@@ -12839,7 +12839,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>7.13739395141602</v>
+        <v>7.13739347457886</v>
       </c>
       <c r="H430" t="n">
         <v>908</v>
@@ -12897,7 +12897,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H432" t="n">
         <v>7444</v>
@@ -12926,7 +12926,7 @@
         <v>9</v>
       </c>
       <c r="G433" t="n">
-        <v>7.73934316635132</v>
+        <v>7.73934364318848</v>
       </c>
       <c r="H433" t="n">
         <v>12673</v>
@@ -12984,7 +12984,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G435" t="n">
-        <v>7.65334987640381</v>
+        <v>7.65334939956665</v>
       </c>
       <c r="H435" t="n">
         <v>1451</v>
@@ -13013,7 +13013,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>7.48136472702026</v>
+        <v>7.48136425018311</v>
       </c>
       <c r="H436" t="n">
         <v>2489</v>
@@ -13042,7 +13042,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G437" t="n">
-        <v>7.61035442352295</v>
+        <v>7.61035346984863</v>
       </c>
       <c r="H437" t="n">
         <v>5810</v>
@@ -13071,7 +13071,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H438" t="n">
         <v>5485</v>
@@ -13100,7 +13100,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H439" t="n">
         <v>572</v>
@@ -13187,7 +13187,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>7.78233861923218</v>
+        <v>7.78233909606934</v>
       </c>
       <c r="H442" t="n">
         <v>10</v>
@@ -13245,7 +13245,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H444" t="n">
         <v>800</v>
@@ -13274,7 +13274,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>7.56735754013062</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H445" t="n">
         <v>8557</v>
@@ -13970,7 +13970,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G469" t="n">
-        <v>7.15537786483765</v>
+        <v>7.1553783416748</v>
       </c>
       <c r="H469" t="n">
         <v>1420</v>
@@ -14028,7 +14028,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>7.2887077331543</v>
+        <v>7.28870725631714</v>
       </c>
       <c r="H471" t="n">
         <v>30</v>
@@ -14260,7 +14260,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G479" t="n">
-        <v>7.2887077331543</v>
+        <v>7.28870725631714</v>
       </c>
       <c r="H479" t="n">
         <v>3000</v>
@@ -14289,7 +14289,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G480" t="n">
-        <v>7.46648073196411</v>
+        <v>7.46648120880127</v>
       </c>
       <c r="H480" t="n">
         <v>10</v>
@@ -14318,7 +14318,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G481" t="n">
-        <v>7.46648073196411</v>
+        <v>7.46648120880127</v>
       </c>
       <c r="H481" t="n">
         <v>0</v>
@@ -14347,7 +14347,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G482" t="n">
-        <v>7.46648073196411</v>
+        <v>7.46648120880127</v>
       </c>
       <c r="H482" t="n">
         <v>0</v>
@@ -14666,7 +14666,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G493" t="n">
-        <v>7.46648073196411</v>
+        <v>7.46648120880127</v>
       </c>
       <c r="H493" t="n">
         <v>2584</v>
@@ -15275,7 +15275,7 @@
         <v>7.75</v>
       </c>
       <c r="G514" t="n">
-        <v>6.88871765136719</v>
+        <v>6.88871812820435</v>
       </c>
       <c r="H514" t="n">
         <v>1660</v>
@@ -15304,7 +15304,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G515" t="n">
-        <v>7.15537786483765</v>
+        <v>7.1553783416748</v>
       </c>
       <c r="H515" t="n">
         <v>10</v>
@@ -15333,7 +15333,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>6.97760438919067</v>
+        <v>6.97760391235352</v>
       </c>
       <c r="H516" t="n">
         <v>192</v>
@@ -15362,7 +15362,7 @@
         <v>7.5</v>
       </c>
       <c r="G517" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H517" t="n">
         <v>2568</v>
@@ -15420,7 +15420,7 @@
         <v>7.5</v>
       </c>
       <c r="G519" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H519" t="n">
         <v>610</v>
@@ -15449,7 +15449,7 @@
         <v>7.5</v>
       </c>
       <c r="G520" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H520" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>7.5</v>
       </c>
       <c r="G525" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H525" t="n">
         <v>400</v>
@@ -15623,7 +15623,7 @@
         <v>7.5</v>
       </c>
       <c r="G526" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H526" t="n">
         <v>0</v>
@@ -15652,7 +15652,7 @@
         <v>7.5</v>
       </c>
       <c r="G527" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>7.5</v>
       </c>
       <c r="G528" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H528" t="n">
         <v>3103</v>
@@ -15855,7 +15855,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.39984083175659</v>
+        <v>6.39984035491943</v>
       </c>
       <c r="H534" t="n">
         <v>2911</v>
@@ -16087,7 +16087,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.39984083175659</v>
+        <v>6.39984035491943</v>
       </c>
       <c r="H542" t="n">
         <v>6172</v>
@@ -16116,7 +16116,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>6.39984083175659</v>
+        <v>6.39984035491943</v>
       </c>
       <c r="H543" t="n">
         <v>3219</v>
@@ -16377,7 +16377,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G552" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H552" t="n">
         <v>1717</v>
@@ -16493,7 +16493,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G556" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H556" t="n">
         <v>670</v>
@@ -16957,7 +16957,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G572" t="n">
-        <v>6.17762422561646</v>
+        <v>6.1776237487793</v>
       </c>
       <c r="H572" t="n">
         <v>12462</v>
@@ -16986,7 +16986,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G573" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H573" t="n">
         <v>4179</v>
@@ -17015,7 +17015,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G574" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H574" t="n">
         <v>2117</v>
@@ -17073,7 +17073,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G576" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H576" t="n">
         <v>3710</v>
@@ -17102,7 +17102,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H577" t="n">
         <v>2610</v>
@@ -17131,7 +17131,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -17247,7 +17247,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G582" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H582" t="n">
         <v>2138</v>
@@ -17276,7 +17276,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G583" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H583" t="n">
         <v>18938</v>
@@ -17363,7 +17363,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G586" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H586" t="n">
         <v>2734</v>
@@ -17392,7 +17392,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H587" t="n">
         <v>3257</v>
@@ -17537,7 +17537,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H592" t="n">
         <v>3684</v>
@@ -17566,7 +17566,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H593" t="n">
         <v>5400</v>
@@ -17682,7 +17682,7 @@
         <v>6.5</v>
       </c>
       <c r="G597" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H597" t="n">
         <v>12670</v>
@@ -17711,7 +17711,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H598" t="n">
         <v>8965</v>
@@ -17740,7 +17740,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G599" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H599" t="n">
         <v>11436</v>
@@ -17769,7 +17769,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G600" t="n">
-        <v>5.59986114501953</v>
+        <v>5.59986066818237</v>
       </c>
       <c r="H600" t="n">
         <v>44660</v>
@@ -17798,7 +17798,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G601" t="n">
-        <v>5.59986114501953</v>
+        <v>5.59986066818237</v>
       </c>
       <c r="H601" t="n">
         <v>43295</v>
@@ -17827,7 +17827,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G602" t="n">
-        <v>5.59986114501953</v>
+        <v>5.59986066818237</v>
       </c>
       <c r="H602" t="n">
         <v>9860</v>
@@ -17914,7 +17914,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G605" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H605" t="n">
         <v>2051</v>
@@ -17972,7 +17972,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G607" t="n">
-        <v>5.86652040481567</v>
+        <v>5.86652088165283</v>
       </c>
       <c r="H607" t="n">
         <v>17462</v>
@@ -18233,7 +18233,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G616" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H616" t="n">
         <v>3231</v>
@@ -18262,7 +18262,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G618" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H618" t="n">
         <v>2032</v>
@@ -18320,7 +18320,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G619" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H619" t="n">
         <v>50</v>
@@ -18349,7 +18349,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>6.31095409393311</v>
+        <v>6.31095457077026</v>
       </c>
       <c r="H620" t="n">
         <v>7613</v>
@@ -18726,7 +18726,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.86652040481567</v>
+        <v>5.86652088165283</v>
       </c>
       <c r="H633" t="n">
         <v>5366</v>
@@ -18755,7 +18755,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G634" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H634" t="n">
         <v>2000</v>
@@ -18784,7 +18784,7 @@
         <v>6.5</v>
       </c>
       <c r="G635" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H635" t="n">
         <v>12636</v>
@@ -18813,7 +18813,7 @@
         <v>6.5</v>
       </c>
       <c r="G636" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H636" t="n">
         <v>4185</v>
@@ -18842,7 +18842,7 @@
         <v>6.5</v>
       </c>
       <c r="G637" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H637" t="n">
         <v>0</v>
@@ -18871,7 +18871,7 @@
         <v>6.5</v>
       </c>
       <c r="G638" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H638" t="n">
         <v>3450</v>
@@ -18900,7 +18900,7 @@
         <v>6.5</v>
       </c>
       <c r="G639" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H639" t="n">
         <v>0</v>
@@ -18929,7 +18929,7 @@
         <v>6.5</v>
       </c>
       <c r="G640" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H640" t="n">
         <v>1550</v>
@@ -18987,7 +18987,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H642" t="n">
         <v>2879</v>
@@ -19016,7 +19016,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G643" t="n">
-        <v>5.59986114501953</v>
+        <v>5.59986066818237</v>
       </c>
       <c r="H643" t="n">
         <v>4049</v>
@@ -19045,7 +19045,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>5.64430379867554</v>
+        <v>5.6443042755127</v>
       </c>
       <c r="H644" t="n">
         <v>5286</v>
@@ -19103,7 +19103,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.64430379867554</v>
+        <v>5.6443042755127</v>
       </c>
       <c r="H646" t="n">
         <v>297</v>
@@ -19190,7 +19190,7 @@
         <v>6.5</v>
       </c>
       <c r="G649" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H649" t="n">
         <v>6789</v>
@@ -19248,7 +19248,7 @@
         <v>6.5</v>
       </c>
       <c r="G651" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H651" t="n">
         <v>1008</v>
@@ -19277,7 +19277,7 @@
         <v>6.5</v>
       </c>
       <c r="G652" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H652" t="n">
         <v>11094</v>
@@ -19306,7 +19306,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G653" t="n">
-        <v>5.73319053649902</v>
+        <v>5.73319101333618</v>
       </c>
       <c r="H653" t="n">
         <v>4753</v>
@@ -19393,7 +19393,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G656" t="n">
-        <v>5.59986114501953</v>
+        <v>5.59986066818237</v>
       </c>
       <c r="H656" t="n">
         <v>2652</v>
@@ -19567,7 +19567,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G662" t="n">
-        <v>5.37764453887939</v>
+        <v>5.37764406204224</v>
       </c>
       <c r="H662" t="n">
         <v>1</v>
@@ -19683,7 +19683,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G666" t="n">
-        <v>4.35544681549072</v>
+        <v>4.35544729232788</v>
       </c>
       <c r="H666" t="n">
         <v>11395</v>
@@ -19712,7 +19712,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>4.26656103134155</v>
+        <v>4.26656055450439</v>
       </c>
       <c r="H667" t="n">
         <v>8251</v>
@@ -19799,7 +19799,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G670" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H670" t="n">
         <v>10643</v>
@@ -19828,7 +19828,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G671" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -19857,7 +19857,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G672" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G673" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G674" t="n">
-        <v>4.24878358840942</v>
+        <v>4.24878311157227</v>
       </c>
       <c r="H674" t="n">
         <v>0</v>
@@ -20002,7 +20002,7 @@
         <v>4.5</v>
       </c>
       <c r="G677" t="n">
-        <v>3.99990081787109</v>
+        <v>3.99990105628967</v>
       </c>
       <c r="H677" t="n">
         <v>2379</v>
@@ -20118,7 +20118,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>3.73324036598206</v>
+        <v>3.73324060440063</v>
       </c>
       <c r="H681" t="n">
         <v>1886</v>
@@ -20176,7 +20176,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G683" t="n">
-        <v>3.64435386657715</v>
+        <v>3.64435362815857</v>
       </c>
       <c r="H683" t="n">
         <v>1800</v>
@@ -20263,7 +20263,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G686" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H686" t="n">
         <v>4888</v>
@@ -20350,7 +20350,7 @@
         <v>4.5</v>
       </c>
       <c r="G689" t="n">
-        <v>3.99990081787109</v>
+        <v>3.99990105628967</v>
       </c>
       <c r="H689" t="n">
         <v>1891</v>
@@ -20379,7 +20379,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G690" t="n">
-        <v>4.08878755569458</v>
+        <v>4.08878707885742</v>
       </c>
       <c r="H690" t="n">
         <v>5209</v>
@@ -20524,7 +20524,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H695" t="n">
         <v>4540</v>
@@ -20553,7 +20553,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H696" t="n">
         <v>470</v>
@@ -20611,7 +20611,7 @@
         <v>4.5</v>
       </c>
       <c r="G698" t="n">
-        <v>3.99990081787109</v>
+        <v>3.99990105628967</v>
       </c>
       <c r="H698" t="n">
         <v>1703</v>
@@ -20698,7 +20698,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G701" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H701" t="n">
         <v>11088</v>
@@ -20785,7 +20785,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G704" t="n">
-        <v>3.90212512016296</v>
+        <v>3.90212488174438</v>
       </c>
       <c r="H704" t="n">
         <v>1895</v>
@@ -20901,7 +20901,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G708" t="n">
-        <v>3.83101606369019</v>
+        <v>3.83101558685303</v>
       </c>
       <c r="H708" t="n">
         <v>6323</v>
@@ -20930,7 +20930,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>3.83101606369019</v>
+        <v>3.83101558685303</v>
       </c>
       <c r="H709" t="n">
         <v>2542</v>
@@ -21104,7 +21104,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G715" t="n">
-        <v>3.81323838233948</v>
+        <v>3.81323862075806</v>
       </c>
       <c r="H715" t="n">
         <v>611</v>
@@ -21220,7 +21220,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G719" t="n">
-        <v>4.08878755569458</v>
+        <v>4.08878707885742</v>
       </c>
       <c r="H719" t="n">
         <v>10718</v>
@@ -21249,7 +21249,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G720" t="n">
-        <v>4.06212139129639</v>
+        <v>4.06212091445923</v>
       </c>
       <c r="H720" t="n">
         <v>15398</v>
@@ -21278,7 +21278,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>4.13323020935059</v>
+        <v>4.13323068618774</v>
       </c>
       <c r="H721" t="n">
         <v>12913</v>
@@ -21452,7 +21452,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G727" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767627716064</v>
       </c>
       <c r="H727" t="n">
         <v>30466</v>
@@ -21539,7 +21539,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>4.38185501098633</v>
+        <v>4.38185453414917</v>
       </c>
       <c r="H730" t="n">
         <v>61399</v>
@@ -21568,7 +21568,7 @@
         <v>4.75</v>
       </c>
       <c r="G731" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H731" t="n">
         <v>16376</v>
@@ -21655,7 +21655,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G734" t="n">
-        <v>4.38185501098633</v>
+        <v>4.38185453414917</v>
       </c>
       <c r="H734" t="n">
         <v>34375</v>
@@ -21684,7 +21684,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G735" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H735" t="n">
         <v>17125</v>
@@ -21713,7 +21713,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G736" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H736" t="n">
         <v>9606</v>
@@ -21742,7 +21742,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G737" t="n">
-        <v>4.40935611724854</v>
+        <v>4.40935564041138</v>
       </c>
       <c r="H737" t="n">
         <v>2683</v>
@@ -21771,7 +21771,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H738" t="n">
         <v>600</v>
@@ -21800,7 +21800,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H739" t="n">
         <v>680</v>
@@ -21829,7 +21829,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G740" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H740" t="n">
         <v>7403</v>
@@ -21916,7 +21916,7 @@
         <v>4.75</v>
       </c>
       <c r="G743" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H743" t="n">
         <v>607</v>
@@ -21945,7 +21945,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G744" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H744" t="n">
         <v>11032</v>
@@ -22032,7 +22032,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G747" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H747" t="n">
         <v>2630</v>
@@ -22061,7 +22061,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H748" t="n">
         <v>1000</v>
@@ -22177,7 +22177,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G752" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H752" t="n">
         <v>1350</v>
@@ -22380,7 +22380,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G759" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H759" t="n">
         <v>3488</v>
@@ -22467,7 +22467,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H762" t="n">
         <v>4900</v>
@@ -22641,7 +22641,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H768" t="n">
         <v>8119</v>
@@ -22902,7 +22902,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H777" t="n">
         <v>7930</v>
@@ -22931,7 +22931,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>4.08850908279419</v>
+        <v>4.08850860595703</v>
       </c>
       <c r="H778" t="n">
         <v>10894</v>
@@ -23105,7 +23105,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G784" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H784" t="n">
         <v>10522</v>
@@ -23163,7 +23163,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G786" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H786" t="n">
         <v>1030</v>
@@ -23192,7 +23192,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G787" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>4.07934141159058</v>
+        <v>4.07934188842773</v>
       </c>
       <c r="H788" t="n">
         <v>5464</v>
@@ -23250,7 +23250,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G789" t="n">
-        <v>4.07934141159058</v>
+        <v>4.07934188842773</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -23337,7 +23337,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>4.04267358779907</v>
+        <v>4.04267311096191</v>
       </c>
       <c r="H792" t="n">
         <v>1205</v>
@@ -23482,7 +23482,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G797" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H797" t="n">
         <v>2403</v>
@@ -23511,7 +23511,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G798" t="n">
-        <v>4.09767532348633</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H798" t="n">
         <v>1860</v>
@@ -23598,7 +23598,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>3.91433453559875</v>
+        <v>3.91433477401733</v>
       </c>
       <c r="H801" t="n">
         <v>1035</v>
@@ -23743,7 +23743,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.86849904060364</v>
+        <v>3.86849927902222</v>
       </c>
       <c r="H806" t="n">
         <v>3833</v>
@@ -23772,7 +23772,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G807" t="n">
-        <v>3.88683319091797</v>
+        <v>3.88683342933655</v>
       </c>
       <c r="H807" t="n">
         <v>13265</v>
@@ -23801,7 +23801,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G808" t="n">
-        <v>3.88683319091797</v>
+        <v>3.88683342933655</v>
       </c>
       <c r="H808" t="n">
         <v>12349</v>
@@ -23946,7 +23946,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G813" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H813" t="n">
         <v>11042</v>
@@ -24004,7 +24004,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>4.37268733978271</v>
+        <v>4.37268781661987</v>
       </c>
       <c r="H815" t="n">
         <v>4760</v>
@@ -24033,7 +24033,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G816" t="n">
-        <v>4.36352109909058</v>
+        <v>4.36352062225342</v>
       </c>
       <c r="H816" t="n">
         <v>7780</v>
@@ -24120,7 +24120,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G819" t="n">
-        <v>4.3268518447876</v>
+        <v>4.32685232162476</v>
       </c>
       <c r="H819" t="n">
         <v>785</v>
@@ -24178,7 +24178,7 @@
         <v>4.75</v>
       </c>
       <c r="G821" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H821" t="n">
         <v>6878</v>
@@ -24294,7 +24294,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G825" t="n">
-        <v>4.51936054229736</v>
+        <v>4.51936006546021</v>
       </c>
       <c r="H825" t="n">
         <v>1867</v>
@@ -24352,7 +24352,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>4.51019334793091</v>
+        <v>4.51019382476807</v>
       </c>
       <c r="H827" t="n">
         <v>10424</v>
@@ -24410,7 +24410,7 @@
         <v>4.75</v>
       </c>
       <c r="G829" t="n">
-        <v>4.35435342788696</v>
+        <v>4.35435390472412</v>
       </c>
       <c r="H829" t="n">
         <v>5800</v>
@@ -24468,7 +24468,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.04267358779907</v>
+        <v>4.04267311096191</v>
       </c>
       <c r="H831" t="n">
         <v>16333</v>
@@ -24555,7 +24555,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>3.94183588027954</v>
+        <v>3.94183611869812</v>
       </c>
       <c r="H834" t="n">
         <v>25951</v>
@@ -24642,7 +24642,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H837" t="n">
         <v>21835</v>
@@ -24729,7 +24729,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G840" t="n">
-        <v>4.18934631347656</v>
+        <v>4.18934679031372</v>
       </c>
       <c r="H840" t="n">
         <v>34559</v>
@@ -24758,7 +24758,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>4.23518133163452</v>
+        <v>4.23518180847168</v>
       </c>
       <c r="H841" t="n">
         <v>225</v>
@@ -24845,7 +24845,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G844" t="n">
-        <v>4.21684741973877</v>
+        <v>4.21684789657593</v>
       </c>
       <c r="H844" t="n">
         <v>16368</v>
@@ -25193,7 +25193,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>4.96854639053345</v>
+        <v>4.96854686737061</v>
       </c>
       <c r="H856" t="n">
         <v>13143</v>
@@ -25309,7 +25309,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>5.1152195930481</v>
+        <v>5.11521911621094</v>
       </c>
       <c r="H860" t="n">
         <v>16237</v>
@@ -25367,7 +25367,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G862" t="n">
-        <v>5.13355350494385</v>
+        <v>5.13355398178101</v>
       </c>
       <c r="H862" t="n">
         <v>13036</v>
@@ -25396,7 +25396,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G863" t="n">
-        <v>5.1518874168396</v>
+        <v>5.15188789367676</v>
       </c>
       <c r="H863" t="n">
         <v>7153</v>
@@ -25454,7 +25454,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>5.00521516799927</v>
+        <v>5.00521469116211</v>
       </c>
       <c r="H865" t="n">
         <v>3756</v>
@@ -25686,7 +25686,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G873" t="n">
-        <v>5.39023113250732</v>
+        <v>5.39023160934448</v>
       </c>
       <c r="H873" t="n">
         <v>31741</v>
@@ -25715,7 +25715,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G874" t="n">
-        <v>5.39023113250732</v>
+        <v>5.39023160934448</v>
       </c>
       <c r="H874" t="n">
         <v>13377</v>
@@ -25831,7 +25831,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G878" t="n">
-        <v>5.61024045944214</v>
+        <v>5.6102409362793</v>
       </c>
       <c r="H878" t="n">
         <v>24852</v>
@@ -25947,7 +25947,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G882" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H882" t="n">
         <v>8738</v>
@@ -25976,7 +25976,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>5.88525247573853</v>
+        <v>5.88525295257568</v>
       </c>
       <c r="H883" t="n">
         <v>11732</v>
@@ -26121,7 +26121,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>5.94025468826294</v>
+        <v>5.9402551651001</v>
       </c>
       <c r="H888" t="n">
         <v>7733</v>
@@ -26266,7 +26266,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G893" t="n">
-        <v>5.83025074005127</v>
+        <v>5.83025026321411</v>
       </c>
       <c r="H893" t="n">
         <v>46103</v>
@@ -26324,7 +26324,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H895" t="n">
         <v>1658</v>
@@ -26382,7 +26382,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H897" t="n">
         <v>3856</v>
@@ -26469,7 +26469,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>5.92192125320435</v>
+        <v>5.92192077636719</v>
       </c>
       <c r="H900" t="n">
         <v>19114</v>
@@ -26498,7 +26498,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H901" t="n">
         <v>5834</v>
@@ -26527,7 +26527,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H902" t="n">
         <v>4663</v>
@@ -26643,7 +26643,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G906" t="n">
-        <v>6.01359176635742</v>
+        <v>6.01359128952026</v>
       </c>
       <c r="H906" t="n">
         <v>7547</v>
@@ -26759,7 +26759,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G910" t="n">
-        <v>6.19693326950073</v>
+        <v>6.19693279266357</v>
       </c>
       <c r="H910" t="n">
         <v>32257</v>
@@ -26817,7 +26817,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>6.38027429580688</v>
+        <v>6.38027381896973</v>
       </c>
       <c r="H912" t="n">
         <v>24783</v>
@@ -26846,7 +26846,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G913" t="n">
-        <v>6.28860378265381</v>
+        <v>6.28860330581665</v>
       </c>
       <c r="H913" t="n">
         <v>13157</v>
@@ -26991,7 +26991,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>6.47194480895996</v>
+        <v>6.4719443321228</v>
       </c>
       <c r="H918" t="n">
         <v>6002</v>
@@ -27049,7 +27049,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G920" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H920" t="n">
         <v>2787</v>
@@ -27078,7 +27078,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H921" t="n">
         <v>4737</v>
@@ -27107,7 +27107,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G922" t="n">
-        <v>6.58194875717163</v>
+        <v>6.58194923400879</v>
       </c>
       <c r="H922" t="n">
         <v>5358</v>
@@ -27165,7 +27165,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G924" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H924" t="n">
         <v>4250</v>
@@ -27252,7 +27252,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G927" t="n">
-        <v>6.61861705780029</v>
+        <v>6.61861753463745</v>
       </c>
       <c r="H927" t="n">
         <v>9701</v>
@@ -27339,7 +27339,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>6.58194875717163</v>
+        <v>6.58194923400879</v>
       </c>
       <c r="H930" t="n">
         <v>1400</v>
@@ -27368,7 +27368,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G931" t="n">
-        <v>6.61861705780029</v>
+        <v>6.61861753463745</v>
       </c>
       <c r="H931" t="n">
         <v>4392</v>
@@ -27542,7 +27542,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G937" t="n">
-        <v>6.54528093338013</v>
+        <v>6.54528045654297</v>
       </c>
       <c r="H937" t="n">
         <v>11503</v>
@@ -27600,7 +27600,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G939" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H939" t="n">
         <v>14602</v>
@@ -27658,7 +27658,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>6.85696077346802</v>
+        <v>6.85696125030518</v>
       </c>
       <c r="H941" t="n">
         <v>21995</v>
@@ -27890,7 +27890,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>6.56361532211304</v>
+        <v>6.56361484527588</v>
       </c>
       <c r="H949" t="n">
         <v>6250</v>
@@ -28093,7 +28093,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G956" t="n">
-        <v>6.78362464904785</v>
+        <v>6.78362417221069</v>
       </c>
       <c r="H956" t="n">
         <v>5975</v>
@@ -68670,6 +68670,35 @@
         <v>1759</v>
       </c>
       <c r="I2355" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2356">
+      <c r="A2356" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2356" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2356" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="D2356" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E2356" t="n">
+        <v>2.21000003814697</v>
+      </c>
+      <c r="F2356" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="G2356" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="H2356" t="n">
+        <v>19545</v>
+      </c>
+      <c r="I2356" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2" t="n">
-        <v>9.40188121795654</v>
+        <v>9.40188026428223</v>
       </c>
       <c r="H2" t="n">
         <v>56600</v>
@@ -485,7 +485,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.41868495941162</v>
+        <v>9.41868591308594</v>
       </c>
       <c r="H4" t="n">
         <v>41600</v>
@@ -514,7 +514,7 @@
         <v>11.25</v>
       </c>
       <c r="G5" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229434967041</v>
       </c>
       <c r="H5" t="n">
         <v>13000</v>
@@ -543,7 +543,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.65394115447998</v>
+        <v>9.6539421081543</v>
       </c>
       <c r="H6" t="n">
         <v>18000</v>
@@ -601,7 +601,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.65394115447998</v>
+        <v>9.6539421081543</v>
       </c>
       <c r="H8" t="n">
         <v>4800</v>
@@ -717,7 +717,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G12" t="n">
-        <v>9.67074680328369</v>
+        <v>9.67074584960938</v>
       </c>
       <c r="H12" t="n">
         <v>1600</v>
@@ -833,7 +833,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G16" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H16" t="n">
         <v>11400</v>
@@ -862,7 +862,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H17" t="n">
         <v>248200</v>
@@ -891,7 +891,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G18" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H18" t="n">
         <v>2600</v>
@@ -1065,7 +1065,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G24" t="n">
-        <v>9.40188121795654</v>
+        <v>9.40188026428223</v>
       </c>
       <c r="H24" t="n">
         <v>600</v>
@@ -1181,7 +1181,7 @@
         <v>11.25</v>
       </c>
       <c r="G28" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229434967041</v>
       </c>
       <c r="H28" t="n">
         <v>3600</v>
@@ -1268,7 +1268,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G31" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H31" t="n">
         <v>4600</v>
@@ -1355,7 +1355,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G34" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H34" t="n">
         <v>14200</v>
@@ -1587,7 +1587,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G42" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H42" t="n">
         <v>7000</v>
@@ -1616,7 +1616,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H43" t="n">
         <v>2000</v>
@@ -1645,7 +1645,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H44" t="n">
         <v>4400</v>
@@ -1674,7 +1674,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G45" t="n">
-        <v>9.82198143005371</v>
+        <v>9.82198238372803</v>
       </c>
       <c r="H45" t="n">
         <v>14000</v>
@@ -1703,7 +1703,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>9.77157020568848</v>
+        <v>9.77157115936279</v>
       </c>
       <c r="H46" t="n">
         <v>47600</v>
@@ -1761,7 +1761,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H48" t="n">
         <v>8800</v>
@@ -1790,7 +1790,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G49" t="n">
-        <v>9.77157020568848</v>
+        <v>9.77157115936279</v>
       </c>
       <c r="H49" t="n">
         <v>37000</v>
@@ -1848,7 +1848,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G51" t="n">
-        <v>10.1832704544067</v>
+        <v>10.1832695007324</v>
       </c>
       <c r="H51" t="n">
         <v>127800</v>
@@ -1906,7 +1906,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G53" t="n">
-        <v>9.77997207641602</v>
+        <v>9.77997303009033</v>
       </c>
       <c r="H53" t="n">
         <v>4200</v>
@@ -1935,7 +1935,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G54" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H54" t="n">
         <v>30200</v>
@@ -2080,7 +2080,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>10.0404348373413</v>
+        <v>10.0404357910156</v>
       </c>
       <c r="H59" t="n">
         <v>61400</v>
@@ -2109,7 +2109,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G60" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320320129395</v>
       </c>
       <c r="H60" t="n">
         <v>10600</v>
@@ -2138,7 +2138,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G61" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320320129395</v>
       </c>
       <c r="H61" t="n">
         <v>11200</v>
@@ -2196,7 +2196,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G63" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H63" t="n">
         <v>14400</v>
@@ -2225,7 +2225,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G64" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H64" t="n">
         <v>24000</v>
@@ -2254,7 +2254,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>9.82198143005371</v>
+        <v>9.82198238372803</v>
       </c>
       <c r="H65" t="n">
         <v>8600</v>
@@ -2283,7 +2283,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G66" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H66" t="n">
         <v>16400</v>
@@ -2312,7 +2312,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G67" t="n">
-        <v>9.93961048126221</v>
+        <v>9.93961143493652</v>
       </c>
       <c r="H67" t="n">
         <v>18400</v>
@@ -2428,7 +2428,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G71" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H71" t="n">
         <v>64600</v>
@@ -2515,7 +2515,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G74" t="n">
-        <v>10.0656404495239</v>
+        <v>10.0656414031982</v>
       </c>
       <c r="H74" t="n">
         <v>7000</v>
@@ -2544,7 +2544,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>9.99842548370361</v>
+        <v>9.9984245300293</v>
       </c>
       <c r="H75" t="n">
         <v>26800</v>
@@ -2602,7 +2602,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G77" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320320129395</v>
       </c>
       <c r="H77" t="n">
         <v>58000</v>
@@ -2631,7 +2631,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>9.99842548370361</v>
+        <v>9.9984245300293</v>
       </c>
       <c r="H78" t="n">
         <v>14600</v>
@@ -2660,7 +2660,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G79" t="n">
-        <v>10.0404348373413</v>
+        <v>10.0404357910156</v>
       </c>
       <c r="H79" t="n">
         <v>13600</v>
@@ -2950,7 +2950,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H89" t="n">
         <v>22400</v>
@@ -2979,7 +2979,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H90" t="n">
         <v>2000</v>
@@ -3153,7 +3153,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H96" t="n">
         <v>2600</v>
@@ -3211,7 +3211,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G98" t="n">
-        <v>9.98162174224854</v>
+        <v>9.98162078857422</v>
       </c>
       <c r="H98" t="n">
         <v>13400</v>
@@ -3269,7 +3269,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H100" t="n">
         <v>36600</v>
@@ -3327,7 +3327,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G102" t="n">
-        <v>9.82198143005371</v>
+        <v>9.82198238372803</v>
       </c>
       <c r="H102" t="n">
         <v>8200</v>
@@ -3356,7 +3356,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G103" t="n">
-        <v>9.82198143005371</v>
+        <v>9.82198238372803</v>
       </c>
       <c r="H103" t="n">
         <v>600</v>
@@ -3414,7 +3414,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G105" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H105" t="n">
         <v>6400</v>
@@ -3501,7 +3501,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G108" t="n">
-        <v>9.65394115447998</v>
+        <v>9.6539421081543</v>
       </c>
       <c r="H108" t="n">
         <v>20400</v>
@@ -3733,7 +3733,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H116" t="n">
         <v>4600</v>
@@ -3762,7 +3762,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H117" t="n">
         <v>16400</v>
@@ -3820,7 +3820,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H119" t="n">
         <v>5400</v>
@@ -3849,7 +3849,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H120" t="n">
         <v>4800</v>
@@ -3878,7 +3878,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H121" t="n">
         <v>6200</v>
@@ -3907,7 +3907,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H122" t="n">
         <v>14000</v>
@@ -3936,7 +3936,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G123" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H123" t="n">
         <v>15800</v>
@@ -3965,7 +3965,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H124" t="n">
         <v>14200</v>
@@ -3994,7 +3994,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H125" t="n">
         <v>8000</v>
@@ -4023,7 +4023,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H126" t="n">
         <v>24600</v>
@@ -4052,7 +4052,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H127" t="n">
         <v>39200</v>
@@ -4081,7 +4081,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H128" t="n">
         <v>20000</v>
@@ -4110,7 +4110,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H129" t="n">
         <v>1600</v>
@@ -4168,7 +4168,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H131" t="n">
         <v>5600</v>
@@ -4197,7 +4197,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G132" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H132" t="n">
         <v>11400</v>
@@ -4226,7 +4226,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G133" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H133" t="n">
         <v>9800</v>
@@ -4255,7 +4255,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>9.74636554718018</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H134" t="n">
         <v>3400</v>
@@ -4284,7 +4284,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H135" t="n">
         <v>5600</v>
@@ -4371,7 +4371,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H138" t="n">
         <v>50800</v>
@@ -4922,7 +4922,7 @@
         <v>11.25</v>
       </c>
       <c r="G157" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229434967041</v>
       </c>
       <c r="H157" t="n">
         <v>18800</v>
@@ -5589,7 +5589,7 @@
         <v>11.25</v>
       </c>
       <c r="G180" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229434967041</v>
       </c>
       <c r="H180" t="n">
         <v>12000</v>
@@ -5618,7 +5618,7 @@
         <v>11.25</v>
       </c>
       <c r="G181" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229434967041</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G184" t="n">
-        <v>9.11621189117432</v>
+        <v>9.1162109375</v>
       </c>
       <c r="H184" t="n">
         <v>7200</v>
@@ -5879,7 +5879,7 @@
         <v>10.75</v>
       </c>
       <c r="G190" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H190" t="n">
         <v>400</v>
@@ -5908,7 +5908,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>9.11621189117432</v>
+        <v>9.1162109375</v>
       </c>
       <c r="H191" t="n">
         <v>11600</v>
@@ -5937,7 +5937,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>9.11621189117432</v>
+        <v>9.1162109375</v>
       </c>
       <c r="H192" t="n">
         <v>400</v>
@@ -5966,7 +5966,7 @@
         <v>10.75</v>
       </c>
       <c r="G193" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H193" t="n">
         <v>400</v>
@@ -5995,7 +5995,7 @@
         <v>10.75</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H194" t="n">
         <v>600</v>
@@ -6053,7 +6053,7 @@
         <v>10.75</v>
       </c>
       <c r="G196" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H196" t="n">
         <v>10200</v>
@@ -6807,7 +6807,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G222" t="n">
-        <v>9.07223033905029</v>
+        <v>9.07222938537598</v>
       </c>
       <c r="H222" t="n">
         <v>8600</v>
@@ -7474,7 +7474,7 @@
         <v>11</v>
       </c>
       <c r="G245" t="n">
-        <v>9.45919609069824</v>
+        <v>9.45919704437256</v>
       </c>
       <c r="H245" t="n">
         <v>7000</v>
@@ -7503,7 +7503,7 @@
         <v>11</v>
       </c>
       <c r="G246" t="n">
-        <v>9.45919609069824</v>
+        <v>9.45919704437256</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>9.07223033905029</v>
+        <v>9.07222938537598</v>
       </c>
       <c r="H264" t="n">
         <v>8000</v>
@@ -8228,7 +8228,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>8.49607753753662</v>
+        <v>8.49607849121094</v>
       </c>
       <c r="H271" t="n">
         <v>9400</v>
@@ -8315,7 +8315,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H274" t="n">
         <v>4800</v>
@@ -8344,7 +8344,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H275" t="n">
         <v>2000</v>
@@ -8373,7 +8373,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G277" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G278" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G279" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G281" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H281" t="n">
         <v>400</v>
@@ -8663,7 +8663,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H286" t="n">
         <v>10600</v>
@@ -8692,7 +8692,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G288" t="n">
-        <v>8.22090148925781</v>
+        <v>8.22090244293213</v>
       </c>
       <c r="H288" t="n">
         <v>2600</v>
@@ -8750,7 +8750,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.25529861450195</v>
+        <v>8.25529956817627</v>
       </c>
       <c r="H289" t="n">
         <v>800</v>
@@ -8779,7 +8779,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G290" t="n">
-        <v>8.32409381866455</v>
+        <v>8.32409286499023</v>
       </c>
       <c r="H290" t="n">
         <v>24800</v>
@@ -8895,7 +8895,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G294" t="n">
-        <v>8.32409381866455</v>
+        <v>8.32409286499023</v>
       </c>
       <c r="H294" t="n">
         <v>13000</v>
@@ -8924,7 +8924,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G295" t="n">
-        <v>8.32409381866455</v>
+        <v>8.32409286499023</v>
       </c>
       <c r="H295" t="n">
         <v>5000</v>
@@ -9185,7 +9185,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H304" t="n">
         <v>1200</v>
@@ -9214,7 +9214,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H305" t="n">
         <v>400</v>
@@ -9272,7 +9272,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G307" t="n">
-        <v>8.03171825408936</v>
+        <v>8.03171920776367</v>
       </c>
       <c r="H307" t="n">
         <v>2000</v>
@@ -9330,7 +9330,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G309" t="n">
-        <v>8.03171825408936</v>
+        <v>8.03171920776367</v>
       </c>
       <c r="H309" t="n">
         <v>600</v>
@@ -9475,7 +9475,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H314" t="n">
         <v>23200</v>
@@ -9504,7 +9504,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H315" t="n">
         <v>14000</v>
@@ -9533,7 +9533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G323" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H323" t="n">
         <v>800</v>
@@ -9765,7 +9765,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G324" t="n">
-        <v>6.86221742630005</v>
+        <v>6.86221694946289</v>
       </c>
       <c r="H324" t="n">
         <v>3200</v>
@@ -9794,7 +9794,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>7.20618772506714</v>
+        <v>7.2061882019043</v>
       </c>
       <c r="H325" t="n">
         <v>3000</v>
@@ -9823,7 +9823,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G326" t="n">
-        <v>7.20618772506714</v>
+        <v>7.2061882019043</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>9</v>
       </c>
       <c r="G327" t="n">
-        <v>7.73934364318848</v>
+        <v>7.73934316635132</v>
       </c>
       <c r="H327" t="n">
         <v>3600</v>
@@ -9939,7 +9939,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>7.48136425018311</v>
+        <v>7.48136472702026</v>
       </c>
       <c r="H330" t="n">
         <v>800</v>
@@ -10142,7 +10142,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>7.41256952285767</v>
+        <v>7.41257047653198</v>
       </c>
       <c r="H337" t="n">
         <v>3600</v>
@@ -10316,7 +10316,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G343" t="n">
-        <v>7.06859970092773</v>
+        <v>7.06860017776489</v>
       </c>
       <c r="H343" t="n">
         <v>5200</v>
@@ -10374,7 +10374,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G345" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H345" t="n">
         <v>5400</v>
@@ -10519,7 +10519,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G350" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H350" t="n">
         <v>18548</v>
@@ -10577,7 +10577,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>6.91381216049194</v>
+        <v>6.9138126373291</v>
       </c>
       <c r="H352" t="n">
         <v>4342</v>
@@ -10809,7 +10809,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>6.74182748794556</v>
+        <v>6.7418270111084</v>
       </c>
       <c r="H360" t="n">
         <v>3952</v>
@@ -10838,7 +10838,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>6.74182748794556</v>
+        <v>6.7418270111084</v>
       </c>
       <c r="H361" t="n">
         <v>4250</v>
@@ -10896,7 +10896,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>6.74182748794556</v>
+        <v>6.7418270111084</v>
       </c>
       <c r="H363" t="n">
         <v>6700</v>
@@ -11012,7 +11012,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G367" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H367" t="n">
         <v>3300</v>
@@ -11070,7 +11070,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G369" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H369" t="n">
         <v>472</v>
@@ -11099,7 +11099,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G371" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H371" t="n">
         <v>1981</v>
@@ -11186,7 +11186,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>7.05140066146851</v>
+        <v>7.05140113830566</v>
       </c>
       <c r="H373" t="n">
         <v>354</v>
@@ -11273,7 +11273,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G376" t="n">
-        <v>6.7762246131897</v>
+        <v>6.77622509002686</v>
       </c>
       <c r="H376" t="n">
         <v>2400</v>
@@ -11302,7 +11302,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G377" t="n">
-        <v>6.84501886367798</v>
+        <v>6.84501838684082</v>
       </c>
       <c r="H377" t="n">
         <v>2353</v>
@@ -11331,7 +11331,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>6.84501886367798</v>
+        <v>6.84501838684082</v>
       </c>
       <c r="H378" t="n">
         <v>4149</v>
@@ -11360,7 +11360,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>6.86221742630005</v>
+        <v>6.86221694946289</v>
       </c>
       <c r="H379" t="n">
         <v>1210</v>
@@ -11389,7 +11389,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>6.86221742630005</v>
+        <v>6.86221694946289</v>
       </c>
       <c r="H380" t="n">
         <v>1253</v>
@@ -11476,7 +11476,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G383" t="n">
-        <v>6.93101119995117</v>
+        <v>6.93101167678833</v>
       </c>
       <c r="H383" t="n">
         <v>4605</v>
@@ -11650,7 +11650,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>6.91381216049194</v>
+        <v>6.9138126373291</v>
       </c>
       <c r="H389" t="n">
         <v>7543</v>
@@ -11708,7 +11708,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>6.86221742630005</v>
+        <v>6.86221694946289</v>
       </c>
       <c r="H391" t="n">
         <v>2600</v>
@@ -11737,7 +11737,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>6.84501886367798</v>
+        <v>6.84501838684082</v>
       </c>
       <c r="H392" t="n">
         <v>2665</v>
@@ -11911,7 +11911,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>6.93101119995117</v>
+        <v>6.93101167678833</v>
       </c>
       <c r="H398" t="n">
         <v>2460</v>
@@ -11940,7 +11940,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G399" t="n">
-        <v>6.89661455154419</v>
+        <v>6.89661407470703</v>
       </c>
       <c r="H399" t="n">
         <v>3410</v>
@@ -12317,7 +12317,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G412" t="n">
-        <v>7.48136425018311</v>
+        <v>7.48136472702026</v>
       </c>
       <c r="H412" t="n">
         <v>4587</v>
@@ -12375,7 +12375,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G414" t="n">
-        <v>7.44696760177612</v>
+        <v>7.44696807861328</v>
       </c>
       <c r="H414" t="n">
         <v>2400</v>
@@ -12404,7 +12404,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G415" t="n">
-        <v>7.61895275115967</v>
+        <v>7.61895227432251</v>
       </c>
       <c r="H415" t="n">
         <v>5660</v>
@@ -12462,7 +12462,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G417" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H417" t="n">
         <v>1940</v>
@@ -12520,7 +12520,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G419" t="n">
-        <v>7.41256952285767</v>
+        <v>7.41257047653198</v>
       </c>
       <c r="H419" t="n">
         <v>8008</v>
@@ -12694,7 +12694,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H425" t="n">
         <v>1500</v>
@@ -12723,7 +12723,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H426" t="n">
         <v>822</v>
@@ -12897,7 +12897,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H432" t="n">
         <v>7444</v>
@@ -12926,7 +12926,7 @@
         <v>9</v>
       </c>
       <c r="G433" t="n">
-        <v>7.73934364318848</v>
+        <v>7.73934316635132</v>
       </c>
       <c r="H433" t="n">
         <v>12673</v>
@@ -12955,7 +12955,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H434" t="n">
         <v>1098</v>
@@ -13013,7 +13013,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>7.48136425018311</v>
+        <v>7.48136472702026</v>
       </c>
       <c r="H436" t="n">
         <v>2489</v>
@@ -13071,7 +13071,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H438" t="n">
         <v>5485</v>
@@ -13100,7 +13100,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H439" t="n">
         <v>572</v>
@@ -13129,7 +13129,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H440" t="n">
         <v>1662</v>
@@ -13158,7 +13158,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>7.78233909606934</v>
+        <v>7.78233814239502</v>
       </c>
       <c r="H442" t="n">
         <v>10</v>
@@ -13216,7 +13216,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H443" t="n">
         <v>4760</v>
@@ -13245,7 +13245,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H444" t="n">
         <v>800</v>
@@ -13274,7 +13274,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>7.56735706329346</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H445" t="n">
         <v>8557</v>
@@ -13970,7 +13970,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G469" t="n">
-        <v>7.1553783416748</v>
+        <v>7.15537786483765</v>
       </c>
       <c r="H469" t="n">
         <v>1420</v>
@@ -14028,7 +14028,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>7.28870725631714</v>
+        <v>7.2887077331543</v>
       </c>
       <c r="H471" t="n">
         <v>30</v>
@@ -14260,7 +14260,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G479" t="n">
-        <v>7.28870725631714</v>
+        <v>7.2887077331543</v>
       </c>
       <c r="H479" t="n">
         <v>3000</v>
@@ -14289,7 +14289,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G480" t="n">
-        <v>7.46648120880127</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H480" t="n">
         <v>10</v>
@@ -14318,7 +14318,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G481" t="n">
-        <v>7.46648120880127</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H481" t="n">
         <v>0</v>
@@ -14347,7 +14347,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G482" t="n">
-        <v>7.46648120880127</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H482" t="n">
         <v>0</v>
@@ -14666,7 +14666,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G493" t="n">
-        <v>7.46648120880127</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H493" t="n">
         <v>2584</v>
@@ -15275,7 +15275,7 @@
         <v>7.75</v>
       </c>
       <c r="G514" t="n">
-        <v>6.88871812820435</v>
+        <v>6.88871765136719</v>
       </c>
       <c r="H514" t="n">
         <v>1660</v>
@@ -15304,7 +15304,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G515" t="n">
-        <v>7.1553783416748</v>
+        <v>7.15537786483765</v>
       </c>
       <c r="H515" t="n">
         <v>10</v>
@@ -15333,7 +15333,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>6.97760391235352</v>
+        <v>6.97760438919067</v>
       </c>
       <c r="H516" t="n">
         <v>192</v>
@@ -15362,7 +15362,7 @@
         <v>7.5</v>
       </c>
       <c r="G517" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H517" t="n">
         <v>2568</v>
@@ -15420,7 +15420,7 @@
         <v>7.5</v>
       </c>
       <c r="G519" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H519" t="n">
         <v>610</v>
@@ -15449,7 +15449,7 @@
         <v>7.5</v>
       </c>
       <c r="G520" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H520" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>7.5</v>
       </c>
       <c r="G525" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H525" t="n">
         <v>400</v>
@@ -15623,7 +15623,7 @@
         <v>7.5</v>
       </c>
       <c r="G526" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H526" t="n">
         <v>0</v>
@@ -15652,7 +15652,7 @@
         <v>7.5</v>
       </c>
       <c r="G527" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>7.5</v>
       </c>
       <c r="G528" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H528" t="n">
         <v>3103</v>
@@ -15855,7 +15855,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.39984035491943</v>
+        <v>6.39984083175659</v>
       </c>
       <c r="H534" t="n">
         <v>2911</v>
@@ -16087,7 +16087,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>6.39984035491943</v>
+        <v>6.39984083175659</v>
       </c>
       <c r="H542" t="n">
         <v>6172</v>
@@ -16116,7 +16116,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>6.39984035491943</v>
+        <v>6.39984083175659</v>
       </c>
       <c r="H543" t="n">
         <v>3219</v>
@@ -16377,7 +16377,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G552" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H552" t="n">
         <v>1717</v>
@@ -16493,7 +16493,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G556" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H556" t="n">
         <v>670</v>
@@ -16957,7 +16957,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G572" t="n">
-        <v>6.1776237487793</v>
+        <v>6.17762422561646</v>
       </c>
       <c r="H572" t="n">
         <v>12462</v>
@@ -16986,7 +16986,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G573" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H573" t="n">
         <v>4179</v>
@@ -17015,7 +17015,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G574" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H574" t="n">
         <v>2117</v>
@@ -17073,7 +17073,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G576" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H576" t="n">
         <v>3710</v>
@@ -17102,7 +17102,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H577" t="n">
         <v>2610</v>
@@ -17131,7 +17131,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -17247,7 +17247,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G582" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H582" t="n">
         <v>2138</v>
@@ -17276,7 +17276,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G583" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H583" t="n">
         <v>18938</v>
@@ -17363,7 +17363,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G586" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H586" t="n">
         <v>2734</v>
@@ -17392,7 +17392,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H587" t="n">
         <v>3257</v>
@@ -17537,7 +17537,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H592" t="n">
         <v>3684</v>
@@ -17566,7 +17566,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H593" t="n">
         <v>5400</v>
@@ -17682,7 +17682,7 @@
         <v>6.5</v>
       </c>
       <c r="G597" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H597" t="n">
         <v>12670</v>
@@ -17711,7 +17711,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H598" t="n">
         <v>8965</v>
@@ -17740,7 +17740,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G599" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H599" t="n">
         <v>11436</v>
@@ -17769,7 +17769,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G600" t="n">
-        <v>5.59986066818237</v>
+        <v>5.59986114501953</v>
       </c>
       <c r="H600" t="n">
         <v>44660</v>
@@ -17798,7 +17798,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G601" t="n">
-        <v>5.59986066818237</v>
+        <v>5.59986114501953</v>
       </c>
       <c r="H601" t="n">
         <v>43295</v>
@@ -17827,7 +17827,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G602" t="n">
-        <v>5.59986066818237</v>
+        <v>5.59986114501953</v>
       </c>
       <c r="H602" t="n">
         <v>9860</v>
@@ -17914,7 +17914,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G605" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H605" t="n">
         <v>2051</v>
@@ -17972,7 +17972,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G607" t="n">
-        <v>5.86652088165283</v>
+        <v>5.86652040481567</v>
       </c>
       <c r="H607" t="n">
         <v>17462</v>
@@ -18233,7 +18233,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G616" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H616" t="n">
         <v>3231</v>
@@ -18262,7 +18262,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G618" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H618" t="n">
         <v>2032</v>
@@ -18320,7 +18320,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G619" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H619" t="n">
         <v>50</v>
@@ -18349,7 +18349,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>6.31095457077026</v>
+        <v>6.31095409393311</v>
       </c>
       <c r="H620" t="n">
         <v>7613</v>
@@ -18726,7 +18726,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.86652088165283</v>
+        <v>5.86652040481567</v>
       </c>
       <c r="H633" t="n">
         <v>5366</v>
@@ -18755,7 +18755,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G634" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H634" t="n">
         <v>2000</v>
@@ -18784,7 +18784,7 @@
         <v>6.5</v>
       </c>
       <c r="G635" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H635" t="n">
         <v>12636</v>
@@ -18813,7 +18813,7 @@
         <v>6.5</v>
       </c>
       <c r="G636" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H636" t="n">
         <v>4185</v>
@@ -18842,7 +18842,7 @@
         <v>6.5</v>
       </c>
       <c r="G637" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H637" t="n">
         <v>0</v>
@@ -18871,7 +18871,7 @@
         <v>6.5</v>
       </c>
       <c r="G638" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H638" t="n">
         <v>3450</v>
@@ -18900,7 +18900,7 @@
         <v>6.5</v>
       </c>
       <c r="G639" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H639" t="n">
         <v>0</v>
@@ -18929,7 +18929,7 @@
         <v>6.5</v>
       </c>
       <c r="G640" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H640" t="n">
         <v>1550</v>
@@ -18987,7 +18987,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H642" t="n">
         <v>2879</v>
@@ -19016,7 +19016,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G643" t="n">
-        <v>5.59986066818237</v>
+        <v>5.59986114501953</v>
       </c>
       <c r="H643" t="n">
         <v>4049</v>
@@ -19045,7 +19045,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>5.6443042755127</v>
+        <v>5.64430379867554</v>
       </c>
       <c r="H644" t="n">
         <v>5286</v>
@@ -19103,7 +19103,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.6443042755127</v>
+        <v>5.64430379867554</v>
       </c>
       <c r="H646" t="n">
         <v>297</v>
@@ -19190,7 +19190,7 @@
         <v>6.5</v>
       </c>
       <c r="G649" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H649" t="n">
         <v>6789</v>
@@ -19248,7 +19248,7 @@
         <v>6.5</v>
       </c>
       <c r="G651" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H651" t="n">
         <v>1008</v>
@@ -19277,7 +19277,7 @@
         <v>6.5</v>
       </c>
       <c r="G652" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H652" t="n">
         <v>11094</v>
@@ -19306,7 +19306,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G653" t="n">
-        <v>5.73319101333618</v>
+        <v>5.73319053649902</v>
       </c>
       <c r="H653" t="n">
         <v>4753</v>
@@ -19393,7 +19393,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G656" t="n">
-        <v>5.59986066818237</v>
+        <v>5.59986114501953</v>
       </c>
       <c r="H656" t="n">
         <v>2652</v>
@@ -19567,7 +19567,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G662" t="n">
-        <v>5.37764406204224</v>
+        <v>5.37764453887939</v>
       </c>
       <c r="H662" t="n">
         <v>1</v>
@@ -19683,7 +19683,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G666" t="n">
-        <v>4.35544729232788</v>
+        <v>4.35544681549072</v>
       </c>
       <c r="H666" t="n">
         <v>11395</v>
@@ -19712,7 +19712,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>4.26656055450439</v>
+        <v>4.26656103134155</v>
       </c>
       <c r="H667" t="n">
         <v>8251</v>
@@ -19799,7 +19799,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G670" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H670" t="n">
         <v>10643</v>
@@ -19828,7 +19828,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G671" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -19857,7 +19857,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G672" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G673" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G674" t="n">
-        <v>4.24878311157227</v>
+        <v>4.24878358840942</v>
       </c>
       <c r="H674" t="n">
         <v>0</v>
@@ -20002,7 +20002,7 @@
         <v>4.5</v>
       </c>
       <c r="G677" t="n">
-        <v>3.99990105628967</v>
+        <v>3.99990081787109</v>
       </c>
       <c r="H677" t="n">
         <v>2379</v>
@@ -20118,7 +20118,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>3.73324060440063</v>
+        <v>3.73324036598206</v>
       </c>
       <c r="H681" t="n">
         <v>1886</v>
@@ -20176,7 +20176,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G683" t="n">
-        <v>3.64435362815857</v>
+        <v>3.64435386657715</v>
       </c>
       <c r="H683" t="n">
         <v>1800</v>
@@ -20263,7 +20263,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G686" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H686" t="n">
         <v>4888</v>
@@ -20350,7 +20350,7 @@
         <v>4.5</v>
       </c>
       <c r="G689" t="n">
-        <v>3.99990105628967</v>
+        <v>3.99990081787109</v>
       </c>
       <c r="H689" t="n">
         <v>1891</v>
@@ -20379,7 +20379,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G690" t="n">
-        <v>4.08878707885742</v>
+        <v>4.08878755569458</v>
       </c>
       <c r="H690" t="n">
         <v>5209</v>
@@ -20524,7 +20524,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H695" t="n">
         <v>4540</v>
@@ -20553,7 +20553,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H696" t="n">
         <v>470</v>
@@ -20611,7 +20611,7 @@
         <v>4.5</v>
       </c>
       <c r="G698" t="n">
-        <v>3.99990105628967</v>
+        <v>3.99990081787109</v>
       </c>
       <c r="H698" t="n">
         <v>1703</v>
@@ -20698,7 +20698,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G701" t="n">
-        <v>3.91101384162903</v>
+        <v>3.91101408004761</v>
       </c>
       <c r="H701" t="n">
         <v>11088</v>
@@ -20785,7 +20785,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G704" t="n">
-        <v>3.90212488174438</v>
+        <v>3.90212512016296</v>
       </c>
       <c r="H704" t="n">
         <v>1895</v>
@@ -20901,7 +20901,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G708" t="n">
-        <v>3.83101558685303</v>
+        <v>3.83101606369019</v>
       </c>
       <c r="H708" t="n">
         <v>6323</v>
@@ -20930,7 +20930,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>3.83101558685303</v>
+        <v>3.83101606369019</v>
       </c>
       <c r="H709" t="n">
         <v>2542</v>
@@ -21104,7 +21104,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G715" t="n">
-        <v>3.81323862075806</v>
+        <v>3.81323838233948</v>
       </c>
       <c r="H715" t="n">
         <v>611</v>
@@ -21220,7 +21220,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G719" t="n">
-        <v>4.08878707885742</v>
+        <v>4.08878755569458</v>
       </c>
       <c r="H719" t="n">
         <v>10718</v>
@@ -21249,7 +21249,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G720" t="n">
-        <v>4.06212091445923</v>
+        <v>4.06212139129639</v>
       </c>
       <c r="H720" t="n">
         <v>15398</v>
@@ -21278,7 +21278,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>4.13323068618774</v>
+        <v>4.13323020935059</v>
       </c>
       <c r="H721" t="n">
         <v>12913</v>
@@ -21452,7 +21452,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G727" t="n">
-        <v>4.09767627716064</v>
+        <v>4.09767580032349</v>
       </c>
       <c r="H727" t="n">
         <v>30466</v>
@@ -21539,7 +21539,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>4.38185453414917</v>
+        <v>4.38185501098633</v>
       </c>
       <c r="H730" t="n">
         <v>61399</v>
@@ -21568,7 +21568,7 @@
         <v>4.75</v>
       </c>
       <c r="G731" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H731" t="n">
         <v>16376</v>
@@ -21655,7 +21655,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G734" t="n">
-        <v>4.38185453414917</v>
+        <v>4.38185501098633</v>
       </c>
       <c r="H734" t="n">
         <v>34375</v>
@@ -21684,7 +21684,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G735" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H735" t="n">
         <v>17125</v>
@@ -21713,7 +21713,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G736" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H736" t="n">
         <v>9606</v>
@@ -21742,7 +21742,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G737" t="n">
-        <v>4.40935564041138</v>
+        <v>4.40935611724854</v>
       </c>
       <c r="H737" t="n">
         <v>2683</v>
@@ -21771,7 +21771,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>4.37268781661987</v>
+        <v>4.37268733978271</v>
       </c>
       <c r="H738" t="n">
         <v>600</v>
@@ -21800,7 +21800,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>4.37268781661987</v>
+        <v>4.37268733978271</v>
       </c>
       <c r="H739" t="n">
         <v>680</v>
@@ -21829,7 +21829,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G740" t="n">
-        <v>4.32685232162476</v>
+        <v>4.3268518447876</v>
       </c>
       <c r="H740" t="n">
         <v>7403</v>
@@ -21916,7 +21916,7 @@
         <v>4.75</v>
       </c>
       <c r="G743" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H743" t="n">
         <v>607</v>
@@ -21945,7 +21945,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G744" t="n">
-        <v>4.32685232162476</v>
+        <v>4.3268518447876</v>
       </c>
       <c r="H744" t="n">
         <v>11032</v>
@@ -22032,7 +22032,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G747" t="n">
-        <v>4.23518180847168</v>
+        <v>4.23518133163452</v>
       </c>
       <c r="H747" t="n">
         <v>2630</v>
@@ -22061,7 +22061,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>4.23518180847168</v>
+        <v>4.23518133163452</v>
       </c>
       <c r="H748" t="n">
         <v>1000</v>
@@ -22177,7 +22177,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G752" t="n">
-        <v>4.18934679031372</v>
+        <v>4.18934631347656</v>
       </c>
       <c r="H752" t="n">
         <v>1350</v>
@@ -22380,7 +22380,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G759" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H759" t="n">
         <v>3488</v>
@@ -22467,7 +22467,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.18934679031372</v>
+        <v>4.18934631347656</v>
       </c>
       <c r="H762" t="n">
         <v>4900</v>
@@ -22641,7 +22641,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G768" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H768" t="n">
         <v>8119</v>
@@ -22902,7 +22902,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G777" t="n">
-        <v>4.21684789657593</v>
+        <v>4.21684741973877</v>
       </c>
       <c r="H777" t="n">
         <v>7930</v>
@@ -22931,7 +22931,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>4.08850860595703</v>
+        <v>4.08850908279419</v>
       </c>
       <c r="H778" t="n">
         <v>10894</v>
@@ -23105,7 +23105,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G784" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H784" t="n">
         <v>10522</v>
@@ -23163,7 +23163,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G786" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H786" t="n">
         <v>1030</v>
@@ -23192,7 +23192,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G787" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G788" t="n">
-        <v>4.07934188842773</v>
+        <v>4.07934141159058</v>
       </c>
       <c r="H788" t="n">
         <v>5464</v>
@@ -23250,7 +23250,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G789" t="n">
-        <v>4.07934188842773</v>
+        <v>4.07934141159058</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -23337,7 +23337,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G792" t="n">
-        <v>4.04267311096191</v>
+        <v>4.04267358779907</v>
       </c>
       <c r="H792" t="n">
         <v>1205</v>
@@ -23482,7 +23482,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G797" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H797" t="n">
         <v>2403</v>
@@ -23511,7 +23511,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G798" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767532348633</v>
       </c>
       <c r="H798" t="n">
         <v>1860</v>
@@ -23598,7 +23598,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>3.91433477401733</v>
+        <v>3.91433453559875</v>
       </c>
       <c r="H801" t="n">
         <v>1035</v>
@@ -23743,7 +23743,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G806" t="n">
-        <v>3.86849927902222</v>
+        <v>3.86849904060364</v>
       </c>
       <c r="H806" t="n">
         <v>3833</v>
@@ -23772,7 +23772,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G807" t="n">
-        <v>3.88683342933655</v>
+        <v>3.88683319091797</v>
       </c>
       <c r="H807" t="n">
         <v>13265</v>
@@ -23801,7 +23801,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G808" t="n">
-        <v>3.88683342933655</v>
+        <v>3.88683319091797</v>
       </c>
       <c r="H808" t="n">
         <v>12349</v>
@@ -23946,7 +23946,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G813" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H813" t="n">
         <v>11042</v>
@@ -24004,7 +24004,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>4.37268781661987</v>
+        <v>4.37268733978271</v>
       </c>
       <c r="H815" t="n">
         <v>4760</v>
@@ -24033,7 +24033,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G816" t="n">
-        <v>4.36352062225342</v>
+        <v>4.36352109909058</v>
       </c>
       <c r="H816" t="n">
         <v>7780</v>
@@ -24120,7 +24120,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G819" t="n">
-        <v>4.32685232162476</v>
+        <v>4.3268518447876</v>
       </c>
       <c r="H819" t="n">
         <v>785</v>
@@ -24178,7 +24178,7 @@
         <v>4.75</v>
       </c>
       <c r="G821" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H821" t="n">
         <v>6878</v>
@@ -24294,7 +24294,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G825" t="n">
-        <v>4.51936006546021</v>
+        <v>4.51936054229736</v>
       </c>
       <c r="H825" t="n">
         <v>1867</v>
@@ -24352,7 +24352,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>4.51019382476807</v>
+        <v>4.51019334793091</v>
       </c>
       <c r="H827" t="n">
         <v>10424</v>
@@ -24410,7 +24410,7 @@
         <v>4.75</v>
       </c>
       <c r="G829" t="n">
-        <v>4.35435390472412</v>
+        <v>4.35435342788696</v>
       </c>
       <c r="H829" t="n">
         <v>5800</v>
@@ -24468,7 +24468,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.04267311096191</v>
+        <v>4.04267358779907</v>
       </c>
       <c r="H831" t="n">
         <v>16333</v>
@@ -24555,7 +24555,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>3.94183611869812</v>
+        <v>3.94183588027954</v>
       </c>
       <c r="H834" t="n">
         <v>25951</v>
@@ -24642,7 +24642,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>4.21684789657593</v>
+        <v>4.21684741973877</v>
       </c>
       <c r="H837" t="n">
         <v>21835</v>
@@ -24729,7 +24729,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G840" t="n">
-        <v>4.18934679031372</v>
+        <v>4.18934631347656</v>
       </c>
       <c r="H840" t="n">
         <v>34559</v>
@@ -24758,7 +24758,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>4.23518180847168</v>
+        <v>4.23518133163452</v>
       </c>
       <c r="H841" t="n">
         <v>225</v>
@@ -24845,7 +24845,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G844" t="n">
-        <v>4.21684789657593</v>
+        <v>4.21684741973877</v>
       </c>
       <c r="H844" t="n">
         <v>16368</v>
@@ -25193,7 +25193,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>4.96854686737061</v>
+        <v>4.96854639053345</v>
       </c>
       <c r="H856" t="n">
         <v>13143</v>
@@ -25309,7 +25309,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G860" t="n">
-        <v>5.11521911621094</v>
+        <v>5.1152195930481</v>
       </c>
       <c r="H860" t="n">
         <v>16237</v>
@@ -25367,7 +25367,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G862" t="n">
-        <v>5.13355398178101</v>
+        <v>5.13355350494385</v>
       </c>
       <c r="H862" t="n">
         <v>13036</v>
@@ -25396,7 +25396,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G863" t="n">
-        <v>5.15188789367676</v>
+        <v>5.1518874168396</v>
       </c>
       <c r="H863" t="n">
         <v>7153</v>
@@ -25454,7 +25454,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>5.00521469116211</v>
+        <v>5.00521516799927</v>
       </c>
       <c r="H865" t="n">
         <v>3756</v>
@@ -25686,7 +25686,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G873" t="n">
-        <v>5.39023160934448</v>
+        <v>5.39023113250732</v>
       </c>
       <c r="H873" t="n">
         <v>31741</v>
@@ -25715,7 +25715,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G874" t="n">
-        <v>5.39023160934448</v>
+        <v>5.39023113250732</v>
       </c>
       <c r="H874" t="n">
         <v>13377</v>
@@ -25831,7 +25831,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G878" t="n">
-        <v>5.6102409362793</v>
+        <v>5.61024045944214</v>
       </c>
       <c r="H878" t="n">
         <v>24852</v>
@@ -25947,7 +25947,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G882" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H882" t="n">
         <v>8738</v>
@@ -25976,7 +25976,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>5.88525295257568</v>
+        <v>5.88525247573853</v>
       </c>
       <c r="H883" t="n">
         <v>11732</v>
@@ -26121,7 +26121,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>5.9402551651001</v>
+        <v>5.94025468826294</v>
       </c>
       <c r="H888" t="n">
         <v>7733</v>
@@ -26266,7 +26266,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G893" t="n">
-        <v>5.83025026321411</v>
+        <v>5.83025074005127</v>
       </c>
       <c r="H893" t="n">
         <v>46103</v>
@@ -26324,7 +26324,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>5.92192077636719</v>
+        <v>5.92192125320435</v>
       </c>
       <c r="H895" t="n">
         <v>1658</v>
@@ -26382,7 +26382,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>5.92192077636719</v>
+        <v>5.92192125320435</v>
       </c>
       <c r="H897" t="n">
         <v>3856</v>
@@ -26469,7 +26469,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>5.92192077636719</v>
+        <v>5.92192125320435</v>
       </c>
       <c r="H900" t="n">
         <v>19114</v>
@@ -26498,7 +26498,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G901" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H901" t="n">
         <v>5834</v>
@@ -26527,7 +26527,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G902" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H902" t="n">
         <v>4663</v>
@@ -26643,7 +26643,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G906" t="n">
-        <v>6.01359128952026</v>
+        <v>6.01359176635742</v>
       </c>
       <c r="H906" t="n">
         <v>7547</v>
@@ -26759,7 +26759,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G910" t="n">
-        <v>6.19693279266357</v>
+        <v>6.19693326950073</v>
       </c>
       <c r="H910" t="n">
         <v>32257</v>
@@ -26817,7 +26817,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>6.38027381896973</v>
+        <v>6.38027429580688</v>
       </c>
       <c r="H912" t="n">
         <v>24783</v>
@@ -26846,7 +26846,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G913" t="n">
-        <v>6.28860330581665</v>
+        <v>6.28860378265381</v>
       </c>
       <c r="H913" t="n">
         <v>13157</v>
@@ -26991,7 +26991,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>6.4719443321228</v>
+        <v>6.47194480895996</v>
       </c>
       <c r="H918" t="n">
         <v>6002</v>
@@ -27049,7 +27049,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G920" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H920" t="n">
         <v>2787</v>
@@ -27078,7 +27078,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H921" t="n">
         <v>4737</v>
@@ -27107,7 +27107,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G922" t="n">
-        <v>6.58194923400879</v>
+        <v>6.58194875717163</v>
       </c>
       <c r="H922" t="n">
         <v>5358</v>
@@ -27165,7 +27165,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G924" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H924" t="n">
         <v>4250</v>
@@ -27252,7 +27252,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G927" t="n">
-        <v>6.61861753463745</v>
+        <v>6.61861705780029</v>
       </c>
       <c r="H927" t="n">
         <v>9701</v>
@@ -27339,7 +27339,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G930" t="n">
-        <v>6.58194923400879</v>
+        <v>6.58194875717163</v>
       </c>
       <c r="H930" t="n">
         <v>1400</v>
@@ -27368,7 +27368,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G931" t="n">
-        <v>6.61861753463745</v>
+        <v>6.61861705780029</v>
       </c>
       <c r="H931" t="n">
         <v>4392</v>
@@ -27542,7 +27542,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G937" t="n">
-        <v>6.54528045654297</v>
+        <v>6.54528093338013</v>
       </c>
       <c r="H937" t="n">
         <v>11503</v>
@@ -27600,7 +27600,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G939" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H939" t="n">
         <v>14602</v>
@@ -27658,7 +27658,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G941" t="n">
-        <v>6.85696125030518</v>
+        <v>6.85696077346802</v>
       </c>
       <c r="H941" t="n">
         <v>21995</v>
@@ -27890,7 +27890,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>6.56361484527588</v>
+        <v>6.56361532211304</v>
       </c>
       <c r="H949" t="n">
         <v>6250</v>
@@ -28093,7 +28093,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G956" t="n">
-        <v>6.78362417221069</v>
+        <v>6.78362464904785</v>
       </c>
       <c r="H956" t="n">
         <v>5975</v>
@@ -68699,6 +68699,35 @@
         <v>19545</v>
       </c>
       <c r="I2356" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="A2357" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2357" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2357" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D2357" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="E2357" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="F2357" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G2357" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H2357" t="n">
+        <v>6572</v>
+      </c>
+      <c r="I2357" t="s">
         <v>9</v>
       </c>
     </row>
